--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4837,7 +4837,7 @@
         <v>1571225468928</v>
       </c>
       <c r="K2" t="n">
-        <v>22.988073</v>
+        <v>23.256788</v>
       </c>
       <c r="L2" t="n">
         <v>17.642334</v>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:34:52</t>
+          <t>2026-09-06 05:41:52</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4777,25 +4777,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4843,7 +4863,7 @@
         <v>17.642334</v>
       </c>
       <c r="M2" t="n">
-        <v>26.83</v>
+        <v>26.52</v>
       </c>
       <c r="N2" t="n">
         <v>790.8</v>
@@ -4879,29 +4899,41 @@
       <c r="W2" t="n">
         <v>2.226</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>102.52</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.0160947</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.134</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2205128509</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Internet Content &amp; Information</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.meta.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc. engages in the development of products that enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) headsets, and AI glasses in the United States, Canada, Europe, Asia-Pacific, and internationally. It operates through two segments, Family of Apps (FoA) and Reality Labs (RL). The FoA segment offers Facebook, which enables people to build community through feed, reels, stories, groups, marketplace, and other; Instagram that brings people closer through Instagram feed, stories, reels, live, and messaging; Messenger, a messaging application for people to connect with friends, family, communities, and businesses across platforms and devices through text, audio, and video calls; Meta AI, an assistant that's available across apps, as a stand-alone app, on AI glasses, and on the web; Threads, an application for text-based updates and public conversations; and WhatsApp, a messaging application that is used by people and businesses to communicate and transact. The RL segment provides virtual and augmented reality products, including consumer hardware, software, and content that help people feel connected, as well as Meta Quest devices that enable social experiences across gaming, fitness, entertainment, and more. The segment also includes wearables such as AI glasses like Ray Ban Meta and Oakley Meta glasses; and the Meta Ray Ban Display, which combines AI glasses with an integrated lens display and the Meta Neural Band, a wrist worn device using electromyography that lets people control their AI glasses through neuromuscular signals. Meta Platforms, Inc. has a collaboration with Microsoft Corporation, NVIDIA Corporation, Advanced Micro Devices, Inc., Broadcom Inc., and OpenAI, L.L.C. The company was formerly known as Facebook, Inc. and changed its name to Meta Platforms, Inc. in October 2021. The company was incorporated in 2004 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:41:52</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:09:55</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:09:55</t>
+          <t>2026-09-06 16:24:31</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:31</t>
+          <t>2026-09-06 16:34:25</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:25</t>
+          <t>2026-09-06 16:49:00</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4877,15 +4877,11 @@
       <c r="Q2" t="n">
         <v>0.34</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.29834998</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.34827</v>
       </c>
       <c r="T2" t="n">
         <v>0.29848</v>
@@ -4933,7 +4929,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:49:00</t>
+          <t>2026-09-06 16:59:30</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4797,25 +4797,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -4907,29 +4922,38 @@
       <c r="AA2" t="n">
         <v>2205128509</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>228246994944</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1593283444736</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>109654999040</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Internet Content &amp; Information</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.meta.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc. engages in the development of products that enable people to connect and share with friends and family through mobile devices, personal computers, virtual reality (VR) headsets, and AI glasses in the United States, Canada, Europe, Asia-Pacific, and internationally. It operates through two segments, Family of Apps (FoA) and Reality Labs (RL). The FoA segment offers Facebook, which enables people to build community through feed, reels, stories, groups, marketplace, and other; Instagram that brings people closer through Instagram feed, stories, reels, live, and messaging; Messenger, a messaging application for people to connect with friends, family, communities, and businesses across platforms and devices through text, audio, and video calls; Meta AI, an assistant that's available across apps, as a stand-alone app, on AI glasses, and on the web; Threads, an application for text-based updates and public conversations; and WhatsApp, a messaging application that is used by people and businesses to communicate and transact. The RL segment provides virtual and augmented reality products, including consumer hardware, software, and content that help people feel connected, as well as Meta Quest devices that enable social experiences across gaming, fitness, entertainment, and more. The segment also includes wearables such as AI glasses like Ray Ban Meta and Oakley Meta glasses; and the Meta Ray Ban Display, which combines AI glasses with an integrated lens display and the Meta Neural Band, a wrist worn device using electromyography that lets people control their AI glasses through neuromuscular signals. Meta Platforms, Inc. has a collaboration with Microsoft Corporation, NVIDIA Corporation, Advanced Micro Devices, Inc., Broadcom Inc., and OpenAI, L.L.C. The company was formerly known as Facebook, Inc. and changed its name to Meta Platforms, Inc. in October 2021. The company was incorporated in 2004 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:30</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:35</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:35</t>
+          <t>2026-09-06 22:41:30</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -4953,7 +4953,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:30</t>
+          <t>2026-09-06 22:59:25</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>600.4600219726562</v>
+        <v>750.1613099282893</v>
       </c>
       <c r="C2" t="n">
-        <v>601</v>
+        <v>755.4739147328357</v>
       </c>
       <c r="D2" t="n">
-        <v>580.1199951171875</v>
+        <v>742.5961392724259</v>
       </c>
       <c r="E2" t="n">
-        <v>588.77001953125</v>
+        <v>749.9918823242188</v>
       </c>
       <c r="F2" t="n">
-        <v>14897200</v>
+        <v>9663400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>586.9500122070312</v>
+        <v>753.5302710608411</v>
       </c>
       <c r="C3" t="n">
-        <v>595.3099975585938</v>
+        <v>764.0059463353695</v>
       </c>
       <c r="D3" t="n">
-        <v>586</v>
+        <v>749.5632925404257</v>
       </c>
       <c r="E3" t="n">
-        <v>589.9000244140625</v>
+        <v>749.8423461914062</v>
       </c>
       <c r="F3" t="n">
-        <v>11811500</v>
+        <v>13087800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>585.6400146484375</v>
+        <v>755.0154070864886</v>
       </c>
       <c r="C4" t="n">
-        <v>598.739990234375</v>
+        <v>763.7966239723705</v>
       </c>
       <c r="D4" t="n">
-        <v>585.6199951171875</v>
+        <v>750.9686728075005</v>
       </c>
       <c r="E4" t="n">
-        <v>592.0999755859375</v>
+        <v>763.1986083984375</v>
       </c>
       <c r="F4" t="n">
-        <v>11250300</v>
+        <v>10999000</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>599.1300048828125</v>
+        <v>762.6305659580242</v>
       </c>
       <c r="C5" t="n">
-        <v>608.2100219726562</v>
+        <v>763.198711247707</v>
       </c>
       <c r="D5" t="n">
-        <v>592.030029296875</v>
+        <v>748.5467193541789</v>
       </c>
       <c r="E5" t="n">
-        <v>594.9199829101562</v>
+        <v>749.5234985351562</v>
       </c>
       <c r="F5" t="n">
-        <v>14967300</v>
+        <v>12478300</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>598</v>
+        <v>752.184771170502</v>
       </c>
       <c r="C6" t="n">
-        <v>612.4299926757812</v>
+        <v>754.6267189634892</v>
       </c>
       <c r="D6" t="n">
-        <v>593.4000244140625</v>
+        <v>745.9252571616319</v>
       </c>
       <c r="E6" t="n">
-        <v>599.1199951171875</v>
+        <v>748.447021484375</v>
       </c>
       <c r="F6" t="n">
-        <v>13146900</v>
+        <v>7923300</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>601.0700073242188</v>
+        <v>746.2840072815898</v>
       </c>
       <c r="C7" t="n">
-        <v>604.5</v>
+        <v>755.095155276553</v>
       </c>
       <c r="D7" t="n">
-        <v>578.2100219726562</v>
+        <v>741.330272625368</v>
       </c>
       <c r="E7" t="n">
-        <v>578.8499755859375</v>
+        <v>753.1216430664062</v>
       </c>
       <c r="F7" t="n">
-        <v>16186900</v>
+        <v>8248600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>580.7100219726562</v>
+        <v>754.995481759339</v>
       </c>
       <c r="C8" t="n">
-        <v>595.8499755859375</v>
+        <v>771.5412896866574</v>
       </c>
       <c r="D8" t="n">
-        <v>579.3900146484375</v>
+        <v>749.5334031898147</v>
       </c>
       <c r="E8" t="n">
-        <v>594.969970703125</v>
+        <v>762.201904296875</v>
       </c>
       <c r="F8" t="n">
-        <v>11164200</v>
+        <v>10533800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>596.97998046875</v>
+        <v>764.4944012192615</v>
       </c>
       <c r="C9" t="n">
-        <v>601.8599853515625</v>
+        <v>778.8074760600178</v>
       </c>
       <c r="D9" t="n">
-        <v>589.2899780273438</v>
+        <v>762.6005837137456</v>
       </c>
       <c r="E9" t="n">
-        <v>589.8499755859375</v>
+        <v>776.4552001953125</v>
       </c>
       <c r="F9" t="n">
-        <v>8758000</v>
+        <v>11782500</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>589.75</v>
+        <v>777.4419223006557</v>
       </c>
       <c r="C10" t="n">
-        <v>590.239990234375</v>
+        <v>780.7311297077449</v>
       </c>
       <c r="D10" t="n">
-        <v>564.75</v>
+        <v>763.8066193659058</v>
       </c>
       <c r="E10" t="n">
-        <v>568.969970703125</v>
+        <v>773.1858520507812</v>
       </c>
       <c r="F10" t="n">
-        <v>17225600</v>
+        <v>9400900</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>557.47998046875</v>
+        <v>778.1994163857863</v>
       </c>
       <c r="C11" t="n">
-        <v>560.6599731445312</v>
+        <v>786.2032128794</v>
       </c>
       <c r="D11" t="n">
-        <v>543.2100219726562</v>
+        <v>770.8335437165625</v>
       </c>
       <c r="E11" t="n">
-        <v>543.6699829101562</v>
+        <v>777.7010498046875</v>
       </c>
       <c r="F11" t="n">
-        <v>27094900</v>
+        <v>10955000</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>541.3400268554688</v>
+        <v>783.8509325355676</v>
       </c>
       <c r="C12" t="n">
-        <v>554.0700073242188</v>
+        <v>788.2166289656076</v>
       </c>
       <c r="D12" t="n">
-        <v>537.27001953125</v>
+        <v>766.6772383880447</v>
       </c>
       <c r="E12" t="n">
-        <v>546.030029296875</v>
+        <v>775.8372192382812</v>
       </c>
       <c r="F12" t="n">
-        <v>16971700</v>
+        <v>23696800</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,25 +755,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>546.9500122070312</v>
+        <v>779.8218176027002</v>
       </c>
       <c r="C13" t="n">
-        <v>549.989990234375</v>
+        <v>783.6917575585782</v>
       </c>
       <c r="D13" t="n">
-        <v>539.3099975585938</v>
+        <v>762.4868973227559</v>
       </c>
       <c r="E13" t="n">
-        <v>545.8300170898438</v>
+        <v>763.1751098632812</v>
       </c>
       <c r="F13" t="n">
-        <v>13872200</v>
+        <v>11706900</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>546.8900146484375</v>
+        <v>767.2545389947088</v>
       </c>
       <c r="C14" t="n">
-        <v>553.8699951171875</v>
+        <v>768.6010126974617</v>
       </c>
       <c r="D14" t="n">
-        <v>543.22998046875</v>
+        <v>749.1217058463387</v>
       </c>
       <c r="E14" t="n">
-        <v>549.9000244140625</v>
+        <v>753.4404907226562</v>
       </c>
       <c r="F14" t="n">
-        <v>13848000</v>
+        <v>10872600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>550.2000122070312</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C15" t="n">
-        <v>561.4199829101562</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D15" t="n">
-        <v>546.2999877929688</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E15" t="n">
-        <v>559.02001953125</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F15" t="n">
-        <v>12990600</v>
+        <v>8828200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>563.8800048828125</v>
+        <v>751.4955472633491</v>
       </c>
       <c r="C16" t="n">
-        <v>570.7999877929688</v>
+        <v>754.806942419776</v>
       </c>
       <c r="D16" t="n">
-        <v>561.4000244140625</v>
+        <v>742.6186096970315</v>
       </c>
       <c r="E16" t="n">
-        <v>570.0499877929688</v>
+        <v>746.96728515625</v>
       </c>
       <c r="F16" t="n">
-        <v>9769100</v>
+        <v>10591100</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>590.3099975585938</v>
+        <v>748.0544043789391</v>
       </c>
       <c r="C17" t="n">
-        <v>593.3400268554688</v>
+        <v>749.9793904076555</v>
       </c>
       <c r="D17" t="n">
-        <v>561.8800048828125</v>
+        <v>735.4371957410184</v>
       </c>
       <c r="E17" t="n">
-        <v>576.1400146484375</v>
+        <v>741.8206176757812</v>
       </c>
       <c r="F17" t="n">
-        <v>31416300</v>
+        <v>9696300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>576.47998046875</v>
+        <v>746.7777648139662</v>
       </c>
       <c r="C18" t="n">
-        <v>588.3900146484375</v>
+        <v>748.832479543402</v>
       </c>
       <c r="D18" t="n">
-        <v>567.6199951171875</v>
+        <v>737.2326433015477</v>
       </c>
       <c r="E18" t="n">
-        <v>571.0999755859375</v>
+        <v>741.4716186523438</v>
       </c>
       <c r="F18" t="n">
-        <v>15221400</v>
+        <v>9246800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>571.5499877929688</v>
+        <v>740.3244937368279</v>
       </c>
       <c r="C19" t="n">
-        <v>589.1900024414062</v>
+        <v>741.0425967294805</v>
       </c>
       <c r="D19" t="n">
-        <v>571</v>
+        <v>724.4158582201331</v>
       </c>
       <c r="E19" t="n">
-        <v>578.02001953125</v>
+        <v>732.4749145507812</v>
       </c>
       <c r="F19" t="n">
-        <v>16042400</v>
+        <v>16226800</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>577.6300048828125</v>
+        <v>719.618385039583</v>
       </c>
       <c r="C20" t="n">
-        <v>578.6799926757812</v>
+        <v>719.9774365591268</v>
       </c>
       <c r="D20" t="n">
-        <v>569.1400146484375</v>
+        <v>708.3576941566364</v>
       </c>
       <c r="E20" t="n">
-        <v>572.3400268554688</v>
+        <v>715.4791870117188</v>
       </c>
       <c r="F20" t="n">
-        <v>13383800</v>
+        <v>20419600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>558.3499755859375</v>
+        <v>720.7055653205383</v>
       </c>
       <c r="C21" t="n">
-        <v>584.9500122070312</v>
+        <v>725.8821043267139</v>
       </c>
       <c r="D21" t="n">
-        <v>556.0999755859375</v>
+        <v>716.2770807321521</v>
       </c>
       <c r="E21" t="n">
-        <v>578.5399780273438</v>
+        <v>725.1639404296875</v>
       </c>
       <c r="F21" t="n">
-        <v>15796900</v>
+        <v>11415300</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>578.7899780273438</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C22" t="n">
-        <v>600.3800048828125</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D22" t="n">
-        <v>577</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E22" t="n">
-        <v>592.8499755859375</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F22" t="n">
-        <v>16552700</v>
+        <v>16154300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>604.489990234375</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C23" t="n">
-        <v>619.4600219726562</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D23" t="n">
-        <v>604.3499755859375</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E23" t="n">
-        <v>610.6799926757812</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F23" t="n">
-        <v>19737100</v>
+        <v>21654700</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>715.8581417735932</v>
+      </c>
+      <c r="C24" t="n">
+        <v>716.6361476056489</v>
+      </c>
+      <c r="D24" t="n">
+        <v>703.9192222306009</v>
+      </c>
+      <c r="E24" t="n">
+        <v>711.230224609375</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12062900</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>711.599278595462</v>
+      </c>
+      <c r="C25" t="n">
+        <v>717.7832075860277</v>
+      </c>
+      <c r="D25" t="n">
+        <v>705.9738944950672</v>
+      </c>
+      <c r="E25" t="n">
+        <v>715.9779052734375</v>
+      </c>
+      <c r="F25" t="n">
+        <v>10790600</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>716.4167658258609</v>
+      </c>
+      <c r="C26" t="n">
+        <v>731.6072387695312</v>
+      </c>
+      <c r="D26" t="n">
+        <v>710.5918883665408</v>
+      </c>
+      <c r="E26" t="n">
+        <v>731.6072387695312</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12717200</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>729.0239332852144</v>
+      </c>
+      <c r="C27" t="n">
+        <v>733.3626856542741</v>
+      </c>
+      <c r="D27" t="n">
+        <v>702.6824691715568</v>
+      </c>
+      <c r="E27" t="n">
+        <v>703.4703979492188</v>
+      </c>
+      <c r="F27" t="n">
+        <v>16980100</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>711.1603595995662</v>
+      </c>
+      <c r="C28" t="n">
+        <v>718.072374881022</v>
+      </c>
+      <c r="D28" t="n">
+        <v>705.8042950194317</v>
+      </c>
+      <c r="E28" t="n">
+        <v>713.8433837890625</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9251800</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>705.9439682909708</v>
+      </c>
+      <c r="C29" t="n">
+        <v>713.6937706407739</v>
+      </c>
+      <c r="D29" t="n">
+        <v>697.5158763660478</v>
+      </c>
+      <c r="E29" t="n">
+        <v>706.8117065429688</v>
+      </c>
+      <c r="F29" t="n">
+        <v>8829800</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>715.1998794771447</v>
+      </c>
+      <c r="C30" t="n">
+        <v>722.0221626881838</v>
+      </c>
+      <c r="D30" t="n">
+        <v>707.6694770310874</v>
+      </c>
+      <c r="E30" t="n">
+        <v>715.6885986328125</v>
+      </c>
+      <c r="F30" t="n">
+        <v>10246800</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>715.6886043056783</v>
+      </c>
+      <c r="C31" t="n">
+        <v>723.6080097298942</v>
+      </c>
+      <c r="D31" t="n">
+        <v>702.0540824517458</v>
+      </c>
+      <c r="E31" t="n">
+        <v>710.2228393554688</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9017000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>705.2458014471516</v>
+      </c>
+      <c r="C32" t="n">
+        <v>716.6760344343375</v>
+      </c>
+      <c r="D32" t="n">
+        <v>704.2882698394852</v>
+      </c>
+      <c r="E32" t="n">
+        <v>715.0602416992188</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12232400</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>719.3191931642514</v>
+      </c>
+      <c r="C33" t="n">
+        <v>731.8665769499745</v>
+      </c>
+      <c r="D33" t="n">
+        <v>718.3118034233538</v>
+      </c>
+      <c r="E33" t="n">
+        <v>730.2706909179688</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8900200</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>734.1107251683979</v>
+      </c>
+      <c r="C34" t="n">
+        <v>736.5842723709278</v>
+      </c>
+      <c r="D34" t="n">
+        <v>726.8595646449745</v>
+      </c>
+      <c r="E34" t="n">
+        <v>731.3678588867188</v>
+      </c>
+      <c r="F34" t="n">
+        <v>7647300</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>731.9264006052239</v>
+      </c>
+      <c r="C35" t="n">
+        <v>738.6787972623451</v>
+      </c>
+      <c r="D35" t="n">
+        <v>722.1518348008319</v>
+      </c>
+      <c r="E35" t="n">
+        <v>731.5074462890625</v>
+      </c>
+      <c r="F35" t="n">
+        <v>8734500</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>732.7941435868839</v>
+      </c>
+      <c r="C36" t="n">
+        <v>740.4841042897723</v>
+      </c>
+      <c r="D36" t="n">
+        <v>731.1982575844598</v>
+      </c>
+      <c r="E36" t="n">
+        <v>732.095947265625</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9856000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>734.8786455644157</v>
+      </c>
+      <c r="C37" t="n">
+        <v>739.2872233202683</v>
+      </c>
+      <c r="D37" t="n">
+        <v>729.2533227506186</v>
+      </c>
+      <c r="E37" t="n">
+        <v>736.444580078125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9151300</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>747.7851152228061</v>
+      </c>
+      <c r="C38" t="n">
+        <v>753.7895182960361</v>
+      </c>
+      <c r="D38" t="n">
+        <v>746.069606274355</v>
+      </c>
+      <c r="E38" t="n">
+        <v>748.872314453125</v>
+      </c>
+      <c r="F38" t="n">
+        <v>11321100</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>750.6776381609803</v>
+      </c>
+      <c r="C39" t="n">
+        <v>756.4326899204912</v>
+      </c>
+      <c r="D39" t="n">
+        <v>743.5860965317024</v>
+      </c>
+      <c r="E39" t="n">
+        <v>749.49072265625</v>
+      </c>
+      <c r="F39" t="n">
+        <v>12193800</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>752.7921200604676</v>
+      </c>
+      <c r="C40" t="n">
+        <v>757.1906533932021</v>
+      </c>
+      <c r="D40" t="n">
+        <v>740.5838813084906</v>
+      </c>
+      <c r="E40" t="n">
+        <v>749.7200927734375</v>
+      </c>
+      <c r="F40" t="n">
+        <v>26818600</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>667.414190282622</v>
+      </c>
+      <c r="C41" t="n">
+        <v>679.1935516668058</v>
+      </c>
+      <c r="D41" t="n">
+        <v>648.4833846789722</v>
+      </c>
+      <c r="E41" t="n">
+        <v>664.7410888671875</v>
+      </c>
+      <c r="F41" t="n">
+        <v>88440100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>672.7602632515434</v>
+      </c>
+      <c r="C42" t="n">
+        <v>673.1392823636344</v>
+      </c>
+      <c r="D42" t="n">
+        <v>643.8953340746643</v>
+      </c>
+      <c r="E42" t="n">
+        <v>646.6680908203125</v>
+      </c>
+      <c r="F42" t="n">
+        <v>56953200</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>654.298319497033</v>
+      </c>
+      <c r="C43" t="n">
+        <v>657.6196984387726</v>
+      </c>
+      <c r="D43" t="n">
+        <v>634.5297257704245</v>
+      </c>
+      <c r="E43" t="n">
+        <v>636.0557861328125</v>
+      </c>
+      <c r="F43" t="n">
+        <v>33003600</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>626.4107910285981</v>
+      </c>
+      <c r="C44" t="n">
+        <v>640.0752642850032</v>
+      </c>
+      <c r="D44" t="n">
+        <v>624.3860886703497</v>
+      </c>
+      <c r="E44" t="n">
+        <v>625.6926879882812</v>
+      </c>
+      <c r="F44" t="n">
+        <v>27356600</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>630.6697208898194</v>
+      </c>
+      <c r="C45" t="n">
+        <v>640.5639703518489</v>
+      </c>
+      <c r="D45" t="n">
+        <v>624.9146693781357</v>
+      </c>
+      <c r="E45" t="n">
+        <v>634.30029296875</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20219900</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>634.2005186436334</v>
+      </c>
+      <c r="C46" t="n">
+        <v>634.3501538797125</v>
+      </c>
+      <c r="D46" t="n">
+        <v>616.3968476378337</v>
+      </c>
+      <c r="E46" t="n">
+        <v>617.3344116210938</v>
+      </c>
+      <c r="F46" t="n">
+        <v>23628800</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>614.8907386759073</v>
+      </c>
+      <c r="C47" t="n">
+        <v>620.5161224262619</v>
+      </c>
+      <c r="D47" t="n">
+        <v>599.6404247494841</v>
+      </c>
+      <c r="E47" t="n">
+        <v>620.0972290039062</v>
+      </c>
+      <c r="F47" t="n">
+        <v>29946800</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>629.4529098843899</v>
+      </c>
+      <c r="C48" t="n">
+        <v>633.3527401283538</v>
+      </c>
+      <c r="D48" t="n">
+        <v>616.5065400363918</v>
+      </c>
+      <c r="E48" t="n">
+        <v>630.1211547851562</v>
+      </c>
+      <c r="F48" t="n">
+        <v>19245000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>626.3709044869131</v>
+      </c>
+      <c r="C49" t="n">
+        <v>627.9268552540688</v>
+      </c>
+      <c r="D49" t="n">
+        <v>617.7832543081277</v>
+      </c>
+      <c r="E49" t="n">
+        <v>625.4533081054688</v>
+      </c>
+      <c r="F49" t="n">
+        <v>13302200</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>626.5005716840028</v>
+      </c>
+      <c r="C50" t="n">
+        <v>627.3583261459861</v>
+      </c>
+      <c r="D50" t="n">
+        <v>606.1934022078184</v>
+      </c>
+      <c r="E50" t="n">
+        <v>607.43017578125</v>
+      </c>
+      <c r="F50" t="n">
+        <v>24493300</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>611.4796659420805</v>
+      </c>
+      <c r="C51" t="n">
+        <v>616.0478021853295</v>
+      </c>
+      <c r="D51" t="n">
+        <v>601.4357808374693</v>
+      </c>
+      <c r="E51" t="n">
+        <v>608.3079223632812</v>
+      </c>
+      <c r="F51" t="n">
+        <v>20973800</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>600.2288811530552</v>
+      </c>
+      <c r="C52" t="n">
+        <v>612.088052043071</v>
+      </c>
+      <c r="D52" t="n">
+        <v>593.6560102918138</v>
+      </c>
+      <c r="E52" t="n">
+        <v>607.8790283203125</v>
+      </c>
+      <c r="F52" t="n">
+        <v>20724100</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>607.4600964135232</v>
+      </c>
+      <c r="C53" t="n">
+        <v>610.1032465254069</v>
+      </c>
+      <c r="D53" t="n">
+        <v>593.855525554584</v>
+      </c>
+      <c r="E53" t="n">
+        <v>600.4483642578125</v>
+      </c>
+      <c r="F53" t="n">
+        <v>16501300</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>590.0652977363707</v>
+      </c>
+      <c r="C54" t="n">
+        <v>602.0940102850205</v>
+      </c>
+      <c r="D54" t="n">
+        <v>582.2656372803878</v>
+      </c>
+      <c r="E54" t="n">
+        <v>596.1395263671875</v>
+      </c>
+      <c r="F54" t="n">
+        <v>25500600</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>592.1797786556917</v>
+      </c>
+      <c r="C55" t="n">
+        <v>593.7856483585136</v>
+      </c>
+      <c r="D55" t="n">
+        <v>579.7421567881397</v>
+      </c>
+      <c r="E55" t="n">
+        <v>588.7886352539062</v>
+      </c>
+      <c r="F55" t="n">
+        <v>24744700</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>601.9345167857809</v>
+      </c>
+      <c r="C56" t="n">
+        <v>605.1461348624172</v>
+      </c>
+      <c r="D56" t="n">
+        <v>581.8367616757555</v>
+      </c>
+      <c r="E56" t="n">
+        <v>587.6217651367188</v>
+      </c>
+      <c r="F56" t="n">
+        <v>20603000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>586.9733513369498</v>
+      </c>
+      <c r="C57" t="n">
+        <v>596.5683908845805</v>
+      </c>
+      <c r="D57" t="n">
+        <v>580.3505617853443</v>
+      </c>
+      <c r="E57" t="n">
+        <v>592.7084350585938</v>
+      </c>
+      <c r="F57" t="n">
+        <v>21052600</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>597.1668126146857</v>
+      </c>
+      <c r="C58" t="n">
+        <v>615.1002115339802</v>
+      </c>
+      <c r="D58" t="n">
+        <v>596.0796743085915</v>
+      </c>
+      <c r="E58" t="n">
+        <v>611.4596557617188</v>
+      </c>
+      <c r="F58" t="n">
+        <v>23554900</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>622.3813086708644</v>
+      </c>
+      <c r="C59" t="n">
+        <v>635.3974440566444</v>
+      </c>
+      <c r="D59" t="n">
+        <v>616.696082618217</v>
+      </c>
+      <c r="E59" t="n">
+        <v>634.569580078125</v>
+      </c>
+      <c r="F59" t="n">
+        <v>25213000</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>636.0358029520913</v>
+      </c>
+      <c r="C60" t="n">
+        <v>636.7040478933542</v>
+      </c>
+      <c r="D60" t="n">
+        <v>629.9915253276793</v>
+      </c>
+      <c r="E60" t="n">
+        <v>631.9663696289062</v>
+      </c>
+      <c r="F60" t="n">
+        <v>15209500</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>634.4299618769652</v>
+      </c>
+      <c r="C61" t="n">
+        <v>646.3688812783262</v>
+      </c>
+      <c r="D61" t="n">
+        <v>633.8514494094911</v>
+      </c>
+      <c r="E61" t="n">
+        <v>646.2691650390625</v>
+      </c>
+      <c r="F61" t="n">
+        <v>11033200</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>637.890997336621</v>
+      </c>
+      <c r="C62" t="n">
+        <v>643.6460494571635</v>
+      </c>
+      <c r="D62" t="n">
+        <v>636.1056625060893</v>
+      </c>
+      <c r="E62" t="n">
+        <v>639.2075805664062</v>
+      </c>
+      <c r="F62" t="n">
+        <v>13029900</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>640.6737247939117</v>
+      </c>
+      <c r="C63" t="n">
+        <v>646.1893476978298</v>
+      </c>
+      <c r="D63" t="n">
+        <v>636.4147821721649</v>
+      </c>
+      <c r="E63" t="n">
+        <v>645.4213256835938</v>
+      </c>
+      <c r="F63" t="n">
+        <v>11640900</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>642.7383773862279</v>
+      </c>
+      <c r="C64" t="n">
+        <v>647.1668624868771</v>
+      </c>
+      <c r="D64" t="n">
+        <v>635.8961867971512</v>
+      </c>
+      <c r="E64" t="n">
+        <v>637.9408569335938</v>
+      </c>
+      <c r="F64" t="n">
+        <v>11134300</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>674.2463992276428</v>
+      </c>
+      <c r="C65" t="n">
+        <v>674.3461154685141</v>
+      </c>
+      <c r="D65" t="n">
+        <v>658.3377626918029</v>
+      </c>
+      <c r="E65" t="n">
+        <v>659.81396484375</v>
+      </c>
+      <c r="F65" t="n">
+        <v>29874600</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>662.2775487290173</v>
+      </c>
+      <c r="C66" t="n">
+        <v>672.9398207362489</v>
+      </c>
+      <c r="D66" t="n">
+        <v>660.6717397649775</v>
+      </c>
+      <c r="E66" t="n">
+        <v>671.673095703125</v>
+      </c>
+      <c r="F66" t="n">
+        <v>21207900</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>667.603701448277</v>
+      </c>
+      <c r="C67" t="n">
+        <v>674.9545781663558</v>
+      </c>
+      <c r="D67" t="n">
+        <v>663.344758713728</v>
+      </c>
+      <c r="E67" t="n">
+        <v>665.0702514648438</v>
+      </c>
+      <c r="F67" t="n">
+        <v>13161000</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>662.0481300460407</v>
+      </c>
+      <c r="C68" t="n">
+        <v>662.7562492699393</v>
+      </c>
+      <c r="D68" t="n">
+        <v>651.6451938720459</v>
+      </c>
+      <c r="E68" t="n">
+        <v>655.2557983398438</v>
+      </c>
+      <c r="F68" t="n">
+        <v>12997100</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>648.2639556943986</v>
+      </c>
+      <c r="C69" t="n">
+        <v>652.8121240146866</v>
+      </c>
+      <c r="D69" t="n">
+        <v>641.730959438269</v>
+      </c>
+      <c r="E69" t="n">
+        <v>648.4434814453125</v>
+      </c>
+      <c r="F69" t="n">
+        <v>16910900</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>641.6212380225077</v>
+      </c>
+      <c r="C70" t="n">
+        <v>653.5801862453618</v>
+      </c>
+      <c r="D70" t="n">
+        <v>639.1377070000864</v>
+      </c>
+      <c r="E70" t="n">
+        <v>651.016845703125</v>
+      </c>
+      <c r="F70" t="n">
+        <v>13056700</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>648.1143965293088</v>
+      </c>
+      <c r="C71" t="n">
+        <v>709.1556549538686</v>
+      </c>
+      <c r="D71" t="n">
+        <v>636.9534211280841</v>
+      </c>
+      <c r="E71" t="n">
+        <v>642.558837890625</v>
+      </c>
+      <c r="F71" t="n">
+        <v>14016900</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>644.5502809809109</v>
+      </c>
+      <c r="C72" t="n">
+        <v>651.8372704406642</v>
+      </c>
+      <c r="D72" t="n">
+        <v>637.5627451568915</v>
+      </c>
+      <c r="E72" t="n">
+        <v>646.3570556640625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>15549100</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>642.3541999133257</v>
+      </c>
+      <c r="C73" t="n">
+        <v>661.3602758295988</v>
+      </c>
+      <c r="D73" t="n">
+        <v>642.054746271156</v>
+      </c>
+      <c r="E73" t="n">
+        <v>655.9799194335938</v>
+      </c>
+      <c r="F73" t="n">
+        <v>14309100</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>654.4426118233187</v>
+      </c>
+      <c r="C74" t="n">
+        <v>660.0526000253047</v>
+      </c>
+      <c r="D74" t="n">
+        <v>648.0440522221027</v>
+      </c>
+      <c r="E74" t="n">
+        <v>648.343505859375</v>
+      </c>
+      <c r="F74" t="n">
+        <v>15598500</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>655.8600753372949</v>
+      </c>
+      <c r="C75" t="n">
+        <v>669.3659511843067</v>
+      </c>
+      <c r="D75" t="n">
+        <v>655.2910830082761</v>
+      </c>
+      <c r="E75" t="n">
+        <v>663.266845703125</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20260300</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>665.2333263832898</v>
+      </c>
+      <c r="C76" t="n">
+        <v>669.8051880946751</v>
+      </c>
+      <c r="D76" t="n">
+        <v>657.0080086354003</v>
+      </c>
+      <c r="E76" t="n">
+        <v>657.5969848632812</v>
+      </c>
+      <c r="F76" t="n">
+        <v>49977100</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>660.4719008376494</v>
+      </c>
+      <c r="C77" t="n">
+        <v>672.3806511570199</v>
+      </c>
+      <c r="D77" t="n">
+        <v>655.4808037586267</v>
+      </c>
+      <c r="E77" t="n">
+        <v>660.3221435546875</v>
+      </c>
+      <c r="F77" t="n">
+        <v>15659400</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>658.8746741689592</v>
+      </c>
+      <c r="C78" t="n">
+        <v>664.8140915262984</v>
+      </c>
+      <c r="D78" t="n">
+        <v>657.0778915122911</v>
+      </c>
+      <c r="E78" t="n">
+        <v>663.7559814453125</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8486800</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>661.3503083186049</v>
+      </c>
+      <c r="C79" t="n">
+        <v>666.9902112020924</v>
+      </c>
+      <c r="D79" t="n">
+        <v>661.0208788671576</v>
+      </c>
+      <c r="E79" t="n">
+        <v>666.361328125</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5627500</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>666.8704739599774</v>
+      </c>
+      <c r="C80" t="n">
+        <v>667.7589038803495</v>
+      </c>
+      <c r="D80" t="n">
+        <v>660.1424847097468</v>
+      </c>
+      <c r="E80" t="n">
+        <v>662.1089477539062</v>
+      </c>
+      <c r="F80" t="n">
+        <v>7133800</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>656.8383689858442</v>
+      </c>
+      <c r="C81" t="n">
+        <v>659.0743707339258</v>
+      </c>
+      <c r="D81" t="n">
+        <v>653.2248195668056</v>
+      </c>
+      <c r="E81" t="n">
+        <v>657.5171508789062</v>
+      </c>
+      <c r="F81" t="n">
+        <v>8506500</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>657.5171386037911</v>
+      </c>
+      <c r="C82" t="n">
+        <v>671.0230153954109</v>
+      </c>
+      <c r="D82" t="n">
+        <v>656.6686764849229</v>
+      </c>
+      <c r="E82" t="n">
+        <v>664.7642211914062</v>
+      </c>
+      <c r="F82" t="n">
+        <v>9187500</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>663.5662869980947</v>
+      </c>
+      <c r="C83" t="n">
+        <v>663.8158418258488</v>
+      </c>
+      <c r="D83" t="n">
+        <v>658.2657448936569</v>
+      </c>
+      <c r="E83" t="n">
+        <v>658.9146118164062</v>
+      </c>
+      <c r="F83" t="n">
+        <v>7940400</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>661.5499009554064</v>
+      </c>
+      <c r="C84" t="n">
+        <v>663.2069792218492</v>
+      </c>
+      <c r="D84" t="n">
+        <v>642.3541620430398</v>
+      </c>
+      <c r="E84" t="n">
+        <v>649.2518310546875</v>
+      </c>
+      <c r="F84" t="n">
+        <v>13726500</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>649.8508280292294</v>
+      </c>
+      <c r="C85" t="n">
+        <v>663.3567049684374</v>
+      </c>
+      <c r="D85" t="n">
+        <v>646.5966230035071</v>
+      </c>
+      <c r="E85" t="n">
+        <v>657.616943359375</v>
+      </c>
+      <c r="F85" t="n">
+        <v>12213700</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>658.3955464147172</v>
+      </c>
+      <c r="C86" t="n">
+        <v>664.3349637543794</v>
+      </c>
+      <c r="D86" t="n">
+        <v>650.7392210314413</v>
+      </c>
+      <c r="E86" t="n">
+        <v>659.4436645507812</v>
+      </c>
+      <c r="F86" t="n">
+        <v>11074400</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>654.4725487720359</v>
+      </c>
+      <c r="C87" t="n">
+        <v>657.9763084361789</v>
+      </c>
+      <c r="D87" t="n">
+        <v>643.6618161601232</v>
+      </c>
+      <c r="E87" t="n">
+        <v>647.534912109375</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12846300</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>644.7299347572825</v>
+      </c>
+      <c r="C88" t="n">
+        <v>645.9477331499952</v>
+      </c>
+      <c r="D88" t="n">
+        <v>634.5879917891143</v>
+      </c>
+      <c r="E88" t="n">
+        <v>644.9096069335938</v>
+      </c>
+      <c r="F88" t="n">
+        <v>11921700</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>644.2907288447692</v>
+      </c>
+      <c r="C89" t="n">
+        <v>653.7838050409127</v>
+      </c>
+      <c r="D89" t="n">
+        <v>641.7053138036724</v>
+      </c>
+      <c r="E89" t="n">
+        <v>651.8971557617188</v>
+      </c>
+      <c r="F89" t="n">
+        <v>11634900</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>651.3680980277007</v>
+      </c>
+      <c r="C90" t="n">
+        <v>652.8054753941815</v>
+      </c>
+      <c r="D90" t="n">
+        <v>640.0881706951194</v>
+      </c>
+      <c r="E90" t="n">
+        <v>640.8268432617188</v>
+      </c>
+      <c r="F90" t="n">
+        <v>14797200</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>641.1263941859123</v>
+      </c>
+      <c r="C91" t="n">
+        <v>641.1263941859123</v>
+      </c>
+      <c r="D91" t="n">
+        <v>622.9887038024194</v>
+      </c>
+      <c r="E91" t="n">
+        <v>629.96630859375</v>
+      </c>
+      <c r="F91" t="n">
+        <v>18030400</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>625.3844405077801</v>
+      </c>
+      <c r="C92" t="n">
+        <v>627.3309804807691</v>
+      </c>
+      <c r="D92" t="n">
+        <v>613.7252454803604</v>
+      </c>
+      <c r="E92" t="n">
+        <v>614.4240112304688</v>
+      </c>
+      <c r="F92" t="n">
+        <v>15527900</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>617.378703801015</v>
+      </c>
+      <c r="C93" t="n">
+        <v>623.0585745209008</v>
+      </c>
+      <c r="D93" t="n">
+        <v>613.1362714280776</v>
+      </c>
+      <c r="E93" t="n">
+        <v>619.694580078125</v>
+      </c>
+      <c r="F93" t="n">
+        <v>13076100</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>623.0685636897582</v>
+      </c>
+      <c r="C94" t="n">
+        <v>627.9598630097294</v>
+      </c>
+      <c r="D94" t="n">
+        <v>618.9758886129073</v>
+      </c>
+      <c r="E94" t="n">
+        <v>619.1455688476562</v>
+      </c>
+      <c r="F94" t="n">
+        <v>17012500</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>606.7976262932837</v>
+      </c>
+      <c r="C95" t="n">
+        <v>610.3113781504126</v>
+      </c>
+      <c r="D95" t="n">
+        <v>598.9316523845154</v>
+      </c>
+      <c r="E95" t="n">
+        <v>603.0443115234375</v>
+      </c>
+      <c r="F95" t="n">
+        <v>15169600</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>605.659634898437</v>
+      </c>
+      <c r="C96" t="n">
+        <v>617.169133937088</v>
+      </c>
+      <c r="D96" t="n">
+        <v>599.0115204374271</v>
+      </c>
+      <c r="E96" t="n">
+        <v>611.8685913085938</v>
+      </c>
+      <c r="F96" t="n">
+        <v>14494700</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>628.2293275614567</v>
+      </c>
+      <c r="C97" t="n">
+        <v>659.3937675491238</v>
+      </c>
+      <c r="D97" t="n">
+        <v>625.4343255489129</v>
+      </c>
+      <c r="E97" t="n">
+        <v>646.476806640625</v>
+      </c>
+      <c r="F97" t="n">
+        <v>21394700</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>643.6219561683764</v>
+      </c>
+      <c r="C98" t="n">
+        <v>665.3032527677875</v>
+      </c>
+      <c r="D98" t="n">
+        <v>643.3025186421843</v>
+      </c>
+      <c r="E98" t="n">
+        <v>657.5870361328125</v>
+      </c>
+      <c r="F98" t="n">
+        <v>22797700</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>663.9456136216552</v>
+      </c>
+      <c r="C99" t="n">
+        <v>674.0775639748149</v>
+      </c>
+      <c r="D99" t="n">
+        <v>660.1124246688775</v>
+      </c>
+      <c r="E99" t="n">
+        <v>671.1627197265625</v>
+      </c>
+      <c r="F99" t="n">
+        <v>16327400</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>673.3888389297905</v>
+      </c>
+      <c r="C100" t="n">
+        <v>675.6148486525956</v>
+      </c>
+      <c r="D100" t="n">
+        <v>663.4764668627315</v>
+      </c>
+      <c r="E100" t="n">
+        <v>671.7716674804688</v>
+      </c>
+      <c r="F100" t="n">
+        <v>13297400</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>673.2989295276801</v>
+      </c>
+      <c r="C101" t="n">
+        <v>676.4732596455591</v>
+      </c>
+      <c r="D101" t="n">
+        <v>664.9138628916613</v>
+      </c>
+      <c r="E101" t="n">
+        <v>667.5391845703125</v>
+      </c>
+      <c r="F101" t="n">
+        <v>25709600</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>736.1169233837337</v>
+      </c>
+      <c r="C102" t="n">
+        <v>742.6752321400184</v>
+      </c>
+      <c r="D102" t="n">
+        <v>711.2812198864386</v>
+      </c>
+      <c r="E102" t="n">
+        <v>736.995361328125</v>
+      </c>
+      <c r="F102" t="n">
+        <v>59852900</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>726.2045952530067</v>
+      </c>
+      <c r="C103" t="n">
+        <v>730.8662626744616</v>
+      </c>
+      <c r="D103" t="n">
+        <v>712.3193905555435</v>
+      </c>
+      <c r="E103" t="n">
+        <v>715.2241821289062</v>
+      </c>
+      <c r="F103" t="n">
+        <v>23744600</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>713.3275184694113</v>
+      </c>
+      <c r="C104" t="n">
+        <v>720.0156002559207</v>
+      </c>
+      <c r="D104" t="n">
+        <v>702.2672920108814</v>
+      </c>
+      <c r="E104" t="n">
+        <v>705.152099609375</v>
+      </c>
+      <c r="F104" t="n">
+        <v>14365200</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>706.1104025957663</v>
+      </c>
+      <c r="C105" t="n">
+        <v>715.7232596178901</v>
+      </c>
+      <c r="D105" t="n">
+        <v>685.1877035052055</v>
+      </c>
+      <c r="E105" t="n">
+        <v>690.4683227539062</v>
+      </c>
+      <c r="F105" t="n">
+        <v>13760700</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>686.5054510943589</v>
+      </c>
+      <c r="C106" t="n">
+        <v>687.6035290584308</v>
+      </c>
+      <c r="D106" t="n">
+        <v>666.2715840299333</v>
+      </c>
+      <c r="E106" t="n">
+        <v>667.798828125</v>
+      </c>
+      <c r="F106" t="n">
+        <v>16882800</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>662.3984629374214</v>
+      </c>
+      <c r="C107" t="n">
+        <v>680.2865379695924</v>
+      </c>
+      <c r="D107" t="n">
+        <v>652.3363940764909</v>
+      </c>
+      <c r="E107" t="n">
+        <v>669.0166625976562</v>
+      </c>
+      <c r="F107" t="n">
+        <v>17131800</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>664.3050190645899</v>
+      </c>
+      <c r="C108" t="n">
+        <v>670.7934451675868</v>
+      </c>
+      <c r="D108" t="n">
+        <v>645.3488423980709</v>
+      </c>
+      <c r="E108" t="n">
+        <v>660.2822265625</v>
+      </c>
+      <c r="F108" t="n">
+        <v>18159300</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>661.9991209626965</v>
+      </c>
+      <c r="C109" t="n">
+        <v>682.0932819515241</v>
+      </c>
+      <c r="D109" t="n">
+        <v>657.6069922476072</v>
+      </c>
+      <c r="E109" t="n">
+        <v>676.0140991210938</v>
+      </c>
+      <c r="F109" t="n">
+        <v>14837500</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>676.39338857878</v>
+      </c>
+      <c r="C110" t="n">
+        <v>679.4380062536881</v>
+      </c>
+      <c r="D110" t="n">
+        <v>668.5972981068446</v>
+      </c>
+      <c r="E110" t="n">
+        <v>669.525634765625</v>
+      </c>
+      <c r="F110" t="n">
+        <v>10455800</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>672.7998711552045</v>
+      </c>
+      <c r="C111" t="n">
+        <v>678.0605068549233</v>
+      </c>
+      <c r="D111" t="n">
+        <v>655.9299390360635</v>
+      </c>
+      <c r="E111" t="n">
+        <v>667.4993286132812</v>
+      </c>
+      <c r="F111" t="n">
+        <v>14323800</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>668.7770306530766</v>
+      </c>
+      <c r="C112" t="n">
+        <v>674.7963229561075</v>
+      </c>
+      <c r="D112" t="n">
+        <v>644.1310518439949</v>
+      </c>
+      <c r="E112" t="n">
+        <v>648.6529541015625</v>
+      </c>
+      <c r="F112" t="n">
+        <v>14960100</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>643.9512634857649</v>
+      </c>
+      <c r="C113" t="n">
+        <v>650.2700088851722</v>
+      </c>
+      <c r="D113" t="n">
+        <v>633.4400456540794</v>
+      </c>
+      <c r="E113" t="n">
+        <v>638.6307983398438</v>
+      </c>
+      <c r="F113" t="n">
+        <v>12336400</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>638.3613203754355</v>
+      </c>
+      <c r="C114" t="n">
+        <v>641.4557762130754</v>
+      </c>
+      <c r="D114" t="n">
+        <v>627.6803603746322</v>
+      </c>
+      <c r="E114" t="n">
+        <v>638.1516723632812</v>
+      </c>
+      <c r="F114" t="n">
+        <v>12674700</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>632.67143641335</v>
+      </c>
+      <c r="C115" t="n">
+        <v>643.8515057528024</v>
+      </c>
+      <c r="D115" t="n">
+        <v>627.0315334227189</v>
+      </c>
+      <c r="E115" t="n">
+        <v>642.0746459960938</v>
+      </c>
+      <c r="F115" t="n">
+        <v>14649200</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>637.432932921519</v>
+      </c>
+      <c r="C116" t="n">
+        <v>646.0375787806976</v>
+      </c>
+      <c r="D116" t="n">
+        <v>635.5861905818066</v>
+      </c>
+      <c r="E116" t="n">
+        <v>643.6318969726562</v>
+      </c>
+      <c r="F116" t="n">
+        <v>10035700</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>638.5510179511008</v>
+      </c>
+      <c r="C117" t="n">
+        <v>662.1688639053526</v>
+      </c>
+      <c r="D117" t="n">
+        <v>637.642665037141</v>
+      </c>
+      <c r="E117" t="n">
+        <v>654.4925537109375</v>
+      </c>
+      <c r="F117" t="n">
+        <v>14183500</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>651.3781101885919</v>
+      </c>
+      <c r="C118" t="n">
+        <v>656.5289567660449</v>
+      </c>
+      <c r="D118" t="n">
+        <v>634.8675821094057</v>
+      </c>
+      <c r="E118" t="n">
+        <v>636.1153564453125</v>
+      </c>
+      <c r="F118" t="n">
+        <v>8605900</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>631.9527863953055</v>
+      </c>
+      <c r="C119" t="n">
+        <v>639.9684568961466</v>
+      </c>
+      <c r="D119" t="n">
+        <v>627.8600500948714</v>
+      </c>
+      <c r="E119" t="n">
+        <v>638.1616821289062</v>
+      </c>
+      <c r="F119" t="n">
+        <v>10135600</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>641.3858999809694</v>
+      </c>
+      <c r="C120" t="n">
+        <v>652.7156650876909</v>
+      </c>
+      <c r="D120" t="n">
+        <v>640.9965798171046</v>
+      </c>
+      <c r="E120" t="n">
+        <v>652.5260009765625</v>
+      </c>
+      <c r="F120" t="n">
+        <v>11330700</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>649.3916295582877</v>
+      </c>
+      <c r="C121" t="n">
+        <v>659.823034651462</v>
+      </c>
+      <c r="D121" t="n">
+        <v>646.3470725216666</v>
+      </c>
+      <c r="E121" t="n">
+        <v>655.8401489257812</v>
+      </c>
+      <c r="F121" t="n">
+        <v>10637700</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>642.3042597917192</v>
+      </c>
+      <c r="C122" t="n">
+        <v>648.2835840137412</v>
+      </c>
+      <c r="D122" t="n">
+        <v>636.9837335400734</v>
+      </c>
+      <c r="E122" t="n">
+        <v>647.0258178710938</v>
+      </c>
+      <c r="F122" t="n">
+        <v>15703000</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>636.0254184162494</v>
+      </c>
+      <c r="C123" t="n">
+        <v>658.764884603327</v>
+      </c>
+      <c r="D123" t="n">
+        <v>633.3701817354564</v>
+      </c>
+      <c r="E123" t="n">
+        <v>652.396240234375</v>
+      </c>
+      <c r="F123" t="n">
+        <v>9816100</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>647.1356255764312</v>
+      </c>
+      <c r="C124" t="n">
+        <v>657.866484005116</v>
+      </c>
+      <c r="D124" t="n">
+        <v>637.7025010942567</v>
+      </c>
+      <c r="E124" t="n">
+        <v>653.91357421875</v>
+      </c>
+      <c r="F124" t="n">
+        <v>12263800</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>656.7884535878291</v>
+      </c>
+      <c r="C125" t="n">
+        <v>671.5720803574089</v>
+      </c>
+      <c r="D125" t="n">
+        <v>656.4989309709863</v>
+      </c>
+      <c r="E125" t="n">
+        <v>666.541015625</v>
+      </c>
+      <c r="F125" t="n">
+        <v>10810100</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>660.751362594833</v>
+      </c>
+      <c r="C126" t="n">
+        <v>669.5057662619517</v>
+      </c>
+      <c r="D126" t="n">
+        <v>649.1520579976961</v>
+      </c>
+      <c r="E126" t="n">
+        <v>659.393798828125</v>
+      </c>
+      <c r="F126" t="n">
+        <v>13341400</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>646.7463568472266</v>
+      </c>
+      <c r="C127" t="n">
+        <v>648.3135076492586</v>
+      </c>
+      <c r="D127" t="n">
+        <v>634.9773114336934</v>
+      </c>
+      <c r="E127" t="n">
+        <v>643.7117309570312</v>
+      </c>
+      <c r="F127" t="n">
+        <v>13159400</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>633.6497121926325</v>
+      </c>
+      <c r="C128" t="n">
+        <v>646.5965879982328</v>
+      </c>
+      <c r="D128" t="n">
+        <v>625.6639573427893</v>
+      </c>
+      <c r="E128" t="n">
+        <v>646.2372436523438</v>
+      </c>
+      <c r="F128" t="n">
+        <v>13489700</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>652.3962938458964</v>
+      </c>
+      <c r="C129" t="n">
+        <v>659.1242831137364</v>
+      </c>
+      <c r="D129" t="n">
+        <v>647.8444156429986</v>
+      </c>
+      <c r="E129" t="n">
+        <v>652.9053955078125</v>
+      </c>
+      <c r="F129" t="n">
+        <v>9859300</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>653.5941721528687</v>
+      </c>
+      <c r="C130" t="n">
+        <v>657.9463943013674</v>
+      </c>
+      <c r="D130" t="n">
+        <v>647.2055433479961</v>
+      </c>
+      <c r="E130" t="n">
+        <v>653.6939697265625</v>
+      </c>
+      <c r="F130" t="n">
+        <v>8977200</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>647.5948883988538</v>
+      </c>
+      <c r="C131" t="n">
+        <v>652.3364309343367</v>
+      </c>
+      <c r="D131" t="n">
+        <v>635.7660119177681</v>
+      </c>
+      <c r="E131" t="n">
+        <v>637.043701171875</v>
+      </c>
+      <c r="F131" t="n">
+        <v>11617500</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>622.7790526456299</v>
+      </c>
+      <c r="C132" t="n">
+        <v>628.0496188589474</v>
+      </c>
+      <c r="D132" t="n">
+        <v>608.4645611002024</v>
+      </c>
+      <c r="E132" t="n">
+        <v>612.6171875</v>
+      </c>
+      <c r="F132" t="n">
+        <v>18957600</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>631.4147932406764</v>
+      </c>
+      <c r="C133" t="n">
+        <v>634.1622468505053</v>
+      </c>
+      <c r="D133" t="n">
+        <v>622.5230098937741</v>
+      </c>
+      <c r="E133" t="n">
+        <v>626.8690185546875</v>
+      </c>
+      <c r="F133" t="n">
+        <v>15134900</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>627.4085169382369</v>
+      </c>
+      <c r="C134" t="n">
+        <v>635.9605885584036</v>
+      </c>
+      <c r="D134" t="n">
+        <v>621.1243629754691</v>
+      </c>
+      <c r="E134" t="n">
+        <v>622.0834350585938</v>
+      </c>
+      <c r="F134" t="n">
+        <v>10348800</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>615.7693473594539</v>
+      </c>
+      <c r="C135" t="n">
+        <v>622.0735023862151</v>
+      </c>
+      <c r="D135" t="n">
+        <v>614.04090772979</v>
+      </c>
+      <c r="E135" t="n">
+        <v>615.1099243164062</v>
+      </c>
+      <c r="F135" t="n">
+        <v>11726300</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>611.5832104537112</v>
+      </c>
+      <c r="C136" t="n">
+        <v>612.4323990135786</v>
+      </c>
+      <c r="D136" t="n">
+        <v>601.7023533616688</v>
+      </c>
+      <c r="E136" t="n">
+        <v>606.1382446289062</v>
+      </c>
+      <c r="F136" t="n">
+        <v>13247700</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>602.9712077810872</v>
+      </c>
+      <c r="C137" t="n">
+        <v>603.400802317344</v>
+      </c>
+      <c r="D137" t="n">
+        <v>586.7062525156723</v>
+      </c>
+      <c r="E137" t="n">
+        <v>593.1102905273438</v>
+      </c>
+      <c r="F137" t="n">
+        <v>21214900</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>605.2290499891692</v>
+      </c>
+      <c r="C138" t="n">
+        <v>608.0764476338709</v>
+      </c>
+      <c r="D138" t="n">
+        <v>598.4553596033379</v>
+      </c>
+      <c r="E138" t="n">
+        <v>603.5006713867188</v>
+      </c>
+      <c r="F138" t="n">
+        <v>13638000</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>598.5452420228083</v>
+      </c>
+      <c r="C139" t="n">
+        <v>600.443507118967</v>
+      </c>
+      <c r="D139" t="n">
+        <v>590.4527665679026</v>
+      </c>
+      <c r="E139" t="n">
+        <v>592.3709716796875</v>
+      </c>
+      <c r="F139" t="n">
+        <v>10739700</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>598.1855830392399</v>
+      </c>
+      <c r="C140" t="n">
+        <v>603.1110107561809</v>
+      </c>
+      <c r="D140" t="n">
+        <v>592.8505617950721</v>
+      </c>
+      <c r="E140" t="n">
+        <v>594.3391723632812</v>
+      </c>
+      <c r="F140" t="n">
+        <v>12585000</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>581.9506076701073</v>
+      </c>
+      <c r="C141" t="n">
+        <v>582.460145169462</v>
+      </c>
+      <c r="D141" t="n">
+        <v>542.8468364624507</v>
+      </c>
+      <c r="E141" t="n">
+        <v>547.032958984375</v>
+      </c>
+      <c r="F141" t="n">
+        <v>35780100</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>539.599843303006</v>
+      </c>
+      <c r="C142" t="n">
+        <v>543.0966023049141</v>
+      </c>
+      <c r="D142" t="n">
+        <v>519.7782492802263</v>
+      </c>
+      <c r="E142" t="n">
+        <v>525.233154296875</v>
+      </c>
+      <c r="F142" t="n">
+        <v>30133000</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>535.8833618164062</v>
+      </c>
+      <c r="C143" t="n">
+        <v>539.0504095872608</v>
+      </c>
+      <c r="D143" t="n">
+        <v>528.0505941707193</v>
+      </c>
+      <c r="E143" t="n">
+        <v>535.8833618164062</v>
+      </c>
+      <c r="F143" t="n">
+        <v>22795200</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>549.4707059552647</v>
+      </c>
+      <c r="C144" t="n">
+        <v>573.1587727471259</v>
+      </c>
+      <c r="D144" t="n">
+        <v>546.2637174010383</v>
+      </c>
+      <c r="E144" t="n">
+        <v>571.6002197265625</v>
+      </c>
+      <c r="F144" t="n">
+        <v>32898300</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>579.5928556215499</v>
+      </c>
+      <c r="C145" t="n">
+        <v>592.0013387220274</v>
+      </c>
+      <c r="D145" t="n">
+        <v>573.2887005646345</v>
+      </c>
+      <c r="E145" t="n">
+        <v>578.6936645507812</v>
+      </c>
+      <c r="F145" t="n">
+        <v>23608100</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>565.5158531822124</v>
+      </c>
+      <c r="C146" t="n">
+        <v>577.9643377947169</v>
+      </c>
+      <c r="D146" t="n">
+        <v>559.1817578546791</v>
+      </c>
+      <c r="E146" t="n">
+        <v>573.9281005859375</v>
+      </c>
+      <c r="F146" t="n">
+        <v>13518500</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>577.1550997330287</v>
+      </c>
+      <c r="C147" t="n">
+        <v>582.2503530791108</v>
+      </c>
+      <c r="D147" t="n">
+        <v>571.4703658572956</v>
+      </c>
+      <c r="E147" t="n">
+        <v>572.4894409179688</v>
+      </c>
+      <c r="F147" t="n">
+        <v>9515700</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>571.9498894780604</v>
+      </c>
+      <c r="C148" t="n">
+        <v>574.6973431004155</v>
+      </c>
+      <c r="D148" t="n">
+        <v>564.2370671243236</v>
+      </c>
+      <c r="E148" t="n">
+        <v>574.5175170898438</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9580800</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>605.4388670235439</v>
+      </c>
+      <c r="C149" t="n">
+        <v>629.3667024291958</v>
+      </c>
+      <c r="D149" t="n">
+        <v>591.2820049792073</v>
+      </c>
+      <c r="E149" t="n">
+        <v>611.8529052734375</v>
+      </c>
+      <c r="F149" t="n">
+        <v>32036600</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>626.3894374266143</v>
+      </c>
+      <c r="C150" t="n">
+        <v>636.9097166035551</v>
+      </c>
+      <c r="D150" t="n">
+        <v>622.4231426572783</v>
+      </c>
+      <c r="E150" t="n">
+        <v>627.8081665039062</v>
+      </c>
+      <c r="F150" t="n">
+        <v>19012900</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>633.882449891805</v>
+      </c>
+      <c r="C151" t="n">
+        <v>637.9886903650855</v>
+      </c>
+      <c r="D151" t="n">
+        <v>623.7518859014353</v>
+      </c>
+      <c r="E151" t="n">
+        <v>629.2767333984375</v>
+      </c>
+      <c r="F151" t="n">
+        <v>13294800</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>628.9171329935918</v>
+      </c>
+      <c r="C152" t="n">
+        <v>634.4120404303904</v>
+      </c>
+      <c r="D152" t="n">
+        <v>623.8218795800174</v>
+      </c>
+      <c r="E152" t="n">
+        <v>633.9425048828125</v>
+      </c>
+      <c r="F152" t="n">
+        <v>9538900</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>642.624350345733</v>
+      </c>
+      <c r="C153" t="n">
+        <v>665.6430543798978</v>
+      </c>
+      <c r="D153" t="n">
+        <v>638.7779398291946</v>
+      </c>
+      <c r="E153" t="n">
+        <v>661.8765258789062</v>
+      </c>
+      <c r="F153" t="n">
+        <v>17818000</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>666.3824145357423</v>
+      </c>
+      <c r="C154" t="n">
+        <v>677.8717665104965</v>
+      </c>
+      <c r="D154" t="n">
+        <v>663.6049593103575</v>
+      </c>
+      <c r="E154" t="n">
+        <v>670.9581909179688</v>
+      </c>
+      <c r="F154" t="n">
+        <v>14952600</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>675.3640350842893</v>
+      </c>
+      <c r="C155" t="n">
+        <v>676.9525896021297</v>
+      </c>
+      <c r="D155" t="n">
+        <v>667.131674939706</v>
+      </c>
+      <c r="E155" t="n">
+        <v>676.2432250976562</v>
+      </c>
+      <c r="F155" t="n">
+        <v>9544800</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>677.9716157075654</v>
+      </c>
+      <c r="C156" t="n">
+        <v>690.8796961433965</v>
+      </c>
+      <c r="D156" t="n">
+        <v>674.5048580761284</v>
+      </c>
+      <c r="E156" t="n">
+        <v>687.9124145507812</v>
+      </c>
+      <c r="F156" t="n">
+        <v>16283500</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>680.7290935491282</v>
+      </c>
+      <c r="C157" t="n">
+        <v>682.7472426832454</v>
+      </c>
+      <c r="D157" t="n">
+        <v>667.381478611767</v>
+      </c>
+      <c r="E157" t="n">
+        <v>670.2887573242188</v>
+      </c>
+      <c r="F157" t="n">
+        <v>12534000</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>670.3786762058809</v>
+      </c>
+      <c r="C158" t="n">
+        <v>675.5738733736962</v>
+      </c>
+      <c r="D158" t="n">
+        <v>666.7120915784461</v>
+      </c>
+      <c r="E158" t="n">
+        <v>668.220703125</v>
+      </c>
+      <c r="F158" t="n">
+        <v>8660100</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>673.7355628200382</v>
+      </c>
+      <c r="C159" t="n">
+        <v>677.7518600207422</v>
+      </c>
+      <c r="D159" t="n">
+        <v>669.1298460769134</v>
+      </c>
+      <c r="E159" t="n">
+        <v>674.09521484375</v>
+      </c>
+      <c r="F159" t="n">
+        <v>9215600</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>663.0854475032797</v>
+      </c>
+      <c r="C160" t="n">
+        <v>668.9400066983026</v>
+      </c>
+      <c r="D160" t="n">
+        <v>652.4452846667049</v>
+      </c>
+      <c r="E160" t="n">
+        <v>658.5396728515625</v>
+      </c>
+      <c r="F160" t="n">
+        <v>11667000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>659.7085674039201</v>
+      </c>
+      <c r="C161" t="n">
+        <v>680.0396994180859</v>
+      </c>
+      <c r="D161" t="n">
+        <v>653.2345872360809</v>
+      </c>
+      <c r="E161" t="n">
+        <v>674.4049682617188</v>
+      </c>
+      <c r="F161" t="n">
+        <v>13348300</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>670.3786986745525</v>
+      </c>
+      <c r="C162" t="n">
+        <v>681.8680504402118</v>
+      </c>
+      <c r="D162" t="n">
+        <v>670.2188736545023</v>
+      </c>
+      <c r="E162" t="n">
+        <v>677.9916381835938</v>
+      </c>
+      <c r="F162" t="n">
+        <v>12805200</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>673.6156618787633</v>
+      </c>
+      <c r="C163" t="n">
+        <v>677.5520159823654</v>
+      </c>
+      <c r="D163" t="n">
+        <v>665.0136491453696</v>
+      </c>
+      <c r="E163" t="n">
+        <v>670.7183837890625</v>
+      </c>
+      <c r="F163" t="n">
+        <v>10606800</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>668.2905997420939</v>
+      </c>
+      <c r="C164" t="n">
+        <v>673.6256820299297</v>
+      </c>
+      <c r="D164" t="n">
+        <v>663.1953464496755</v>
+      </c>
+      <c r="E164" t="n">
+        <v>668.5004272460938</v>
+      </c>
+      <c r="F164" t="n">
+        <v>18947500</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>618.7465567527638</v>
+      </c>
+      <c r="C165" t="n">
+        <v>620.2751083620838</v>
+      </c>
+      <c r="D165" t="n">
+        <v>599.4444385151393</v>
+      </c>
+      <c r="E165" t="n">
+        <v>611.3433837890625</v>
+      </c>
+      <c r="F165" t="n">
+        <v>52765000</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>614.120842749119</v>
+      </c>
+      <c r="C166" t="n">
+        <v>618.3069655430758</v>
+      </c>
+      <c r="D166" t="n">
+        <v>605.5487701514051</v>
+      </c>
+      <c r="E166" t="n">
+        <v>608.1863403320312</v>
+      </c>
+      <c r="F166" t="n">
+        <v>21404000</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>607.3771038685389</v>
+      </c>
+      <c r="C167" t="n">
+        <v>613.4314904063681</v>
+      </c>
+      <c r="D167" t="n">
+        <v>602.1919069095087</v>
+      </c>
+      <c r="E167" t="n">
+        <v>609.8447875976562</v>
+      </c>
+      <c r="F167" t="n">
+        <v>16203900</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>612.7420849871345</v>
+      </c>
+      <c r="C168" t="n">
+        <v>613.7811000159977</v>
+      </c>
+      <c r="D168" t="n">
+        <v>599.8040642277598</v>
+      </c>
+      <c r="E168" t="n">
+        <v>604.3998413085938</v>
+      </c>
+      <c r="F168" t="n">
+        <v>17171300</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>600.4934370812971</v>
+      </c>
+      <c r="C169" t="n">
+        <v>619.3759607512419</v>
+      </c>
+      <c r="D169" t="n">
+        <v>597.5461564796674</v>
+      </c>
+      <c r="E169" t="n">
+        <v>612.3125</v>
+      </c>
+      <c r="F169" t="n">
+        <v>19915500</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>614.150739078972</v>
+      </c>
+      <c r="C170" t="n">
+        <v>624.4012480600104</v>
+      </c>
+      <c r="D170" t="n">
+        <v>612.9718390781961</v>
+      </c>
+      <c r="E170" t="n">
+        <v>616.2388305664062</v>
+      </c>
+      <c r="F170" t="n">
+        <v>12307400</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>614.6303402495529</v>
+      </c>
+      <c r="C171" t="n">
+        <v>616.1988937552933</v>
+      </c>
+      <c r="D171" t="n">
+        <v>605.4987892063378</v>
+      </c>
+      <c r="E171" t="n">
+        <v>609.0654907226562</v>
+      </c>
+      <c r="F171" t="n">
+        <v>13557000</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>604.010215830275</v>
+      </c>
+      <c r="C172" t="n">
+        <v>604.3498668649182</v>
+      </c>
+      <c r="D172" t="n">
+        <v>597.5262348938886</v>
+      </c>
+      <c r="E172" t="n">
+        <v>598.3054809570312</v>
+      </c>
+      <c r="F172" t="n">
+        <v>15940600</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>594.2692320029287</v>
+      </c>
+      <c r="C173" t="n">
+        <v>603.1909559259367</v>
+      </c>
+      <c r="D173" t="n">
+        <v>592.0512559095129</v>
+      </c>
+      <c r="E173" t="n">
+        <v>602.441650390625</v>
+      </c>
+      <c r="F173" t="n">
+        <v>11351600</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>598.275515544453</v>
+      </c>
+      <c r="C174" t="n">
+        <v>619.3260125714435</v>
+      </c>
+      <c r="D174" t="n">
+        <v>596.1074810052941</v>
+      </c>
+      <c r="E174" t="n">
+        <v>616.0590209960938</v>
+      </c>
+      <c r="F174" t="n">
+        <v>14634400</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>615.4296182023591</v>
+      </c>
+      <c r="C175" t="n">
+        <v>623.152441138389</v>
+      </c>
+      <c r="D175" t="n">
+        <v>614.4305441468357</v>
+      </c>
+      <c r="E175" t="n">
+        <v>617.8573608398438</v>
+      </c>
+      <c r="F175" t="n">
+        <v>10651200</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>613.421486859321</v>
+      </c>
+      <c r="C176" t="n">
+        <v>620.6248329546977</v>
+      </c>
+      <c r="D176" t="n">
+        <v>608.7458274653094</v>
+      </c>
+      <c r="E176" t="n">
+        <v>613.6612548828125</v>
+      </c>
+      <c r="F176" t="n">
+        <v>13272600</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>608.5459509764945</v>
+      </c>
+      <c r="C177" t="n">
+        <v>615.0199919776213</v>
+      </c>
+      <c r="D177" t="n">
+        <v>603.1309869574205</v>
+      </c>
+      <c r="E177" t="n">
+        <v>610.64404296875</v>
+      </c>
+      <c r="F177" t="n">
+        <v>13772400</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>608.3561568042173</v>
+      </c>
+      <c r="C178" t="n">
+        <v>613.361527578881</v>
+      </c>
+      <c r="D178" t="n">
+        <v>599.9939118379299</v>
+      </c>
+      <c r="E178" t="n">
+        <v>602.052001953125</v>
+      </c>
+      <c r="F178" t="n">
+        <v>11749900</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>600.2037495434126</v>
+      </c>
+      <c r="C179" t="n">
+        <v>607.4370360716302</v>
+      </c>
+      <c r="D179" t="n">
+        <v>597.2564688338498</v>
+      </c>
+      <c r="E179" t="n">
+        <v>604.499755859375</v>
+      </c>
+      <c r="F179" t="n">
+        <v>11329700</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>599.4443949814065</v>
+      </c>
+      <c r="C180" t="n">
+        <v>609.0354809096541</v>
+      </c>
+      <c r="D180" t="n">
+        <v>594.2591985256718</v>
+      </c>
+      <c r="E180" t="n">
+        <v>606.8175659179688</v>
+      </c>
+      <c r="F180" t="n">
+        <v>13476100</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>607.3171451453314</v>
+      </c>
+      <c r="C181" t="n">
+        <v>614.2407210713809</v>
+      </c>
+      <c r="D181" t="n">
+        <v>606.3880135859368</v>
+      </c>
+      <c r="E181" t="n">
+        <v>609.6949462890625</v>
+      </c>
+      <c r="F181" t="n">
+        <v>11688600</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>608.3261927003538</v>
+      </c>
+      <c r="C182" t="n">
+        <v>613.9009818092591</v>
+      </c>
+      <c r="D182" t="n">
+        <v>604.7394901495815</v>
+      </c>
+      <c r="E182" t="n">
+        <v>611.7730102539062</v>
+      </c>
+      <c r="F182" t="n">
+        <v>12234200</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>608.8357727220844</v>
+      </c>
+      <c r="C183" t="n">
+        <v>637.908804248614</v>
+      </c>
+      <c r="D183" t="n">
+        <v>608.4361186960156</v>
+      </c>
+      <c r="E183" t="n">
+        <v>634.6718139648438</v>
+      </c>
+      <c r="F183" t="n">
+        <v>23143600</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>638.9078448274123</v>
+      </c>
+      <c r="C184" t="n">
+        <v>642.4046039468743</v>
+      </c>
+      <c r="D184" t="n">
+        <v>628.7272779804616</v>
+      </c>
+      <c r="E184" t="n">
+        <v>634.7017211914062</v>
+      </c>
+      <c r="F184" t="n">
+        <v>16772400</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>632.9133899267435</v>
+      </c>
+      <c r="C185" t="n">
+        <v>633.9124639439917</v>
+      </c>
+      <c r="D185" t="n">
+        <v>622.7727642602187</v>
+      </c>
+      <c r="E185" t="n">
+        <v>631.92431640625</v>
+      </c>
+      <c r="F185" t="n">
+        <v>19806500</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>629.8162791560948</v>
+      </c>
+      <c r="C186" t="n">
+        <v>635.1613007084701</v>
+      </c>
+      <c r="D186" t="n">
+        <v>598.9748694014791</v>
+      </c>
+      <c r="E186" t="n">
+        <v>599.9139404296875</v>
+      </c>
+      <c r="F186" t="n">
+        <v>29138800</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>602.6813896226799</v>
+      </c>
+      <c r="C187" t="n">
+        <v>608.3161816139932</v>
+      </c>
+      <c r="D187" t="n">
+        <v>596.1274666259658</v>
+      </c>
+      <c r="E187" t="n">
+        <v>597.0765991210938</v>
+      </c>
+      <c r="F187" t="n">
+        <v>18252000</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>602.4416570391962</v>
+      </c>
+      <c r="C188" t="n">
+        <v>623.5720977596394</v>
+      </c>
+      <c r="D188" t="n">
+        <v>599.7142043737263</v>
+      </c>
+      <c r="E188" t="n">
+        <v>622.4031372070312</v>
+      </c>
+      <c r="F188" t="n">
+        <v>23020100</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>623.0924785224576</v>
+      </c>
+      <c r="C189" t="n">
+        <v>641.8051764288737</v>
+      </c>
+      <c r="D189" t="n">
+        <v>621.8536364911718</v>
+      </c>
+      <c r="E189" t="n">
+        <v>626.9888916015625</v>
+      </c>
+      <c r="F189" t="n">
+        <v>21469200</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>622.8827460758752</v>
+      </c>
+      <c r="C190" t="n">
+        <v>628.5674800138549</v>
+      </c>
+      <c r="D190" t="n">
+        <v>582.3702434655938</v>
+      </c>
+      <c r="E190" t="n">
+        <v>592.450927734375</v>
+      </c>
+      <c r="F190" t="n">
+        <v>30091600</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>591.4518261333767</v>
+      </c>
+      <c r="C191" t="n">
+        <v>591.4518261333767</v>
+      </c>
+      <c r="D191" t="n">
+        <v>578.6836307521693</v>
+      </c>
+      <c r="E191" t="n">
+        <v>584.8479614257812</v>
+      </c>
+      <c r="F191" t="n">
+        <v>19512400</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>590.4527436689563</v>
+      </c>
+      <c r="C192" t="n">
+        <v>597.0766092757164</v>
+      </c>
+      <c r="D192" t="n">
+        <v>580.4720040020986</v>
+      </c>
+      <c r="E192" t="n">
+        <v>584.0487060546875</v>
+      </c>
+      <c r="F192" t="n">
+        <v>16977400</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>580.192266144374</v>
+      </c>
+      <c r="C193" t="n">
+        <v>590.7724873942649</v>
+      </c>
+      <c r="D193" t="n">
+        <v>570.0716409197756</v>
+      </c>
+      <c r="E193" t="n">
+        <v>570.4512939453125</v>
+      </c>
+      <c r="F193" t="n">
+        <v>17064000</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>565.3060574843756</v>
+      </c>
+      <c r="C194" t="n">
+        <v>571.6401524850257</v>
+      </c>
+      <c r="D194" t="n">
+        <v>556.4942175026772</v>
+      </c>
+      <c r="E194" t="n">
+        <v>567.9036254882812</v>
+      </c>
+      <c r="F194" t="n">
+        <v>17628000</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>572.4194595335534</v>
+      </c>
+      <c r="C195" t="n">
+        <v>575.5365655300229</v>
+      </c>
+      <c r="D195" t="n">
+        <v>560.3806300495169</v>
+      </c>
+      <c r="E195" t="n">
+        <v>566.4549560546875</v>
+      </c>
+      <c r="F195" t="n">
+        <v>14326400</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>579.9000244140625</v>
+      </c>
+      <c r="C196" t="n">
+        <v>601.27001953125</v>
+      </c>
+      <c r="D196" t="n">
+        <v>579.2999877929688</v>
+      </c>
+      <c r="E196" t="n">
+        <v>593.47998046875</v>
+      </c>
+      <c r="F196" t="n">
+        <v>17653300</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>593.6500244140625</v>
+      </c>
+      <c r="C197" t="n">
+        <v>605.8099975585938</v>
+      </c>
+      <c r="D197" t="n">
+        <v>592</v>
+      </c>
+      <c r="E197" t="n">
+        <v>600.2100219726562</v>
+      </c>
+      <c r="F197" t="n">
+        <v>11344400</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>592</v>
+      </c>
+      <c r="C198" t="n">
+        <v>593.8099975585938</v>
+      </c>
+      <c r="D198" t="n">
+        <v>566.1900024414062</v>
+      </c>
+      <c r="E198" t="n">
+        <v>567.5800170898438</v>
+      </c>
+      <c r="F198" t="n">
+        <v>20478300</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>572.8200073242188</v>
+      </c>
+      <c r="C199" t="n">
+        <v>580.219970703125</v>
+      </c>
+      <c r="D199" t="n">
+        <v>563.0999755859375</v>
+      </c>
+      <c r="E199" t="n">
+        <v>577.219970703125</v>
+      </c>
+      <c r="F199" t="n">
+        <v>28824600</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>572.02001953125</v>
+      </c>
+      <c r="C200" t="n">
+        <v>575.8099975585938</v>
+      </c>
+      <c r="D200" t="n">
+        <v>559.8099975585938</v>
+      </c>
+      <c r="E200" t="n">
+        <v>563.8499755859375</v>
+      </c>
+      <c r="F200" t="n">
+        <v>15405500</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>562.25</v>
+      </c>
+      <c r="C201" t="n">
+        <v>572.2000122070312</v>
+      </c>
+      <c r="D201" t="n">
+        <v>561.02001953125</v>
+      </c>
+      <c r="E201" t="n">
+        <v>562.2000122070312</v>
+      </c>
+      <c r="F201" t="n">
+        <v>13103300</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>561.8900146484375</v>
+      </c>
+      <c r="C202" t="n">
+        <v>569.0399780273438</v>
+      </c>
+      <c r="D202" t="n">
+        <v>555.5499877929688</v>
+      </c>
+      <c r="E202" t="n">
+        <v>557.6699829101562</v>
+      </c>
+      <c r="F202" t="n">
+        <v>13963600</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>555.5499877929688</v>
+      </c>
+      <c r="C203" t="n">
+        <v>556.3400268554688</v>
+      </c>
+      <c r="D203" t="n">
+        <v>540.1799926757812</v>
+      </c>
+      <c r="E203" t="n">
+        <v>542.8699951171875</v>
+      </c>
+      <c r="F203" t="n">
+        <v>16968600</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>543.3400268554688</v>
+      </c>
+      <c r="C204" t="n">
+        <v>556.8499755859375</v>
+      </c>
+      <c r="D204" t="n">
+        <v>540.4000244140625</v>
+      </c>
+      <c r="E204" t="n">
+        <v>550.25</v>
+      </c>
+      <c r="F204" t="n">
+        <v>18867700</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>560</v>
+      </c>
+      <c r="C205" t="n">
+        <v>570.9000244140625</v>
+      </c>
+      <c r="D205" t="n">
+        <v>558</v>
+      </c>
+      <c r="E205" t="n">
+        <v>562.5999755859375</v>
+      </c>
+      <c r="F205" t="n">
+        <v>15011400</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>560.9400024414062</v>
+      </c>
+      <c r="C206" t="n">
+        <v>565.5399780273438</v>
+      </c>
+      <c r="D206" t="n">
+        <v>551.4299926757812</v>
+      </c>
+      <c r="E206" t="n">
+        <v>563.2899780273438</v>
+      </c>
+      <c r="F206" t="n">
+        <v>18111100</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>607.9099731445312</v>
+      </c>
+      <c r="C207" t="n">
+        <v>628.280029296875</v>
+      </c>
+      <c r="D207" t="n">
+        <v>595.0999755859375</v>
+      </c>
+      <c r="E207" t="n">
+        <v>612.9099731445312</v>
+      </c>
+      <c r="F207" t="n">
+        <v>45536300</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>607.9000244140625</v>
+      </c>
+      <c r="C208" t="n">
+        <v>610</v>
+      </c>
+      <c r="D208" t="n">
+        <v>580.4199829101562</v>
+      </c>
+      <c r="E208" t="n">
+        <v>582.9000244140625</v>
+      </c>
+      <c r="F208" t="n">
+        <v>21705900</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>594.8400268554688</v>
+      </c>
+      <c r="C209" t="n">
+        <v>603.5800170898438</v>
+      </c>
+      <c r="D209" t="n">
+        <v>581.760009765625</v>
+      </c>
+      <c r="E209" t="n">
+        <v>600.2899780273438</v>
+      </c>
+      <c r="F209" t="n">
+        <v>17674100</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>607.5900268554688</v>
+      </c>
+      <c r="C210" t="n">
+        <v>625.3699951171875</v>
+      </c>
+      <c r="D210" t="n">
+        <v>603.6599731445312</v>
+      </c>
+      <c r="E210" t="n">
+        <v>615.5800170898438</v>
+      </c>
+      <c r="F210" t="n">
+        <v>18560800</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>614.3900146484375</v>
+      </c>
+      <c r="C211" t="n">
+        <v>616</v>
+      </c>
+      <c r="D211" t="n">
+        <v>598.010009765625</v>
+      </c>
+      <c r="E211" t="n">
+        <v>603.1199951171875</v>
+      </c>
+      <c r="F211" t="n">
+        <v>13606500</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>583.989990234375</v>
+      </c>
+      <c r="C212" t="n">
+        <v>633.27001953125</v>
+      </c>
+      <c r="D212" t="n">
+        <v>577.0700073242188</v>
+      </c>
+      <c r="E212" t="n">
+        <v>631.47998046875</v>
+      </c>
+      <c r="F212" t="n">
+        <v>26579700</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>660.3400268554688</v>
+      </c>
+      <c r="C213" t="n">
+        <v>677.8599853515625</v>
+      </c>
+      <c r="D213" t="n">
+        <v>658.010009765625</v>
+      </c>
+      <c r="E213" t="n">
+        <v>669.2100219726562</v>
+      </c>
+      <c r="F213" t="n">
+        <v>40608900</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>661.3800048828125</v>
+      </c>
+      <c r="C214" t="n">
+        <v>676.6199951171875</v>
+      </c>
+      <c r="D214" t="n">
+        <v>654.2000122070312</v>
+      </c>
+      <c r="E214" t="n">
+        <v>656.72998046875</v>
+      </c>
+      <c r="F214" t="n">
+        <v>19840700</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>652</v>
+      </c>
+      <c r="C215" t="n">
+        <v>666.5</v>
+      </c>
+      <c r="D215" t="n">
+        <v>649.0499877929688</v>
+      </c>
+      <c r="E215" t="n">
+        <v>661.0399780273438</v>
+      </c>
+      <c r="F215" t="n">
+        <v>16748200</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>663.5999755859375</v>
+      </c>
+      <c r="C216" t="n">
+        <v>686.0800170898438</v>
+      </c>
+      <c r="D216" t="n">
+        <v>656.6599731445312</v>
+      </c>
+      <c r="E216" t="n">
+        <v>681.3099975585938</v>
+      </c>
+      <c r="F216" t="n">
+        <v>19003400</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>677.280029296875</v>
+      </c>
+      <c r="C217" t="n">
+        <v>681.9000244140625</v>
+      </c>
+      <c r="D217" t="n">
+        <v>660.1599731445312</v>
+      </c>
+      <c r="E217" t="n">
+        <v>664.5399780273438</v>
+      </c>
+      <c r="F217" t="n">
+        <v>15816000</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>647.7000122070312</v>
+      </c>
+      <c r="C218" t="n">
+        <v>652.2000122070312</v>
+      </c>
+      <c r="D218" t="n">
+        <v>626</v>
+      </c>
+      <c r="E218" t="n">
+        <v>646.010009765625</v>
+      </c>
+      <c r="F218" t="n">
+        <v>22267900</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>646.7000122070312</v>
+      </c>
+      <c r="C219" t="n">
+        <v>653.2999877929688</v>
+      </c>
+      <c r="D219" t="n">
+        <v>636.010009765625</v>
+      </c>
+      <c r="E219" t="n">
+        <v>645.8499755859375</v>
+      </c>
+      <c r="F219" t="n">
+        <v>10225200</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>654.1799926757812</v>
+      </c>
+      <c r="C220" t="n">
+        <v>655.8800048828125</v>
+      </c>
+      <c r="D220" t="n">
+        <v>643.2000122070312</v>
+      </c>
+      <c r="E220" t="n">
+        <v>643.8099975585938</v>
+      </c>
+      <c r="F220" t="n">
+        <v>9140500</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>647.7000122070312</v>
+      </c>
+      <c r="C221" t="n">
+        <v>649</v>
+      </c>
+      <c r="D221" t="n">
+        <v>624</v>
+      </c>
+      <c r="E221" t="n">
+        <v>627.1699829101562</v>
+      </c>
+      <c r="F221" t="n">
+        <v>11019600</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>608.4099731445312</v>
+      </c>
+      <c r="C222" t="n">
+        <v>614.6500244140625</v>
+      </c>
+      <c r="D222" t="n">
+        <v>597.219970703125</v>
+      </c>
+      <c r="E222" t="n">
+        <v>606.0999755859375</v>
+      </c>
+      <c r="F222" t="n">
+        <v>15494800</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>605.2999877929688</v>
+      </c>
+      <c r="C223" t="n">
+        <v>609.97998046875</v>
+      </c>
+      <c r="D223" t="n">
+        <v>594.4500122070312</v>
+      </c>
+      <c r="E223" t="n">
+        <v>595.1900024414062</v>
+      </c>
+      <c r="F223" t="n">
+        <v>11503500</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>607.219970703125</v>
+      </c>
+      <c r="C224" t="n">
+        <v>611.260009765625</v>
+      </c>
+      <c r="D224" t="n">
+        <v>593.1300048828125</v>
+      </c>
+      <c r="E224" t="n">
+        <v>593.8699951171875</v>
+      </c>
+      <c r="F224" t="n">
+        <v>11195300</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>596.8200073242188</v>
+      </c>
+      <c r="C225" t="n">
+        <v>601</v>
+      </c>
+      <c r="D225" t="n">
+        <v>587</v>
+      </c>
+      <c r="E225" t="n">
+        <v>593.4099731445312</v>
+      </c>
+      <c r="F225" t="n">
+        <v>12009300</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>593.25</v>
+      </c>
+      <c r="C226" t="n">
+        <v>599.969970703125</v>
+      </c>
+      <c r="D226" t="n">
+        <v>582.219970703125</v>
+      </c>
+      <c r="E226" t="n">
+        <v>585.6099853515625</v>
+      </c>
+      <c r="F226" t="n">
+        <v>22371100</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>526</v>
+      </c>
+      <c r="C227" t="n">
+        <v>539.8800048828125</v>
+      </c>
+      <c r="D227" t="n">
+        <v>524.489990234375</v>
+      </c>
+      <c r="E227" t="n">
+        <v>539.030029296875</v>
+      </c>
+      <c r="F227" t="n">
+        <v>42271500</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>543.5999755859375</v>
+      </c>
+      <c r="C228" t="n">
+        <v>558.3300170898438</v>
+      </c>
+      <c r="D228" t="n">
+        <v>540.219970703125</v>
+      </c>
+      <c r="E228" t="n">
+        <v>556.7100219726562</v>
+      </c>
+      <c r="F228" t="n">
+        <v>24261500</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>562.239990234375</v>
+      </c>
+      <c r="C229" t="n">
+        <v>597.52001953125</v>
+      </c>
+      <c r="D229" t="n">
+        <v>559.3599853515625</v>
+      </c>
+      <c r="E229" t="n">
+        <v>590.239990234375</v>
+      </c>
+      <c r="F229" t="n">
+        <v>25938100</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>581.5</v>
+      </c>
+      <c r="C230" t="n">
+        <v>592.7899780273438</v>
+      </c>
+      <c r="D230" t="n">
+        <v>578.25</v>
+      </c>
+      <c r="E230" t="n">
+        <v>587.9400024414062</v>
+      </c>
+      <c r="F230" t="n">
+        <v>17959200</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>600.4600219726562</v>
+      </c>
+      <c r="C231" t="n">
+        <v>601</v>
+      </c>
+      <c r="D231" t="n">
+        <v>580.1199951171875</v>
+      </c>
+      <c r="E231" t="n">
+        <v>588.77001953125</v>
+      </c>
+      <c r="F231" t="n">
+        <v>14897200</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>586.9500122070312</v>
+      </c>
+      <c r="C232" t="n">
+        <v>595.3099975585938</v>
+      </c>
+      <c r="D232" t="n">
+        <v>586</v>
+      </c>
+      <c r="E232" t="n">
+        <v>589.9000244140625</v>
+      </c>
+      <c r="F232" t="n">
+        <v>11811500</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>585.6400146484375</v>
+      </c>
+      <c r="C233" t="n">
+        <v>598.739990234375</v>
+      </c>
+      <c r="D233" t="n">
+        <v>585.6199951171875</v>
+      </c>
+      <c r="E233" t="n">
+        <v>592.0999755859375</v>
+      </c>
+      <c r="F233" t="n">
+        <v>11250300</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>599.1300048828125</v>
+      </c>
+      <c r="C234" t="n">
+        <v>608.2100219726562</v>
+      </c>
+      <c r="D234" t="n">
+        <v>592.030029296875</v>
+      </c>
+      <c r="E234" t="n">
+        <v>594.9199829101562</v>
+      </c>
+      <c r="F234" t="n">
+        <v>14967300</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>598</v>
+      </c>
+      <c r="C235" t="n">
+        <v>612.4299926757812</v>
+      </c>
+      <c r="D235" t="n">
+        <v>593.4000244140625</v>
+      </c>
+      <c r="E235" t="n">
+        <v>599.1199951171875</v>
+      </c>
+      <c r="F235" t="n">
+        <v>13146900</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>601.0700073242188</v>
+      </c>
+      <c r="C236" t="n">
+        <v>604.5</v>
+      </c>
+      <c r="D236" t="n">
+        <v>578.2100219726562</v>
+      </c>
+      <c r="E236" t="n">
+        <v>578.8499755859375</v>
+      </c>
+      <c r="F236" t="n">
+        <v>16186900</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>580.7100219726562</v>
+      </c>
+      <c r="C237" t="n">
+        <v>595.8499755859375</v>
+      </c>
+      <c r="D237" t="n">
+        <v>579.3900146484375</v>
+      </c>
+      <c r="E237" t="n">
+        <v>594.969970703125</v>
+      </c>
+      <c r="F237" t="n">
+        <v>11164200</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>596.97998046875</v>
+      </c>
+      <c r="C238" t="n">
+        <v>601.8599853515625</v>
+      </c>
+      <c r="D238" t="n">
+        <v>589.2899780273438</v>
+      </c>
+      <c r="E238" t="n">
+        <v>589.8499755859375</v>
+      </c>
+      <c r="F238" t="n">
+        <v>8758000</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>589.75</v>
+      </c>
+      <c r="C239" t="n">
+        <v>590.239990234375</v>
+      </c>
+      <c r="D239" t="n">
+        <v>564.75</v>
+      </c>
+      <c r="E239" t="n">
+        <v>568.969970703125</v>
+      </c>
+      <c r="F239" t="n">
+        <v>17225600</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>557.47998046875</v>
+      </c>
+      <c r="C240" t="n">
+        <v>560.6599731445312</v>
+      </c>
+      <c r="D240" t="n">
+        <v>543.2100219726562</v>
+      </c>
+      <c r="E240" t="n">
+        <v>543.6699829101562</v>
+      </c>
+      <c r="F240" t="n">
+        <v>27094900</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>541.3400268554688</v>
+      </c>
+      <c r="C241" t="n">
+        <v>554.0700073242188</v>
+      </c>
+      <c r="D241" t="n">
+        <v>537.27001953125</v>
+      </c>
+      <c r="E241" t="n">
+        <v>546.030029296875</v>
+      </c>
+      <c r="F241" t="n">
+        <v>16971700</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>546.9500122070312</v>
+      </c>
+      <c r="C242" t="n">
+        <v>549.989990234375</v>
+      </c>
+      <c r="D242" t="n">
+        <v>539.3099975585938</v>
+      </c>
+      <c r="E242" t="n">
+        <v>545.8300170898438</v>
+      </c>
+      <c r="F242" t="n">
+        <v>13872200</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>546.8900146484375</v>
+      </c>
+      <c r="C243" t="n">
+        <v>553.8699951171875</v>
+      </c>
+      <c r="D243" t="n">
+        <v>543.22998046875</v>
+      </c>
+      <c r="E243" t="n">
+        <v>549.9000244140625</v>
+      </c>
+      <c r="F243" t="n">
+        <v>13848000</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>550.2000122070312</v>
+      </c>
+      <c r="C244" t="n">
+        <v>561.4199829101562</v>
+      </c>
+      <c r="D244" t="n">
+        <v>546.2999877929688</v>
+      </c>
+      <c r="E244" t="n">
+        <v>559.02001953125</v>
+      </c>
+      <c r="F244" t="n">
+        <v>12990600</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>563.8800048828125</v>
+      </c>
+      <c r="C245" t="n">
+        <v>570.7999877929688</v>
+      </c>
+      <c r="D245" t="n">
+        <v>561.4000244140625</v>
+      </c>
+      <c r="E245" t="n">
+        <v>570.0499877929688</v>
+      </c>
+      <c r="F245" t="n">
+        <v>9769100</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>590.3099975585938</v>
+      </c>
+      <c r="C246" t="n">
+        <v>593.3400268554688</v>
+      </c>
+      <c r="D246" t="n">
+        <v>561.8800048828125</v>
+      </c>
+      <c r="E246" t="n">
+        <v>576.1400146484375</v>
+      </c>
+      <c r="F246" t="n">
+        <v>31416300</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>576.47998046875</v>
+      </c>
+      <c r="C247" t="n">
+        <v>588.3900146484375</v>
+      </c>
+      <c r="D247" t="n">
+        <v>567.6199951171875</v>
+      </c>
+      <c r="E247" t="n">
+        <v>571.0999755859375</v>
+      </c>
+      <c r="F247" t="n">
+        <v>15221400</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>571.5499877929688</v>
+      </c>
+      <c r="C248" t="n">
+        <v>589.1900024414062</v>
+      </c>
+      <c r="D248" t="n">
+        <v>571</v>
+      </c>
+      <c r="E248" t="n">
+        <v>578.02001953125</v>
+      </c>
+      <c r="F248" t="n">
+        <v>16042400</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>577.6300048828125</v>
+      </c>
+      <c r="C249" t="n">
+        <v>578.6799926757812</v>
+      </c>
+      <c r="D249" t="n">
+        <v>569.1400146484375</v>
+      </c>
+      <c r="E249" t="n">
+        <v>572.3400268554688</v>
+      </c>
+      <c r="F249" t="n">
+        <v>13383800</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>558.3499755859375</v>
+      </c>
+      <c r="C250" t="n">
+        <v>584.9500122070312</v>
+      </c>
+      <c r="D250" t="n">
+        <v>556.0999755859375</v>
+      </c>
+      <c r="E250" t="n">
+        <v>578.5399780273438</v>
+      </c>
+      <c r="F250" t="n">
+        <v>15796900</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>578.7899780273438</v>
+      </c>
+      <c r="C251" t="n">
+        <v>600.3800048828125</v>
+      </c>
+      <c r="D251" t="n">
+        <v>577</v>
+      </c>
+      <c r="E251" t="n">
+        <v>592.8499755859375</v>
+      </c>
+      <c r="F251" t="n">
+        <v>16552700</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>604.489990234375</v>
+      </c>
+      <c r="C252" t="n">
+        <v>619.4600219726562</v>
+      </c>
+      <c r="D252" t="n">
+        <v>604.3499755859375</v>
+      </c>
+      <c r="E252" t="n">
+        <v>610.6799926757812</v>
+      </c>
+      <c r="F252" t="n">
+        <v>19737100</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>612.3499755859375</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>617.4600219726562</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>605.27001953125</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>616.77001953125</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>15942700</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4857,13 +10811,13 @@
         <v>612.495</v>
       </c>
       <c r="F2" t="n">
-        <v>617.4299999999999</v>
+        <v>617.46</v>
       </c>
       <c r="G2" t="n">
         <v>605.27</v>
       </c>
       <c r="H2" t="n">
-        <v>15745973</v>
+        <v>15966213</v>
       </c>
       <c r="I2" t="n">
         <v>17851201</v>
@@ -4953,7 +10907,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:25</t>
+          <t>2026-09-07 03:08:15</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -524,16 +524,16 @@
         <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>755.0154070864886</v>
+        <v>755.0153467057662</v>
       </c>
       <c r="C4" t="n">
-        <v>763.7966239723705</v>
+        <v>763.7965628893893</v>
       </c>
       <c r="D4" t="n">
-        <v>750.9686728075005</v>
+        <v>750.9686127504068</v>
       </c>
       <c r="E4" t="n">
-        <v>763.1986083984375</v>
+        <v>763.1985473632812</v>
       </c>
       <c r="F4" t="n">
         <v>10999000</v>
@@ -550,16 +550,16 @@
         <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>762.6305659580242</v>
+        <v>762.6305038555339</v>
       </c>
       <c r="C5" t="n">
-        <v>763.198711247707</v>
+        <v>763.1986490989516</v>
       </c>
       <c r="D5" t="n">
-        <v>748.5467193541789</v>
+        <v>748.5466583985636</v>
       </c>
       <c r="E5" t="n">
-        <v>749.5234985351562</v>
+        <v>749.5234375</v>
       </c>
       <c r="F5" t="n">
         <v>12478300</v>
@@ -628,16 +628,16 @@
         <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>754.995481759339</v>
+        <v>754.9954213012545</v>
       </c>
       <c r="C8" t="n">
-        <v>771.5412896866574</v>
+        <v>771.5412279036273</v>
       </c>
       <c r="D8" t="n">
-        <v>749.5334031898147</v>
+        <v>749.5333431691193</v>
       </c>
       <c r="E8" t="n">
-        <v>762.201904296875</v>
+        <v>762.2018432617188</v>
       </c>
       <c r="F8" t="n">
         <v>10533800</v>
@@ -654,16 +654,16 @@
         <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>764.4944012192615</v>
+        <v>764.494341124313</v>
       </c>
       <c r="C9" t="n">
-        <v>778.8074760600178</v>
+        <v>778.8074148399552</v>
       </c>
       <c r="D9" t="n">
-        <v>762.6005837137456</v>
+        <v>762.6005237676653</v>
       </c>
       <c r="E9" t="n">
-        <v>776.4552001953125</v>
+        <v>776.4551391601562</v>
       </c>
       <c r="F9" t="n">
         <v>11782500</v>
@@ -706,16 +706,16 @@
         <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>778.1994163857863</v>
+        <v>778.1994774600552</v>
       </c>
       <c r="C11" t="n">
-        <v>786.2032128794</v>
+        <v>786.203274581819</v>
       </c>
       <c r="D11" t="n">
-        <v>770.8335437165625</v>
+        <v>770.8336042127465</v>
       </c>
       <c r="E11" t="n">
-        <v>777.7010498046875</v>
+        <v>777.7011108398438</v>
       </c>
       <c r="F11" t="n">
         <v>10955000</v>
@@ -732,16 +732,16 @@
         <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>783.8509325355676</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C12" t="n">
-        <v>788.2166289656076</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D12" t="n">
-        <v>766.6772383880447</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E12" t="n">
-        <v>775.8372192382812</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F12" t="n">
         <v>23696800</v>
@@ -836,16 +836,16 @@
         <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>751.4955472633491</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C16" t="n">
-        <v>754.806942419776</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D16" t="n">
-        <v>742.6186096970315</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E16" t="n">
-        <v>746.96728515625</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F16" t="n">
         <v>10591100</v>
@@ -1174,16 +1174,16 @@
         <v>45944</v>
       </c>
       <c r="B29" t="n">
-        <v>705.9439682909708</v>
+        <v>705.9440292511955</v>
       </c>
       <c r="C29" t="n">
-        <v>713.6937706407739</v>
+        <v>713.6938322702155</v>
       </c>
       <c r="D29" t="n">
-        <v>697.5158763660478</v>
+        <v>697.5159365984832</v>
       </c>
       <c r="E29" t="n">
-        <v>706.8117065429688</v>
+        <v>706.811767578125</v>
       </c>
       <c r="F29" t="n">
         <v>8829800</v>
@@ -1460,16 +1460,16 @@
         <v>45959</v>
       </c>
       <c r="B40" t="n">
-        <v>752.7921200604676</v>
+        <v>752.7921813457194</v>
       </c>
       <c r="C40" t="n">
-        <v>757.1906533932021</v>
+        <v>757.1907150365412</v>
       </c>
       <c r="D40" t="n">
-        <v>740.5838813084906</v>
+        <v>740.5839415998626</v>
       </c>
       <c r="E40" t="n">
-        <v>749.7200927734375</v>
+        <v>749.7201538085938</v>
       </c>
       <c r="F40" t="n">
         <v>26818600</v>
@@ -1694,16 +1694,16 @@
         <v>45972</v>
       </c>
       <c r="B49" t="n">
-        <v>626.3709044869131</v>
+        <v>626.3709656116134</v>
       </c>
       <c r="C49" t="n">
-        <v>627.9268552540688</v>
+        <v>627.9269165306073</v>
       </c>
       <c r="D49" t="n">
-        <v>617.7832543081277</v>
+        <v>617.7833145947981</v>
       </c>
       <c r="E49" t="n">
-        <v>625.4533081054688</v>
+        <v>625.453369140625</v>
       </c>
       <c r="F49" t="n">
         <v>13302200</v>
@@ -1798,16 +1798,16 @@
         <v>45978</v>
       </c>
       <c r="B53" t="n">
-        <v>607.4600964135232</v>
+        <v>607.4600346656293</v>
       </c>
       <c r="C53" t="n">
-        <v>610.1032465254069</v>
+        <v>610.1031845088386</v>
       </c>
       <c r="D53" t="n">
-        <v>593.855525554584</v>
+        <v>593.8554651895852</v>
       </c>
       <c r="E53" t="n">
-        <v>600.4483642578125</v>
+        <v>600.4483032226562</v>
       </c>
       <c r="F53" t="n">
         <v>16501300</v>
@@ -1824,16 +1824,16 @@
         <v>45979</v>
       </c>
       <c r="B54" t="n">
-        <v>590.0652977363707</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C54" t="n">
-        <v>602.0940102850205</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D54" t="n">
-        <v>582.2656372803878</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E54" t="n">
-        <v>596.1395263671875</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F54" t="n">
         <v>25500600</v>
@@ -1902,16 +1902,16 @@
         <v>45982</v>
       </c>
       <c r="B57" t="n">
-        <v>586.9733513369498</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C57" t="n">
-        <v>596.5683908845805</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D57" t="n">
-        <v>580.3505617853443</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E57" t="n">
-        <v>592.7084350585938</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F57" t="n">
         <v>21052600</v>
@@ -1928,16 +1928,16 @@
         <v>45985</v>
       </c>
       <c r="B58" t="n">
-        <v>597.1668126146857</v>
+        <v>597.1668722231478</v>
       </c>
       <c r="C58" t="n">
-        <v>615.1002115339802</v>
+        <v>615.1002729325323</v>
       </c>
       <c r="D58" t="n">
-        <v>596.0796743085915</v>
+        <v>596.0797338085368</v>
       </c>
       <c r="E58" t="n">
-        <v>611.4596557617188</v>
+        <v>611.459716796875</v>
       </c>
       <c r="F58" t="n">
         <v>23554900</v>
@@ -1980,16 +1980,16 @@
         <v>45987</v>
       </c>
       <c r="B60" t="n">
-        <v>636.0358029520913</v>
+        <v>636.0358643802724</v>
       </c>
       <c r="C60" t="n">
-        <v>636.7040478933542</v>
+        <v>636.7041093860743</v>
       </c>
       <c r="D60" t="n">
-        <v>629.9915253276793</v>
+        <v>629.9915861721055</v>
       </c>
       <c r="E60" t="n">
-        <v>631.9663696289062</v>
+        <v>631.9664306640625</v>
       </c>
       <c r="F60" t="n">
         <v>15209500</v>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:15</t>
+          <t>2026-09-08 08:52:06</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>750.1613099282893</v>
+        <v>755.0154070864886</v>
       </c>
       <c r="C2" t="n">
-        <v>755.4739147328357</v>
+        <v>763.7966239723705</v>
       </c>
       <c r="D2" t="n">
-        <v>742.5961392724259</v>
+        <v>750.9686728075005</v>
       </c>
       <c r="E2" t="n">
-        <v>749.9918823242188</v>
+        <v>763.1986083984375</v>
       </c>
       <c r="F2" t="n">
-        <v>9663400</v>
+        <v>10999000</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>753.5302710608411</v>
+        <v>762.6304417530438</v>
       </c>
       <c r="C3" t="n">
-        <v>764.0059463353695</v>
+        <v>763.1985869501963</v>
       </c>
       <c r="D3" t="n">
-        <v>749.5632925404257</v>
+        <v>748.5465974429485</v>
       </c>
       <c r="E3" t="n">
-        <v>749.8423461914062</v>
+        <v>749.5233764648438</v>
       </c>
       <c r="F3" t="n">
-        <v>13087800</v>
+        <v>12478300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>755.0153467057662</v>
+        <v>752.1846484905694</v>
       </c>
       <c r="C4" t="n">
-        <v>763.7965628893893</v>
+        <v>754.6265958852796</v>
       </c>
       <c r="D4" t="n">
-        <v>750.9686127504068</v>
+        <v>745.9251355026145</v>
       </c>
       <c r="E4" t="n">
-        <v>763.1985473632812</v>
+        <v>748.4468994140625</v>
       </c>
       <c r="F4" t="n">
-        <v>10999000</v>
+        <v>7923300</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>762.6305038555339</v>
+        <v>746.2840072815898</v>
       </c>
       <c r="C5" t="n">
-        <v>763.1986490989516</v>
+        <v>755.095155276553</v>
       </c>
       <c r="D5" t="n">
-        <v>748.5466583985636</v>
+        <v>741.330272625368</v>
       </c>
       <c r="E5" t="n">
-        <v>749.5234375</v>
+        <v>753.1216430664062</v>
       </c>
       <c r="F5" t="n">
-        <v>12478300</v>
+        <v>8248600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>752.184771170502</v>
+        <v>754.9954213012545</v>
       </c>
       <c r="C6" t="n">
-        <v>754.6267189634892</v>
+        <v>771.5412279036273</v>
       </c>
       <c r="D6" t="n">
-        <v>745.9252571616319</v>
+        <v>749.5333431691193</v>
       </c>
       <c r="E6" t="n">
-        <v>748.447021484375</v>
+        <v>762.2018432617188</v>
       </c>
       <c r="F6" t="n">
-        <v>7923300</v>
+        <v>10533800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>746.2840072815898</v>
+        <v>764.494341124313</v>
       </c>
       <c r="C7" t="n">
-        <v>755.095155276553</v>
+        <v>778.8074148399552</v>
       </c>
       <c r="D7" t="n">
-        <v>741.330272625368</v>
+        <v>762.6005237676653</v>
       </c>
       <c r="E7" t="n">
-        <v>753.1216430664062</v>
+        <v>776.4551391601562</v>
       </c>
       <c r="F7" t="n">
-        <v>8248600</v>
+        <v>11782500</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>754.9954213012545</v>
+        <v>777.4419223006557</v>
       </c>
       <c r="C8" t="n">
-        <v>771.5412279036273</v>
+        <v>780.7311297077449</v>
       </c>
       <c r="D8" t="n">
-        <v>749.5333431691193</v>
+        <v>763.8066193659058</v>
       </c>
       <c r="E8" t="n">
-        <v>762.2018432617188</v>
+        <v>773.1858520507812</v>
       </c>
       <c r="F8" t="n">
-        <v>10533800</v>
+        <v>9400900</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>764.494341124313</v>
+        <v>778.1994774600552</v>
       </c>
       <c r="C9" t="n">
-        <v>778.8074148399552</v>
+        <v>786.203274581819</v>
       </c>
       <c r="D9" t="n">
-        <v>762.6005237676653</v>
+        <v>770.8336042127465</v>
       </c>
       <c r="E9" t="n">
-        <v>776.4551391601562</v>
+        <v>777.7011108398438</v>
       </c>
       <c r="F9" t="n">
-        <v>11782500</v>
+        <v>10955000</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>777.4419223006557</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C10" t="n">
-        <v>780.7311297077449</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D10" t="n">
-        <v>763.8066193659058</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E10" t="n">
-        <v>773.1858520507812</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F10" t="n">
-        <v>9400900</v>
+        <v>23696800</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,25 +703,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>778.1994774600552</v>
+        <v>779.8217552362186</v>
       </c>
       <c r="C11" t="n">
-        <v>786.203274581819</v>
+        <v>783.6916948825968</v>
       </c>
       <c r="D11" t="n">
-        <v>770.8336042127465</v>
+        <v>762.4868363426395</v>
       </c>
       <c r="E11" t="n">
-        <v>777.7011108398438</v>
+        <v>763.175048828125</v>
       </c>
       <c r="F11" t="n">
-        <v>10955000</v>
+        <v>11706900</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>783.8508708699721</v>
+        <v>767.254476840496</v>
       </c>
       <c r="C12" t="n">
-        <v>788.2165669565625</v>
+        <v>768.6009504341728</v>
       </c>
       <c r="D12" t="n">
-        <v>766.6771780735046</v>
+        <v>749.1216451610411</v>
       </c>
       <c r="E12" t="n">
-        <v>775.837158203125</v>
+        <v>753.4404296875</v>
       </c>
       <c r="F12" t="n">
-        <v>23696800</v>
+        <v>10872600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,25 +755,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>779.8218176027002</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C13" t="n">
-        <v>783.6917575585782</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D13" t="n">
-        <v>762.4868973227559</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E13" t="n">
-        <v>763.1751098632812</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F13" t="n">
-        <v>11706900</v>
+        <v>8828200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>767.2545389947088</v>
+        <v>751.4955472633491</v>
       </c>
       <c r="C14" t="n">
-        <v>768.6010126974617</v>
+        <v>754.806942419776</v>
       </c>
       <c r="D14" t="n">
-        <v>749.1217058463387</v>
+        <v>742.6186096970315</v>
       </c>
       <c r="E14" t="n">
-        <v>753.4404907226562</v>
+        <v>746.96728515625</v>
       </c>
       <c r="F14" t="n">
-        <v>10872600</v>
+        <v>10591100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>755.5349916265823</v>
+        <v>748.0544659269957</v>
       </c>
       <c r="C15" t="n">
-        <v>759.1356124217834</v>
+        <v>749.9794521140951</v>
       </c>
       <c r="D15" t="n">
-        <v>750.5779133776451</v>
+        <v>735.4372562509625</v>
       </c>
       <c r="E15" t="n">
-        <v>758.686767578125</v>
+        <v>741.8206787109375</v>
       </c>
       <c r="F15" t="n">
-        <v>8828200</v>
+        <v>9696300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>751.4954858581857</v>
+        <v>746.777703342028</v>
       </c>
       <c r="C16" t="n">
-        <v>754.8068807440363</v>
+        <v>748.8324179023273</v>
       </c>
       <c r="D16" t="n">
-        <v>742.6185490172081</v>
+        <v>737.2325826153279</v>
       </c>
       <c r="E16" t="n">
-        <v>746.9672241210938</v>
+        <v>741.4715576171875</v>
       </c>
       <c r="F16" t="n">
-        <v>10591100</v>
+        <v>9246800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>748.0544043789391</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C17" t="n">
-        <v>749.9793904076555</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D17" t="n">
-        <v>735.4371957410184</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E17" t="n">
-        <v>741.8206176757812</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F17" t="n">
-        <v>9696300</v>
+        <v>16226800</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>746.7777648139662</v>
+        <v>719.618385039583</v>
       </c>
       <c r="C18" t="n">
-        <v>748.832479543402</v>
+        <v>719.9774365591268</v>
       </c>
       <c r="D18" t="n">
-        <v>737.2326433015477</v>
+        <v>708.3576941566364</v>
       </c>
       <c r="E18" t="n">
-        <v>741.4716186523438</v>
+        <v>715.4791870117188</v>
       </c>
       <c r="F18" t="n">
-        <v>9246800</v>
+        <v>20419600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>740.3244937368279</v>
+        <v>720.7056259804448</v>
       </c>
       <c r="C19" t="n">
-        <v>741.0425967294805</v>
+        <v>725.8821654223162</v>
       </c>
       <c r="D19" t="n">
-        <v>724.4158582201331</v>
+        <v>716.2771410193245</v>
       </c>
       <c r="E19" t="n">
-        <v>732.4749145507812</v>
+        <v>725.1640014648438</v>
       </c>
       <c r="F19" t="n">
-        <v>16226800</v>
+        <v>11415300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>719.618385039583</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C20" t="n">
-        <v>719.9774365591268</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D20" t="n">
-        <v>708.3576941566364</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E20" t="n">
-        <v>715.4791870117188</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F20" t="n">
-        <v>20419600</v>
+        <v>16154300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>720.7055653205383</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C21" t="n">
-        <v>725.8821043267139</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D21" t="n">
-        <v>716.2770807321521</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E21" t="n">
-        <v>725.1639404296875</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F21" t="n">
-        <v>11415300</v>
+        <v>21654700</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>727.7372737109582</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C22" t="n">
-        <v>729.1037149276121</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D22" t="n">
-        <v>708.3377167266436</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E22" t="n">
-        <v>708.7167358398438</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F22" t="n">
-        <v>16154300</v>
+        <v>12062900</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>703.3607165744016</v>
+        <v>711.5993392573523</v>
       </c>
       <c r="C23" t="n">
-        <v>715.0203947681905</v>
+        <v>717.783268775081</v>
       </c>
       <c r="D23" t="n">
-        <v>688.718804278428</v>
+        <v>705.9739546774089</v>
       </c>
       <c r="E23" t="n">
-        <v>713.8035278320312</v>
+        <v>715.9779663085938</v>
       </c>
       <c r="F23" t="n">
-        <v>21654700</v>
+        <v>10790600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>715.8581417735932</v>
+        <v>716.416706057987</v>
       </c>
       <c r="C24" t="n">
-        <v>716.6361476056489</v>
+        <v>731.607177734375</v>
       </c>
       <c r="D24" t="n">
-        <v>703.9192222306009</v>
+        <v>710.5918290846139</v>
       </c>
       <c r="E24" t="n">
-        <v>711.230224609375</v>
+        <v>731.607177734375</v>
       </c>
       <c r="F24" t="n">
-        <v>12062900</v>
+        <v>12717200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>711.599278595462</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C25" t="n">
-        <v>717.7832075860277</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D25" t="n">
-        <v>705.9738944950672</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E25" t="n">
-        <v>715.9779052734375</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F25" t="n">
-        <v>10790600</v>
+        <v>16980100</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>716.4167658258609</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C26" t="n">
-        <v>731.6072387695312</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D26" t="n">
-        <v>710.5918883665408</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E26" t="n">
-        <v>731.6072387695312</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F26" t="n">
-        <v>12717200</v>
+        <v>9251800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>729.0239332852144</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C27" t="n">
-        <v>733.3626856542741</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D27" t="n">
-        <v>702.6824691715568</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E27" t="n">
-        <v>703.4703979492188</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F27" t="n">
-        <v>16980100</v>
+        <v>8829800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>711.1603595995662</v>
+        <v>715.1999404706222</v>
       </c>
       <c r="C28" t="n">
-        <v>718.072374881022</v>
+        <v>722.0222242634773</v>
       </c>
       <c r="D28" t="n">
-        <v>705.8042950194317</v>
+        <v>707.6695373823591</v>
       </c>
       <c r="E28" t="n">
-        <v>713.8433837890625</v>
+        <v>715.6886596679688</v>
       </c>
       <c r="F28" t="n">
-        <v>9251800</v>
+        <v>10246800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>705.9440292511955</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C29" t="n">
-        <v>713.6938322702155</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D29" t="n">
-        <v>697.5159365984832</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E29" t="n">
-        <v>706.811767578125</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F29" t="n">
-        <v>8829800</v>
+        <v>9017000</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>715.1998794771447</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C30" t="n">
-        <v>722.0221626881838</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D30" t="n">
-        <v>707.6694770310874</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E30" t="n">
-        <v>715.6885986328125</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F30" t="n">
-        <v>10246800</v>
+        <v>12232400</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>715.6886043056783</v>
+        <v>719.3191330444083</v>
       </c>
       <c r="C31" t="n">
-        <v>723.6080097298942</v>
+        <v>731.866515781436</v>
       </c>
       <c r="D31" t="n">
-        <v>702.0540824517458</v>
+        <v>718.3117433877071</v>
       </c>
       <c r="E31" t="n">
-        <v>710.2228393554688</v>
+        <v>730.2706298828125</v>
       </c>
       <c r="F31" t="n">
-        <v>9017000</v>
+        <v>8900200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>705.2458014471516</v>
+        <v>734.1107864324557</v>
       </c>
       <c r="C32" t="n">
-        <v>716.6760344343375</v>
+        <v>736.5843338414116</v>
       </c>
       <c r="D32" t="n">
-        <v>704.2882698394852</v>
+        <v>726.859625303898</v>
       </c>
       <c r="E32" t="n">
-        <v>715.0602416992188</v>
+        <v>731.367919921875</v>
       </c>
       <c r="F32" t="n">
-        <v>12232400</v>
+        <v>7647300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>719.3191931642514</v>
+        <v>731.9264616753367</v>
       </c>
       <c r="C33" t="n">
-        <v>731.8665769499745</v>
+        <v>738.6788588958609</v>
       </c>
       <c r="D33" t="n">
-        <v>718.3118034233538</v>
+        <v>722.1518950553793</v>
       </c>
       <c r="E33" t="n">
-        <v>730.2706909179688</v>
+        <v>731.5075073242188</v>
       </c>
       <c r="F33" t="n">
-        <v>8900200</v>
+        <v>8734500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>734.1107251683979</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C34" t="n">
-        <v>736.5842723709278</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D34" t="n">
-        <v>726.8595646449745</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E34" t="n">
-        <v>731.3678588867188</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F34" t="n">
-        <v>7647300</v>
+        <v>9856000</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>731.9264006052239</v>
+        <v>734.8787064697904</v>
       </c>
       <c r="C35" t="n">
-        <v>738.6787972623451</v>
+        <v>739.2872845910176</v>
       </c>
       <c r="D35" t="n">
-        <v>722.1518348008319</v>
+        <v>729.253383189777</v>
       </c>
       <c r="E35" t="n">
-        <v>731.5074462890625</v>
+        <v>736.4446411132812</v>
       </c>
       <c r="F35" t="n">
-        <v>8734500</v>
+        <v>9151300</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>732.7941435868839</v>
+        <v>747.7851152228061</v>
       </c>
       <c r="C36" t="n">
-        <v>740.4841042897723</v>
+        <v>753.7895182960361</v>
       </c>
       <c r="D36" t="n">
-        <v>731.1982575844598</v>
+        <v>746.069606274355</v>
       </c>
       <c r="E36" t="n">
-        <v>732.095947265625</v>
+        <v>748.872314453125</v>
       </c>
       <c r="F36" t="n">
-        <v>9856000</v>
+        <v>11321100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>734.8786455644157</v>
+        <v>750.677577029167</v>
       </c>
       <c r="C37" t="n">
-        <v>739.2872233202683</v>
+        <v>756.4326283200122</v>
       </c>
       <c r="D37" t="n">
-        <v>729.2533227506186</v>
+        <v>743.5860359773924</v>
       </c>
       <c r="E37" t="n">
-        <v>736.444580078125</v>
+        <v>749.4906616210938</v>
       </c>
       <c r="F37" t="n">
-        <v>9151300</v>
+        <v>12193800</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>747.7851152228061</v>
+        <v>752.7921200604676</v>
       </c>
       <c r="C38" t="n">
-        <v>753.7895182960361</v>
+        <v>757.1906533932021</v>
       </c>
       <c r="D38" t="n">
-        <v>746.069606274355</v>
+        <v>740.5838813084906</v>
       </c>
       <c r="E38" t="n">
-        <v>748.872314453125</v>
+        <v>749.7200927734375</v>
       </c>
       <c r="F38" t="n">
-        <v>11321100</v>
+        <v>26818600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>750.6776381609803</v>
+        <v>667.414190282622</v>
       </c>
       <c r="C39" t="n">
-        <v>756.4326899204912</v>
+        <v>679.1935516668058</v>
       </c>
       <c r="D39" t="n">
-        <v>743.5860965317024</v>
+        <v>648.4833846789722</v>
       </c>
       <c r="E39" t="n">
-        <v>749.49072265625</v>
+        <v>664.7410888671875</v>
       </c>
       <c r="F39" t="n">
-        <v>12193800</v>
+        <v>88440100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>752.7921813457194</v>
+        <v>672.7603267493847</v>
       </c>
       <c r="C40" t="n">
-        <v>757.1907150365412</v>
+        <v>673.139345897249</v>
       </c>
       <c r="D40" t="n">
-        <v>740.5839415998626</v>
+        <v>643.8953948481166</v>
       </c>
       <c r="E40" t="n">
-        <v>749.7201538085938</v>
+        <v>646.6681518554688</v>
       </c>
       <c r="F40" t="n">
-        <v>26818600</v>
+        <v>56953200</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>667.414190282622</v>
+        <v>654.298319497033</v>
       </c>
       <c r="C41" t="n">
-        <v>679.1935516668058</v>
+        <v>657.6196984387726</v>
       </c>
       <c r="D41" t="n">
-        <v>648.4833846789722</v>
+        <v>634.5297257704245</v>
       </c>
       <c r="E41" t="n">
-        <v>664.7410888671875</v>
+        <v>636.0557861328125</v>
       </c>
       <c r="F41" t="n">
-        <v>88440100</v>
+        <v>33003600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>672.7602632515434</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C42" t="n">
-        <v>673.1392823636344</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D42" t="n">
-        <v>643.8953340746643</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E42" t="n">
-        <v>646.6680908203125</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F42" t="n">
-        <v>56953200</v>
+        <v>27356600</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>654.298319497033</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C43" t="n">
-        <v>657.6196984387726</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D43" t="n">
-        <v>634.5297257704245</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E43" t="n">
-        <v>636.0557861328125</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F43" t="n">
-        <v>33003600</v>
+        <v>20219900</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>626.4107910285981</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C44" t="n">
-        <v>640.0752642850032</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D44" t="n">
-        <v>624.3860886703497</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E44" t="n">
-        <v>625.6926879882812</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F44" t="n">
-        <v>27356600</v>
+        <v>23628800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>630.6697208898194</v>
+        <v>614.8907991985972</v>
       </c>
       <c r="C45" t="n">
-        <v>640.5639703518489</v>
+        <v>620.516183502649</v>
       </c>
       <c r="D45" t="n">
-        <v>624.9146693781357</v>
+        <v>599.6404837711106</v>
       </c>
       <c r="E45" t="n">
-        <v>634.30029296875</v>
+        <v>620.0972900390625</v>
       </c>
       <c r="F45" t="n">
-        <v>20219900</v>
+        <v>29946800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>634.2005186436334</v>
+        <v>629.4529098843899</v>
       </c>
       <c r="C46" t="n">
-        <v>634.3501538797125</v>
+        <v>633.3527401283538</v>
       </c>
       <c r="D46" t="n">
-        <v>616.3968476378337</v>
+        <v>616.5065400363918</v>
       </c>
       <c r="E46" t="n">
-        <v>617.3344116210938</v>
+        <v>630.1211547851562</v>
       </c>
       <c r="F46" t="n">
-        <v>23628800</v>
+        <v>19245000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>614.8907386759073</v>
+        <v>626.3709044869131</v>
       </c>
       <c r="C47" t="n">
-        <v>620.5161224262619</v>
+        <v>627.9268552540688</v>
       </c>
       <c r="D47" t="n">
-        <v>599.6404247494841</v>
+        <v>617.7832543081277</v>
       </c>
       <c r="E47" t="n">
-        <v>620.0972290039062</v>
+        <v>625.4533081054688</v>
       </c>
       <c r="F47" t="n">
-        <v>29946800</v>
+        <v>13302200</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>629.4529098843899</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C48" t="n">
-        <v>633.3527401283538</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D48" t="n">
-        <v>616.5065400363918</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E48" t="n">
-        <v>630.1211547851562</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F48" t="n">
-        <v>19245000</v>
+        <v>24493300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>626.3709656116134</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C49" t="n">
-        <v>627.9269165306073</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D49" t="n">
-        <v>617.7833145947981</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E49" t="n">
-        <v>625.453369140625</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F49" t="n">
-        <v>13302200</v>
+        <v>20973800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>626.5005716840028</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C50" t="n">
-        <v>627.3583261459861</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D50" t="n">
-        <v>606.1934022078184</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E50" t="n">
-        <v>607.43017578125</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F50" t="n">
-        <v>24493300</v>
+        <v>20724100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>611.4796659420805</v>
+        <v>607.4600346656293</v>
       </c>
       <c r="C51" t="n">
-        <v>616.0478021853295</v>
+        <v>610.1031845088386</v>
       </c>
       <c r="D51" t="n">
-        <v>601.4357808374693</v>
+        <v>593.8554651895852</v>
       </c>
       <c r="E51" t="n">
-        <v>608.3079223632812</v>
+        <v>600.4483032226562</v>
       </c>
       <c r="F51" t="n">
-        <v>20973800</v>
+        <v>16501300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>600.2288811530552</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C52" t="n">
-        <v>612.088052043071</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D52" t="n">
-        <v>593.6560102918138</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E52" t="n">
-        <v>607.8790283203125</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F52" t="n">
-        <v>20724100</v>
+        <v>25500600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>607.4600346656293</v>
+        <v>592.1798400423816</v>
       </c>
       <c r="C53" t="n">
-        <v>610.1031845088386</v>
+        <v>593.7857099116716</v>
       </c>
       <c r="D53" t="n">
-        <v>593.8554651895852</v>
+        <v>579.7422168855177</v>
       </c>
       <c r="E53" t="n">
-        <v>600.4483032226562</v>
+        <v>588.7886962890625</v>
       </c>
       <c r="F53" t="n">
-        <v>16501300</v>
+        <v>24744700</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>590.065358149623</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C54" t="n">
-        <v>602.0940719298206</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D54" t="n">
-        <v>582.2656968950795</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E54" t="n">
-        <v>596.1395874023438</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F54" t="n">
-        <v>25500600</v>
+        <v>20603000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>592.1797786556917</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C55" t="n">
-        <v>593.7856483585136</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D55" t="n">
-        <v>579.7421567881397</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E55" t="n">
-        <v>588.7886352539062</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F55" t="n">
-        <v>24744700</v>
+        <v>21052600</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>601.9345167857809</v>
+        <v>597.1668722231478</v>
       </c>
       <c r="C56" t="n">
-        <v>605.1461348624172</v>
+        <v>615.1002729325323</v>
       </c>
       <c r="D56" t="n">
-        <v>581.8367616757555</v>
+        <v>596.0797338085368</v>
       </c>
       <c r="E56" t="n">
-        <v>587.6217651367188</v>
+        <v>611.459716796875</v>
       </c>
       <c r="F56" t="n">
-        <v>20603000</v>
+        <v>23554900</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>586.9734117815261</v>
+        <v>622.3812488080194</v>
       </c>
       <c r="C57" t="n">
-        <v>596.5684523172222</v>
+        <v>635.3973829418613</v>
       </c>
       <c r="D57" t="n">
-        <v>580.3506215479276</v>
+        <v>616.6960233021972</v>
       </c>
       <c r="E57" t="n">
-        <v>592.70849609375</v>
+        <v>634.5695190429688</v>
       </c>
       <c r="F57" t="n">
-        <v>21052600</v>
+        <v>25213000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>597.1668722231478</v>
+        <v>636.0357415239101</v>
       </c>
       <c r="C58" t="n">
-        <v>615.1002729325323</v>
+        <v>636.7039864006342</v>
       </c>
       <c r="D58" t="n">
-        <v>596.0797338085368</v>
+        <v>629.9914644832529</v>
       </c>
       <c r="E58" t="n">
-        <v>611.459716796875</v>
+        <v>631.96630859375</v>
       </c>
       <c r="F58" t="n">
-        <v>23554900</v>
+        <v>15209500</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>622.3813086708644</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C59" t="n">
-        <v>635.3974440566444</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D59" t="n">
-        <v>616.696082618217</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E59" t="n">
-        <v>634.569580078125</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F59" t="n">
-        <v>25213000</v>
+        <v>11033200</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>636.0358643802724</v>
+        <v>637.8908755177382</v>
       </c>
       <c r="C60" t="n">
-        <v>636.7041093860743</v>
+        <v>643.6459265392308</v>
       </c>
       <c r="D60" t="n">
-        <v>629.9915861721055</v>
+        <v>636.1055410281542</v>
       </c>
       <c r="E60" t="n">
-        <v>631.9664306640625</v>
+        <v>639.2074584960938</v>
       </c>
       <c r="F60" t="n">
-        <v>15209500</v>
+        <v>13029900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>634.4299618769652</v>
+        <v>640.6737247939117</v>
       </c>
       <c r="C61" t="n">
-        <v>646.3688812783262</v>
+        <v>646.1893476978298</v>
       </c>
       <c r="D61" t="n">
-        <v>633.8514494094911</v>
+        <v>636.4147821721649</v>
       </c>
       <c r="E61" t="n">
-        <v>646.2691650390625</v>
+        <v>645.4213256835938</v>
       </c>
       <c r="F61" t="n">
-        <v>11033200</v>
+        <v>11640900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>637.890997336621</v>
+        <v>642.7383158920676</v>
       </c>
       <c r="C62" t="n">
-        <v>643.6460494571635</v>
+        <v>647.1668005690203</v>
       </c>
       <c r="D62" t="n">
-        <v>636.1056625060893</v>
+        <v>635.8961259576193</v>
       </c>
       <c r="E62" t="n">
-        <v>639.2075805664062</v>
+        <v>637.9407958984375</v>
       </c>
       <c r="F62" t="n">
-        <v>13029900</v>
+        <v>11134300</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>640.6737247939117</v>
+        <v>674.2463992276428</v>
       </c>
       <c r="C63" t="n">
-        <v>646.1893476978298</v>
+        <v>674.3461154685141</v>
       </c>
       <c r="D63" t="n">
-        <v>636.4147821721649</v>
+        <v>658.3377626918029</v>
       </c>
       <c r="E63" t="n">
-        <v>645.4213256835938</v>
+        <v>659.81396484375</v>
       </c>
       <c r="F63" t="n">
-        <v>11640900</v>
+        <v>29874600</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>642.7383773862279</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C64" t="n">
-        <v>647.1668624868771</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D64" t="n">
-        <v>635.8961867971512</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E64" t="n">
-        <v>637.9408569335938</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F64" t="n">
-        <v>11134300</v>
+        <v>21207900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>674.2463992276428</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C65" t="n">
-        <v>674.3461154685141</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D65" t="n">
-        <v>658.3377626918029</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E65" t="n">
-        <v>659.81396484375</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F65" t="n">
-        <v>29874600</v>
+        <v>13161000</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>662.2775487290173</v>
+        <v>662.0481300460407</v>
       </c>
       <c r="C66" t="n">
-        <v>672.9398207362489</v>
+        <v>662.7562492699393</v>
       </c>
       <c r="D66" t="n">
-        <v>660.6717397649775</v>
+        <v>651.6451938720459</v>
       </c>
       <c r="E66" t="n">
-        <v>671.673095703125</v>
+        <v>655.2557983398438</v>
       </c>
       <c r="F66" t="n">
-        <v>21207900</v>
+        <v>12997100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>667.603701448277</v>
+        <v>648.2640167126568</v>
       </c>
       <c r="C67" t="n">
-        <v>674.9545781663558</v>
+        <v>652.812185461044</v>
       </c>
       <c r="D67" t="n">
-        <v>663.344758713728</v>
+        <v>641.7310198416047</v>
       </c>
       <c r="E67" t="n">
-        <v>665.0702514648438</v>
+        <v>648.4435424804688</v>
       </c>
       <c r="F67" t="n">
-        <v>13161000</v>
+        <v>16910900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>662.0481300460407</v>
+        <v>641.6212380225077</v>
       </c>
       <c r="C68" t="n">
-        <v>662.7562492699393</v>
+        <v>653.5801862453618</v>
       </c>
       <c r="D68" t="n">
-        <v>651.6451938720459</v>
+        <v>639.1377070000864</v>
       </c>
       <c r="E68" t="n">
-        <v>655.2557983398438</v>
+        <v>651.016845703125</v>
       </c>
       <c r="F68" t="n">
-        <v>12997100</v>
+        <v>13056700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>648.2639556943986</v>
+        <v>648.1143349664432</v>
       </c>
       <c r="C69" t="n">
-        <v>652.8121240146866</v>
+        <v>709.1555875928369</v>
       </c>
       <c r="D69" t="n">
-        <v>641.730959438269</v>
+        <v>636.9533606253732</v>
       </c>
       <c r="E69" t="n">
-        <v>648.4434814453125</v>
+        <v>642.5587768554688</v>
       </c>
       <c r="F69" t="n">
-        <v>16910900</v>
+        <v>14016900</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>641.6212380225077</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C70" t="n">
-        <v>653.5801862453618</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D70" t="n">
-        <v>639.1377070000864</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E70" t="n">
-        <v>651.016845703125</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F70" t="n">
-        <v>13056700</v>
+        <v>15549100</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>648.1143965293088</v>
+        <v>642.3541401459643</v>
       </c>
       <c r="C71" t="n">
-        <v>709.1556549538686</v>
+        <v>661.3602142938313</v>
       </c>
       <c r="D71" t="n">
-        <v>636.9534211280841</v>
+        <v>642.054686531657</v>
       </c>
       <c r="E71" t="n">
-        <v>642.558837890625</v>
+        <v>655.9798583984375</v>
       </c>
       <c r="F71" t="n">
-        <v>14016900</v>
+        <v>14309100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,25 +2289,25 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>644.5502809809109</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C72" t="n">
-        <v>651.8372704406642</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D72" t="n">
-        <v>637.5627451568915</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E72" t="n">
-        <v>646.3570556640625</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F72" t="n">
-        <v>15549100</v>
+        <v>15598500</v>
       </c>
       <c r="G72" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>642.3541999133257</v>
+        <v>655.8601356908653</v>
       </c>
       <c r="C73" t="n">
-        <v>661.3602758295988</v>
+        <v>669.366012780715</v>
       </c>
       <c r="D73" t="n">
-        <v>642.054746271156</v>
+        <v>655.2911433094866</v>
       </c>
       <c r="E73" t="n">
-        <v>655.9799194335938</v>
+        <v>663.2669067382812</v>
       </c>
       <c r="F73" t="n">
-        <v>14309100</v>
+        <v>20260300</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>654.4426118233187</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C74" t="n">
-        <v>660.0526000253047</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D74" t="n">
-        <v>648.0440522221027</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E74" t="n">
-        <v>648.343505859375</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F74" t="n">
-        <v>15598500</v>
+        <v>49977100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>655.8600753372949</v>
+        <v>660.4718397886508</v>
       </c>
       <c r="C75" t="n">
-        <v>669.3659511843067</v>
+        <v>672.380589007267</v>
       </c>
       <c r="D75" t="n">
-        <v>655.2910830082761</v>
+        <v>655.4807431709672</v>
       </c>
       <c r="E75" t="n">
-        <v>663.266845703125</v>
+        <v>660.3220825195312</v>
       </c>
       <c r="F75" t="n">
-        <v>20260300</v>
+        <v>15659400</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>665.2333263832898</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C76" t="n">
-        <v>669.8051880946751</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D76" t="n">
-        <v>657.0080086354003</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E76" t="n">
-        <v>657.5969848632812</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F76" t="n">
-        <v>49977100</v>
+        <v>8486800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>660.4719008376494</v>
+        <v>661.3503688947783</v>
       </c>
       <c r="C77" t="n">
-        <v>672.3806511570199</v>
+        <v>666.9902722948509</v>
       </c>
       <c r="D77" t="n">
-        <v>655.4808037586267</v>
+        <v>661.0209394131572</v>
       </c>
       <c r="E77" t="n">
-        <v>660.3221435546875</v>
+        <v>666.3613891601562</v>
       </c>
       <c r="F77" t="n">
-        <v>15659400</v>
+        <v>5627500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>658.8746741689592</v>
+        <v>666.8704124858896</v>
       </c>
       <c r="C78" t="n">
-        <v>664.8140915262984</v>
+        <v>667.7588423243637</v>
       </c>
       <c r="D78" t="n">
-        <v>657.0778915122911</v>
+        <v>660.1424238558649</v>
       </c>
       <c r="E78" t="n">
-        <v>663.7559814453125</v>
+        <v>662.10888671875</v>
       </c>
       <c r="F78" t="n">
-        <v>8486800</v>
+        <v>7133800</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>661.3503083186049</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C79" t="n">
-        <v>666.9902112020924</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D79" t="n">
-        <v>661.0208788671576</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E79" t="n">
-        <v>666.361328125</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F79" t="n">
-        <v>5627500</v>
+        <v>8506500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>666.8704739599774</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C80" t="n">
-        <v>667.7589038803495</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D80" t="n">
-        <v>660.1424847097468</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E80" t="n">
-        <v>662.1089477539062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F80" t="n">
-        <v>7133800</v>
+        <v>9187500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>656.8383689858442</v>
+        <v>663.5663484641349</v>
       </c>
       <c r="C81" t="n">
-        <v>659.0743707339258</v>
+        <v>663.8159033150052</v>
       </c>
       <c r="D81" t="n">
-        <v>653.2248195668056</v>
+        <v>658.2658058687088</v>
       </c>
       <c r="E81" t="n">
-        <v>657.5171508789062</v>
+        <v>658.9146728515625</v>
       </c>
       <c r="F81" t="n">
-        <v>8506500</v>
+        <v>7940400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>657.5171386037911</v>
+        <v>661.5499631466852</v>
       </c>
       <c r="C82" t="n">
-        <v>671.0230153954109</v>
+        <v>663.2070415689074</v>
       </c>
       <c r="D82" t="n">
-        <v>656.6686764849229</v>
+        <v>642.3542224297569</v>
       </c>
       <c r="E82" t="n">
-        <v>664.7642211914062</v>
+        <v>649.2518920898438</v>
       </c>
       <c r="F82" t="n">
-        <v>9187500</v>
+        <v>13726500</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>663.5662869980947</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C83" t="n">
-        <v>663.8158418258488</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D83" t="n">
-        <v>658.2657448936569</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E83" t="n">
-        <v>658.9146118164062</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F83" t="n">
-        <v>7940400</v>
+        <v>12213700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>661.5499009554064</v>
+        <v>658.3956073528642</v>
       </c>
       <c r="C84" t="n">
-        <v>663.2069792218492</v>
+        <v>664.3350252422523</v>
       </c>
       <c r="D84" t="n">
-        <v>642.3541620430398</v>
+        <v>650.7392812609531</v>
       </c>
       <c r="E84" t="n">
-        <v>649.2518310546875</v>
+        <v>659.4437255859375</v>
       </c>
       <c r="F84" t="n">
-        <v>13726500</v>
+        <v>11074400</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>649.8508280292294</v>
+        <v>654.4726104611178</v>
       </c>
       <c r="C85" t="n">
-        <v>663.3567049684374</v>
+        <v>657.9763704555172</v>
       </c>
       <c r="D85" t="n">
-        <v>646.5966230035071</v>
+        <v>643.6618768302103</v>
       </c>
       <c r="E85" t="n">
-        <v>657.616943359375</v>
+        <v>647.5349731445312</v>
       </c>
       <c r="F85" t="n">
-        <v>12213700</v>
+        <v>12846300</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>658.3955464147172</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C86" t="n">
-        <v>664.3349637543794</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D86" t="n">
-        <v>650.7392210314413</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E86" t="n">
-        <v>659.4436645507812</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F86" t="n">
-        <v>11074400</v>
+        <v>11921700</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>654.4725487720359</v>
+        <v>644.2906685217797</v>
       </c>
       <c r="C87" t="n">
-        <v>657.9763084361789</v>
+        <v>653.7837438291153</v>
       </c>
       <c r="D87" t="n">
-        <v>643.6618161601232</v>
+        <v>641.7052537227476</v>
       </c>
       <c r="E87" t="n">
-        <v>647.534912109375</v>
+        <v>651.8970947265625</v>
       </c>
       <c r="F87" t="n">
-        <v>12846300</v>
+        <v>11634900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>644.7299347572825</v>
+        <v>651.3681600668523</v>
       </c>
       <c r="C88" t="n">
-        <v>645.9477331499952</v>
+        <v>652.8055375702352</v>
       </c>
       <c r="D88" t="n">
-        <v>634.5879917891143</v>
+        <v>640.0882316599212</v>
       </c>
       <c r="E88" t="n">
-        <v>644.9096069335938</v>
+        <v>640.826904296875</v>
       </c>
       <c r="F88" t="n">
-        <v>11921700</v>
+        <v>14797200</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>644.2907288447692</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C89" t="n">
-        <v>653.7838050409127</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D89" t="n">
-        <v>641.7053138036724</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E89" t="n">
-        <v>651.8971557617188</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F89" t="n">
-        <v>11634900</v>
+        <v>18030400</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>651.3680980277007</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C90" t="n">
-        <v>652.8054753941815</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D90" t="n">
-        <v>640.0881706951194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E90" t="n">
-        <v>640.8268432617188</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F90" t="n">
-        <v>14797200</v>
+        <v>15527900</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>641.1263941859123</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C91" t="n">
-        <v>641.1263941859123</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D91" t="n">
-        <v>622.9887038024194</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E91" t="n">
-        <v>629.96630859375</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F91" t="n">
-        <v>18030400</v>
+        <v>13076100</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>625.3844405077801</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C92" t="n">
-        <v>627.3309804807691</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D92" t="n">
-        <v>613.7252454803604</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E92" t="n">
-        <v>614.4240112304688</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F92" t="n">
-        <v>15527900</v>
+        <v>17012500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>617.378703801015</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C93" t="n">
-        <v>623.0585745209008</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D93" t="n">
-        <v>613.1362714280776</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E93" t="n">
-        <v>619.694580078125</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F93" t="n">
-        <v>13076100</v>
+        <v>15169600</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>623.0685636897582</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C94" t="n">
-        <v>627.9598630097294</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D94" t="n">
-        <v>618.9758886129073</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E94" t="n">
-        <v>619.1455688476562</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F94" t="n">
-        <v>17012500</v>
+        <v>14494700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>606.7976262932837</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C95" t="n">
-        <v>610.3113781504126</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D95" t="n">
-        <v>598.9316523845154</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E95" t="n">
-        <v>603.0443115234375</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F95" t="n">
-        <v>15169600</v>
+        <v>21394700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>605.659634898437</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C96" t="n">
-        <v>617.169133937088</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D96" t="n">
-        <v>599.0115204374271</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E96" t="n">
-        <v>611.8685913085938</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F96" t="n">
-        <v>14494700</v>
+        <v>22797700</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>628.2293275614567</v>
+        <v>663.9456740004919</v>
       </c>
       <c r="C97" t="n">
-        <v>659.3937675491238</v>
+        <v>674.0776252750454</v>
       </c>
       <c r="D97" t="n">
-        <v>625.4343255489129</v>
+        <v>660.1124846991261</v>
       </c>
       <c r="E97" t="n">
-        <v>646.476806640625</v>
+        <v>671.1627807617188</v>
       </c>
       <c r="F97" t="n">
-        <v>21394700</v>
+        <v>16327400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>643.6219561683764</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C98" t="n">
-        <v>665.3032527677875</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D98" t="n">
-        <v>643.3025186421843</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E98" t="n">
-        <v>657.5870361328125</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F98" t="n">
-        <v>22797700</v>
+        <v>13297400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>663.9456136216552</v>
+        <v>673.2989910894674</v>
       </c>
       <c r="C99" t="n">
-        <v>674.0775639748149</v>
+        <v>676.4733214975852</v>
       </c>
       <c r="D99" t="n">
-        <v>660.1124246688775</v>
+        <v>664.9139236867763</v>
       </c>
       <c r="E99" t="n">
-        <v>671.1627197265625</v>
+        <v>667.5392456054688</v>
       </c>
       <c r="F99" t="n">
-        <v>16327400</v>
+        <v>25709600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>673.3888389297905</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C100" t="n">
-        <v>675.6148486525956</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D100" t="n">
-        <v>663.4764668627315</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E100" t="n">
-        <v>671.7716674804688</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F100" t="n">
-        <v>13297400</v>
+        <v>59852900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>673.2989295276801</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C101" t="n">
-        <v>676.4732596455591</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D101" t="n">
-        <v>664.9138628916613</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E101" t="n">
-        <v>667.5391845703125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F101" t="n">
-        <v>25709600</v>
+        <v>23744600</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>736.1169233837337</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C102" t="n">
-        <v>742.6752321400184</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D102" t="n">
-        <v>711.2812198864386</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E102" t="n">
-        <v>736.995361328125</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F102" t="n">
-        <v>59852900</v>
+        <v>14365200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>726.2045952530067</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C103" t="n">
-        <v>730.8662626744616</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D103" t="n">
-        <v>712.3193905555435</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E103" t="n">
-        <v>715.2241821289062</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F103" t="n">
-        <v>23744600</v>
+        <v>13760700</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>713.3275184694113</v>
+        <v>686.5053883494637</v>
       </c>
       <c r="C104" t="n">
-        <v>720.0156002559207</v>
+        <v>687.603466213174</v>
       </c>
       <c r="D104" t="n">
-        <v>702.2672920108814</v>
+        <v>666.2715231343633</v>
       </c>
       <c r="E104" t="n">
-        <v>705.152099609375</v>
+        <v>667.7987670898438</v>
       </c>
       <c r="F104" t="n">
-        <v>14365200</v>
+        <v>16882800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>706.1104025957663</v>
+        <v>662.3984025060512</v>
       </c>
       <c r="C105" t="n">
-        <v>715.7232596178901</v>
+        <v>680.2864759062725</v>
       </c>
       <c r="D105" t="n">
-        <v>685.1877035052055</v>
+        <v>652.3363345630947</v>
       </c>
       <c r="E105" t="n">
-        <v>690.4683227539062</v>
+        <v>669.0166015625</v>
       </c>
       <c r="F105" t="n">
-        <v>13760700</v>
+        <v>17131800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>686.5054510943589</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C106" t="n">
-        <v>687.6035290584308</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D106" t="n">
-        <v>666.2715840299333</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E106" t="n">
-        <v>667.798828125</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F106" t="n">
-        <v>16882800</v>
+        <v>18159300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>662.3984629374214</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C107" t="n">
-        <v>680.2865379695924</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D107" t="n">
-        <v>652.3363940764909</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E107" t="n">
-        <v>669.0166625976562</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F107" t="n">
-        <v>17131800</v>
+        <v>14837500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>664.3050190645899</v>
+        <v>676.3934502400131</v>
       </c>
       <c r="C108" t="n">
-        <v>670.7934451675868</v>
+        <v>679.4380681924739</v>
       </c>
       <c r="D108" t="n">
-        <v>645.3488423980709</v>
+        <v>668.597359057372</v>
       </c>
       <c r="E108" t="n">
-        <v>660.2822265625</v>
+        <v>669.5256958007812</v>
       </c>
       <c r="F108" t="n">
-        <v>18159300</v>
+        <v>10455800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>661.9991209626965</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C109" t="n">
-        <v>682.0932819515241</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D109" t="n">
-        <v>657.6069922476072</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E109" t="n">
-        <v>676.0140991210938</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F109" t="n">
-        <v>14837500</v>
+        <v>14323800</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>676.39338857878</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C110" t="n">
-        <v>679.4380062536881</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D110" t="n">
-        <v>668.5972981068446</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E110" t="n">
-        <v>669.525634765625</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F110" t="n">
-        <v>10455800</v>
+        <v>14960100</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>672.7998711552045</v>
+        <v>643.9513250294082</v>
       </c>
       <c r="C111" t="n">
-        <v>678.0605068549233</v>
+        <v>650.2700710327099</v>
       </c>
       <c r="D111" t="n">
-        <v>655.9299390360635</v>
+        <v>633.4401061931457</v>
       </c>
       <c r="E111" t="n">
-        <v>667.4993286132812</v>
+        <v>638.630859375</v>
       </c>
       <c r="F111" t="n">
-        <v>14323800</v>
+        <v>12336400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>668.7770306530766</v>
+        <v>638.3612593202278</v>
       </c>
       <c r="C112" t="n">
-        <v>674.7963229561075</v>
+        <v>641.4557148619026</v>
       </c>
       <c r="D112" t="n">
-        <v>644.1310518439949</v>
+        <v>627.6803003409905</v>
       </c>
       <c r="E112" t="n">
-        <v>648.6529541015625</v>
+        <v>638.151611328125</v>
       </c>
       <c r="F112" t="n">
-        <v>14960100</v>
+        <v>12674700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>643.9512634857649</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C113" t="n">
-        <v>650.2700088851722</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D113" t="n">
-        <v>633.4400456540794</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E113" t="n">
-        <v>638.6307983398438</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F113" t="n">
-        <v>12336400</v>
+        <v>14649200</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>638.3613203754355</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C114" t="n">
-        <v>641.4557762130754</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D114" t="n">
-        <v>627.6803603746322</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E114" t="n">
-        <v>638.1516723632812</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F114" t="n">
-        <v>12674700</v>
+        <v>10035700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>632.67143641335</v>
+        <v>638.5509584025834</v>
       </c>
       <c r="C115" t="n">
-        <v>643.8515057528024</v>
+        <v>662.1688021543367</v>
       </c>
       <c r="D115" t="n">
-        <v>627.0315334227189</v>
+        <v>637.6426055733327</v>
       </c>
       <c r="E115" t="n">
-        <v>642.0746459960938</v>
+        <v>654.4924926757812</v>
       </c>
       <c r="F115" t="n">
-        <v>14649200</v>
+        <v>14183500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>637.432932921519</v>
+        <v>651.3780476889771</v>
       </c>
       <c r="C116" t="n">
-        <v>646.0375787806976</v>
+        <v>656.5288937722072</v>
       </c>
       <c r="D116" t="n">
-        <v>635.5861905818066</v>
+        <v>634.8675211939732</v>
       </c>
       <c r="E116" t="n">
-        <v>643.6318969726562</v>
+        <v>636.1152954101562</v>
       </c>
       <c r="F116" t="n">
-        <v>10035700</v>
+        <v>8605900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>638.5510179511008</v>
+        <v>631.9527259539814</v>
       </c>
       <c r="C117" t="n">
-        <v>662.1688639053526</v>
+        <v>639.9683956881865</v>
       </c>
       <c r="D117" t="n">
-        <v>637.642665037141</v>
+        <v>627.8599900449855</v>
       </c>
       <c r="E117" t="n">
-        <v>654.4925537109375</v>
+        <v>638.16162109375</v>
       </c>
       <c r="F117" t="n">
-        <v>14183500</v>
+        <v>10135600</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>651.3781101885919</v>
+        <v>641.3859599741169</v>
       </c>
       <c r="C118" t="n">
-        <v>656.5289567660449</v>
+        <v>652.7157261405878</v>
       </c>
       <c r="D118" t="n">
-        <v>634.8675821094057</v>
+        <v>640.9966397738364</v>
       </c>
       <c r="E118" t="n">
-        <v>636.1153564453125</v>
+        <v>652.5260620117188</v>
       </c>
       <c r="F118" t="n">
-        <v>8605900</v>
+        <v>11330700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>631.9527863953055</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C119" t="n">
-        <v>639.9684568961466</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D119" t="n">
-        <v>627.8600500948714</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E119" t="n">
-        <v>638.1616821289062</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F119" t="n">
-        <v>10135600</v>
+        <v>10637700</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>641.3858999809694</v>
+        <v>642.3043203814821</v>
       </c>
       <c r="C120" t="n">
-        <v>652.7156650876909</v>
+        <v>648.2836451675449</v>
       </c>
       <c r="D120" t="n">
-        <v>640.9965798171046</v>
+        <v>636.9837936279411</v>
       </c>
       <c r="E120" t="n">
-        <v>652.5260009765625</v>
+        <v>647.02587890625</v>
       </c>
       <c r="F120" t="n">
-        <v>11330700</v>
+        <v>15703000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>649.3916295582877</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C121" t="n">
-        <v>659.823034651462</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D121" t="n">
-        <v>646.3470725216666</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E121" t="n">
-        <v>655.8401489257812</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F121" t="n">
-        <v>10637700</v>
+        <v>9816100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>642.3042597917192</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C122" t="n">
-        <v>648.2835840137412</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D122" t="n">
-        <v>636.9837335400734</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E122" t="n">
-        <v>647.0258178710938</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F122" t="n">
-        <v>15703000</v>
+        <v>12263800</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>636.0254184162494</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C123" t="n">
-        <v>658.764884603327</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D123" t="n">
-        <v>633.3701817354564</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E123" t="n">
-        <v>652.396240234375</v>
+        <v>666.541015625</v>
       </c>
       <c r="F123" t="n">
-        <v>9816100</v>
+        <v>10810100</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>647.1356255764312</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C124" t="n">
-        <v>657.866484005116</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D124" t="n">
-        <v>637.7025010942567</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E124" t="n">
-        <v>653.91357421875</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F124" t="n">
-        <v>12263800</v>
+        <v>13341400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>656.7884535878291</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C125" t="n">
-        <v>671.5720803574089</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D125" t="n">
-        <v>656.4989309709863</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E125" t="n">
-        <v>666.541015625</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F125" t="n">
-        <v>10810100</v>
+        <v>13159400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>660.751362594833</v>
+        <v>633.6497720389343</v>
       </c>
       <c r="C126" t="n">
-        <v>669.5057662619517</v>
+        <v>646.596649067328</v>
       </c>
       <c r="D126" t="n">
-        <v>649.1520579976961</v>
+        <v>625.6640164348609</v>
       </c>
       <c r="E126" t="n">
-        <v>659.393798828125</v>
+        <v>646.2373046875</v>
       </c>
       <c r="F126" t="n">
-        <v>13341400</v>
+        <v>13489700</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>646.7463568472266</v>
+        <v>652.3962328583322</v>
       </c>
       <c r="C127" t="n">
-        <v>648.3135076492586</v>
+        <v>659.1242214972237</v>
       </c>
       <c r="D127" t="n">
-        <v>634.9773114336934</v>
+        <v>647.8443550809549</v>
       </c>
       <c r="E127" t="n">
-        <v>643.7117309570312</v>
+        <v>652.9053344726562</v>
       </c>
       <c r="F127" t="n">
-        <v>13159400</v>
+        <v>9859300</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>633.6497121926325</v>
+        <v>653.5941111270305</v>
       </c>
       <c r="C128" t="n">
-        <v>646.5965879982328</v>
+        <v>657.9463328691638</v>
       </c>
       <c r="D128" t="n">
-        <v>625.6639573427893</v>
+        <v>647.2054829186618</v>
       </c>
       <c r="E128" t="n">
-        <v>646.2372436523438</v>
+        <v>653.6939086914062</v>
       </c>
       <c r="F128" t="n">
-        <v>13489700</v>
+        <v>8977200</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>652.3962938458964</v>
+        <v>647.5948263527883</v>
       </c>
       <c r="C129" t="n">
-        <v>659.1242831137364</v>
+        <v>652.336368433984</v>
       </c>
       <c r="D129" t="n">
-        <v>647.8444156429986</v>
+        <v>635.7659510050273</v>
       </c>
       <c r="E129" t="n">
-        <v>652.9053955078125</v>
+        <v>637.0436401367188</v>
       </c>
       <c r="F129" t="n">
-        <v>9859300</v>
+        <v>11617500</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>653.5941721528687</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C130" t="n">
-        <v>657.9463943013674</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D130" t="n">
-        <v>647.2055433479961</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E130" t="n">
-        <v>653.6939697265625</v>
+        <v>612.6171875</v>
       </c>
       <c r="F130" t="n">
-        <v>8977200</v>
+        <v>18957600</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>647.5948883988538</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C131" t="n">
-        <v>652.3364309343367</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D131" t="n">
-        <v>635.7660119177681</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E131" t="n">
-        <v>637.043701171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F131" t="n">
-        <v>11617500</v>
+        <v>15134900</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>622.7790526456299</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C132" t="n">
-        <v>628.0496188589474</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D132" t="n">
-        <v>608.4645611002024</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E132" t="n">
-        <v>612.6171875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F132" t="n">
-        <v>18957600</v>
+        <v>10348800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,25 +3875,25 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>631.4147932406764</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C133" t="n">
-        <v>634.1622468505053</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D133" t="n">
-        <v>622.5230098937741</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E133" t="n">
-        <v>626.8690185546875</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F133" t="n">
-        <v>15134900</v>
+        <v>11726300</v>
       </c>
       <c r="G133" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>627.4085169382369</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C134" t="n">
-        <v>635.9605885584036</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D134" t="n">
-        <v>621.1243629754691</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E134" t="n">
-        <v>622.0834350585938</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F134" t="n">
-        <v>10348800</v>
+        <v>13247700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>615.7693473594539</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C135" t="n">
-        <v>622.0735023862151</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D135" t="n">
-        <v>614.04090772979</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E135" t="n">
-        <v>615.1099243164062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F135" t="n">
-        <v>11726300</v>
+        <v>21214900</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>611.5832104537112</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C136" t="n">
-        <v>612.4323990135786</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D136" t="n">
-        <v>601.7023533616688</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E136" t="n">
-        <v>606.1382446289062</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F136" t="n">
-        <v>13247700</v>
+        <v>13638000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>602.9712077810872</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C137" t="n">
-        <v>603.400802317344</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D137" t="n">
-        <v>586.7062525156723</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E137" t="n">
-        <v>593.1102905273438</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F137" t="n">
-        <v>21214900</v>
+        <v>10739700</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>605.2290499891692</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C138" t="n">
-        <v>608.0764476338709</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D138" t="n">
-        <v>598.4553596033379</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E138" t="n">
-        <v>603.5006713867188</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F138" t="n">
-        <v>13638000</v>
+        <v>12585000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>598.5452420228083</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C139" t="n">
-        <v>600.443507118967</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D139" t="n">
-        <v>590.4527665679026</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E139" t="n">
-        <v>592.3709716796875</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F139" t="n">
-        <v>10739700</v>
+        <v>35780100</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>598.1855830392399</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C140" t="n">
-        <v>603.1110107561809</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D140" t="n">
-        <v>592.8505617950721</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E140" t="n">
-        <v>594.3391723632812</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F140" t="n">
-        <v>12585000</v>
+        <v>30133000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>581.9506076701073</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C141" t="n">
-        <v>582.460145169462</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D141" t="n">
-        <v>542.8468364624507</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E141" t="n">
-        <v>547.032958984375</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F141" t="n">
-        <v>35780100</v>
+        <v>22795200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>539.599843303006</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C142" t="n">
-        <v>543.0966023049141</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D142" t="n">
-        <v>519.7782492802263</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E142" t="n">
-        <v>525.233154296875</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F142" t="n">
-        <v>30133000</v>
+        <v>32898300</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>535.8833618164062</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C143" t="n">
-        <v>539.0504095872608</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D143" t="n">
-        <v>528.0505941707193</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E143" t="n">
-        <v>535.8833618164062</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F143" t="n">
-        <v>22795200</v>
+        <v>23608100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>549.4707059552647</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C144" t="n">
-        <v>573.1587727471259</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D144" t="n">
-        <v>546.2637174010383</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E144" t="n">
-        <v>571.6002197265625</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F144" t="n">
-        <v>32898300</v>
+        <v>13518500</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>579.5928556215499</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C145" t="n">
-        <v>592.0013387220274</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D145" t="n">
-        <v>573.2887005646345</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E145" t="n">
-        <v>578.6936645507812</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F145" t="n">
-        <v>23608100</v>
+        <v>9515700</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>565.5158531822124</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C146" t="n">
-        <v>577.9643377947169</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D146" t="n">
-        <v>559.1817578546791</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E146" t="n">
-        <v>573.9281005859375</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F146" t="n">
-        <v>13518500</v>
+        <v>9580800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>577.1550997330287</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C147" t="n">
-        <v>582.2503530791108</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D147" t="n">
-        <v>571.4703658572956</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E147" t="n">
-        <v>572.4894409179688</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F147" t="n">
-        <v>9515700</v>
+        <v>32036600</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>571.9498894780604</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C148" t="n">
-        <v>574.6973431004155</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D148" t="n">
-        <v>564.2370671243236</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E148" t="n">
-        <v>574.5175170898438</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F148" t="n">
-        <v>9580800</v>
+        <v>19012900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>605.4388670235439</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C149" t="n">
-        <v>629.3667024291958</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D149" t="n">
-        <v>591.2820049792073</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E149" t="n">
-        <v>611.8529052734375</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F149" t="n">
-        <v>32036600</v>
+        <v>13294800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>626.3894374266143</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C150" t="n">
-        <v>636.9097166035551</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D150" t="n">
-        <v>622.4231426572783</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E150" t="n">
-        <v>627.8081665039062</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F150" t="n">
-        <v>19012900</v>
+        <v>9538900</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>633.882449891805</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C151" t="n">
-        <v>637.9886903650855</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D151" t="n">
-        <v>623.7518859014353</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E151" t="n">
-        <v>629.2767333984375</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F151" t="n">
-        <v>13294800</v>
+        <v>17818000</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>628.9171329935918</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C152" t="n">
-        <v>634.4120404303904</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D152" t="n">
-        <v>623.8218795800174</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E152" t="n">
-        <v>633.9425048828125</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F152" t="n">
-        <v>9538900</v>
+        <v>14952600</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>642.624350345733</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C153" t="n">
-        <v>665.6430543798978</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D153" t="n">
-        <v>638.7779398291946</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E153" t="n">
-        <v>661.8765258789062</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F153" t="n">
-        <v>17818000</v>
+        <v>9544800</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>666.3824145357423</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C154" t="n">
-        <v>677.8717665104965</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D154" t="n">
-        <v>663.6049593103575</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E154" t="n">
-        <v>670.9581909179688</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F154" t="n">
-        <v>14952600</v>
+        <v>16283500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>675.3640350842893</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C155" t="n">
-        <v>676.9525896021297</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D155" t="n">
-        <v>667.131674939706</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E155" t="n">
-        <v>676.2432250976562</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F155" t="n">
-        <v>9544800</v>
+        <v>12534000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>677.9716157075654</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C156" t="n">
-        <v>690.8796961433965</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D156" t="n">
-        <v>674.5048580761284</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E156" t="n">
-        <v>687.9124145507812</v>
+        <v>668.220703125</v>
       </c>
       <c r="F156" t="n">
-        <v>16283500</v>
+        <v>8660100</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>680.7290935491282</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C157" t="n">
-        <v>682.7472426832454</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D157" t="n">
-        <v>667.381478611767</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E157" t="n">
-        <v>670.2887573242188</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F157" t="n">
-        <v>12534000</v>
+        <v>9215600</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>670.3786762058809</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C158" t="n">
-        <v>675.5738733736962</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D158" t="n">
-        <v>666.7120915784461</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E158" t="n">
-        <v>668.220703125</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F158" t="n">
-        <v>8660100</v>
+        <v>11667000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>673.7355628200382</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C159" t="n">
-        <v>677.7518600207422</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D159" t="n">
-        <v>669.1298460769134</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E159" t="n">
-        <v>674.09521484375</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F159" t="n">
-        <v>9215600</v>
+        <v>13348300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>663.0854475032797</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C160" t="n">
-        <v>668.9400066983026</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D160" t="n">
-        <v>652.4452846667049</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E160" t="n">
-        <v>658.5396728515625</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F160" t="n">
-        <v>11667000</v>
+        <v>12805200</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>659.7085674039201</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C161" t="n">
-        <v>680.0396994180859</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D161" t="n">
-        <v>653.2345872360809</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E161" t="n">
-        <v>674.4049682617188</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F161" t="n">
-        <v>13348300</v>
+        <v>10606800</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>670.3786986745525</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C162" t="n">
-        <v>681.8680504402118</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D162" t="n">
-        <v>670.2188736545023</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E162" t="n">
-        <v>677.9916381835938</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F162" t="n">
-        <v>12805200</v>
+        <v>18947500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>673.6156618787633</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C163" t="n">
-        <v>677.5520159823654</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D163" t="n">
-        <v>665.0136491453696</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E163" t="n">
-        <v>670.7183837890625</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F163" t="n">
-        <v>10606800</v>
+        <v>52765000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>668.2905997420939</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C164" t="n">
-        <v>673.6256820299297</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D164" t="n">
-        <v>663.1953464496755</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E164" t="n">
-        <v>668.5004272460938</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F164" t="n">
-        <v>18947500</v>
+        <v>21404000</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>618.7465567527638</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C165" t="n">
-        <v>620.2751083620838</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D165" t="n">
-        <v>599.4444385151393</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E165" t="n">
-        <v>611.3433837890625</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F165" t="n">
-        <v>52765000</v>
+        <v>16203900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>614.120842749119</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C166" t="n">
-        <v>618.3069655430758</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D166" t="n">
-        <v>605.5487701514051</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E166" t="n">
-        <v>608.1863403320312</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F166" t="n">
-        <v>21404000</v>
+        <v>17171300</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>607.3771038685389</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C167" t="n">
-        <v>613.4314904063681</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D167" t="n">
-        <v>602.1919069095087</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E167" t="n">
-        <v>609.8447875976562</v>
+        <v>612.3125</v>
       </c>
       <c r="F167" t="n">
-        <v>16203900</v>
+        <v>19915500</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>612.7420849871345</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C168" t="n">
-        <v>613.7811000159977</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D168" t="n">
-        <v>599.8040642277598</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E168" t="n">
-        <v>604.3998413085938</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F168" t="n">
-        <v>17171300</v>
+        <v>12307400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>600.4934370812971</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C169" t="n">
-        <v>619.3759607512419</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D169" t="n">
-        <v>597.5461564796674</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E169" t="n">
-        <v>612.3125</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F169" t="n">
-        <v>19915500</v>
+        <v>13557000</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>614.150739078972</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C170" t="n">
-        <v>624.4012480600104</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D170" t="n">
-        <v>612.9718390781961</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E170" t="n">
-        <v>616.2388305664062</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F170" t="n">
-        <v>12307400</v>
+        <v>15940600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>614.6303402495529</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C171" t="n">
-        <v>616.1988937552933</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D171" t="n">
-        <v>605.4987892063378</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E171" t="n">
-        <v>609.0654907226562</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F171" t="n">
-        <v>13557000</v>
+        <v>11351600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>604.010215830275</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C172" t="n">
-        <v>604.3498668649182</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D172" t="n">
-        <v>597.5262348938886</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E172" t="n">
-        <v>598.3054809570312</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F172" t="n">
-        <v>15940600</v>
+        <v>14634400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>594.2692320029287</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C173" t="n">
-        <v>603.1909559259367</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D173" t="n">
-        <v>592.0512559095129</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E173" t="n">
-        <v>602.441650390625</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F173" t="n">
-        <v>11351600</v>
+        <v>10651200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>598.275515544453</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C174" t="n">
-        <v>619.3260125714435</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D174" t="n">
-        <v>596.1074810052941</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E174" t="n">
-        <v>616.0590209960938</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F174" t="n">
-        <v>14634400</v>
+        <v>13272600</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>615.4296182023591</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C175" t="n">
-        <v>623.152441138389</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D175" t="n">
-        <v>614.4305441468357</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E175" t="n">
-        <v>617.8573608398438</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F175" t="n">
-        <v>10651200</v>
+        <v>13772400</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>613.421486859321</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C176" t="n">
-        <v>620.6248329546977</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D176" t="n">
-        <v>608.7458274653094</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E176" t="n">
-        <v>613.6612548828125</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F176" t="n">
-        <v>13272600</v>
+        <v>11749900</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>608.5459509764945</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C177" t="n">
-        <v>615.0199919776213</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D177" t="n">
-        <v>603.1309869574205</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E177" t="n">
-        <v>610.64404296875</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F177" t="n">
-        <v>13772400</v>
+        <v>11329700</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>608.3561568042173</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C178" t="n">
-        <v>613.361527578881</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D178" t="n">
-        <v>599.9939118379299</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E178" t="n">
-        <v>602.052001953125</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F178" t="n">
-        <v>11749900</v>
+        <v>13476100</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>600.2037495434126</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C179" t="n">
-        <v>607.4370360716302</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D179" t="n">
-        <v>597.2564688338498</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E179" t="n">
-        <v>604.499755859375</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F179" t="n">
-        <v>11329700</v>
+        <v>11688600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>599.4443949814065</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C180" t="n">
-        <v>609.0354809096541</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D180" t="n">
-        <v>594.2591985256718</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E180" t="n">
-        <v>606.8175659179688</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F180" t="n">
-        <v>13476100</v>
+        <v>12234200</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>607.3171451453314</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C181" t="n">
-        <v>614.2407210713809</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D181" t="n">
-        <v>606.3880135859368</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E181" t="n">
-        <v>609.6949462890625</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F181" t="n">
-        <v>11688600</v>
+        <v>23143600</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>608.3261927003538</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C182" t="n">
-        <v>613.9009818092591</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D182" t="n">
-        <v>604.7394901495815</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E182" t="n">
-        <v>611.7730102539062</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F182" t="n">
-        <v>12234200</v>
+        <v>16772400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>608.8357727220844</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C183" t="n">
-        <v>637.908804248614</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D183" t="n">
-        <v>608.4361186960156</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E183" t="n">
-        <v>634.6718139648438</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F183" t="n">
-        <v>23143600</v>
+        <v>19806500</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>638.9078448274123</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C184" t="n">
-        <v>642.4046039468743</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D184" t="n">
-        <v>628.7272779804616</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E184" t="n">
-        <v>634.7017211914062</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F184" t="n">
-        <v>16772400</v>
+        <v>29138800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>632.9133899267435</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C185" t="n">
-        <v>633.9124639439917</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D185" t="n">
-        <v>622.7727642602187</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E185" t="n">
-        <v>631.92431640625</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F185" t="n">
-        <v>19806500</v>
+        <v>18252000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>629.8162791560948</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C186" t="n">
-        <v>635.1613007084701</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D186" t="n">
-        <v>598.9748694014791</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E186" t="n">
-        <v>599.9139404296875</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F186" t="n">
-        <v>29138800</v>
+        <v>23020100</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>602.6813896226799</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C187" t="n">
-        <v>608.3161816139932</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D187" t="n">
-        <v>596.1274666259658</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E187" t="n">
-        <v>597.0765991210938</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F187" t="n">
-        <v>18252000</v>
+        <v>21469200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>602.4416570391962</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C188" t="n">
-        <v>623.5720977596394</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D188" t="n">
-        <v>599.7142043737263</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E188" t="n">
-        <v>622.4031372070312</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F188" t="n">
-        <v>23020100</v>
+        <v>30091600</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>623.0924785224576</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C189" t="n">
-        <v>641.8051764288737</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D189" t="n">
-        <v>621.8536364911718</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E189" t="n">
-        <v>626.9888916015625</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F189" t="n">
-        <v>21469200</v>
+        <v>19512400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>622.8827460758752</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C190" t="n">
-        <v>628.5674800138549</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D190" t="n">
-        <v>582.3702434655938</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E190" t="n">
-        <v>592.450927734375</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F190" t="n">
-        <v>30091600</v>
+        <v>16977400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>591.4518261333767</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C191" t="n">
-        <v>591.4518261333767</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D191" t="n">
-        <v>578.6836307521693</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E191" t="n">
-        <v>584.8479614257812</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F191" t="n">
-        <v>19512400</v>
+        <v>17064000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>590.4527436689563</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C192" t="n">
-        <v>597.0766092757164</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D192" t="n">
-        <v>580.4720040020986</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E192" t="n">
-        <v>584.0487060546875</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F192" t="n">
-        <v>16977400</v>
+        <v>17628000</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>580.192266144374</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C193" t="n">
-        <v>590.7724873942649</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D193" t="n">
-        <v>570.0716409197756</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E193" t="n">
-        <v>570.4512939453125</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F193" t="n">
-        <v>17064000</v>
+        <v>14326400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>565.3060574843756</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C194" t="n">
-        <v>571.6401524850257</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D194" t="n">
-        <v>556.4942175026772</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E194" t="n">
-        <v>567.9036254882812</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F194" t="n">
-        <v>17628000</v>
+        <v>17653300</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>572.4194595335534</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C195" t="n">
-        <v>575.5365655300229</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D195" t="n">
-        <v>560.3806300495169</v>
+        <v>592</v>
       </c>
       <c r="E195" t="n">
-        <v>566.4549560546875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F195" t="n">
-        <v>14326400</v>
+        <v>11344400</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,25 +5513,25 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>579.9000244140625</v>
+        <v>592</v>
       </c>
       <c r="C196" t="n">
-        <v>601.27001953125</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D196" t="n">
-        <v>579.2999877929688</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E196" t="n">
-        <v>593.47998046875</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F196" t="n">
-        <v>17653300</v>
+        <v>20478300</v>
       </c>
       <c r="G196" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>593.6500244140625</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C197" t="n">
-        <v>605.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D197" t="n">
-        <v>592</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E197" t="n">
-        <v>600.2100219726562</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F197" t="n">
-        <v>11344400</v>
+        <v>28824600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>592</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C198" t="n">
-        <v>593.8099975585938</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D198" t="n">
-        <v>566.1900024414062</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E198" t="n">
-        <v>567.5800170898438</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F198" t="n">
-        <v>20478300</v>
+        <v>15405500</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>572.8200073242188</v>
+        <v>562.25</v>
       </c>
       <c r="C199" t="n">
-        <v>580.219970703125</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D199" t="n">
-        <v>563.0999755859375</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E199" t="n">
-        <v>577.219970703125</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F199" t="n">
-        <v>28824600</v>
+        <v>13103300</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>572.02001953125</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C200" t="n">
-        <v>575.8099975585938</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D200" t="n">
-        <v>559.8099975585938</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E200" t="n">
-        <v>563.8499755859375</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F200" t="n">
-        <v>15405500</v>
+        <v>13963600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>562.25</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C201" t="n">
-        <v>572.2000122070312</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D201" t="n">
-        <v>561.02001953125</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E201" t="n">
-        <v>562.2000122070312</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F201" t="n">
-        <v>13103300</v>
+        <v>16968600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>561.8900146484375</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C202" t="n">
-        <v>569.0399780273438</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D202" t="n">
-        <v>555.5499877929688</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E202" t="n">
-        <v>557.6699829101562</v>
+        <v>550.25</v>
       </c>
       <c r="F202" t="n">
-        <v>13963600</v>
+        <v>18867700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>555.5499877929688</v>
+        <v>560</v>
       </c>
       <c r="C203" t="n">
-        <v>556.3400268554688</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D203" t="n">
-        <v>540.1799926757812</v>
+        <v>558</v>
       </c>
       <c r="E203" t="n">
-        <v>542.8699951171875</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F203" t="n">
-        <v>16968600</v>
+        <v>15011400</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>543.3400268554688</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C204" t="n">
-        <v>556.8499755859375</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D204" t="n">
-        <v>540.4000244140625</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E204" t="n">
-        <v>550.25</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F204" t="n">
-        <v>18867700</v>
+        <v>18111100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>560</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C205" t="n">
-        <v>570.9000244140625</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D205" t="n">
-        <v>558</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E205" t="n">
-        <v>562.5999755859375</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F205" t="n">
-        <v>15011400</v>
+        <v>45536300</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C206" t="n">
-        <v>565.5399780273438</v>
+        <v>610</v>
       </c>
       <c r="D206" t="n">
-        <v>551.4299926757812</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E206" t="n">
-        <v>563.2899780273438</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F206" t="n">
-        <v>18111100</v>
+        <v>21705900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>607.9099731445312</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C207" t="n">
-        <v>628.280029296875</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D207" t="n">
-        <v>595.0999755859375</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E207" t="n">
-        <v>612.9099731445312</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F207" t="n">
-        <v>45536300</v>
+        <v>17674100</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>607.9000244140625</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C208" t="n">
-        <v>610</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D208" t="n">
-        <v>580.4199829101562</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E208" t="n">
-        <v>582.9000244140625</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F208" t="n">
-        <v>21705900</v>
+        <v>18560800</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>594.8400268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C209" t="n">
-        <v>603.5800170898438</v>
+        <v>616</v>
       </c>
       <c r="D209" t="n">
-        <v>581.760009765625</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E209" t="n">
-        <v>600.2899780273438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F209" t="n">
-        <v>17674100</v>
+        <v>13606500</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>607.5900268554688</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C210" t="n">
-        <v>625.3699951171875</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D210" t="n">
-        <v>603.6599731445312</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E210" t="n">
-        <v>615.5800170898438</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F210" t="n">
-        <v>18560800</v>
+        <v>26579700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>614.3900146484375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C211" t="n">
-        <v>616</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D211" t="n">
-        <v>598.010009765625</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E211" t="n">
-        <v>603.1199951171875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F211" t="n">
-        <v>13606500</v>
+        <v>40608900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>583.989990234375</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C212" t="n">
-        <v>633.27001953125</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D212" t="n">
-        <v>577.0700073242188</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E212" t="n">
-        <v>631.47998046875</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F212" t="n">
-        <v>26579700</v>
+        <v>19840700</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>660.3400268554688</v>
+        <v>652</v>
       </c>
       <c r="C213" t="n">
-        <v>677.8599853515625</v>
+        <v>666.5</v>
       </c>
       <c r="D213" t="n">
-        <v>658.010009765625</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E213" t="n">
-        <v>669.2100219726562</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F213" t="n">
-        <v>40608900</v>
+        <v>16748200</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>661.3800048828125</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C214" t="n">
-        <v>676.6199951171875</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D214" t="n">
-        <v>654.2000122070312</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E214" t="n">
-        <v>656.72998046875</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F214" t="n">
-        <v>19840700</v>
+        <v>19003400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>652</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C215" t="n">
-        <v>666.5</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D215" t="n">
-        <v>649.0499877929688</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E215" t="n">
-        <v>661.0399780273438</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F215" t="n">
-        <v>16748200</v>
+        <v>15816000</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>663.5999755859375</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C216" t="n">
-        <v>686.0800170898438</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D216" t="n">
-        <v>656.6599731445312</v>
+        <v>626</v>
       </c>
       <c r="E216" t="n">
-        <v>681.3099975585938</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F216" t="n">
-        <v>19003400</v>
+        <v>22267900</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>677.280029296875</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C217" t="n">
-        <v>681.9000244140625</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D217" t="n">
-        <v>660.1599731445312</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E217" t="n">
-        <v>664.5399780273438</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F217" t="n">
-        <v>15816000</v>
+        <v>10225200</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>647.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C218" t="n">
-        <v>652.2000122070312</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D218" t="n">
-        <v>626</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E218" t="n">
-        <v>646.010009765625</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F218" t="n">
-        <v>22267900</v>
+        <v>9140500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>646.7000122070312</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C219" t="n">
-        <v>653.2999877929688</v>
+        <v>649</v>
       </c>
       <c r="D219" t="n">
-        <v>636.010009765625</v>
+        <v>624</v>
       </c>
       <c r="E219" t="n">
-        <v>645.8499755859375</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F219" t="n">
-        <v>10225200</v>
+        <v>11019600</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>654.1799926757812</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C220" t="n">
-        <v>655.8800048828125</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D220" t="n">
-        <v>643.2000122070312</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E220" t="n">
-        <v>643.8099975585938</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F220" t="n">
-        <v>9140500</v>
+        <v>15494800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>647.7000122070312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C221" t="n">
-        <v>649</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D221" t="n">
-        <v>624</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E221" t="n">
-        <v>627.1699829101562</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F221" t="n">
-        <v>11019600</v>
+        <v>11503500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>608.4099731445312</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C222" t="n">
-        <v>614.6500244140625</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D222" t="n">
-        <v>597.219970703125</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E222" t="n">
-        <v>606.0999755859375</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F222" t="n">
-        <v>15494800</v>
+        <v>11195300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>605.2999877929688</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C223" t="n">
-        <v>609.97998046875</v>
+        <v>601</v>
       </c>
       <c r="D223" t="n">
-        <v>594.4500122070312</v>
+        <v>587</v>
       </c>
       <c r="E223" t="n">
-        <v>595.1900024414062</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F223" t="n">
-        <v>11503500</v>
+        <v>12009300</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>607.219970703125</v>
+        <v>593.25</v>
       </c>
       <c r="C224" t="n">
-        <v>611.260009765625</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D224" t="n">
-        <v>593.1300048828125</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E224" t="n">
-        <v>593.8699951171875</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F224" t="n">
-        <v>11195300</v>
+        <v>22371100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>596.8200073242188</v>
+        <v>526</v>
       </c>
       <c r="C225" t="n">
-        <v>601</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D225" t="n">
-        <v>587</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E225" t="n">
-        <v>593.4099731445312</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F225" t="n">
-        <v>12009300</v>
+        <v>42271500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>593.25</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C226" t="n">
-        <v>599.969970703125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D226" t="n">
-        <v>582.219970703125</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E226" t="n">
-        <v>585.6099853515625</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F226" t="n">
-        <v>22371100</v>
+        <v>24261500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>526</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C227" t="n">
-        <v>539.8800048828125</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D227" t="n">
-        <v>524.489990234375</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E227" t="n">
-        <v>539.030029296875</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F227" t="n">
-        <v>42271500</v>
+        <v>25938100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>543.5999755859375</v>
+        <v>581.5</v>
       </c>
       <c r="C228" t="n">
-        <v>558.3300170898438</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D228" t="n">
-        <v>540.219970703125</v>
+        <v>578.25</v>
       </c>
       <c r="E228" t="n">
-        <v>556.7100219726562</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F228" t="n">
-        <v>24261500</v>
+        <v>17959200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>562.239990234375</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C229" t="n">
-        <v>597.52001953125</v>
+        <v>601</v>
       </c>
       <c r="D229" t="n">
-        <v>559.3599853515625</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E229" t="n">
-        <v>590.239990234375</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F229" t="n">
-        <v>25938100</v>
+        <v>14897200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>581.5</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C230" t="n">
-        <v>592.7899780273438</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D230" t="n">
-        <v>578.25</v>
+        <v>586</v>
       </c>
       <c r="E230" t="n">
-        <v>587.9400024414062</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F230" t="n">
-        <v>17959200</v>
+        <v>11811500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>600.4600219726562</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C231" t="n">
-        <v>601</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D231" t="n">
-        <v>580.1199951171875</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E231" t="n">
-        <v>588.77001953125</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F231" t="n">
-        <v>14897200</v>
+        <v>11250300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>586.9500122070312</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C232" t="n">
-        <v>595.3099975585938</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D232" t="n">
-        <v>586</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E232" t="n">
-        <v>589.9000244140625</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F232" t="n">
-        <v>11811500</v>
+        <v>14967300</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>585.6400146484375</v>
+        <v>598</v>
       </c>
       <c r="C233" t="n">
-        <v>598.739990234375</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D233" t="n">
-        <v>585.6199951171875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E233" t="n">
-        <v>592.0999755859375</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F233" t="n">
-        <v>11250300</v>
+        <v>13146900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>599.1300048828125</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C234" t="n">
-        <v>608.2100219726562</v>
+        <v>604.5</v>
       </c>
       <c r="D234" t="n">
-        <v>592.030029296875</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E234" t="n">
-        <v>594.9199829101562</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F234" t="n">
-        <v>14967300</v>
+        <v>16186900</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>598</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C235" t="n">
-        <v>612.4299926757812</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D235" t="n">
-        <v>593.4000244140625</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E235" t="n">
-        <v>599.1199951171875</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F235" t="n">
-        <v>13146900</v>
+        <v>11164200</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>601.0700073242188</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C236" t="n">
-        <v>604.5</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D236" t="n">
-        <v>578.2100219726562</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E236" t="n">
-        <v>578.8499755859375</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F236" t="n">
-        <v>16186900</v>
+        <v>8758000</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>580.7100219726562</v>
+        <v>589.75</v>
       </c>
       <c r="C237" t="n">
-        <v>595.8499755859375</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D237" t="n">
-        <v>579.3900146484375</v>
+        <v>564.75</v>
       </c>
       <c r="E237" t="n">
-        <v>594.969970703125</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F237" t="n">
-        <v>11164200</v>
+        <v>17225600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>596.97998046875</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C238" t="n">
-        <v>601.8599853515625</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D238" t="n">
-        <v>589.2899780273438</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E238" t="n">
-        <v>589.8499755859375</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F238" t="n">
-        <v>8758000</v>
+        <v>27094900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>589.75</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C239" t="n">
-        <v>590.239990234375</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D239" t="n">
-        <v>564.75</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E239" t="n">
-        <v>568.969970703125</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F239" t="n">
-        <v>17225600</v>
+        <v>16971700</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>557.47998046875</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C240" t="n">
-        <v>560.6599731445312</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D240" t="n">
-        <v>543.2100219726562</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E240" t="n">
-        <v>543.6699829101562</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F240" t="n">
-        <v>27094900</v>
+        <v>13872200</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>541.3400268554688</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C241" t="n">
-        <v>554.0700073242188</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D241" t="n">
-        <v>537.27001953125</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E241" t="n">
-        <v>546.030029296875</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F241" t="n">
-        <v>16971700</v>
+        <v>13848000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>546.9500122070312</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C242" t="n">
-        <v>549.989990234375</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D242" t="n">
-        <v>539.3099975585938</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E242" t="n">
-        <v>545.8300170898438</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F242" t="n">
-        <v>13872200</v>
+        <v>12990600</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>546.8900146484375</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>553.8699951171875</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D243" t="n">
-        <v>543.22998046875</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E243" t="n">
-        <v>549.9000244140625</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F243" t="n">
-        <v>13848000</v>
+        <v>9769100</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>550.2000122070312</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C244" t="n">
-        <v>561.4199829101562</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D244" t="n">
-        <v>546.2999877929688</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E244" t="n">
-        <v>559.02001953125</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F244" t="n">
-        <v>12990600</v>
+        <v>31416300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>563.8800048828125</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C245" t="n">
-        <v>570.7999877929688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D245" t="n">
-        <v>561.4000244140625</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E245" t="n">
-        <v>570.0499877929688</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F245" t="n">
-        <v>9769100</v>
+        <v>15221400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>590.3099975585938</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C246" t="n">
-        <v>593.3400268554688</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D246" t="n">
-        <v>561.8800048828125</v>
+        <v>571</v>
       </c>
       <c r="E246" t="n">
-        <v>576.1400146484375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F246" t="n">
-        <v>31416300</v>
+        <v>16042400</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>576.47998046875</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C247" t="n">
-        <v>588.3900146484375</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D247" t="n">
-        <v>567.6199951171875</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E247" t="n">
-        <v>571.0999755859375</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F247" t="n">
-        <v>15221400</v>
+        <v>13383800</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>571.5499877929688</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C248" t="n">
-        <v>589.1900024414062</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D248" t="n">
-        <v>571</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E248" t="n">
-        <v>578.02001953125</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F248" t="n">
-        <v>16042400</v>
+        <v>15796900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>577.6300048828125</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C249" t="n">
-        <v>578.6799926757812</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D249" t="n">
-        <v>569.1400146484375</v>
+        <v>577</v>
       </c>
       <c r="E249" t="n">
-        <v>572.3400268554688</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F249" t="n">
-        <v>13383800</v>
+        <v>16552700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>558.3499755859375</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C250" t="n">
-        <v>584.9500122070312</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D250" t="n">
-        <v>556.0999755859375</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E250" t="n">
-        <v>578.5399780273438</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F250" t="n">
-        <v>15796900</v>
+        <v>19737100</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>578.7899780273438</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C251" t="n">
-        <v>600.3800048828125</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D251" t="n">
-        <v>577</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E251" t="n">
-        <v>592.8499755859375</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F251" t="n">
-        <v>16552700</v>
+        <v>15942700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>604.489990234375</v>
-      </c>
-      <c r="C252" t="n">
-        <v>619.4600219726562</v>
-      </c>
-      <c r="D252" t="n">
-        <v>604.3499755859375</v>
-      </c>
-      <c r="E252" t="n">
-        <v>610.6799926757812</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>19737100</v>
+        <v>18296627</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>612.3499755859375</v>
-      </c>
-      <c r="C253" t="n">
-        <v>617.4600219726562</v>
-      </c>
-      <c r="D253" t="n">
-        <v>605.27001953125</v>
-      </c>
-      <c r="E253" t="n">
-        <v>616.77001953125</v>
-      </c>
-      <c r="F253" t="n">
-        <v>15942700</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10802,34 +10768,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>613.48</v>
+      </c>
+      <c r="D2" t="n">
         <v>616.77</v>
       </c>
-      <c r="D2" t="n">
-        <v>610.6799999999999</v>
-      </c>
       <c r="E2" t="n">
-        <v>612.495</v>
+        <v>615.875</v>
       </c>
       <c r="F2" t="n">
-        <v>617.46</v>
+        <v>624.8</v>
       </c>
       <c r="G2" t="n">
-        <v>605.27</v>
+        <v>609.74</v>
       </c>
       <c r="H2" t="n">
-        <v>15966213</v>
+        <v>18296627</v>
       </c>
       <c r="I2" t="n">
-        <v>17851201</v>
+        <v>17824408</v>
       </c>
       <c r="J2" t="n">
-        <v>1571225468928</v>
+        <v>1562844069888</v>
       </c>
       <c r="K2" t="n">
-        <v>23.256788</v>
+        <v>23.132729</v>
       </c>
       <c r="L2" t="n">
-        <v>17.642334</v>
+        <v>17.548225</v>
       </c>
       <c r="M2" t="n">
         <v>26.52</v>
@@ -10868,7 +10834,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.0160947</v>
+        <v>5.984003</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10880,7 +10846,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1593283444736</v>
+        <v>1584902176768</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10907,7 +10873,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:52:06</t>
+          <t>2026-09-09 09:15:02</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>755.0154070864886</v>
+        <v>762.6305038555339</v>
       </c>
       <c r="C2" t="n">
-        <v>763.7966239723705</v>
+        <v>763.1986490989516</v>
       </c>
       <c r="D2" t="n">
-        <v>750.9686728075005</v>
+        <v>748.5466583985636</v>
       </c>
       <c r="E2" t="n">
-        <v>763.1986083984375</v>
+        <v>749.5234375</v>
       </c>
       <c r="F2" t="n">
-        <v>10999000</v>
+        <v>12478300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>762.6304417530438</v>
+        <v>752.1847098305358</v>
       </c>
       <c r="C3" t="n">
-        <v>763.1985869501963</v>
+        <v>754.6266574243845</v>
       </c>
       <c r="D3" t="n">
-        <v>748.5465974429485</v>
+        <v>745.9251963321232</v>
       </c>
       <c r="E3" t="n">
-        <v>749.5233764648438</v>
+        <v>748.4469604492188</v>
       </c>
       <c r="F3" t="n">
-        <v>12478300</v>
+        <v>7923300</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>752.1846484905694</v>
+        <v>746.2840677626042</v>
       </c>
       <c r="C4" t="n">
-        <v>754.6265958852796</v>
+        <v>755.0952164716484</v>
       </c>
       <c r="D4" t="n">
-        <v>745.9251355026145</v>
+        <v>741.3303327049176</v>
       </c>
       <c r="E4" t="n">
-        <v>748.4468994140625</v>
+        <v>753.1217041015625</v>
       </c>
       <c r="F4" t="n">
-        <v>7923300</v>
+        <v>8248600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>746.2840072815898</v>
+        <v>754.995481759339</v>
       </c>
       <c r="C5" t="n">
-        <v>755.095155276553</v>
+        <v>771.5412896866574</v>
       </c>
       <c r="D5" t="n">
-        <v>741.330272625368</v>
+        <v>749.5334031898147</v>
       </c>
       <c r="E5" t="n">
-        <v>753.1216430664062</v>
+        <v>762.201904296875</v>
       </c>
       <c r="F5" t="n">
-        <v>8248600</v>
+        <v>10533800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>754.9954213012545</v>
+        <v>764.4944012192615</v>
       </c>
       <c r="C6" t="n">
-        <v>771.5412279036273</v>
+        <v>778.8074760600178</v>
       </c>
       <c r="D6" t="n">
-        <v>749.5333431691193</v>
+        <v>762.6005837137456</v>
       </c>
       <c r="E6" t="n">
-        <v>762.2018432617188</v>
+        <v>776.4552001953125</v>
       </c>
       <c r="F6" t="n">
-        <v>10533800</v>
+        <v>11782500</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>764.494341124313</v>
+        <v>777.4419223006557</v>
       </c>
       <c r="C7" t="n">
-        <v>778.8074148399552</v>
+        <v>780.7311297077449</v>
       </c>
       <c r="D7" t="n">
-        <v>762.6005237676653</v>
+        <v>763.8066193659058</v>
       </c>
       <c r="E7" t="n">
-        <v>776.4551391601562</v>
+        <v>773.1858520507812</v>
       </c>
       <c r="F7" t="n">
-        <v>11782500</v>
+        <v>9400900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>777.4419223006557</v>
+        <v>778.1994163857863</v>
       </c>
       <c r="C8" t="n">
-        <v>780.7311297077449</v>
+        <v>786.2032128794</v>
       </c>
       <c r="D8" t="n">
-        <v>763.8066193659058</v>
+        <v>770.8335437165625</v>
       </c>
       <c r="E8" t="n">
-        <v>773.1858520507812</v>
+        <v>777.7010498046875</v>
       </c>
       <c r="F8" t="n">
-        <v>9400900</v>
+        <v>10955000</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>778.1994774600552</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C9" t="n">
-        <v>786.203274581819</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D9" t="n">
-        <v>770.8336042127465</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E9" t="n">
-        <v>777.7011108398438</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F9" t="n">
-        <v>10955000</v>
+        <v>23696800</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,25 +677,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>783.8508708699721</v>
+        <v>779.8218176027002</v>
       </c>
       <c r="C10" t="n">
-        <v>788.2165669565625</v>
+        <v>783.6917575585782</v>
       </c>
       <c r="D10" t="n">
-        <v>766.6771780735046</v>
+        <v>762.4868973227559</v>
       </c>
       <c r="E10" t="n">
-        <v>775.837158203125</v>
+        <v>763.1751098632812</v>
       </c>
       <c r="F10" t="n">
-        <v>23696800</v>
+        <v>11706900</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -703,25 +703,25 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>779.8217552362186</v>
+        <v>767.254476840496</v>
       </c>
       <c r="C11" t="n">
-        <v>783.6916948825968</v>
+        <v>768.6009504341728</v>
       </c>
       <c r="D11" t="n">
-        <v>762.4868363426395</v>
+        <v>749.1216451610411</v>
       </c>
       <c r="E11" t="n">
-        <v>763.175048828125</v>
+        <v>753.4404296875</v>
       </c>
       <c r="F11" t="n">
-        <v>11706900</v>
+        <v>10872600</v>
       </c>
       <c r="G11" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>767.254476840496</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C12" t="n">
-        <v>768.6009504341728</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D12" t="n">
-        <v>749.1216451610411</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E12" t="n">
-        <v>753.4404296875</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F12" t="n">
-        <v>10872600</v>
+        <v>8828200</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>755.5349916265823</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C13" t="n">
-        <v>759.1356124217834</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D13" t="n">
-        <v>750.5779133776451</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E13" t="n">
-        <v>758.686767578125</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F13" t="n">
-        <v>8828200</v>
+        <v>10591100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>751.4955472633491</v>
+        <v>748.0544043789391</v>
       </c>
       <c r="C14" t="n">
-        <v>754.806942419776</v>
+        <v>749.9793904076555</v>
       </c>
       <c r="D14" t="n">
-        <v>742.6186096970315</v>
+        <v>735.4371957410184</v>
       </c>
       <c r="E14" t="n">
-        <v>746.96728515625</v>
+        <v>741.8206176757812</v>
       </c>
       <c r="F14" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>748.0544659269957</v>
+        <v>746.777703342028</v>
       </c>
       <c r="C15" t="n">
-        <v>749.9794521140951</v>
+        <v>748.8324179023273</v>
       </c>
       <c r="D15" t="n">
-        <v>735.4372562509625</v>
+        <v>737.2325826153279</v>
       </c>
       <c r="E15" t="n">
-        <v>741.8206787109375</v>
+        <v>741.4715576171875</v>
       </c>
       <c r="F15" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>746.777703342028</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C16" t="n">
-        <v>748.8324179023273</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D16" t="n">
-        <v>737.2325826153279</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E16" t="n">
-        <v>741.4715576171875</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F16" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>740.3245554260684</v>
+        <v>719.6183236513255</v>
       </c>
       <c r="C17" t="n">
-        <v>741.0426584785586</v>
+        <v>719.9773751402398</v>
       </c>
       <c r="D17" t="n">
-        <v>724.4159185837501</v>
+        <v>708.357633728991</v>
       </c>
       <c r="E17" t="n">
-        <v>732.4749755859375</v>
+        <v>715.4791259765625</v>
       </c>
       <c r="F17" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>719.618385039583</v>
+        <v>720.7055653205383</v>
       </c>
       <c r="C18" t="n">
-        <v>719.9774365591268</v>
+        <v>725.8821043267139</v>
       </c>
       <c r="D18" t="n">
-        <v>708.3576941566364</v>
+        <v>716.2770807321521</v>
       </c>
       <c r="E18" t="n">
-        <v>715.4791870117188</v>
+        <v>725.1639404296875</v>
       </c>
       <c r="F18" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>720.7056259804448</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C19" t="n">
-        <v>725.8821654223162</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D19" t="n">
-        <v>716.2771410193245</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E19" t="n">
-        <v>725.1640014648438</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F19" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>727.7372737109582</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C20" t="n">
-        <v>729.1037149276121</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D20" t="n">
-        <v>708.3377167266436</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E20" t="n">
-        <v>708.7167358398438</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F20" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>703.3607165744016</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C21" t="n">
-        <v>715.0203947681905</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D21" t="n">
-        <v>688.718804278428</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E21" t="n">
-        <v>713.8035278320312</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F21" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>715.8581417735932</v>
+        <v>711.599278595462</v>
       </c>
       <c r="C22" t="n">
-        <v>716.6361476056489</v>
+        <v>717.7832075860277</v>
       </c>
       <c r="D22" t="n">
-        <v>703.9192222306009</v>
+        <v>705.9738944950672</v>
       </c>
       <c r="E22" t="n">
-        <v>711.230224609375</v>
+        <v>715.9779052734375</v>
       </c>
       <c r="F22" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>711.5993392573523</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C23" t="n">
-        <v>717.783268775081</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D23" t="n">
-        <v>705.9739546774089</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E23" t="n">
-        <v>715.9779663085938</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F23" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>716.416706057987</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C24" t="n">
-        <v>731.607177734375</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D24" t="n">
-        <v>710.5918290846139</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E24" t="n">
-        <v>731.607177734375</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F24" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>729.0239332852144</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C25" t="n">
-        <v>733.3626856542741</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D25" t="n">
-        <v>702.6824691715568</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E25" t="n">
-        <v>703.4703979492188</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F25" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>711.1603595995662</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C26" t="n">
-        <v>718.072374881022</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D26" t="n">
-        <v>705.8042950194317</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E26" t="n">
-        <v>713.8433837890625</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F26" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>705.9439682909708</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C27" t="n">
-        <v>713.6937706407739</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D27" t="n">
-        <v>697.5158763660478</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E27" t="n">
-        <v>706.8117065429688</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F27" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>715.1999404706222</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C28" t="n">
-        <v>722.0222242634773</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D28" t="n">
-        <v>707.6695373823591</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E28" t="n">
-        <v>715.6886596679688</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F28" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>715.6886043056783</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C29" t="n">
-        <v>723.6080097298942</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D29" t="n">
-        <v>702.0540824517458</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E29" t="n">
-        <v>710.2228393554688</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F29" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>705.2458014471516</v>
+        <v>719.3191931642514</v>
       </c>
       <c r="C30" t="n">
-        <v>716.6760344343375</v>
+        <v>731.8665769499745</v>
       </c>
       <c r="D30" t="n">
-        <v>704.2882698394852</v>
+        <v>718.3118034233538</v>
       </c>
       <c r="E30" t="n">
-        <v>715.0602416992188</v>
+        <v>730.2706909179688</v>
       </c>
       <c r="F30" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>719.3191330444083</v>
+        <v>734.1107251683979</v>
       </c>
       <c r="C31" t="n">
-        <v>731.866515781436</v>
+        <v>736.5842723709278</v>
       </c>
       <c r="D31" t="n">
-        <v>718.3117433877071</v>
+        <v>726.8595646449745</v>
       </c>
       <c r="E31" t="n">
-        <v>730.2706298828125</v>
+        <v>731.3678588867188</v>
       </c>
       <c r="F31" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>734.1107864324557</v>
+        <v>731.9264006052239</v>
       </c>
       <c r="C32" t="n">
-        <v>736.5843338414116</v>
+        <v>738.6787972623451</v>
       </c>
       <c r="D32" t="n">
-        <v>726.859625303898</v>
+        <v>722.1518348008319</v>
       </c>
       <c r="E32" t="n">
-        <v>731.367919921875</v>
+        <v>731.5074462890625</v>
       </c>
       <c r="F32" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>731.9264616753367</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C33" t="n">
-        <v>738.6788588958609</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D33" t="n">
-        <v>722.1518950553793</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E33" t="n">
-        <v>731.5075073242188</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F33" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>732.7941435868839</v>
+        <v>734.8787064697904</v>
       </c>
       <c r="C34" t="n">
-        <v>740.4841042897723</v>
+        <v>739.2872845910176</v>
       </c>
       <c r="D34" t="n">
-        <v>731.1982575844598</v>
+        <v>729.253383189777</v>
       </c>
       <c r="E34" t="n">
-        <v>732.095947265625</v>
+        <v>736.4446411132812</v>
       </c>
       <c r="F34" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>734.8787064697904</v>
+        <v>747.7850542762595</v>
       </c>
       <c r="C35" t="n">
-        <v>739.2872845910176</v>
+        <v>753.7894568601143</v>
       </c>
       <c r="D35" t="n">
-        <v>729.253383189777</v>
+        <v>746.0695454676272</v>
       </c>
       <c r="E35" t="n">
-        <v>736.4446411132812</v>
+        <v>748.8722534179688</v>
       </c>
       <c r="F35" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>747.7851152228061</v>
+        <v>750.6776381609803</v>
       </c>
       <c r="C36" t="n">
-        <v>753.7895182960361</v>
+        <v>756.4326899204912</v>
       </c>
       <c r="D36" t="n">
-        <v>746.069606274355</v>
+        <v>743.5860965317024</v>
       </c>
       <c r="E36" t="n">
-        <v>748.872314453125</v>
+        <v>749.49072265625</v>
       </c>
       <c r="F36" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>750.677577029167</v>
+        <v>752.7921200604676</v>
       </c>
       <c r="C37" t="n">
-        <v>756.4326283200122</v>
+        <v>757.1906533932021</v>
       </c>
       <c r="D37" t="n">
-        <v>743.5860359773924</v>
+        <v>740.5838813084906</v>
       </c>
       <c r="E37" t="n">
-        <v>749.4906616210938</v>
+        <v>749.7200927734375</v>
       </c>
       <c r="F37" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>752.7921200604676</v>
+        <v>667.4142515632169</v>
       </c>
       <c r="C38" t="n">
-        <v>757.1906533932021</v>
+        <v>679.1936140289573</v>
       </c>
       <c r="D38" t="n">
-        <v>740.5838813084906</v>
+        <v>648.4834442213796</v>
       </c>
       <c r="E38" t="n">
-        <v>749.7200927734375</v>
+        <v>664.7411499023438</v>
       </c>
       <c r="F38" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>667.414190282622</v>
+        <v>672.7602632515434</v>
       </c>
       <c r="C39" t="n">
-        <v>679.1935516668058</v>
+        <v>673.1392823636344</v>
       </c>
       <c r="D39" t="n">
-        <v>648.4833846789722</v>
+        <v>643.8953340746643</v>
       </c>
       <c r="E39" t="n">
-        <v>664.7410888671875</v>
+        <v>646.6680908203125</v>
       </c>
       <c r="F39" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>672.7603267493847</v>
+        <v>654.298319497033</v>
       </c>
       <c r="C40" t="n">
-        <v>673.139345897249</v>
+        <v>657.6196984387726</v>
       </c>
       <c r="D40" t="n">
-        <v>643.8953948481166</v>
+        <v>634.5297257704245</v>
       </c>
       <c r="E40" t="n">
-        <v>646.6681518554688</v>
+        <v>636.0557861328125</v>
       </c>
       <c r="F40" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>654.298319497033</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C41" t="n">
-        <v>657.6196984387726</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D41" t="n">
-        <v>634.5297257704245</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E41" t="n">
-        <v>636.0557861328125</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F41" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>626.4107910285981</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C42" t="n">
-        <v>640.0752642850032</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D42" t="n">
-        <v>624.3860886703497</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E42" t="n">
-        <v>625.6926879882812</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F42" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>630.6697208898194</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C43" t="n">
-        <v>640.5639703518489</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D43" t="n">
-        <v>624.9146693781357</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E43" t="n">
-        <v>634.30029296875</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F43" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>634.2005186436334</v>
+        <v>614.8907386759073</v>
       </c>
       <c r="C44" t="n">
-        <v>634.3501538797125</v>
+        <v>620.5161224262619</v>
       </c>
       <c r="D44" t="n">
-        <v>616.3968476378337</v>
+        <v>599.6404247494841</v>
       </c>
       <c r="E44" t="n">
-        <v>617.3344116210938</v>
+        <v>620.0972290039062</v>
       </c>
       <c r="F44" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>614.8907991985972</v>
+        <v>629.4529708548182</v>
       </c>
       <c r="C45" t="n">
-        <v>620.516183502649</v>
+        <v>633.3528014765299</v>
       </c>
       <c r="D45" t="n">
-        <v>599.6404837711106</v>
+        <v>616.5065997528014</v>
       </c>
       <c r="E45" t="n">
-        <v>620.0972900390625</v>
+        <v>630.1212158203125</v>
       </c>
       <c r="F45" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>629.4529098843899</v>
+        <v>626.3709656116134</v>
       </c>
       <c r="C46" t="n">
-        <v>633.3527401283538</v>
+        <v>627.9269165306073</v>
       </c>
       <c r="D46" t="n">
-        <v>616.5065400363918</v>
+        <v>617.7833145947981</v>
       </c>
       <c r="E46" t="n">
-        <v>630.1211547851562</v>
+        <v>625.453369140625</v>
       </c>
       <c r="F46" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>626.3709044869131</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C47" t="n">
-        <v>627.9268552540688</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D47" t="n">
-        <v>617.7832543081277</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E47" t="n">
-        <v>625.4533081054688</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F47" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>626.5005716840028</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C48" t="n">
-        <v>627.3583261459861</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D48" t="n">
-        <v>606.1934022078184</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E48" t="n">
-        <v>607.43017578125</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F48" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>611.4796659420805</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C49" t="n">
-        <v>616.0478021853295</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D49" t="n">
-        <v>601.4357808374693</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E49" t="n">
-        <v>608.3079223632812</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F49" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>600.2288811530552</v>
+        <v>607.4600346656293</v>
       </c>
       <c r="C50" t="n">
-        <v>612.088052043071</v>
+        <v>610.1031845088386</v>
       </c>
       <c r="D50" t="n">
-        <v>593.6560102918138</v>
+        <v>593.8554651895852</v>
       </c>
       <c r="E50" t="n">
-        <v>607.8790283203125</v>
+        <v>600.4483032226562</v>
       </c>
       <c r="F50" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>607.4600346656293</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C51" t="n">
-        <v>610.1031845088386</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D51" t="n">
-        <v>593.8554651895852</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E51" t="n">
-        <v>600.4483032226562</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F51" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>590.065358149623</v>
+        <v>592.1797786556917</v>
       </c>
       <c r="C52" t="n">
-        <v>602.0940719298206</v>
+        <v>593.7856483585136</v>
       </c>
       <c r="D52" t="n">
-        <v>582.2656968950795</v>
+        <v>579.7421567881397</v>
       </c>
       <c r="E52" t="n">
-        <v>596.1395874023438</v>
+        <v>588.7886352539062</v>
       </c>
       <c r="F52" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>592.1798400423816</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C53" t="n">
-        <v>593.7857099116716</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D53" t="n">
-        <v>579.7422168855177</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E53" t="n">
-        <v>588.7886962890625</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F53" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>601.9344542639864</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C54" t="n">
-        <v>605.1460720070379</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D54" t="n">
-        <v>581.8367012414765</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E54" t="n">
-        <v>587.6217041015625</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F54" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>586.9734117815261</v>
+        <v>597.1668722231478</v>
       </c>
       <c r="C55" t="n">
-        <v>596.5684523172222</v>
+        <v>615.1002729325323</v>
       </c>
       <c r="D55" t="n">
-        <v>580.3506215479276</v>
+        <v>596.0797338085368</v>
       </c>
       <c r="E55" t="n">
-        <v>592.70849609375</v>
+        <v>611.459716796875</v>
       </c>
       <c r="F55" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>597.1668722231478</v>
+        <v>622.3812488080194</v>
       </c>
       <c r="C56" t="n">
-        <v>615.1002729325323</v>
+        <v>635.3973829418613</v>
       </c>
       <c r="D56" t="n">
-        <v>596.0797338085368</v>
+        <v>616.6960233021972</v>
       </c>
       <c r="E56" t="n">
-        <v>611.459716796875</v>
+        <v>634.5695190429688</v>
       </c>
       <c r="F56" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>622.3812488080194</v>
+        <v>636.0358029520913</v>
       </c>
       <c r="C57" t="n">
-        <v>635.3973829418613</v>
+        <v>636.7040478933542</v>
       </c>
       <c r="D57" t="n">
-        <v>616.6960233021972</v>
+        <v>629.9915253276793</v>
       </c>
       <c r="E57" t="n">
-        <v>634.5695190429688</v>
+        <v>631.9663696289062</v>
       </c>
       <c r="F57" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>636.0357415239101</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C58" t="n">
-        <v>636.7039864006342</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D58" t="n">
-        <v>629.9914644832529</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E58" t="n">
-        <v>631.96630859375</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F58" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>634.4299618769652</v>
+        <v>637.8909364271796</v>
       </c>
       <c r="C59" t="n">
-        <v>646.3688812783262</v>
+        <v>643.6459879981971</v>
       </c>
       <c r="D59" t="n">
-        <v>633.8514494094911</v>
+        <v>636.1056017671217</v>
       </c>
       <c r="E59" t="n">
-        <v>646.2691650390625</v>
+        <v>639.20751953125</v>
       </c>
       <c r="F59" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>637.8908755177382</v>
+        <v>640.6737247939117</v>
       </c>
       <c r="C60" t="n">
-        <v>643.6459265392308</v>
+        <v>646.1893476978298</v>
       </c>
       <c r="D60" t="n">
-        <v>636.1055410281542</v>
+        <v>636.4147821721649</v>
       </c>
       <c r="E60" t="n">
-        <v>639.2074584960938</v>
+        <v>645.4213256835938</v>
       </c>
       <c r="F60" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>640.6737247939117</v>
+        <v>642.7383158920676</v>
       </c>
       <c r="C61" t="n">
-        <v>646.1893476978298</v>
+        <v>647.1668005690203</v>
       </c>
       <c r="D61" t="n">
-        <v>636.4147821721649</v>
+        <v>635.8961259576193</v>
       </c>
       <c r="E61" t="n">
-        <v>645.4213256835938</v>
+        <v>637.9407958984375</v>
       </c>
       <c r="F61" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>642.7383158920676</v>
+        <v>674.246461597851</v>
       </c>
       <c r="C62" t="n">
-        <v>647.1668005690203</v>
+        <v>674.3461778479464</v>
       </c>
       <c r="D62" t="n">
-        <v>635.8961259576193</v>
+        <v>658.3378235904052</v>
       </c>
       <c r="E62" t="n">
-        <v>637.9407958984375</v>
+        <v>659.8140258789062</v>
       </c>
       <c r="F62" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>674.2463992276428</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C63" t="n">
-        <v>674.3461154685141</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D63" t="n">
-        <v>658.3377626918029</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E63" t="n">
-        <v>659.81396484375</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F63" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>662.2775487290173</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C64" t="n">
-        <v>672.9398207362489</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D64" t="n">
-        <v>660.6717397649775</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E64" t="n">
-        <v>671.673095703125</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F64" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>667.603701448277</v>
+        <v>662.0481917138827</v>
       </c>
       <c r="C65" t="n">
-        <v>674.9545781663558</v>
+        <v>662.7563110037405</v>
       </c>
       <c r="D65" t="n">
-        <v>663.344758713728</v>
+        <v>651.645254570885</v>
       </c>
       <c r="E65" t="n">
-        <v>665.0702514648438</v>
+        <v>655.255859375</v>
       </c>
       <c r="F65" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>662.0481300460407</v>
+        <v>648.2639556943986</v>
       </c>
       <c r="C66" t="n">
-        <v>662.7562492699393</v>
+        <v>652.8121240146866</v>
       </c>
       <c r="D66" t="n">
-        <v>651.6451938720459</v>
+        <v>641.730959438269</v>
       </c>
       <c r="E66" t="n">
-        <v>655.2557983398438</v>
+        <v>648.4434814453125</v>
       </c>
       <c r="F66" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>648.2640167126568</v>
+        <v>641.6211778682233</v>
       </c>
       <c r="C67" t="n">
-        <v>652.812185461044</v>
+        <v>653.5801249698833</v>
       </c>
       <c r="D67" t="n">
-        <v>641.7310198416047</v>
+        <v>639.1376470786419</v>
       </c>
       <c r="E67" t="n">
-        <v>648.4435424804688</v>
+        <v>651.0167846679688</v>
       </c>
       <c r="F67" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>641.6212380225077</v>
+        <v>648.1143965293088</v>
       </c>
       <c r="C68" t="n">
-        <v>653.5801862453618</v>
+        <v>709.1556549538686</v>
       </c>
       <c r="D68" t="n">
-        <v>639.1377070000864</v>
+        <v>636.9534211280841</v>
       </c>
       <c r="E68" t="n">
-        <v>651.016845703125</v>
+        <v>642.558837890625</v>
       </c>
       <c r="F68" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>648.1143349664432</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C69" t="n">
-        <v>709.1555875928369</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D69" t="n">
-        <v>636.9533606253732</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E69" t="n">
-        <v>642.5587768554688</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F69" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,25 +2237,25 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>644.5502809809109</v>
+        <v>642.3541999133257</v>
       </c>
       <c r="C70" t="n">
-        <v>651.8372704406642</v>
+        <v>661.3602758295988</v>
       </c>
       <c r="D70" t="n">
-        <v>637.5627451568915</v>
+        <v>642.054746271156</v>
       </c>
       <c r="E70" t="n">
-        <v>646.3570556640625</v>
+        <v>655.9799194335938</v>
       </c>
       <c r="F70" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G70" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>642.3541401459643</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C71" t="n">
-        <v>661.3602142938313</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D71" t="n">
-        <v>642.054686531657</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E71" t="n">
-        <v>655.9798583984375</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F71" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>654.4426118233187</v>
+        <v>655.8600753372949</v>
       </c>
       <c r="C72" t="n">
-        <v>660.0526000253047</v>
+        <v>669.3659511843067</v>
       </c>
       <c r="D72" t="n">
-        <v>648.0440522221027</v>
+        <v>655.2910830082761</v>
       </c>
       <c r="E72" t="n">
-        <v>648.343505859375</v>
+        <v>663.266845703125</v>
       </c>
       <c r="F72" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>655.8601356908653</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C73" t="n">
-        <v>669.366012780715</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D73" t="n">
-        <v>655.2911433094866</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E73" t="n">
-        <v>663.2669067382812</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F73" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>665.2333263832898</v>
+        <v>660.4719008376494</v>
       </c>
       <c r="C74" t="n">
-        <v>669.8051880946751</v>
+        <v>672.3806511570199</v>
       </c>
       <c r="D74" t="n">
-        <v>657.0080086354003</v>
+        <v>655.4808037586267</v>
       </c>
       <c r="E74" t="n">
-        <v>657.5969848632812</v>
+        <v>660.3221435546875</v>
       </c>
       <c r="F74" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>660.4718397886508</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C75" t="n">
-        <v>672.380589007267</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D75" t="n">
-        <v>655.4807431709672</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E75" t="n">
-        <v>660.3220825195312</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F75" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>658.8746741689592</v>
+        <v>661.3503083186049</v>
       </c>
       <c r="C76" t="n">
-        <v>664.8140915262984</v>
+        <v>666.9902112020924</v>
       </c>
       <c r="D76" t="n">
-        <v>657.0778915122911</v>
+        <v>661.0208788671576</v>
       </c>
       <c r="E76" t="n">
-        <v>663.7559814453125</v>
+        <v>666.361328125</v>
       </c>
       <c r="F76" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>661.3503688947783</v>
+        <v>666.8704739599774</v>
       </c>
       <c r="C77" t="n">
-        <v>666.9902722948509</v>
+        <v>667.7589038803495</v>
       </c>
       <c r="D77" t="n">
-        <v>661.0209394131572</v>
+        <v>660.1424847097468</v>
       </c>
       <c r="E77" t="n">
-        <v>666.3613891601562</v>
+        <v>662.1089477539062</v>
       </c>
       <c r="F77" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>666.8704124858896</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C78" t="n">
-        <v>667.7588423243637</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D78" t="n">
-        <v>660.1424238558649</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E78" t="n">
-        <v>662.10888671875</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F78" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>656.8383689858442</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C79" t="n">
-        <v>659.0743707339258</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D79" t="n">
-        <v>653.2248195668056</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E79" t="n">
-        <v>657.5171508789062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F79" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>657.5171386037911</v>
+        <v>663.5662869980947</v>
       </c>
       <c r="C80" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8158418258488</v>
       </c>
       <c r="D80" t="n">
-        <v>656.6686764849229</v>
+        <v>658.2657448936569</v>
       </c>
       <c r="E80" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9146118164062</v>
       </c>
       <c r="F80" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>663.5663484641349</v>
+        <v>661.5499009554064</v>
       </c>
       <c r="C81" t="n">
-        <v>663.8159033150052</v>
+        <v>663.2069792218492</v>
       </c>
       <c r="D81" t="n">
-        <v>658.2658058687088</v>
+        <v>642.3541620430398</v>
       </c>
       <c r="E81" t="n">
-        <v>658.9146728515625</v>
+        <v>649.2518310546875</v>
       </c>
       <c r="F81" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>661.5499631466852</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C82" t="n">
-        <v>663.2070415689074</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D82" t="n">
-        <v>642.3542224297569</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E82" t="n">
-        <v>649.2518920898438</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F82" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>649.8508280292294</v>
+        <v>658.3955464147172</v>
       </c>
       <c r="C83" t="n">
-        <v>663.3567049684374</v>
+        <v>664.3349637543794</v>
       </c>
       <c r="D83" t="n">
-        <v>646.5966230035071</v>
+        <v>650.7392210314413</v>
       </c>
       <c r="E83" t="n">
-        <v>657.616943359375</v>
+        <v>659.4436645507812</v>
       </c>
       <c r="F83" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>658.3956073528642</v>
+        <v>654.4725487720359</v>
       </c>
       <c r="C84" t="n">
-        <v>664.3350252422523</v>
+        <v>657.9763084361789</v>
       </c>
       <c r="D84" t="n">
-        <v>650.7392812609531</v>
+        <v>643.6618161601232</v>
       </c>
       <c r="E84" t="n">
-        <v>659.4437255859375</v>
+        <v>647.534912109375</v>
       </c>
       <c r="F84" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>654.4726104611178</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C85" t="n">
-        <v>657.9763704555172</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D85" t="n">
-        <v>643.6618768302103</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E85" t="n">
-        <v>647.5349731445312</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F85" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>644.7299347572825</v>
+        <v>644.2907288447692</v>
       </c>
       <c r="C86" t="n">
-        <v>645.9477331499952</v>
+        <v>653.7838050409127</v>
       </c>
       <c r="D86" t="n">
-        <v>634.5879917891143</v>
+        <v>641.7053138036724</v>
       </c>
       <c r="E86" t="n">
-        <v>644.9096069335938</v>
+        <v>651.8971557617188</v>
       </c>
       <c r="F86" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>644.2906685217797</v>
+        <v>651.3680980277007</v>
       </c>
       <c r="C87" t="n">
-        <v>653.7837438291153</v>
+        <v>652.8054753941815</v>
       </c>
       <c r="D87" t="n">
-        <v>641.7052537227476</v>
+        <v>640.0881706951194</v>
       </c>
       <c r="E87" t="n">
-        <v>651.8970947265625</v>
+        <v>640.8268432617188</v>
       </c>
       <c r="F87" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>651.3681600668523</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C88" t="n">
-        <v>652.8055375702352</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D88" t="n">
-        <v>640.0882316599212</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E88" t="n">
-        <v>640.826904296875</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F88" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>641.1263941859123</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C89" t="n">
-        <v>641.1263941859123</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D89" t="n">
-        <v>622.9887038024194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E89" t="n">
-        <v>629.96630859375</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F89" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>625.3844405077801</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C90" t="n">
-        <v>627.3309804807691</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D90" t="n">
-        <v>613.7252454803604</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E90" t="n">
-        <v>614.4240112304688</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F90" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>617.378703801015</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C91" t="n">
-        <v>623.0585745209008</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D91" t="n">
-        <v>613.1362714280776</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E91" t="n">
-        <v>619.694580078125</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F91" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>623.0685636897582</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C92" t="n">
-        <v>627.9598630097294</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D92" t="n">
-        <v>618.9758886129073</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E92" t="n">
-        <v>619.1455688476562</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F92" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>606.7976262932837</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C93" t="n">
-        <v>610.3113781504126</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D93" t="n">
-        <v>598.9316523845154</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E93" t="n">
-        <v>603.0443115234375</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F93" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>605.659634898437</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C94" t="n">
-        <v>617.169133937088</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D94" t="n">
-        <v>599.0115204374271</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E94" t="n">
-        <v>611.8685913085938</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F94" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>628.2293275614567</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C95" t="n">
-        <v>659.3937675491238</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D95" t="n">
-        <v>625.4343255489129</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E95" t="n">
-        <v>646.476806640625</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F95" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>643.6219561683764</v>
+        <v>663.9456136216552</v>
       </c>
       <c r="C96" t="n">
-        <v>665.3032527677875</v>
+        <v>674.0775639748149</v>
       </c>
       <c r="D96" t="n">
-        <v>643.3025186421843</v>
+        <v>660.1124246688775</v>
       </c>
       <c r="E96" t="n">
-        <v>657.5870361328125</v>
+        <v>671.1627197265625</v>
       </c>
       <c r="F96" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>663.9456740004919</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C97" t="n">
-        <v>674.0776252750454</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D97" t="n">
-        <v>660.1124846991261</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E97" t="n">
-        <v>671.1627807617188</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F97" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>673.3888389297905</v>
+        <v>673.2989295276801</v>
       </c>
       <c r="C98" t="n">
-        <v>675.6148486525956</v>
+        <v>676.4732596455591</v>
       </c>
       <c r="D98" t="n">
-        <v>663.4764668627315</v>
+        <v>664.9138628916613</v>
       </c>
       <c r="E98" t="n">
-        <v>671.7716674804688</v>
+        <v>667.5391845703125</v>
       </c>
       <c r="F98" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>673.2989910894674</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C99" t="n">
-        <v>676.4733214975852</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D99" t="n">
-        <v>664.9139236867763</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E99" t="n">
-        <v>667.5392456054688</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F99" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>736.1169233837337</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C100" t="n">
-        <v>742.6752321400184</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D100" t="n">
-        <v>711.2812198864386</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E100" t="n">
-        <v>736.995361328125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F100" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>726.2045952530067</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C101" t="n">
-        <v>730.8662626744616</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D101" t="n">
-        <v>712.3193905555435</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E101" t="n">
-        <v>715.2241821289062</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F101" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>713.3275184694113</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C102" t="n">
-        <v>720.0156002559207</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D102" t="n">
-        <v>702.2672920108814</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E102" t="n">
-        <v>705.152099609375</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F102" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>706.1104025957663</v>
+        <v>686.5054510943589</v>
       </c>
       <c r="C103" t="n">
-        <v>715.7232596178901</v>
+        <v>687.6035290584308</v>
       </c>
       <c r="D103" t="n">
-        <v>685.1877035052055</v>
+        <v>666.2715840299333</v>
       </c>
       <c r="E103" t="n">
-        <v>690.4683227539062</v>
+        <v>667.798828125</v>
       </c>
       <c r="F103" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>686.5053883494637</v>
+        <v>662.3984629374214</v>
       </c>
       <c r="C104" t="n">
-        <v>687.603466213174</v>
+        <v>680.2865379695924</v>
       </c>
       <c r="D104" t="n">
-        <v>666.2715231343633</v>
+        <v>652.3363940764909</v>
       </c>
       <c r="E104" t="n">
-        <v>667.7987670898438</v>
+        <v>669.0166625976562</v>
       </c>
       <c r="F104" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>662.3984025060512</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C105" t="n">
-        <v>680.2864759062725</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D105" t="n">
-        <v>652.3363345630947</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E105" t="n">
-        <v>669.0166015625</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F105" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>664.3050190645899</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C106" t="n">
-        <v>670.7934451675868</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D106" t="n">
-        <v>645.3488423980709</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E106" t="n">
-        <v>660.2822265625</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F106" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>661.9991209626965</v>
+        <v>676.39338857878</v>
       </c>
       <c r="C107" t="n">
-        <v>682.0932819515241</v>
+        <v>679.4380062536881</v>
       </c>
       <c r="D107" t="n">
-        <v>657.6069922476072</v>
+        <v>668.5972981068446</v>
       </c>
       <c r="E107" t="n">
-        <v>676.0140991210938</v>
+        <v>669.525634765625</v>
       </c>
       <c r="F107" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>676.3934502400131</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C108" t="n">
-        <v>679.4380681924739</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D108" t="n">
-        <v>668.597359057372</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E108" t="n">
-        <v>669.5256958007812</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F108" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>672.7998711552045</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C109" t="n">
-        <v>678.0605068549233</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D109" t="n">
-        <v>655.9299390360635</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E109" t="n">
-        <v>667.4993286132812</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F109" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>668.7770306530766</v>
+        <v>643.9512634857649</v>
       </c>
       <c r="C110" t="n">
-        <v>674.7963229561075</v>
+        <v>650.2700088851722</v>
       </c>
       <c r="D110" t="n">
-        <v>644.1310518439949</v>
+        <v>633.4400456540794</v>
       </c>
       <c r="E110" t="n">
-        <v>648.6529541015625</v>
+        <v>638.6307983398438</v>
       </c>
       <c r="F110" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>643.9513250294082</v>
+        <v>638.3613203754355</v>
       </c>
       <c r="C111" t="n">
-        <v>650.2700710327099</v>
+        <v>641.4557762130754</v>
       </c>
       <c r="D111" t="n">
-        <v>633.4401061931457</v>
+        <v>627.6803603746322</v>
       </c>
       <c r="E111" t="n">
-        <v>638.630859375</v>
+        <v>638.1516723632812</v>
       </c>
       <c r="F111" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>638.3612593202278</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C112" t="n">
-        <v>641.4557148619026</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D112" t="n">
-        <v>627.6803003409905</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E112" t="n">
-        <v>638.151611328125</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F112" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>632.67143641335</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C113" t="n">
-        <v>643.8515057528024</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D113" t="n">
-        <v>627.0315334227189</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E113" t="n">
-        <v>642.0746459960938</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F113" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>637.432932921519</v>
+        <v>638.5510179511008</v>
       </c>
       <c r="C114" t="n">
-        <v>646.0375787806976</v>
+        <v>662.1688639053526</v>
       </c>
       <c r="D114" t="n">
-        <v>635.5861905818066</v>
+        <v>637.642665037141</v>
       </c>
       <c r="E114" t="n">
-        <v>643.6318969726562</v>
+        <v>654.4925537109375</v>
       </c>
       <c r="F114" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>638.5509584025834</v>
+        <v>651.3781101885919</v>
       </c>
       <c r="C115" t="n">
-        <v>662.1688021543367</v>
+        <v>656.5289567660449</v>
       </c>
       <c r="D115" t="n">
-        <v>637.6426055733327</v>
+        <v>634.8675821094057</v>
       </c>
       <c r="E115" t="n">
-        <v>654.4924926757812</v>
+        <v>636.1153564453125</v>
       </c>
       <c r="F115" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>651.3780476889771</v>
+        <v>631.9527863953055</v>
       </c>
       <c r="C116" t="n">
-        <v>656.5288937722072</v>
+        <v>639.9684568961466</v>
       </c>
       <c r="D116" t="n">
-        <v>634.8675211939732</v>
+        <v>627.8600500948714</v>
       </c>
       <c r="E116" t="n">
-        <v>636.1152954101562</v>
+        <v>638.1616821289062</v>
       </c>
       <c r="F116" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>631.9527259539814</v>
+        <v>641.3858999809694</v>
       </c>
       <c r="C117" t="n">
-        <v>639.9683956881865</v>
+        <v>652.7156650876909</v>
       </c>
       <c r="D117" t="n">
-        <v>627.8599900449855</v>
+        <v>640.9965798171046</v>
       </c>
       <c r="E117" t="n">
-        <v>638.16162109375</v>
+        <v>652.5260009765625</v>
       </c>
       <c r="F117" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>641.3859599741169</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C118" t="n">
-        <v>652.7157261405878</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D118" t="n">
-        <v>640.9966397738364</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E118" t="n">
-        <v>652.5260620117188</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F118" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>649.3916295582877</v>
+        <v>642.3042597917192</v>
       </c>
       <c r="C119" t="n">
-        <v>659.823034651462</v>
+        <v>648.2835840137412</v>
       </c>
       <c r="D119" t="n">
-        <v>646.3470725216666</v>
+        <v>636.9837335400734</v>
       </c>
       <c r="E119" t="n">
-        <v>655.8401489257812</v>
+        <v>647.0258178710938</v>
       </c>
       <c r="F119" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>642.3043203814821</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C120" t="n">
-        <v>648.2836451675449</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D120" t="n">
-        <v>636.9837936279411</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E120" t="n">
-        <v>647.02587890625</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F120" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>636.0254184162494</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C121" t="n">
-        <v>658.764884603327</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D121" t="n">
-        <v>633.3701817354564</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E121" t="n">
-        <v>652.396240234375</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F121" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>647.1356255764312</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C122" t="n">
-        <v>657.866484005116</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D122" t="n">
-        <v>637.7025010942567</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E122" t="n">
-        <v>653.91357421875</v>
+        <v>666.541015625</v>
       </c>
       <c r="F122" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>656.7884535878291</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C123" t="n">
-        <v>671.5720803574089</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D123" t="n">
-        <v>656.4989309709863</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E123" t="n">
-        <v>666.541015625</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F123" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>660.751362594833</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C124" t="n">
-        <v>669.5057662619517</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D124" t="n">
-        <v>649.1520579976961</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E124" t="n">
-        <v>659.393798828125</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F124" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>646.7463568472266</v>
+        <v>633.6497121926325</v>
       </c>
       <c r="C125" t="n">
-        <v>648.3135076492586</v>
+        <v>646.5965879982328</v>
       </c>
       <c r="D125" t="n">
-        <v>634.9773114336934</v>
+        <v>625.6639573427893</v>
       </c>
       <c r="E125" t="n">
-        <v>643.7117309570312</v>
+        <v>646.2372436523438</v>
       </c>
       <c r="F125" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>633.6497720389343</v>
+        <v>652.3962938458964</v>
       </c>
       <c r="C126" t="n">
-        <v>646.596649067328</v>
+        <v>659.1242831137364</v>
       </c>
       <c r="D126" t="n">
-        <v>625.6640164348609</v>
+        <v>647.8444156429986</v>
       </c>
       <c r="E126" t="n">
-        <v>646.2373046875</v>
+        <v>652.9053955078125</v>
       </c>
       <c r="F126" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>652.3962328583322</v>
+        <v>653.5941721528687</v>
       </c>
       <c r="C127" t="n">
-        <v>659.1242214972237</v>
+        <v>657.9463943013674</v>
       </c>
       <c r="D127" t="n">
-        <v>647.8443550809549</v>
+        <v>647.2055433479961</v>
       </c>
       <c r="E127" t="n">
-        <v>652.9053344726562</v>
+        <v>653.6939697265625</v>
       </c>
       <c r="F127" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>653.5941111270305</v>
+        <v>647.5948883988538</v>
       </c>
       <c r="C128" t="n">
-        <v>657.9463328691638</v>
+        <v>652.3364309343367</v>
       </c>
       <c r="D128" t="n">
-        <v>647.2054829186618</v>
+        <v>635.7660119177681</v>
       </c>
       <c r="E128" t="n">
-        <v>653.6939086914062</v>
+        <v>637.043701171875</v>
       </c>
       <c r="F128" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>647.5948263527883</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C129" t="n">
-        <v>652.336368433984</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D129" t="n">
-        <v>635.7659510050273</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E129" t="n">
-        <v>637.0436401367188</v>
+        <v>612.6171875</v>
       </c>
       <c r="F129" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,25 +3797,25 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>622.7790526456299</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C130" t="n">
-        <v>628.0496188589474</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D130" t="n">
-        <v>608.4645611002024</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E130" t="n">
-        <v>612.6171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F130" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>631.4147932406764</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C131" t="n">
-        <v>634.1622468505053</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D131" t="n">
-        <v>622.5230098937741</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E131" t="n">
-        <v>626.8690185546875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F131" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G131" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>627.4085169382369</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C132" t="n">
-        <v>635.9605885584036</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D132" t="n">
-        <v>621.1243629754691</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E132" t="n">
-        <v>622.0834350585938</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F132" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>615.7693473594539</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C133" t="n">
-        <v>622.0735023862151</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D133" t="n">
-        <v>614.04090772979</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E133" t="n">
-        <v>615.1099243164062</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F133" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>611.5832104537112</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C134" t="n">
-        <v>612.4323990135786</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D134" t="n">
-        <v>601.7023533616688</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E134" t="n">
-        <v>606.1382446289062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F134" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>602.9712077810872</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C135" t="n">
-        <v>603.400802317344</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D135" t="n">
-        <v>586.7062525156723</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E135" t="n">
-        <v>593.1102905273438</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F135" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>605.2290499891692</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C136" t="n">
-        <v>608.0764476338709</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D136" t="n">
-        <v>598.4553596033379</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E136" t="n">
-        <v>603.5006713867188</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F136" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>598.5452420228083</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C137" t="n">
-        <v>600.443507118967</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D137" t="n">
-        <v>590.4527665679026</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E137" t="n">
-        <v>592.3709716796875</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F137" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>598.1855830392399</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C138" t="n">
-        <v>603.1110107561809</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D138" t="n">
-        <v>592.8505617950721</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E138" t="n">
-        <v>594.3391723632812</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F138" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>581.9506076701073</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C139" t="n">
-        <v>582.460145169462</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D139" t="n">
-        <v>542.8468364624507</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E139" t="n">
-        <v>547.032958984375</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F139" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>539.599843303006</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C140" t="n">
-        <v>543.0966023049141</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D140" t="n">
-        <v>519.7782492802263</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E140" t="n">
-        <v>525.233154296875</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F140" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>535.8833618164062</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C141" t="n">
-        <v>539.0504095872608</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D141" t="n">
-        <v>528.0505941707193</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E141" t="n">
-        <v>535.8833618164062</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F141" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>549.4707059552647</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C142" t="n">
-        <v>573.1587727471259</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D142" t="n">
-        <v>546.2637174010383</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E142" t="n">
-        <v>571.6002197265625</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F142" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>579.5928556215499</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C143" t="n">
-        <v>592.0013387220274</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D143" t="n">
-        <v>573.2887005646345</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E143" t="n">
-        <v>578.6936645507812</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F143" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>565.5158531822124</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C144" t="n">
-        <v>577.9643377947169</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D144" t="n">
-        <v>559.1817578546791</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E144" t="n">
-        <v>573.9281005859375</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F144" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>577.1550997330287</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C145" t="n">
-        <v>582.2503530791108</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D145" t="n">
-        <v>571.4703658572956</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E145" t="n">
-        <v>572.4894409179688</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F145" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>571.9498894780604</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C146" t="n">
-        <v>574.6973431004155</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D146" t="n">
-        <v>564.2370671243236</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E146" t="n">
-        <v>574.5175170898438</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F146" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>605.4388670235439</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C147" t="n">
-        <v>629.3667024291958</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D147" t="n">
-        <v>591.2820049792073</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E147" t="n">
-        <v>611.8529052734375</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F147" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>626.3894374266143</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C148" t="n">
-        <v>636.9097166035551</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D148" t="n">
-        <v>622.4231426572783</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E148" t="n">
-        <v>627.8081665039062</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F148" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>633.882449891805</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C149" t="n">
-        <v>637.9886903650855</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D149" t="n">
-        <v>623.7518859014353</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E149" t="n">
-        <v>629.2767333984375</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F149" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>628.9171329935918</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C150" t="n">
-        <v>634.4120404303904</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D150" t="n">
-        <v>623.8218795800174</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E150" t="n">
-        <v>633.9425048828125</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F150" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>642.624350345733</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C151" t="n">
-        <v>665.6430543798978</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D151" t="n">
-        <v>638.7779398291946</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E151" t="n">
-        <v>661.8765258789062</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F151" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>666.3824145357423</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C152" t="n">
-        <v>677.8717665104965</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D152" t="n">
-        <v>663.6049593103575</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E152" t="n">
-        <v>670.9581909179688</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F152" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>675.3640350842893</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C153" t="n">
-        <v>676.9525896021297</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D153" t="n">
-        <v>667.131674939706</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E153" t="n">
-        <v>676.2432250976562</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F153" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>677.9716157075654</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C154" t="n">
-        <v>690.8796961433965</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D154" t="n">
-        <v>674.5048580761284</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E154" t="n">
-        <v>687.9124145507812</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F154" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>680.7290935491282</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C155" t="n">
-        <v>682.7472426832454</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D155" t="n">
-        <v>667.381478611767</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E155" t="n">
-        <v>670.2887573242188</v>
+        <v>668.220703125</v>
       </c>
       <c r="F155" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>670.3786762058809</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C156" t="n">
-        <v>675.5738733736962</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D156" t="n">
-        <v>666.7120915784461</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E156" t="n">
-        <v>668.220703125</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F156" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>673.7355628200382</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C157" t="n">
-        <v>677.7518600207422</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D157" t="n">
-        <v>669.1298460769134</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E157" t="n">
-        <v>674.09521484375</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F157" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>663.0854475032797</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C158" t="n">
-        <v>668.9400066983026</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D158" t="n">
-        <v>652.4452846667049</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E158" t="n">
-        <v>658.5396728515625</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F158" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>659.7085674039201</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C159" t="n">
-        <v>680.0396994180859</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D159" t="n">
-        <v>653.2345872360809</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E159" t="n">
-        <v>674.4049682617188</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F159" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>670.3786986745525</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C160" t="n">
-        <v>681.8680504402118</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D160" t="n">
-        <v>670.2188736545023</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E160" t="n">
-        <v>677.9916381835938</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F160" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>673.6156618787633</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C161" t="n">
-        <v>677.5520159823654</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D161" t="n">
-        <v>665.0136491453696</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E161" t="n">
-        <v>670.7183837890625</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F161" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>668.2905997420939</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C162" t="n">
-        <v>673.6256820299297</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D162" t="n">
-        <v>663.1953464496755</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E162" t="n">
-        <v>668.5004272460938</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F162" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>618.7465567527638</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C163" t="n">
-        <v>620.2751083620838</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D163" t="n">
-        <v>599.4444385151393</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E163" t="n">
-        <v>611.3433837890625</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F163" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>614.120842749119</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C164" t="n">
-        <v>618.3069655430758</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D164" t="n">
-        <v>605.5487701514051</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E164" t="n">
-        <v>608.1863403320312</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F164" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>607.3771038685389</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C165" t="n">
-        <v>613.4314904063681</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D165" t="n">
-        <v>602.1919069095087</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E165" t="n">
-        <v>609.8447875976562</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F165" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>612.7420849871345</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C166" t="n">
-        <v>613.7811000159977</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D166" t="n">
-        <v>599.8040642277598</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E166" t="n">
-        <v>604.3998413085938</v>
+        <v>612.3125</v>
       </c>
       <c r="F166" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>600.4934370812971</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C167" t="n">
-        <v>619.3759607512419</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D167" t="n">
-        <v>597.5461564796674</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E167" t="n">
-        <v>612.3125</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F167" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>614.150739078972</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C168" t="n">
-        <v>624.4012480600104</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D168" t="n">
-        <v>612.9718390781961</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E168" t="n">
-        <v>616.2388305664062</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F168" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>614.6303402495529</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C169" t="n">
-        <v>616.1988937552933</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D169" t="n">
-        <v>605.4987892063378</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E169" t="n">
-        <v>609.0654907226562</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F169" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>604.010215830275</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C170" t="n">
-        <v>604.3498668649182</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D170" t="n">
-        <v>597.5262348938886</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E170" t="n">
-        <v>598.3054809570312</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F170" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>594.2692320029287</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C171" t="n">
-        <v>603.1909559259367</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D171" t="n">
-        <v>592.0512559095129</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E171" t="n">
-        <v>602.441650390625</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F171" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>598.275515544453</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C172" t="n">
-        <v>619.3260125714435</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D172" t="n">
-        <v>596.1074810052941</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E172" t="n">
-        <v>616.0590209960938</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F172" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>615.4296182023591</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C173" t="n">
-        <v>623.152441138389</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D173" t="n">
-        <v>614.4305441468357</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E173" t="n">
-        <v>617.8573608398438</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F173" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>613.421486859321</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C174" t="n">
-        <v>620.6248329546977</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D174" t="n">
-        <v>608.7458274653094</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E174" t="n">
-        <v>613.6612548828125</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F174" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>608.5459509764945</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C175" t="n">
-        <v>615.0199919776213</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D175" t="n">
-        <v>603.1309869574205</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E175" t="n">
-        <v>610.64404296875</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F175" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>608.3561568042173</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C176" t="n">
-        <v>613.361527578881</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D176" t="n">
-        <v>599.9939118379299</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E176" t="n">
-        <v>602.052001953125</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F176" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>600.2037495434126</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C177" t="n">
-        <v>607.4370360716302</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D177" t="n">
-        <v>597.2564688338498</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E177" t="n">
-        <v>604.499755859375</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F177" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>599.4443949814065</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C178" t="n">
-        <v>609.0354809096541</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D178" t="n">
-        <v>594.2591985256718</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E178" t="n">
-        <v>606.8175659179688</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F178" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>607.3171451453314</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C179" t="n">
-        <v>614.2407210713809</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D179" t="n">
-        <v>606.3880135859368</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E179" t="n">
-        <v>609.6949462890625</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F179" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>608.3261927003538</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C180" t="n">
-        <v>613.9009818092591</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D180" t="n">
-        <v>604.7394901495815</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E180" t="n">
-        <v>611.7730102539062</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F180" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>608.8357727220844</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C181" t="n">
-        <v>637.908804248614</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D181" t="n">
-        <v>608.4361186960156</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E181" t="n">
-        <v>634.6718139648438</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F181" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>638.9078448274123</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C182" t="n">
-        <v>642.4046039468743</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D182" t="n">
-        <v>628.7272779804616</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E182" t="n">
-        <v>634.7017211914062</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F182" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>632.9133899267435</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C183" t="n">
-        <v>633.9124639439917</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D183" t="n">
-        <v>622.7727642602187</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E183" t="n">
-        <v>631.92431640625</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F183" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>629.8162791560948</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C184" t="n">
-        <v>635.1613007084701</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D184" t="n">
-        <v>598.9748694014791</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E184" t="n">
-        <v>599.9139404296875</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F184" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>602.6813896226799</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C185" t="n">
-        <v>608.3161816139932</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D185" t="n">
-        <v>596.1274666259658</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E185" t="n">
-        <v>597.0765991210938</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F185" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>602.4416570391962</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C186" t="n">
-        <v>623.5720977596394</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D186" t="n">
-        <v>599.7142043737263</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E186" t="n">
-        <v>622.4031372070312</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F186" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>623.0924785224576</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C187" t="n">
-        <v>641.8051764288737</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D187" t="n">
-        <v>621.8536364911718</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E187" t="n">
-        <v>626.9888916015625</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F187" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>622.8827460758752</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C188" t="n">
-        <v>628.5674800138549</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D188" t="n">
-        <v>582.3702434655938</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E188" t="n">
-        <v>592.450927734375</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F188" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>591.4518261333767</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C189" t="n">
-        <v>591.4518261333767</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D189" t="n">
-        <v>578.6836307521693</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E189" t="n">
-        <v>584.8479614257812</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F189" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>590.4527436689563</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C190" t="n">
-        <v>597.0766092757164</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D190" t="n">
-        <v>580.4720040020986</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E190" t="n">
-        <v>584.0487060546875</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F190" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>580.192266144374</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C191" t="n">
-        <v>590.7724873942649</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D191" t="n">
-        <v>570.0716409197756</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E191" t="n">
-        <v>570.4512939453125</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F191" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>565.3060574843756</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C192" t="n">
-        <v>571.6401524850257</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D192" t="n">
-        <v>556.4942175026772</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E192" t="n">
-        <v>567.9036254882812</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F192" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,25 +5435,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>572.4194595335534</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C193" t="n">
-        <v>575.5365655300229</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D193" t="n">
-        <v>560.3806300495169</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E193" t="n">
-        <v>566.4549560546875</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F193" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G193" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5461,25 +5461,25 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>579.9000244140625</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C194" t="n">
-        <v>601.27001953125</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D194" t="n">
-        <v>579.2999877929688</v>
+        <v>592</v>
       </c>
       <c r="E194" t="n">
-        <v>593.47998046875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F194" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G194" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>593.6500244140625</v>
+        <v>592</v>
       </c>
       <c r="C195" t="n">
-        <v>605.8099975585938</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D195" t="n">
-        <v>592</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E195" t="n">
-        <v>600.2100219726562</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F195" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>592</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C196" t="n">
-        <v>593.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D196" t="n">
-        <v>566.1900024414062</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E196" t="n">
-        <v>567.5800170898438</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F196" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>572.8200073242188</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C197" t="n">
-        <v>580.219970703125</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D197" t="n">
-        <v>563.0999755859375</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E197" t="n">
-        <v>577.219970703125</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F197" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>572.02001953125</v>
+        <v>562.25</v>
       </c>
       <c r="C198" t="n">
-        <v>575.8099975585938</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D198" t="n">
-        <v>559.8099975585938</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E198" t="n">
-        <v>563.8499755859375</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F198" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>562.25</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C199" t="n">
-        <v>572.2000122070312</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D199" t="n">
-        <v>561.02001953125</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E199" t="n">
-        <v>562.2000122070312</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F199" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>561.8900146484375</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C200" t="n">
-        <v>569.0399780273438</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D200" t="n">
-        <v>555.5499877929688</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E200" t="n">
-        <v>557.6699829101562</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F200" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>555.5499877929688</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C201" t="n">
-        <v>556.3400268554688</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D201" t="n">
-        <v>540.1799926757812</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E201" t="n">
-        <v>542.8699951171875</v>
+        <v>550.25</v>
       </c>
       <c r="F201" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>543.3400268554688</v>
+        <v>560</v>
       </c>
       <c r="C202" t="n">
-        <v>556.8499755859375</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D202" t="n">
-        <v>540.4000244140625</v>
+        <v>558</v>
       </c>
       <c r="E202" t="n">
-        <v>550.25</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F202" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>560</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C203" t="n">
-        <v>570.9000244140625</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D203" t="n">
-        <v>558</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E203" t="n">
-        <v>562.5999755859375</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F203" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C204" t="n">
-        <v>565.5399780273438</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D204" t="n">
-        <v>551.4299926757812</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E204" t="n">
-        <v>563.2899780273438</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F204" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>607.9099731445312</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C205" t="n">
-        <v>628.280029296875</v>
+        <v>610</v>
       </c>
       <c r="D205" t="n">
-        <v>595.0999755859375</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E205" t="n">
-        <v>612.9099731445312</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F205" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>607.9000244140625</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C206" t="n">
-        <v>610</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D206" t="n">
-        <v>580.4199829101562</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E206" t="n">
-        <v>582.9000244140625</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F206" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>594.8400268554688</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C207" t="n">
-        <v>603.5800170898438</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D207" t="n">
-        <v>581.760009765625</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E207" t="n">
-        <v>600.2899780273438</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F207" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>607.5900268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C208" t="n">
-        <v>625.3699951171875</v>
+        <v>616</v>
       </c>
       <c r="D208" t="n">
-        <v>603.6599731445312</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E208" t="n">
-        <v>615.5800170898438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F208" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>614.3900146484375</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C209" t="n">
-        <v>616</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D209" t="n">
-        <v>598.010009765625</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E209" t="n">
-        <v>603.1199951171875</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F209" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>583.989990234375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C210" t="n">
-        <v>633.27001953125</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D210" t="n">
-        <v>577.0700073242188</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E210" t="n">
-        <v>631.47998046875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F210" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>660.3400268554688</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C211" t="n">
-        <v>677.8599853515625</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D211" t="n">
-        <v>658.010009765625</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E211" t="n">
-        <v>669.2100219726562</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F211" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>661.3800048828125</v>
+        <v>652</v>
       </c>
       <c r="C212" t="n">
-        <v>676.6199951171875</v>
+        <v>666.5</v>
       </c>
       <c r="D212" t="n">
-        <v>654.2000122070312</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E212" t="n">
-        <v>656.72998046875</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F212" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>652</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C213" t="n">
-        <v>666.5</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D213" t="n">
-        <v>649.0499877929688</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E213" t="n">
-        <v>661.0399780273438</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F213" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>663.5999755859375</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C214" t="n">
-        <v>686.0800170898438</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D214" t="n">
-        <v>656.6599731445312</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E214" t="n">
-        <v>681.3099975585938</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F214" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>677.280029296875</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C215" t="n">
-        <v>681.9000244140625</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D215" t="n">
-        <v>660.1599731445312</v>
+        <v>626</v>
       </c>
       <c r="E215" t="n">
-        <v>664.5399780273438</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F215" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>647.7000122070312</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C216" t="n">
-        <v>652.2000122070312</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D216" t="n">
-        <v>626</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E216" t="n">
-        <v>646.010009765625</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F216" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>646.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C217" t="n">
-        <v>653.2999877929688</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D217" t="n">
-        <v>636.010009765625</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E217" t="n">
-        <v>645.8499755859375</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F217" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>654.1799926757812</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C218" t="n">
-        <v>655.8800048828125</v>
+        <v>649</v>
       </c>
       <c r="D218" t="n">
-        <v>643.2000122070312</v>
+        <v>624</v>
       </c>
       <c r="E218" t="n">
-        <v>643.8099975585938</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F218" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>647.7000122070312</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C219" t="n">
-        <v>649</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D219" t="n">
-        <v>624</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E219" t="n">
-        <v>627.1699829101562</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F219" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>608.4099731445312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C220" t="n">
-        <v>614.6500244140625</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D220" t="n">
-        <v>597.219970703125</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E220" t="n">
-        <v>606.0999755859375</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F220" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>605.2999877929688</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C221" t="n">
-        <v>609.97998046875</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D221" t="n">
-        <v>594.4500122070312</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E221" t="n">
-        <v>595.1900024414062</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F221" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>607.219970703125</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C222" t="n">
-        <v>611.260009765625</v>
+        <v>601</v>
       </c>
       <c r="D222" t="n">
-        <v>593.1300048828125</v>
+        <v>587</v>
       </c>
       <c r="E222" t="n">
-        <v>593.8699951171875</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F222" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>596.8200073242188</v>
+        <v>593.25</v>
       </c>
       <c r="C223" t="n">
-        <v>601</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D223" t="n">
-        <v>587</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E223" t="n">
-        <v>593.4099731445312</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F223" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>593.25</v>
+        <v>526</v>
       </c>
       <c r="C224" t="n">
-        <v>599.969970703125</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D224" t="n">
-        <v>582.219970703125</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E224" t="n">
-        <v>585.6099853515625</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F224" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>526</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C225" t="n">
-        <v>539.8800048828125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D225" t="n">
-        <v>524.489990234375</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E225" t="n">
-        <v>539.030029296875</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F225" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>543.5999755859375</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C226" t="n">
-        <v>558.3300170898438</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D226" t="n">
-        <v>540.219970703125</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E226" t="n">
-        <v>556.7100219726562</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F226" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>562.239990234375</v>
+        <v>581.5</v>
       </c>
       <c r="C227" t="n">
-        <v>597.52001953125</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D227" t="n">
-        <v>559.3599853515625</v>
+        <v>578.25</v>
       </c>
       <c r="E227" t="n">
-        <v>590.239990234375</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F227" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>581.5</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C228" t="n">
-        <v>592.7899780273438</v>
+        <v>601</v>
       </c>
       <c r="D228" t="n">
-        <v>578.25</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E228" t="n">
-        <v>587.9400024414062</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F228" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>600.4600219726562</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C229" t="n">
-        <v>601</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D229" t="n">
-        <v>580.1199951171875</v>
+        <v>586</v>
       </c>
       <c r="E229" t="n">
-        <v>588.77001953125</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F229" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>586.9500122070312</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C230" t="n">
-        <v>595.3099975585938</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D230" t="n">
-        <v>586</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E230" t="n">
-        <v>589.9000244140625</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F230" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>585.6400146484375</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C231" t="n">
-        <v>598.739990234375</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D231" t="n">
-        <v>585.6199951171875</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E231" t="n">
-        <v>592.0999755859375</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F231" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>599.1300048828125</v>
+        <v>598</v>
       </c>
       <c r="C232" t="n">
-        <v>608.2100219726562</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D232" t="n">
-        <v>592.030029296875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E232" t="n">
-        <v>594.9199829101562</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F232" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>598</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C233" t="n">
-        <v>612.4299926757812</v>
+        <v>604.5</v>
       </c>
       <c r="D233" t="n">
-        <v>593.4000244140625</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E233" t="n">
-        <v>599.1199951171875</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F233" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>601.0700073242188</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C234" t="n">
-        <v>604.5</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D234" t="n">
-        <v>578.2100219726562</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E234" t="n">
-        <v>578.8499755859375</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F234" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>580.7100219726562</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C235" t="n">
-        <v>595.8499755859375</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D235" t="n">
-        <v>579.3900146484375</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E235" t="n">
-        <v>594.969970703125</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F235" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>596.97998046875</v>
+        <v>589.75</v>
       </c>
       <c r="C236" t="n">
-        <v>601.8599853515625</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D236" t="n">
-        <v>589.2899780273438</v>
+        <v>564.75</v>
       </c>
       <c r="E236" t="n">
-        <v>589.8499755859375</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F236" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>589.75</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C237" t="n">
-        <v>590.239990234375</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D237" t="n">
-        <v>564.75</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E237" t="n">
-        <v>568.969970703125</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F237" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>557.47998046875</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C238" t="n">
-        <v>560.6599731445312</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D238" t="n">
-        <v>543.2100219726562</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E238" t="n">
-        <v>543.6699829101562</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F238" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>541.3400268554688</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C239" t="n">
-        <v>554.0700073242188</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D239" t="n">
-        <v>537.27001953125</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E239" t="n">
-        <v>546.030029296875</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F239" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>546.9500122070312</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C240" t="n">
-        <v>549.989990234375</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D240" t="n">
-        <v>539.3099975585938</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E240" t="n">
-        <v>545.8300170898438</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F240" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>546.8900146484375</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C241" t="n">
-        <v>553.8699951171875</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D241" t="n">
-        <v>543.22998046875</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F241" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>550.2000122070312</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C242" t="n">
-        <v>561.4199829101562</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D242" t="n">
-        <v>546.2999877929688</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E242" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F242" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>563.8800048828125</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C243" t="n">
-        <v>570.7999877929688</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D243" t="n">
-        <v>561.4000244140625</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E243" t="n">
-        <v>570.0499877929688</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F243" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>590.3099975585938</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C244" t="n">
-        <v>593.3400268554688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D244" t="n">
-        <v>561.8800048828125</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E244" t="n">
-        <v>576.1400146484375</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F244" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>576.47998046875</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C245" t="n">
-        <v>588.3900146484375</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D245" t="n">
-        <v>567.6199951171875</v>
+        <v>571</v>
       </c>
       <c r="E245" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F245" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>571.5499877929688</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C246" t="n">
-        <v>589.1900024414062</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D246" t="n">
-        <v>571</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E246" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F246" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>577.6300048828125</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C247" t="n">
-        <v>578.6799926757812</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D247" t="n">
-        <v>569.1400146484375</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E247" t="n">
-        <v>572.3400268554688</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F247" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>558.3499755859375</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C248" t="n">
-        <v>584.9500122070312</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D248" t="n">
-        <v>556.0999755859375</v>
+        <v>577</v>
       </c>
       <c r="E248" t="n">
-        <v>578.5399780273438</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F248" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>578.7899780273438</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C249" t="n">
-        <v>600.3800048828125</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D249" t="n">
-        <v>577</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E249" t="n">
-        <v>592.8499755859375</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F249" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>604.489990234375</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C250" t="n">
-        <v>619.4600219726562</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D250" t="n">
-        <v>604.3499755859375</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E250" t="n">
-        <v>610.6799926757812</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F250" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>612.3499755859375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C251" t="n">
-        <v>617.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D251" t="n">
-        <v>605.27001953125</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E251" t="n">
-        <v>616.77001953125</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F251" t="n">
-        <v>15942700</v>
+        <v>18909700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>648.6400146484375</v>
+      </c>
+      <c r="C252" t="n">
+        <v>657.8599853515625</v>
+      </c>
+      <c r="D252" t="n">
+        <v>638.5599975585938</v>
+      </c>
+      <c r="E252" t="n">
+        <v>653.6900024414062</v>
+      </c>
       <c r="F252" t="n">
-        <v>18296627</v>
+        <v>35843200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10768,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>653.6900000000001</v>
+      </c>
+      <c r="D2" t="n">
         <v>613.48</v>
       </c>
-      <c r="D2" t="n">
-        <v>616.77</v>
-      </c>
       <c r="E2" t="n">
-        <v>615.875</v>
+        <v>648.64</v>
       </c>
       <c r="F2" t="n">
-        <v>624.8</v>
+        <v>657.86</v>
       </c>
       <c r="G2" t="n">
-        <v>609.74</v>
+        <v>638.5601</v>
       </c>
       <c r="H2" t="n">
-        <v>18296627</v>
+        <v>35359694</v>
       </c>
       <c r="I2" t="n">
-        <v>17824408</v>
+        <v>17868936</v>
       </c>
       <c r="J2" t="n">
-        <v>1562844069888</v>
+        <v>1665279328256</v>
       </c>
       <c r="K2" t="n">
-        <v>23.132729</v>
+        <v>23.098587</v>
       </c>
       <c r="L2" t="n">
-        <v>17.548225</v>
+        <v>18.698408</v>
       </c>
       <c r="M2" t="n">
-        <v>26.52</v>
+        <v>28.3</v>
       </c>
       <c r="N2" t="n">
         <v>790.8</v>
@@ -10810,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10834,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.984003</v>
+        <v>6.3762193</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10846,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1584902176768</v>
+        <v>1687337304064</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10873,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:15:02</t>
+          <t>2026-09-10 18:59:19</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>762.6305038555339</v>
+        <v>752.1847098305358</v>
       </c>
       <c r="C2" t="n">
-        <v>763.1986490989516</v>
+        <v>754.6266574243845</v>
       </c>
       <c r="D2" t="n">
-        <v>748.5466583985636</v>
+        <v>745.9251963321232</v>
       </c>
       <c r="E2" t="n">
-        <v>749.5234375</v>
+        <v>748.4469604492188</v>
       </c>
       <c r="F2" t="n">
-        <v>12478300</v>
+        <v>7923300</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>752.1847098305358</v>
+        <v>746.2840072815898</v>
       </c>
       <c r="C3" t="n">
-        <v>754.6266574243845</v>
+        <v>755.095155276553</v>
       </c>
       <c r="D3" t="n">
-        <v>745.9251963321232</v>
+        <v>741.330272625368</v>
       </c>
       <c r="E3" t="n">
-        <v>748.4469604492188</v>
+        <v>753.1216430664062</v>
       </c>
       <c r="F3" t="n">
-        <v>7923300</v>
+        <v>8248600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>746.2840677626042</v>
+        <v>754.995481759339</v>
       </c>
       <c r="C4" t="n">
-        <v>755.0952164716484</v>
+        <v>771.5412896866574</v>
       </c>
       <c r="D4" t="n">
-        <v>741.3303327049176</v>
+        <v>749.5334031898147</v>
       </c>
       <c r="E4" t="n">
-        <v>753.1217041015625</v>
+        <v>762.201904296875</v>
       </c>
       <c r="F4" t="n">
-        <v>8248600</v>
+        <v>10533800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>754.995481759339</v>
+        <v>764.4944012192615</v>
       </c>
       <c r="C5" t="n">
-        <v>771.5412896866574</v>
+        <v>778.8074760600178</v>
       </c>
       <c r="D5" t="n">
-        <v>749.5334031898147</v>
+        <v>762.6005837137456</v>
       </c>
       <c r="E5" t="n">
-        <v>762.201904296875</v>
+        <v>776.4552001953125</v>
       </c>
       <c r="F5" t="n">
-        <v>10533800</v>
+        <v>11782500</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>764.4944012192615</v>
+        <v>777.4419223006557</v>
       </c>
       <c r="C6" t="n">
-        <v>778.8074760600178</v>
+        <v>780.7311297077449</v>
       </c>
       <c r="D6" t="n">
-        <v>762.6005837137456</v>
+        <v>763.8066193659058</v>
       </c>
       <c r="E6" t="n">
-        <v>776.4552001953125</v>
+        <v>773.1858520507812</v>
       </c>
       <c r="F6" t="n">
-        <v>11782500</v>
+        <v>9400900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>777.4419223006557</v>
+        <v>778.1994163857863</v>
       </c>
       <c r="C7" t="n">
-        <v>780.7311297077449</v>
+        <v>786.2032128794</v>
       </c>
       <c r="D7" t="n">
-        <v>763.8066193659058</v>
+        <v>770.8335437165625</v>
       </c>
       <c r="E7" t="n">
-        <v>773.1858520507812</v>
+        <v>777.7010498046875</v>
       </c>
       <c r="F7" t="n">
-        <v>9400900</v>
+        <v>10955000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>778.1994163857863</v>
+        <v>783.8509325355676</v>
       </c>
       <c r="C8" t="n">
-        <v>786.2032128794</v>
+        <v>788.2166289656076</v>
       </c>
       <c r="D8" t="n">
-        <v>770.8335437165625</v>
+        <v>766.6772383880447</v>
       </c>
       <c r="E8" t="n">
-        <v>777.7010498046875</v>
+        <v>775.8372192382812</v>
       </c>
       <c r="F8" t="n">
-        <v>10955000</v>
+        <v>23696800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,25 +651,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>783.8508708699721</v>
+        <v>779.8218176027002</v>
       </c>
       <c r="C9" t="n">
-        <v>788.2165669565625</v>
+        <v>783.6917575585782</v>
       </c>
       <c r="D9" t="n">
-        <v>766.6771780735046</v>
+        <v>762.4868973227559</v>
       </c>
       <c r="E9" t="n">
-        <v>775.837158203125</v>
+        <v>763.1751098632812</v>
       </c>
       <c r="F9" t="n">
-        <v>23696800</v>
+        <v>11706900</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -677,25 +677,25 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>779.8218176027002</v>
+        <v>767.254476840496</v>
       </c>
       <c r="C10" t="n">
-        <v>783.6917575585782</v>
+        <v>768.6009504341728</v>
       </c>
       <c r="D10" t="n">
-        <v>762.4868973227559</v>
+        <v>749.1216451610411</v>
       </c>
       <c r="E10" t="n">
-        <v>763.1751098632812</v>
+        <v>753.4404296875</v>
       </c>
       <c r="F10" t="n">
-        <v>11706900</v>
+        <v>10872600</v>
       </c>
       <c r="G10" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>767.254476840496</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C11" t="n">
-        <v>768.6009504341728</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D11" t="n">
-        <v>749.1216451610411</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E11" t="n">
-        <v>753.4404296875</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F11" t="n">
-        <v>10872600</v>
+        <v>8828200</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>755.5349916265823</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C12" t="n">
-        <v>759.1356124217834</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D12" t="n">
-        <v>750.5779133776451</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E12" t="n">
-        <v>758.686767578125</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F12" t="n">
-        <v>8828200</v>
+        <v>10591100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>751.4954858581857</v>
+        <v>748.0544659269957</v>
       </c>
       <c r="C13" t="n">
-        <v>754.8068807440363</v>
+        <v>749.9794521140951</v>
       </c>
       <c r="D13" t="n">
-        <v>742.6185490172081</v>
+        <v>735.4372562509625</v>
       </c>
       <c r="E13" t="n">
-        <v>746.9672241210938</v>
+        <v>741.8206787109375</v>
       </c>
       <c r="F13" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>748.0544043789391</v>
+        <v>746.777703342028</v>
       </c>
       <c r="C14" t="n">
-        <v>749.9793904076555</v>
+        <v>748.8324179023273</v>
       </c>
       <c r="D14" t="n">
-        <v>735.4371957410184</v>
+        <v>737.2325826153279</v>
       </c>
       <c r="E14" t="n">
-        <v>741.8206176757812</v>
+        <v>741.4715576171875</v>
       </c>
       <c r="F14" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>746.777703342028</v>
+        <v>740.3245554260684</v>
       </c>
       <c r="C15" t="n">
-        <v>748.8324179023273</v>
+        <v>741.0426584785586</v>
       </c>
       <c r="D15" t="n">
-        <v>737.2325826153279</v>
+        <v>724.4159185837501</v>
       </c>
       <c r="E15" t="n">
-        <v>741.4715576171875</v>
+        <v>732.4749755859375</v>
       </c>
       <c r="F15" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>740.3245554260684</v>
+        <v>719.6183236513255</v>
       </c>
       <c r="C16" t="n">
-        <v>741.0426584785586</v>
+        <v>719.9773751402398</v>
       </c>
       <c r="D16" t="n">
-        <v>724.4159185837501</v>
+        <v>708.357633728991</v>
       </c>
       <c r="E16" t="n">
-        <v>732.4749755859375</v>
+        <v>715.4791259765625</v>
       </c>
       <c r="F16" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>719.6183236513255</v>
+        <v>720.7055653205383</v>
       </c>
       <c r="C17" t="n">
-        <v>719.9773751402398</v>
+        <v>725.8821043267139</v>
       </c>
       <c r="D17" t="n">
-        <v>708.357633728991</v>
+        <v>716.2770807321521</v>
       </c>
       <c r="E17" t="n">
-        <v>715.4791259765625</v>
+        <v>725.1639404296875</v>
       </c>
       <c r="F17" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>720.7055653205383</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C18" t="n">
-        <v>725.8821043267139</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D18" t="n">
-        <v>716.2770807321521</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E18" t="n">
-        <v>725.1639404296875</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F18" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>727.7372737109582</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C19" t="n">
-        <v>729.1037149276121</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D19" t="n">
-        <v>708.3377167266436</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E19" t="n">
-        <v>708.7167358398438</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F19" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>703.3607165744016</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C20" t="n">
-        <v>715.0203947681905</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D20" t="n">
-        <v>688.718804278428</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E20" t="n">
-        <v>713.8035278320312</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F20" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>715.8581417735932</v>
+        <v>711.599278595462</v>
       </c>
       <c r="C21" t="n">
-        <v>716.6361476056489</v>
+        <v>717.7832075860277</v>
       </c>
       <c r="D21" t="n">
-        <v>703.9192222306009</v>
+        <v>705.9738944950672</v>
       </c>
       <c r="E21" t="n">
-        <v>711.230224609375</v>
+        <v>715.9779052734375</v>
       </c>
       <c r="F21" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>711.599278595462</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C22" t="n">
-        <v>717.7832075860277</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D22" t="n">
-        <v>705.9738944950672</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E22" t="n">
-        <v>715.9779052734375</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F22" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>716.4167658258609</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C23" t="n">
-        <v>731.6072387695312</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D23" t="n">
-        <v>710.5918883665408</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E23" t="n">
-        <v>731.6072387695312</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F23" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>729.0239332852144</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C24" t="n">
-        <v>733.3626856542741</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D24" t="n">
-        <v>702.6824691715568</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E24" t="n">
-        <v>703.4703979492188</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F24" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>711.1603595995662</v>
+        <v>705.9439682909708</v>
       </c>
       <c r="C25" t="n">
-        <v>718.072374881022</v>
+        <v>713.6937706407739</v>
       </c>
       <c r="D25" t="n">
-        <v>705.8042950194317</v>
+        <v>697.5158763660478</v>
       </c>
       <c r="E25" t="n">
-        <v>713.8433837890625</v>
+        <v>706.8117065429688</v>
       </c>
       <c r="F25" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>705.9439682909708</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C26" t="n">
-        <v>713.6937706407739</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D26" t="n">
-        <v>697.5158763660478</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E26" t="n">
-        <v>706.8117065429688</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F26" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>715.1998794771447</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C27" t="n">
-        <v>722.0221626881838</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D27" t="n">
-        <v>707.6694770310874</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E27" t="n">
-        <v>715.6885986328125</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F27" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>715.6886043056783</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C28" t="n">
-        <v>723.6080097298942</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D28" t="n">
-        <v>702.0540824517458</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E28" t="n">
-        <v>710.2228393554688</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F28" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>705.2458014471516</v>
+        <v>719.3191931642514</v>
       </c>
       <c r="C29" t="n">
-        <v>716.6760344343375</v>
+        <v>731.8665769499745</v>
       </c>
       <c r="D29" t="n">
-        <v>704.2882698394852</v>
+        <v>718.3118034233538</v>
       </c>
       <c r="E29" t="n">
-        <v>715.0602416992188</v>
+        <v>730.2706909179688</v>
       </c>
       <c r="F29" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>719.3191931642514</v>
+        <v>734.1107251683979</v>
       </c>
       <c r="C30" t="n">
-        <v>731.8665769499745</v>
+        <v>736.5842723709278</v>
       </c>
       <c r="D30" t="n">
-        <v>718.3118034233538</v>
+        <v>726.8595646449745</v>
       </c>
       <c r="E30" t="n">
-        <v>730.2706909179688</v>
+        <v>731.3678588867188</v>
       </c>
       <c r="F30" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>734.1107251683979</v>
+        <v>731.9264006052239</v>
       </c>
       <c r="C31" t="n">
-        <v>736.5842723709278</v>
+        <v>738.6787972623451</v>
       </c>
       <c r="D31" t="n">
-        <v>726.8595646449745</v>
+        <v>722.1518348008319</v>
       </c>
       <c r="E31" t="n">
-        <v>731.3678588867188</v>
+        <v>731.5074462890625</v>
       </c>
       <c r="F31" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>731.9264006052239</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C32" t="n">
-        <v>738.6787972623451</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D32" t="n">
-        <v>722.1518348008319</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E32" t="n">
-        <v>731.5074462890625</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F32" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>732.7941435868839</v>
+        <v>734.8786455644157</v>
       </c>
       <c r="C33" t="n">
-        <v>740.4841042897723</v>
+        <v>739.2872233202683</v>
       </c>
       <c r="D33" t="n">
-        <v>731.1982575844598</v>
+        <v>729.2533227506186</v>
       </c>
       <c r="E33" t="n">
-        <v>732.095947265625</v>
+        <v>736.444580078125</v>
       </c>
       <c r="F33" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>734.8787064697904</v>
+        <v>747.7851152228061</v>
       </c>
       <c r="C34" t="n">
-        <v>739.2872845910176</v>
+        <v>753.7895182960361</v>
       </c>
       <c r="D34" t="n">
-        <v>729.253383189777</v>
+        <v>746.069606274355</v>
       </c>
       <c r="E34" t="n">
-        <v>736.4446411132812</v>
+        <v>748.872314453125</v>
       </c>
       <c r="F34" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>747.7850542762595</v>
+        <v>750.6776381609803</v>
       </c>
       <c r="C35" t="n">
-        <v>753.7894568601143</v>
+        <v>756.4326899204912</v>
       </c>
       <c r="D35" t="n">
-        <v>746.0695454676272</v>
+        <v>743.5860965317024</v>
       </c>
       <c r="E35" t="n">
-        <v>748.8722534179688</v>
+        <v>749.49072265625</v>
       </c>
       <c r="F35" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>750.6776381609803</v>
+        <v>752.7921200604676</v>
       </c>
       <c r="C36" t="n">
-        <v>756.4326899204912</v>
+        <v>757.1906533932021</v>
       </c>
       <c r="D36" t="n">
-        <v>743.5860965317024</v>
+        <v>740.5838813084906</v>
       </c>
       <c r="E36" t="n">
-        <v>749.49072265625</v>
+        <v>749.7200927734375</v>
       </c>
       <c r="F36" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>752.7921200604676</v>
+        <v>667.414190282622</v>
       </c>
       <c r="C37" t="n">
-        <v>757.1906533932021</v>
+        <v>679.1935516668058</v>
       </c>
       <c r="D37" t="n">
-        <v>740.5838813084906</v>
+        <v>648.4833846789722</v>
       </c>
       <c r="E37" t="n">
-        <v>749.7200927734375</v>
+        <v>664.7410888671875</v>
       </c>
       <c r="F37" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>667.4142515632169</v>
+        <v>672.7602632515434</v>
       </c>
       <c r="C38" t="n">
-        <v>679.1936140289573</v>
+        <v>673.1392823636344</v>
       </c>
       <c r="D38" t="n">
-        <v>648.4834442213796</v>
+        <v>643.8953340746643</v>
       </c>
       <c r="E38" t="n">
-        <v>664.7411499023438</v>
+        <v>646.6680908203125</v>
       </c>
       <c r="F38" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>672.7602632515434</v>
+        <v>654.2982567113449</v>
       </c>
       <c r="C39" t="n">
-        <v>673.1392823636344</v>
+        <v>657.619635334369</v>
       </c>
       <c r="D39" t="n">
-        <v>643.8953340746643</v>
+        <v>634.5296648817072</v>
       </c>
       <c r="E39" t="n">
-        <v>646.6680908203125</v>
+        <v>636.0557250976562</v>
       </c>
       <c r="F39" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>654.298319497033</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C40" t="n">
-        <v>657.6196984387726</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D40" t="n">
-        <v>634.5297257704245</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E40" t="n">
-        <v>636.0557861328125</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F40" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>626.4107910285981</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C41" t="n">
-        <v>640.0752642850032</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D41" t="n">
-        <v>624.3860886703497</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E41" t="n">
-        <v>625.6926879882812</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F41" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>630.6697208898194</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C42" t="n">
-        <v>640.5639703518489</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D42" t="n">
-        <v>624.9146693781357</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E42" t="n">
-        <v>634.30029296875</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F42" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>634.2005186436334</v>
+        <v>614.8907386759073</v>
       </c>
       <c r="C43" t="n">
-        <v>634.3501538797125</v>
+        <v>620.5161224262619</v>
       </c>
       <c r="D43" t="n">
-        <v>616.3968476378337</v>
+        <v>599.6404247494841</v>
       </c>
       <c r="E43" t="n">
-        <v>617.3344116210938</v>
+        <v>620.0972290039062</v>
       </c>
       <c r="F43" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>614.8907386759073</v>
+        <v>629.4529708548182</v>
       </c>
       <c r="C44" t="n">
-        <v>620.5161224262619</v>
+        <v>633.3528014765299</v>
       </c>
       <c r="D44" t="n">
-        <v>599.6404247494841</v>
+        <v>616.5065997528014</v>
       </c>
       <c r="E44" t="n">
-        <v>620.0972290039062</v>
+        <v>630.1212158203125</v>
       </c>
       <c r="F44" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>629.4529708548182</v>
+        <v>626.3709044869131</v>
       </c>
       <c r="C45" t="n">
-        <v>633.3528014765299</v>
+        <v>627.9268552540688</v>
       </c>
       <c r="D45" t="n">
-        <v>616.5065997528014</v>
+        <v>617.7832543081277</v>
       </c>
       <c r="E45" t="n">
-        <v>630.1212158203125</v>
+        <v>625.4533081054688</v>
       </c>
       <c r="F45" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>626.3709656116134</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C46" t="n">
-        <v>627.9269165306073</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D46" t="n">
-        <v>617.7833145947981</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E46" t="n">
-        <v>625.453369140625</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F46" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>626.5005716840028</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C47" t="n">
-        <v>627.3583261459861</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D47" t="n">
-        <v>606.1934022078184</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E47" t="n">
-        <v>607.43017578125</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F47" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>611.4796659420805</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C48" t="n">
-        <v>616.0478021853295</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D48" t="n">
-        <v>601.4357808374693</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E48" t="n">
-        <v>608.3079223632812</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F48" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>600.2288811530552</v>
+        <v>607.4600964135232</v>
       </c>
       <c r="C49" t="n">
-        <v>612.088052043071</v>
+        <v>610.1032465254069</v>
       </c>
       <c r="D49" t="n">
-        <v>593.6560102918138</v>
+        <v>593.855525554584</v>
       </c>
       <c r="E49" t="n">
-        <v>607.8790283203125</v>
+        <v>600.4483642578125</v>
       </c>
       <c r="F49" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>607.4600346656293</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C50" t="n">
-        <v>610.1031845088386</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D50" t="n">
-        <v>593.8554651895852</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E50" t="n">
-        <v>600.4483032226562</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F50" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>590.065358149623</v>
+        <v>592.1797786556917</v>
       </c>
       <c r="C51" t="n">
-        <v>602.0940719298206</v>
+        <v>593.7856483585136</v>
       </c>
       <c r="D51" t="n">
-        <v>582.2656968950795</v>
+        <v>579.7421567881397</v>
       </c>
       <c r="E51" t="n">
-        <v>596.1395874023438</v>
+        <v>588.7886352539062</v>
       </c>
       <c r="F51" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>592.1797786556917</v>
+        <v>601.9344542639864</v>
       </c>
       <c r="C52" t="n">
-        <v>593.7856483585136</v>
+        <v>605.1460720070379</v>
       </c>
       <c r="D52" t="n">
-        <v>579.7421567881397</v>
+        <v>581.8367012414765</v>
       </c>
       <c r="E52" t="n">
-        <v>588.7886352539062</v>
+        <v>587.6217041015625</v>
       </c>
       <c r="F52" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>601.9344542639864</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C53" t="n">
-        <v>605.1460720070379</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D53" t="n">
-        <v>581.8367012414765</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E53" t="n">
-        <v>587.6217041015625</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F53" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>586.9734117815261</v>
+        <v>597.1668126146857</v>
       </c>
       <c r="C54" t="n">
-        <v>596.5684523172222</v>
+        <v>615.1002115339802</v>
       </c>
       <c r="D54" t="n">
-        <v>580.3506215479276</v>
+        <v>596.0796743085915</v>
       </c>
       <c r="E54" t="n">
-        <v>592.70849609375</v>
+        <v>611.4596557617188</v>
       </c>
       <c r="F54" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>597.1668722231478</v>
+        <v>622.3813086708644</v>
       </c>
       <c r="C55" t="n">
-        <v>615.1002729325323</v>
+        <v>635.3974440566444</v>
       </c>
       <c r="D55" t="n">
-        <v>596.0797338085368</v>
+        <v>616.696082618217</v>
       </c>
       <c r="E55" t="n">
-        <v>611.459716796875</v>
+        <v>634.569580078125</v>
       </c>
       <c r="F55" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>622.3812488080194</v>
+        <v>636.0358029520913</v>
       </c>
       <c r="C56" t="n">
-        <v>635.3973829418613</v>
+        <v>636.7040478933542</v>
       </c>
       <c r="D56" t="n">
-        <v>616.6960233021972</v>
+        <v>629.9915253276793</v>
       </c>
       <c r="E56" t="n">
-        <v>634.5695190429688</v>
+        <v>631.9663696289062</v>
       </c>
       <c r="F56" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>636.0358029520913</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C57" t="n">
-        <v>636.7040478933542</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D57" t="n">
-        <v>629.9915253276793</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E57" t="n">
-        <v>631.9663696289062</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F57" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>634.4299618769652</v>
+        <v>637.8909364271796</v>
       </c>
       <c r="C58" t="n">
-        <v>646.3688812783262</v>
+        <v>643.6459879981971</v>
       </c>
       <c r="D58" t="n">
-        <v>633.8514494094911</v>
+        <v>636.1056017671217</v>
       </c>
       <c r="E58" t="n">
-        <v>646.2691650390625</v>
+        <v>639.20751953125</v>
       </c>
       <c r="F58" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>637.8909364271796</v>
+        <v>640.6737853801045</v>
       </c>
       <c r="C59" t="n">
-        <v>643.6459879981971</v>
+        <v>646.1894088056151</v>
       </c>
       <c r="D59" t="n">
-        <v>636.1056017671217</v>
+        <v>636.4148423556049</v>
       </c>
       <c r="E59" t="n">
-        <v>639.20751953125</v>
+        <v>645.42138671875</v>
       </c>
       <c r="F59" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>640.6737247939117</v>
+        <v>642.7383773862279</v>
       </c>
       <c r="C60" t="n">
-        <v>646.1893476978298</v>
+        <v>647.1668624868771</v>
       </c>
       <c r="D60" t="n">
-        <v>636.4147821721649</v>
+        <v>635.8961867971512</v>
       </c>
       <c r="E60" t="n">
-        <v>645.4213256835938</v>
+        <v>637.9408569335938</v>
       </c>
       <c r="F60" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>642.7383158920676</v>
+        <v>674.2463992276428</v>
       </c>
       <c r="C61" t="n">
-        <v>647.1668005690203</v>
+        <v>674.3461154685141</v>
       </c>
       <c r="D61" t="n">
-        <v>635.8961259576193</v>
+        <v>658.3377626918029</v>
       </c>
       <c r="E61" t="n">
-        <v>637.9407958984375</v>
+        <v>659.81396484375</v>
       </c>
       <c r="F61" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>674.246461597851</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C62" t="n">
-        <v>674.3461778479464</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D62" t="n">
-        <v>658.3378235904052</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E62" t="n">
-        <v>659.8140258789062</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F62" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>662.2775487290173</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C63" t="n">
-        <v>672.9398207362489</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D63" t="n">
-        <v>660.6717397649775</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E63" t="n">
-        <v>671.673095703125</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F63" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>667.603701448277</v>
+        <v>662.0481300460407</v>
       </c>
       <c r="C64" t="n">
-        <v>674.9545781663558</v>
+        <v>662.7562492699393</v>
       </c>
       <c r="D64" t="n">
-        <v>663.344758713728</v>
+        <v>651.6451938720459</v>
       </c>
       <c r="E64" t="n">
-        <v>665.0702514648438</v>
+        <v>655.2557983398438</v>
       </c>
       <c r="F64" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>662.0481917138827</v>
+        <v>648.2639556943986</v>
       </c>
       <c r="C65" t="n">
-        <v>662.7563110037405</v>
+        <v>652.8121240146866</v>
       </c>
       <c r="D65" t="n">
-        <v>651.645254570885</v>
+        <v>641.730959438269</v>
       </c>
       <c r="E65" t="n">
-        <v>655.255859375</v>
+        <v>648.4434814453125</v>
       </c>
       <c r="F65" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>648.2639556943986</v>
+        <v>641.6212380225077</v>
       </c>
       <c r="C66" t="n">
-        <v>652.8121240146866</v>
+        <v>653.5801862453618</v>
       </c>
       <c r="D66" t="n">
-        <v>641.730959438269</v>
+        <v>639.1377070000864</v>
       </c>
       <c r="E66" t="n">
-        <v>648.4434814453125</v>
+        <v>651.016845703125</v>
       </c>
       <c r="F66" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>641.6211778682233</v>
+        <v>648.1143349664432</v>
       </c>
       <c r="C67" t="n">
-        <v>653.5801249698833</v>
+        <v>709.1555875928369</v>
       </c>
       <c r="D67" t="n">
-        <v>639.1376470786419</v>
+        <v>636.9533606253732</v>
       </c>
       <c r="E67" t="n">
-        <v>651.0167846679688</v>
+        <v>642.5587768554688</v>
       </c>
       <c r="F67" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>648.1143965293088</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C68" t="n">
-        <v>709.1556549538686</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D68" t="n">
-        <v>636.9534211280841</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E68" t="n">
-        <v>642.558837890625</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F68" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,25 +2211,25 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>644.5502809809109</v>
+        <v>642.3541401459643</v>
       </c>
       <c r="C69" t="n">
-        <v>651.8372704406642</v>
+        <v>661.3602142938313</v>
       </c>
       <c r="D69" t="n">
-        <v>637.5627451568915</v>
+        <v>642.054686531657</v>
       </c>
       <c r="E69" t="n">
-        <v>646.3570556640625</v>
+        <v>655.9798583984375</v>
       </c>
       <c r="F69" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G69" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>642.3541999133257</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C70" t="n">
-        <v>661.3602758295988</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D70" t="n">
-        <v>642.054746271156</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E70" t="n">
-        <v>655.9799194335938</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F70" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>654.4426118233187</v>
+        <v>655.8601356908653</v>
       </c>
       <c r="C71" t="n">
-        <v>660.0526000253047</v>
+        <v>669.366012780715</v>
       </c>
       <c r="D71" t="n">
-        <v>648.0440522221027</v>
+        <v>655.2911433094866</v>
       </c>
       <c r="E71" t="n">
-        <v>648.343505859375</v>
+        <v>663.2669067382812</v>
       </c>
       <c r="F71" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>655.8600753372949</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C72" t="n">
-        <v>669.3659511843067</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D72" t="n">
-        <v>655.2910830082761</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E72" t="n">
-        <v>663.266845703125</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F72" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>665.2333263832898</v>
+        <v>660.4718397886508</v>
       </c>
       <c r="C73" t="n">
-        <v>669.8051880946751</v>
+        <v>672.380589007267</v>
       </c>
       <c r="D73" t="n">
-        <v>657.0080086354003</v>
+        <v>655.4807431709672</v>
       </c>
       <c r="E73" t="n">
-        <v>657.5969848632812</v>
+        <v>660.3220825195312</v>
       </c>
       <c r="F73" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>660.4719008376494</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C74" t="n">
-        <v>672.3806511570199</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D74" t="n">
-        <v>655.4808037586267</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E74" t="n">
-        <v>660.3221435546875</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F74" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>658.8746741689592</v>
+        <v>661.3503688947783</v>
       </c>
       <c r="C75" t="n">
-        <v>664.8140915262984</v>
+        <v>666.9902722948509</v>
       </c>
       <c r="D75" t="n">
-        <v>657.0778915122911</v>
+        <v>661.0209394131572</v>
       </c>
       <c r="E75" t="n">
-        <v>663.7559814453125</v>
+        <v>666.3613891601562</v>
       </c>
       <c r="F75" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>661.3503083186049</v>
+        <v>666.8704124858896</v>
       </c>
       <c r="C76" t="n">
-        <v>666.9902112020924</v>
+        <v>667.7588423243637</v>
       </c>
       <c r="D76" t="n">
-        <v>661.0208788671576</v>
+        <v>660.1424238558649</v>
       </c>
       <c r="E76" t="n">
-        <v>666.361328125</v>
+        <v>662.10888671875</v>
       </c>
       <c r="F76" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>666.8704739599774</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C77" t="n">
-        <v>667.7589038803495</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D77" t="n">
-        <v>660.1424847097468</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E77" t="n">
-        <v>662.1089477539062</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F77" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>656.8383689858442</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C78" t="n">
-        <v>659.0743707339258</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D78" t="n">
-        <v>653.2248195668056</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E78" t="n">
-        <v>657.5171508789062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F78" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>657.5171386037911</v>
+        <v>663.5663484641349</v>
       </c>
       <c r="C79" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8159033150052</v>
       </c>
       <c r="D79" t="n">
-        <v>656.6686764849229</v>
+        <v>658.2658058687088</v>
       </c>
       <c r="E79" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9146728515625</v>
       </c>
       <c r="F79" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>663.5662869980947</v>
+        <v>661.5499631466852</v>
       </c>
       <c r="C80" t="n">
-        <v>663.8158418258488</v>
+        <v>663.2070415689074</v>
       </c>
       <c r="D80" t="n">
-        <v>658.2657448936569</v>
+        <v>642.3542224297569</v>
       </c>
       <c r="E80" t="n">
-        <v>658.9146118164062</v>
+        <v>649.2518920898438</v>
       </c>
       <c r="F80" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>661.5499009554064</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C81" t="n">
-        <v>663.2069792218492</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D81" t="n">
-        <v>642.3541620430398</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E81" t="n">
-        <v>649.2518310546875</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F81" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>649.8508280292294</v>
+        <v>658.3956073528642</v>
       </c>
       <c r="C82" t="n">
-        <v>663.3567049684374</v>
+        <v>664.3350252422523</v>
       </c>
       <c r="D82" t="n">
-        <v>646.5966230035071</v>
+        <v>650.7392812609531</v>
       </c>
       <c r="E82" t="n">
-        <v>657.616943359375</v>
+        <v>659.4437255859375</v>
       </c>
       <c r="F82" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>658.3955464147172</v>
+        <v>654.4726104611178</v>
       </c>
       <c r="C83" t="n">
-        <v>664.3349637543794</v>
+        <v>657.9763704555172</v>
       </c>
       <c r="D83" t="n">
-        <v>650.7392210314413</v>
+        <v>643.6618768302103</v>
       </c>
       <c r="E83" t="n">
-        <v>659.4436645507812</v>
+        <v>647.5349731445312</v>
       </c>
       <c r="F83" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>654.4725487720359</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C84" t="n">
-        <v>657.9763084361789</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D84" t="n">
-        <v>643.6618161601232</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E84" t="n">
-        <v>647.534912109375</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F84" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>644.7299347572825</v>
+        <v>644.2906685217797</v>
       </c>
       <c r="C85" t="n">
-        <v>645.9477331499952</v>
+        <v>653.7837438291153</v>
       </c>
       <c r="D85" t="n">
-        <v>634.5879917891143</v>
+        <v>641.7052537227476</v>
       </c>
       <c r="E85" t="n">
-        <v>644.9096069335938</v>
+        <v>651.8970947265625</v>
       </c>
       <c r="F85" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>644.2907288447692</v>
+        <v>651.3681600668523</v>
       </c>
       <c r="C86" t="n">
-        <v>653.7838050409127</v>
+        <v>652.8055375702352</v>
       </c>
       <c r="D86" t="n">
-        <v>641.7053138036724</v>
+        <v>640.0882316599212</v>
       </c>
       <c r="E86" t="n">
-        <v>651.8971557617188</v>
+        <v>640.826904296875</v>
       </c>
       <c r="F86" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>651.3680980277007</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C87" t="n">
-        <v>652.8054753941815</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D87" t="n">
-        <v>640.0881706951194</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E87" t="n">
-        <v>640.8268432617188</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F87" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>641.1263941859123</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C88" t="n">
-        <v>641.1263941859123</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D88" t="n">
-        <v>622.9887038024194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E88" t="n">
-        <v>629.96630859375</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F88" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>625.3844405077801</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C89" t="n">
-        <v>627.3309804807691</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D89" t="n">
-        <v>613.7252454803604</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E89" t="n">
-        <v>614.4240112304688</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F89" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>617.378703801015</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C90" t="n">
-        <v>623.0585745209008</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D90" t="n">
-        <v>613.1362714280776</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E90" t="n">
-        <v>619.694580078125</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F90" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>623.0685636897582</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C91" t="n">
-        <v>627.9598630097294</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D91" t="n">
-        <v>618.9758886129073</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E91" t="n">
-        <v>619.1455688476562</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F91" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>606.7976262932837</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C92" t="n">
-        <v>610.3113781504126</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D92" t="n">
-        <v>598.9316523845154</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E92" t="n">
-        <v>603.0443115234375</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F92" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>605.659634898437</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C93" t="n">
-        <v>617.169133937088</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D93" t="n">
-        <v>599.0115204374271</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E93" t="n">
-        <v>611.8685913085938</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F93" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>628.2293275614567</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C94" t="n">
-        <v>659.3937675491238</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D94" t="n">
-        <v>625.4343255489129</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E94" t="n">
-        <v>646.476806640625</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F94" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>643.6219561683764</v>
+        <v>663.9456740004919</v>
       </c>
       <c r="C95" t="n">
-        <v>665.3032527677875</v>
+        <v>674.0776252750454</v>
       </c>
       <c r="D95" t="n">
-        <v>643.3025186421843</v>
+        <v>660.1124846991261</v>
       </c>
       <c r="E95" t="n">
-        <v>657.5870361328125</v>
+        <v>671.1627807617188</v>
       </c>
       <c r="F95" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>663.9456136216552</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C96" t="n">
-        <v>674.0775639748149</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D96" t="n">
-        <v>660.1124246688775</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E96" t="n">
-        <v>671.1627197265625</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F96" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>673.3888389297905</v>
+        <v>673.2989910894674</v>
       </c>
       <c r="C97" t="n">
-        <v>675.6148486525956</v>
+        <v>676.4733214975852</v>
       </c>
       <c r="D97" t="n">
-        <v>663.4764668627315</v>
+        <v>664.9139236867763</v>
       </c>
       <c r="E97" t="n">
-        <v>671.7716674804688</v>
+        <v>667.5392456054688</v>
       </c>
       <c r="F97" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>673.2989295276801</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C98" t="n">
-        <v>676.4732596455591</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D98" t="n">
-        <v>664.9138628916613</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E98" t="n">
-        <v>667.5391845703125</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F98" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>736.1169233837337</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C99" t="n">
-        <v>742.6752321400184</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D99" t="n">
-        <v>711.2812198864386</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E99" t="n">
-        <v>736.995361328125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F99" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>726.2045952530067</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C100" t="n">
-        <v>730.8662626744616</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D100" t="n">
-        <v>712.3193905555435</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E100" t="n">
-        <v>715.2241821289062</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F100" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>713.3275184694113</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C101" t="n">
-        <v>720.0156002559207</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D101" t="n">
-        <v>702.2672920108814</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E101" t="n">
-        <v>705.152099609375</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F101" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>706.1104025957663</v>
+        <v>686.5053883494637</v>
       </c>
       <c r="C102" t="n">
-        <v>715.7232596178901</v>
+        <v>687.603466213174</v>
       </c>
       <c r="D102" t="n">
-        <v>685.1877035052055</v>
+        <v>666.2715231343633</v>
       </c>
       <c r="E102" t="n">
-        <v>690.4683227539062</v>
+        <v>667.7987670898438</v>
       </c>
       <c r="F102" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>686.5054510943589</v>
+        <v>662.3984025060512</v>
       </c>
       <c r="C103" t="n">
-        <v>687.6035290584308</v>
+        <v>680.2864759062725</v>
       </c>
       <c r="D103" t="n">
-        <v>666.2715840299333</v>
+        <v>652.3363345630947</v>
       </c>
       <c r="E103" t="n">
-        <v>667.798828125</v>
+        <v>669.0166015625</v>
       </c>
       <c r="F103" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>662.3984629374214</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C104" t="n">
-        <v>680.2865379695924</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D104" t="n">
-        <v>652.3363940764909</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E104" t="n">
-        <v>669.0166625976562</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F104" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>664.3050190645899</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C105" t="n">
-        <v>670.7934451675868</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D105" t="n">
-        <v>645.3488423980709</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E105" t="n">
-        <v>660.2822265625</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F105" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>661.9991209626965</v>
+        <v>676.3934502400131</v>
       </c>
       <c r="C106" t="n">
-        <v>682.0932819515241</v>
+        <v>679.4380681924739</v>
       </c>
       <c r="D106" t="n">
-        <v>657.6069922476072</v>
+        <v>668.597359057372</v>
       </c>
       <c r="E106" t="n">
-        <v>676.0140991210938</v>
+        <v>669.5256958007812</v>
       </c>
       <c r="F106" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>676.39338857878</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C107" t="n">
-        <v>679.4380062536881</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D107" t="n">
-        <v>668.5972981068446</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E107" t="n">
-        <v>669.525634765625</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F107" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>672.7998711552045</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C108" t="n">
-        <v>678.0605068549233</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D108" t="n">
-        <v>655.9299390360635</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E108" t="n">
-        <v>667.4993286132812</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F108" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>668.7770306530766</v>
+        <v>643.9513250294082</v>
       </c>
       <c r="C109" t="n">
-        <v>674.7963229561075</v>
+        <v>650.2700710327099</v>
       </c>
       <c r="D109" t="n">
-        <v>644.1310518439949</v>
+        <v>633.4401061931457</v>
       </c>
       <c r="E109" t="n">
-        <v>648.6529541015625</v>
+        <v>638.630859375</v>
       </c>
       <c r="F109" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>643.9512634857649</v>
+        <v>638.3612593202278</v>
       </c>
       <c r="C110" t="n">
-        <v>650.2700088851722</v>
+        <v>641.4557148619026</v>
       </c>
       <c r="D110" t="n">
-        <v>633.4400456540794</v>
+        <v>627.6803003409905</v>
       </c>
       <c r="E110" t="n">
-        <v>638.6307983398438</v>
+        <v>638.151611328125</v>
       </c>
       <c r="F110" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>638.3613203754355</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C111" t="n">
-        <v>641.4557762130754</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D111" t="n">
-        <v>627.6803603746322</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E111" t="n">
-        <v>638.1516723632812</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F111" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>632.67143641335</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C112" t="n">
-        <v>643.8515057528024</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D112" t="n">
-        <v>627.0315334227189</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E112" t="n">
-        <v>642.0746459960938</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F112" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>637.432932921519</v>
+        <v>638.5509584025834</v>
       </c>
       <c r="C113" t="n">
-        <v>646.0375787806976</v>
+        <v>662.1688021543367</v>
       </c>
       <c r="D113" t="n">
-        <v>635.5861905818066</v>
+        <v>637.6426055733327</v>
       </c>
       <c r="E113" t="n">
-        <v>643.6318969726562</v>
+        <v>654.4924926757812</v>
       </c>
       <c r="F113" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>638.5510179511008</v>
+        <v>651.3780476889771</v>
       </c>
       <c r="C114" t="n">
-        <v>662.1688639053526</v>
+        <v>656.5288937722072</v>
       </c>
       <c r="D114" t="n">
-        <v>637.642665037141</v>
+        <v>634.8675211939732</v>
       </c>
       <c r="E114" t="n">
-        <v>654.4925537109375</v>
+        <v>636.1152954101562</v>
       </c>
       <c r="F114" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>651.3781101885919</v>
+        <v>631.9527259539814</v>
       </c>
       <c r="C115" t="n">
-        <v>656.5289567660449</v>
+        <v>639.9683956881865</v>
       </c>
       <c r="D115" t="n">
-        <v>634.8675821094057</v>
+        <v>627.8599900449855</v>
       </c>
       <c r="E115" t="n">
-        <v>636.1153564453125</v>
+        <v>638.16162109375</v>
       </c>
       <c r="F115" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>631.9527863953055</v>
+        <v>641.3859599741169</v>
       </c>
       <c r="C116" t="n">
-        <v>639.9684568961466</v>
+        <v>652.7157261405878</v>
       </c>
       <c r="D116" t="n">
-        <v>627.8600500948714</v>
+        <v>640.9966397738364</v>
       </c>
       <c r="E116" t="n">
-        <v>638.1616821289062</v>
+        <v>652.5260620117188</v>
       </c>
       <c r="F116" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>641.3858999809694</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C117" t="n">
-        <v>652.7156650876909</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D117" t="n">
-        <v>640.9965798171046</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E117" t="n">
-        <v>652.5260009765625</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F117" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>649.3916295582877</v>
+        <v>642.3043203814821</v>
       </c>
       <c r="C118" t="n">
-        <v>659.823034651462</v>
+        <v>648.2836451675449</v>
       </c>
       <c r="D118" t="n">
-        <v>646.3470725216666</v>
+        <v>636.9837936279411</v>
       </c>
       <c r="E118" t="n">
-        <v>655.8401489257812</v>
+        <v>647.02587890625</v>
       </c>
       <c r="F118" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>642.3042597917192</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C119" t="n">
-        <v>648.2835840137412</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D119" t="n">
-        <v>636.9837335400734</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E119" t="n">
-        <v>647.0258178710938</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F119" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>636.0254184162494</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C120" t="n">
-        <v>658.764884603327</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D120" t="n">
-        <v>633.3701817354564</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E120" t="n">
-        <v>652.396240234375</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F120" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>647.1356255764312</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C121" t="n">
-        <v>657.866484005116</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D121" t="n">
-        <v>637.7025010942567</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E121" t="n">
-        <v>653.91357421875</v>
+        <v>666.541015625</v>
       </c>
       <c r="F121" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>656.7884535878291</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C122" t="n">
-        <v>671.5720803574089</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D122" t="n">
-        <v>656.4989309709863</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E122" t="n">
-        <v>666.541015625</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F122" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>660.751362594833</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C123" t="n">
-        <v>669.5057662619517</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D123" t="n">
-        <v>649.1520579976961</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E123" t="n">
-        <v>659.393798828125</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F123" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>646.7463568472266</v>
+        <v>633.6497720389343</v>
       </c>
       <c r="C124" t="n">
-        <v>648.3135076492586</v>
+        <v>646.596649067328</v>
       </c>
       <c r="D124" t="n">
-        <v>634.9773114336934</v>
+        <v>625.6640164348609</v>
       </c>
       <c r="E124" t="n">
-        <v>643.7117309570312</v>
+        <v>646.2373046875</v>
       </c>
       <c r="F124" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>633.6497121926325</v>
+        <v>652.3962328583322</v>
       </c>
       <c r="C125" t="n">
-        <v>646.5965879982328</v>
+        <v>659.1242214972237</v>
       </c>
       <c r="D125" t="n">
-        <v>625.6639573427893</v>
+        <v>647.8443550809549</v>
       </c>
       <c r="E125" t="n">
-        <v>646.2372436523438</v>
+        <v>652.9053344726562</v>
       </c>
       <c r="F125" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>652.3962938458964</v>
+        <v>653.5941111270305</v>
       </c>
       <c r="C126" t="n">
-        <v>659.1242831137364</v>
+        <v>657.9463328691638</v>
       </c>
       <c r="D126" t="n">
-        <v>647.8444156429986</v>
+        <v>647.2054829186618</v>
       </c>
       <c r="E126" t="n">
-        <v>652.9053955078125</v>
+        <v>653.6939086914062</v>
       </c>
       <c r="F126" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>653.5941721528687</v>
+        <v>647.5948263527883</v>
       </c>
       <c r="C127" t="n">
-        <v>657.9463943013674</v>
+        <v>652.336368433984</v>
       </c>
       <c r="D127" t="n">
-        <v>647.2055433479961</v>
+        <v>635.7659510050273</v>
       </c>
       <c r="E127" t="n">
-        <v>653.6939697265625</v>
+        <v>637.0436401367188</v>
       </c>
       <c r="F127" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>647.5948883988538</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C128" t="n">
-        <v>652.3364309343367</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D128" t="n">
-        <v>635.7660119177681</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E128" t="n">
-        <v>637.043701171875</v>
+        <v>612.6171875</v>
       </c>
       <c r="F128" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>622.7790526456299</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C129" t="n">
-        <v>628.0496188589474</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D129" t="n">
-        <v>608.4645611002024</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E129" t="n">
-        <v>612.6171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F129" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3797,25 +3797,25 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>631.4147932406764</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C130" t="n">
-        <v>634.1622468505053</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D130" t="n">
-        <v>622.5230098937741</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E130" t="n">
-        <v>626.8690185546875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F130" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G130" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>627.4085169382369</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C131" t="n">
-        <v>635.9605885584036</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D131" t="n">
-        <v>621.1243629754691</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E131" t="n">
-        <v>622.0834350585938</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F131" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>615.7693473594539</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C132" t="n">
-        <v>622.0735023862151</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D132" t="n">
-        <v>614.04090772979</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E132" t="n">
-        <v>615.1099243164062</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F132" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>611.5832104537112</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C133" t="n">
-        <v>612.4323990135786</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D133" t="n">
-        <v>601.7023533616688</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E133" t="n">
-        <v>606.1382446289062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F133" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>602.9712077810872</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C134" t="n">
-        <v>603.400802317344</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D134" t="n">
-        <v>586.7062525156723</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E134" t="n">
-        <v>593.1102905273438</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F134" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>605.2290499891692</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C135" t="n">
-        <v>608.0764476338709</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D135" t="n">
-        <v>598.4553596033379</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E135" t="n">
-        <v>603.5006713867188</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F135" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>598.5452420228083</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C136" t="n">
-        <v>600.443507118967</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D136" t="n">
-        <v>590.4527665679026</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E136" t="n">
-        <v>592.3709716796875</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F136" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>598.1855830392399</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C137" t="n">
-        <v>603.1110107561809</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D137" t="n">
-        <v>592.8505617950721</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E137" t="n">
-        <v>594.3391723632812</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F137" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>581.9506076701073</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C138" t="n">
-        <v>582.460145169462</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D138" t="n">
-        <v>542.8468364624507</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E138" t="n">
-        <v>547.032958984375</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F138" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>539.599843303006</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C139" t="n">
-        <v>543.0966023049141</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D139" t="n">
-        <v>519.7782492802263</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E139" t="n">
-        <v>525.233154296875</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F139" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>535.8833618164062</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C140" t="n">
-        <v>539.0504095872608</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D140" t="n">
-        <v>528.0505941707193</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E140" t="n">
-        <v>535.8833618164062</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F140" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>549.4707059552647</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C141" t="n">
-        <v>573.1587727471259</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D141" t="n">
-        <v>546.2637174010383</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E141" t="n">
-        <v>571.6002197265625</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F141" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>579.5928556215499</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C142" t="n">
-        <v>592.0013387220274</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D142" t="n">
-        <v>573.2887005646345</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E142" t="n">
-        <v>578.6936645507812</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F142" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>565.5158531822124</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C143" t="n">
-        <v>577.9643377947169</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D143" t="n">
-        <v>559.1817578546791</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E143" t="n">
-        <v>573.9281005859375</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F143" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>577.1550997330287</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C144" t="n">
-        <v>582.2503530791108</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D144" t="n">
-        <v>571.4703658572956</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E144" t="n">
-        <v>572.4894409179688</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F144" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>571.9498894780604</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C145" t="n">
-        <v>574.6973431004155</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D145" t="n">
-        <v>564.2370671243236</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E145" t="n">
-        <v>574.5175170898438</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F145" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>605.4388670235439</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C146" t="n">
-        <v>629.3667024291958</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D146" t="n">
-        <v>591.2820049792073</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E146" t="n">
-        <v>611.8529052734375</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F146" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>626.3894374266143</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C147" t="n">
-        <v>636.9097166035551</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D147" t="n">
-        <v>622.4231426572783</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E147" t="n">
-        <v>627.8081665039062</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F147" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>633.882449891805</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C148" t="n">
-        <v>637.9886903650855</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D148" t="n">
-        <v>623.7518859014353</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E148" t="n">
-        <v>629.2767333984375</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F148" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>628.9171329935918</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C149" t="n">
-        <v>634.4120404303904</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D149" t="n">
-        <v>623.8218795800174</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E149" t="n">
-        <v>633.9425048828125</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F149" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>642.624350345733</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C150" t="n">
-        <v>665.6430543798978</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D150" t="n">
-        <v>638.7779398291946</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E150" t="n">
-        <v>661.8765258789062</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F150" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>666.3824145357423</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C151" t="n">
-        <v>677.8717665104965</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D151" t="n">
-        <v>663.6049593103575</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E151" t="n">
-        <v>670.9581909179688</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F151" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>675.3640350842893</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C152" t="n">
-        <v>676.9525896021297</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D152" t="n">
-        <v>667.131674939706</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E152" t="n">
-        <v>676.2432250976562</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F152" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>677.9716157075654</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C153" t="n">
-        <v>690.8796961433965</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D153" t="n">
-        <v>674.5048580761284</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E153" t="n">
-        <v>687.9124145507812</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F153" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>680.7290935491282</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C154" t="n">
-        <v>682.7472426832454</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D154" t="n">
-        <v>667.381478611767</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E154" t="n">
-        <v>670.2887573242188</v>
+        <v>668.220703125</v>
       </c>
       <c r="F154" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>670.3786762058809</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C155" t="n">
-        <v>675.5738733736962</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D155" t="n">
-        <v>666.7120915784461</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E155" t="n">
-        <v>668.220703125</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F155" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>673.7355628200382</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C156" t="n">
-        <v>677.7518600207422</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D156" t="n">
-        <v>669.1298460769134</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E156" t="n">
-        <v>674.09521484375</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F156" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>663.0854475032797</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C157" t="n">
-        <v>668.9400066983026</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D157" t="n">
-        <v>652.4452846667049</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E157" t="n">
-        <v>658.5396728515625</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F157" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>659.7085674039201</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C158" t="n">
-        <v>680.0396994180859</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D158" t="n">
-        <v>653.2345872360809</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E158" t="n">
-        <v>674.4049682617188</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F158" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>670.3786986745525</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C159" t="n">
-        <v>681.8680504402118</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D159" t="n">
-        <v>670.2188736545023</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E159" t="n">
-        <v>677.9916381835938</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F159" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>673.6156618787633</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C160" t="n">
-        <v>677.5520159823654</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D160" t="n">
-        <v>665.0136491453696</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E160" t="n">
-        <v>670.7183837890625</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F160" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>668.2905997420939</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C161" t="n">
-        <v>673.6256820299297</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D161" t="n">
-        <v>663.1953464496755</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E161" t="n">
-        <v>668.5004272460938</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F161" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>618.7465567527638</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C162" t="n">
-        <v>620.2751083620838</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D162" t="n">
-        <v>599.4444385151393</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E162" t="n">
-        <v>611.3433837890625</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F162" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>614.120842749119</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C163" t="n">
-        <v>618.3069655430758</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D163" t="n">
-        <v>605.5487701514051</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E163" t="n">
-        <v>608.1863403320312</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F163" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>607.3771038685389</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C164" t="n">
-        <v>613.4314904063681</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D164" t="n">
-        <v>602.1919069095087</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E164" t="n">
-        <v>609.8447875976562</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F164" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>612.7420849871345</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C165" t="n">
-        <v>613.7811000159977</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D165" t="n">
-        <v>599.8040642277598</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E165" t="n">
-        <v>604.3998413085938</v>
+        <v>612.3125</v>
       </c>
       <c r="F165" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>600.4934370812971</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C166" t="n">
-        <v>619.3759607512419</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D166" t="n">
-        <v>597.5461564796674</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E166" t="n">
-        <v>612.3125</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F166" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>614.150739078972</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C167" t="n">
-        <v>624.4012480600104</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D167" t="n">
-        <v>612.9718390781961</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E167" t="n">
-        <v>616.2388305664062</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F167" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>614.6303402495529</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C168" t="n">
-        <v>616.1988937552933</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D168" t="n">
-        <v>605.4987892063378</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E168" t="n">
-        <v>609.0654907226562</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F168" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>604.010215830275</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C169" t="n">
-        <v>604.3498668649182</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D169" t="n">
-        <v>597.5262348938886</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E169" t="n">
-        <v>598.3054809570312</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F169" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>594.2692320029287</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C170" t="n">
-        <v>603.1909559259367</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D170" t="n">
-        <v>592.0512559095129</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E170" t="n">
-        <v>602.441650390625</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F170" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>598.275515544453</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C171" t="n">
-        <v>619.3260125714435</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D171" t="n">
-        <v>596.1074810052941</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E171" t="n">
-        <v>616.0590209960938</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F171" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>615.4296182023591</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C172" t="n">
-        <v>623.152441138389</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D172" t="n">
-        <v>614.4305441468357</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E172" t="n">
-        <v>617.8573608398438</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F172" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>613.421486859321</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C173" t="n">
-        <v>620.6248329546977</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D173" t="n">
-        <v>608.7458274653094</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E173" t="n">
-        <v>613.6612548828125</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F173" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>608.5459509764945</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C174" t="n">
-        <v>615.0199919776213</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D174" t="n">
-        <v>603.1309869574205</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E174" t="n">
-        <v>610.64404296875</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F174" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>608.3561568042173</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C175" t="n">
-        <v>613.361527578881</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D175" t="n">
-        <v>599.9939118379299</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E175" t="n">
-        <v>602.052001953125</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F175" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>600.2037495434126</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C176" t="n">
-        <v>607.4370360716302</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D176" t="n">
-        <v>597.2564688338498</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E176" t="n">
-        <v>604.499755859375</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F176" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>599.4443949814065</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C177" t="n">
-        <v>609.0354809096541</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D177" t="n">
-        <v>594.2591985256718</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E177" t="n">
-        <v>606.8175659179688</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F177" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>607.3171451453314</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C178" t="n">
-        <v>614.2407210713809</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D178" t="n">
-        <v>606.3880135859368</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E178" t="n">
-        <v>609.6949462890625</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F178" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>608.3261927003538</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C179" t="n">
-        <v>613.9009818092591</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D179" t="n">
-        <v>604.7394901495815</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E179" t="n">
-        <v>611.7730102539062</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F179" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>608.8357727220844</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C180" t="n">
-        <v>637.908804248614</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D180" t="n">
-        <v>608.4361186960156</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E180" t="n">
-        <v>634.6718139648438</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F180" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>638.9078448274123</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C181" t="n">
-        <v>642.4046039468743</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D181" t="n">
-        <v>628.7272779804616</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E181" t="n">
-        <v>634.7017211914062</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F181" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>632.9133899267435</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C182" t="n">
-        <v>633.9124639439917</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D182" t="n">
-        <v>622.7727642602187</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E182" t="n">
-        <v>631.92431640625</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F182" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>629.8162791560948</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C183" t="n">
-        <v>635.1613007084701</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D183" t="n">
-        <v>598.9748694014791</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E183" t="n">
-        <v>599.9139404296875</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F183" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>602.6813896226799</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C184" t="n">
-        <v>608.3161816139932</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D184" t="n">
-        <v>596.1274666259658</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E184" t="n">
-        <v>597.0765991210938</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F184" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>602.4416570391962</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C185" t="n">
-        <v>623.5720977596394</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D185" t="n">
-        <v>599.7142043737263</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E185" t="n">
-        <v>622.4031372070312</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F185" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>623.0924785224576</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C186" t="n">
-        <v>641.8051764288737</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D186" t="n">
-        <v>621.8536364911718</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E186" t="n">
-        <v>626.9888916015625</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F186" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>622.8827460758752</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C187" t="n">
-        <v>628.5674800138549</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D187" t="n">
-        <v>582.3702434655938</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E187" t="n">
-        <v>592.450927734375</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F187" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>591.4518261333767</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C188" t="n">
-        <v>591.4518261333767</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D188" t="n">
-        <v>578.6836307521693</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E188" t="n">
-        <v>584.8479614257812</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F188" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>590.4527436689563</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C189" t="n">
-        <v>597.0766092757164</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D189" t="n">
-        <v>580.4720040020986</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E189" t="n">
-        <v>584.0487060546875</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F189" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>580.192266144374</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C190" t="n">
-        <v>590.7724873942649</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D190" t="n">
-        <v>570.0716409197756</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E190" t="n">
-        <v>570.4512939453125</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F190" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>565.3060574843756</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C191" t="n">
-        <v>571.6401524850257</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D191" t="n">
-        <v>556.4942175026772</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E191" t="n">
-        <v>567.9036254882812</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F191" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,25 +5409,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>572.4194595335534</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C192" t="n">
-        <v>575.5365655300229</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D192" t="n">
-        <v>560.3806300495169</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E192" t="n">
-        <v>566.4549560546875</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F192" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5435,25 +5435,25 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>579.9000244140625</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C193" t="n">
-        <v>601.27001953125</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D193" t="n">
-        <v>579.2999877929688</v>
+        <v>592</v>
       </c>
       <c r="E193" t="n">
-        <v>593.47998046875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F193" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G193" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>593.6500244140625</v>
+        <v>592</v>
       </c>
       <c r="C194" t="n">
-        <v>605.8099975585938</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D194" t="n">
-        <v>592</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E194" t="n">
-        <v>600.2100219726562</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F194" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>592</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C195" t="n">
-        <v>593.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D195" t="n">
-        <v>566.1900024414062</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E195" t="n">
-        <v>567.5800170898438</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F195" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>572.8200073242188</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C196" t="n">
-        <v>580.219970703125</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D196" t="n">
-        <v>563.0999755859375</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E196" t="n">
-        <v>577.219970703125</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F196" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>572.02001953125</v>
+        <v>562.25</v>
       </c>
       <c r="C197" t="n">
-        <v>575.8099975585938</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D197" t="n">
-        <v>559.8099975585938</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E197" t="n">
-        <v>563.8499755859375</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F197" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>562.25</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C198" t="n">
-        <v>572.2000122070312</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D198" t="n">
-        <v>561.02001953125</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E198" t="n">
-        <v>562.2000122070312</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F198" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>561.8900146484375</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C199" t="n">
-        <v>569.0399780273438</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D199" t="n">
-        <v>555.5499877929688</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E199" t="n">
-        <v>557.6699829101562</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F199" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>555.5499877929688</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C200" t="n">
-        <v>556.3400268554688</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D200" t="n">
-        <v>540.1799926757812</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E200" t="n">
-        <v>542.8699951171875</v>
+        <v>550.25</v>
       </c>
       <c r="F200" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>543.3400268554688</v>
+        <v>560</v>
       </c>
       <c r="C201" t="n">
-        <v>556.8499755859375</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D201" t="n">
-        <v>540.4000244140625</v>
+        <v>558</v>
       </c>
       <c r="E201" t="n">
-        <v>550.25</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F201" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>560</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C202" t="n">
-        <v>570.9000244140625</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D202" t="n">
-        <v>558</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E202" t="n">
-        <v>562.5999755859375</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F202" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C203" t="n">
-        <v>565.5399780273438</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D203" t="n">
-        <v>551.4299926757812</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E203" t="n">
-        <v>563.2899780273438</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F203" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>607.9099731445312</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C204" t="n">
-        <v>628.280029296875</v>
+        <v>610</v>
       </c>
       <c r="D204" t="n">
-        <v>595.0999755859375</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E204" t="n">
-        <v>612.9099731445312</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F204" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>607.9000244140625</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C205" t="n">
-        <v>610</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D205" t="n">
-        <v>580.4199829101562</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E205" t="n">
-        <v>582.9000244140625</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F205" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>594.8400268554688</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C206" t="n">
-        <v>603.5800170898438</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D206" t="n">
-        <v>581.760009765625</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E206" t="n">
-        <v>600.2899780273438</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F206" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>607.5900268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C207" t="n">
-        <v>625.3699951171875</v>
+        <v>616</v>
       </c>
       <c r="D207" t="n">
-        <v>603.6599731445312</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E207" t="n">
-        <v>615.5800170898438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F207" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>614.3900146484375</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C208" t="n">
-        <v>616</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D208" t="n">
-        <v>598.010009765625</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E208" t="n">
-        <v>603.1199951171875</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F208" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>583.989990234375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C209" t="n">
-        <v>633.27001953125</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D209" t="n">
-        <v>577.0700073242188</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E209" t="n">
-        <v>631.47998046875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F209" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>660.3400268554688</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C210" t="n">
-        <v>677.8599853515625</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D210" t="n">
-        <v>658.010009765625</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E210" t="n">
-        <v>669.2100219726562</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F210" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>661.3800048828125</v>
+        <v>652</v>
       </c>
       <c r="C211" t="n">
-        <v>676.6199951171875</v>
+        <v>666.5</v>
       </c>
       <c r="D211" t="n">
-        <v>654.2000122070312</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E211" t="n">
-        <v>656.72998046875</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F211" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>652</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C212" t="n">
-        <v>666.5</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D212" t="n">
-        <v>649.0499877929688</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E212" t="n">
-        <v>661.0399780273438</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F212" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>663.5999755859375</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C213" t="n">
-        <v>686.0800170898438</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D213" t="n">
-        <v>656.6599731445312</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E213" t="n">
-        <v>681.3099975585938</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F213" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>677.280029296875</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C214" t="n">
-        <v>681.9000244140625</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D214" t="n">
-        <v>660.1599731445312</v>
+        <v>626</v>
       </c>
       <c r="E214" t="n">
-        <v>664.5399780273438</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F214" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>647.7000122070312</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C215" t="n">
-        <v>652.2000122070312</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D215" t="n">
-        <v>626</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E215" t="n">
-        <v>646.010009765625</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F215" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>646.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C216" t="n">
-        <v>653.2999877929688</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D216" t="n">
-        <v>636.010009765625</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E216" t="n">
-        <v>645.8499755859375</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F216" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>654.1799926757812</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C217" t="n">
-        <v>655.8800048828125</v>
+        <v>649</v>
       </c>
       <c r="D217" t="n">
-        <v>643.2000122070312</v>
+        <v>624</v>
       </c>
       <c r="E217" t="n">
-        <v>643.8099975585938</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F217" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>647.7000122070312</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C218" t="n">
-        <v>649</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D218" t="n">
-        <v>624</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E218" t="n">
-        <v>627.1699829101562</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F218" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>608.4099731445312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C219" t="n">
-        <v>614.6500244140625</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D219" t="n">
-        <v>597.219970703125</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E219" t="n">
-        <v>606.0999755859375</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F219" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>605.2999877929688</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C220" t="n">
-        <v>609.97998046875</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D220" t="n">
-        <v>594.4500122070312</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E220" t="n">
-        <v>595.1900024414062</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F220" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>607.219970703125</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C221" t="n">
-        <v>611.260009765625</v>
+        <v>601</v>
       </c>
       <c r="D221" t="n">
-        <v>593.1300048828125</v>
+        <v>587</v>
       </c>
       <c r="E221" t="n">
-        <v>593.8699951171875</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F221" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>596.8200073242188</v>
+        <v>593.25</v>
       </c>
       <c r="C222" t="n">
-        <v>601</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D222" t="n">
-        <v>587</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E222" t="n">
-        <v>593.4099731445312</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F222" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>593.25</v>
+        <v>526</v>
       </c>
       <c r="C223" t="n">
-        <v>599.969970703125</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D223" t="n">
-        <v>582.219970703125</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E223" t="n">
-        <v>585.6099853515625</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F223" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>526</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C224" t="n">
-        <v>539.8800048828125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D224" t="n">
-        <v>524.489990234375</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E224" t="n">
-        <v>539.030029296875</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F224" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>543.5999755859375</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C225" t="n">
-        <v>558.3300170898438</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D225" t="n">
-        <v>540.219970703125</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E225" t="n">
-        <v>556.7100219726562</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F225" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>562.239990234375</v>
+        <v>581.5</v>
       </c>
       <c r="C226" t="n">
-        <v>597.52001953125</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D226" t="n">
-        <v>559.3599853515625</v>
+        <v>578.25</v>
       </c>
       <c r="E226" t="n">
-        <v>590.239990234375</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F226" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>581.5</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C227" t="n">
-        <v>592.7899780273438</v>
+        <v>601</v>
       </c>
       <c r="D227" t="n">
-        <v>578.25</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E227" t="n">
-        <v>587.9400024414062</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F227" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>600.4600219726562</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C228" t="n">
-        <v>601</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D228" t="n">
-        <v>580.1199951171875</v>
+        <v>586</v>
       </c>
       <c r="E228" t="n">
-        <v>588.77001953125</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F228" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>586.9500122070312</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C229" t="n">
-        <v>595.3099975585938</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D229" t="n">
-        <v>586</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E229" t="n">
-        <v>589.9000244140625</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F229" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>585.6400146484375</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C230" t="n">
-        <v>598.739990234375</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D230" t="n">
-        <v>585.6199951171875</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E230" t="n">
-        <v>592.0999755859375</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F230" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>599.1300048828125</v>
+        <v>598</v>
       </c>
       <c r="C231" t="n">
-        <v>608.2100219726562</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D231" t="n">
-        <v>592.030029296875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E231" t="n">
-        <v>594.9199829101562</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F231" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>598</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C232" t="n">
-        <v>612.4299926757812</v>
+        <v>604.5</v>
       </c>
       <c r="D232" t="n">
-        <v>593.4000244140625</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E232" t="n">
-        <v>599.1199951171875</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F232" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>601.0700073242188</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C233" t="n">
-        <v>604.5</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D233" t="n">
-        <v>578.2100219726562</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E233" t="n">
-        <v>578.8499755859375</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F233" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>580.7100219726562</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C234" t="n">
-        <v>595.8499755859375</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D234" t="n">
-        <v>579.3900146484375</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E234" t="n">
-        <v>594.969970703125</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F234" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>596.97998046875</v>
+        <v>589.75</v>
       </c>
       <c r="C235" t="n">
-        <v>601.8599853515625</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D235" t="n">
-        <v>589.2899780273438</v>
+        <v>564.75</v>
       </c>
       <c r="E235" t="n">
-        <v>589.8499755859375</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F235" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>589.75</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C236" t="n">
-        <v>590.239990234375</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D236" t="n">
-        <v>564.75</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E236" t="n">
-        <v>568.969970703125</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F236" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>557.47998046875</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C237" t="n">
-        <v>560.6599731445312</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D237" t="n">
-        <v>543.2100219726562</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E237" t="n">
-        <v>543.6699829101562</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F237" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>541.3400268554688</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C238" t="n">
-        <v>554.0700073242188</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D238" t="n">
-        <v>537.27001953125</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E238" t="n">
-        <v>546.030029296875</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F238" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>546.9500122070312</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C239" t="n">
-        <v>549.989990234375</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D239" t="n">
-        <v>539.3099975585938</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E239" t="n">
-        <v>545.8300170898438</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F239" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>546.8900146484375</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C240" t="n">
-        <v>553.8699951171875</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D240" t="n">
-        <v>543.22998046875</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E240" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F240" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>550.2000122070312</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C241" t="n">
-        <v>561.4199829101562</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D241" t="n">
-        <v>546.2999877929688</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E241" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F241" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>563.8800048828125</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C242" t="n">
-        <v>570.7999877929688</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D242" t="n">
-        <v>561.4000244140625</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E242" t="n">
-        <v>570.0499877929688</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F242" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>590.3099975585938</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C243" t="n">
-        <v>593.3400268554688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D243" t="n">
-        <v>561.8800048828125</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E243" t="n">
-        <v>576.1400146484375</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F243" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>576.47998046875</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C244" t="n">
-        <v>588.3900146484375</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D244" t="n">
-        <v>567.6199951171875</v>
+        <v>571</v>
       </c>
       <c r="E244" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F244" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>571.5499877929688</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>589.1900024414062</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D245" t="n">
-        <v>571</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E245" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F245" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>577.6300048828125</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C246" t="n">
-        <v>578.6799926757812</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D246" t="n">
-        <v>569.1400146484375</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E246" t="n">
-        <v>572.3400268554688</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F246" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>558.3499755859375</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C247" t="n">
-        <v>584.9500122070312</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D247" t="n">
-        <v>556.0999755859375</v>
+        <v>577</v>
       </c>
       <c r="E247" t="n">
-        <v>578.5399780273438</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F247" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>578.7899780273438</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C248" t="n">
-        <v>600.3800048828125</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D248" t="n">
-        <v>577</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E248" t="n">
-        <v>592.8499755859375</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F248" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>604.489990234375</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C249" t="n">
-        <v>619.4600219726562</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D249" t="n">
-        <v>604.3499755859375</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E249" t="n">
-        <v>610.6799926757812</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F249" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>612.3499755859375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C250" t="n">
-        <v>617.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D250" t="n">
-        <v>605.27001953125</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E250" t="n">
-        <v>616.77001953125</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F250" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>616.2100219726562</v>
+        <v>648.6400146484375</v>
       </c>
       <c r="C251" t="n">
-        <v>624.7999877929688</v>
+        <v>657.8599853515625</v>
       </c>
       <c r="D251" t="n">
-        <v>609.739990234375</v>
+        <v>638.5599975585938</v>
       </c>
       <c r="E251" t="n">
-        <v>613.47998046875</v>
+        <v>653.6900024414062</v>
       </c>
       <c r="F251" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>648.6400146484375</v>
+        <v>653.7100219726562</v>
       </c>
       <c r="C252" t="n">
-        <v>657.8599853515625</v>
+        <v>663.5</v>
       </c>
       <c r="D252" t="n">
-        <v>638.5599975585938</v>
+        <v>642.1400146484375</v>
       </c>
       <c r="E252" t="n">
-        <v>653.6900024414062</v>
+        <v>644.3800048828125</v>
       </c>
       <c r="F252" t="n">
-        <v>35843200</v>
+        <v>21487500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>644.38</v>
+      </c>
+      <c r="D2" t="n">
         <v>653.6900000000001</v>
       </c>
-      <c r="D2" t="n">
-        <v>613.48</v>
-      </c>
       <c r="E2" t="n">
-        <v>648.64</v>
+        <v>653.6</v>
       </c>
       <c r="F2" t="n">
-        <v>657.86</v>
+        <v>663.5</v>
       </c>
       <c r="G2" t="n">
-        <v>638.5601</v>
+        <v>642.14</v>
       </c>
       <c r="H2" t="n">
-        <v>35359694</v>
+        <v>20418899</v>
       </c>
       <c r="I2" t="n">
-        <v>17868936</v>
+        <v>18168488</v>
       </c>
       <c r="J2" t="n">
-        <v>1665279328256</v>
+        <v>1641561980928</v>
       </c>
       <c r="K2" t="n">
-        <v>23.098587</v>
+        <v>24.270433</v>
       </c>
       <c r="L2" t="n">
-        <v>18.698408</v>
+        <v>18.432102</v>
       </c>
       <c r="M2" t="n">
-        <v>28.3</v>
+        <v>26.55</v>
       </c>
       <c r="N2" t="n">
         <v>790.8</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.3762193</v>
+        <v>6.285408</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1687337304064</v>
+        <v>1663620087808</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:19</t>
+          <t>2026-09-11 19:02:54</t>
         </is>
       </c>
     </row>

--- a/data/META_data.xlsx
+++ b/data/META_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>752.1847098305358</v>
+        <v>746.2840072815898</v>
       </c>
       <c r="C2" t="n">
-        <v>754.6266574243845</v>
+        <v>755.095155276553</v>
       </c>
       <c r="D2" t="n">
-        <v>745.9251963321232</v>
+        <v>741.330272625368</v>
       </c>
       <c r="E2" t="n">
-        <v>748.4469604492188</v>
+        <v>753.1216430664062</v>
       </c>
       <c r="F2" t="n">
-        <v>7923300</v>
+        <v>8248600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>746.2840072815898</v>
+        <v>754.9954213012545</v>
       </c>
       <c r="C3" t="n">
-        <v>755.095155276553</v>
+        <v>771.5412279036273</v>
       </c>
       <c r="D3" t="n">
-        <v>741.330272625368</v>
+        <v>749.5333431691193</v>
       </c>
       <c r="E3" t="n">
-        <v>753.1216430664062</v>
+        <v>762.2018432617188</v>
       </c>
       <c r="F3" t="n">
-        <v>8248600</v>
+        <v>10533800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>754.995481759339</v>
+        <v>764.494341124313</v>
       </c>
       <c r="C4" t="n">
-        <v>771.5412896866574</v>
+        <v>778.8074148399552</v>
       </c>
       <c r="D4" t="n">
-        <v>749.5334031898147</v>
+        <v>762.6005237676653</v>
       </c>
       <c r="E4" t="n">
-        <v>762.201904296875</v>
+        <v>776.4551391601562</v>
       </c>
       <c r="F4" t="n">
-        <v>10533800</v>
+        <v>11782500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>764.4944012192615</v>
+        <v>777.4419223006557</v>
       </c>
       <c r="C5" t="n">
-        <v>778.8074760600178</v>
+        <v>780.7311297077449</v>
       </c>
       <c r="D5" t="n">
-        <v>762.6005837137456</v>
+        <v>763.8066193659058</v>
       </c>
       <c r="E5" t="n">
-        <v>776.4552001953125</v>
+        <v>773.1858520507812</v>
       </c>
       <c r="F5" t="n">
-        <v>11782500</v>
+        <v>9400900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>777.4419223006557</v>
+        <v>778.1994774600552</v>
       </c>
       <c r="C6" t="n">
-        <v>780.7311297077449</v>
+        <v>786.203274581819</v>
       </c>
       <c r="D6" t="n">
-        <v>763.8066193659058</v>
+        <v>770.8336042127465</v>
       </c>
       <c r="E6" t="n">
-        <v>773.1858520507812</v>
+        <v>777.7011108398438</v>
       </c>
       <c r="F6" t="n">
-        <v>9400900</v>
+        <v>10955000</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>778.1994163857863</v>
+        <v>783.8508708699721</v>
       </c>
       <c r="C7" t="n">
-        <v>786.2032128794</v>
+        <v>788.2165669565625</v>
       </c>
       <c r="D7" t="n">
-        <v>770.8335437165625</v>
+        <v>766.6771780735046</v>
       </c>
       <c r="E7" t="n">
-        <v>777.7010498046875</v>
+        <v>775.837158203125</v>
       </c>
       <c r="F7" t="n">
-        <v>10955000</v>
+        <v>23696800</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,25 +625,25 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>783.8509325355676</v>
+        <v>779.8218176027002</v>
       </c>
       <c r="C8" t="n">
-        <v>788.2166289656076</v>
+        <v>783.6917575585782</v>
       </c>
       <c r="D8" t="n">
-        <v>766.6772383880447</v>
+        <v>762.4868973227559</v>
       </c>
       <c r="E8" t="n">
-        <v>775.8372192382812</v>
+        <v>763.1751098632812</v>
       </c>
       <c r="F8" t="n">
-        <v>23696800</v>
+        <v>11706900</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -651,25 +651,25 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>779.8218176027002</v>
+        <v>767.2545389947088</v>
       </c>
       <c r="C9" t="n">
-        <v>783.6917575585782</v>
+        <v>768.6010126974617</v>
       </c>
       <c r="D9" t="n">
-        <v>762.4868973227559</v>
+        <v>749.1217058463387</v>
       </c>
       <c r="E9" t="n">
-        <v>763.1751098632812</v>
+        <v>753.4404907226562</v>
       </c>
       <c r="F9" t="n">
-        <v>11706900</v>
+        <v>10872600</v>
       </c>
       <c r="G9" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>767.254476840496</v>
+        <v>755.5349916265823</v>
       </c>
       <c r="C10" t="n">
-        <v>768.6009504341728</v>
+        <v>759.1356124217834</v>
       </c>
       <c r="D10" t="n">
-        <v>749.1216451610411</v>
+        <v>750.5779133776451</v>
       </c>
       <c r="E10" t="n">
-        <v>753.4404296875</v>
+        <v>758.686767578125</v>
       </c>
       <c r="F10" t="n">
-        <v>10872600</v>
+        <v>8828200</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>755.5349916265823</v>
+        <v>751.4954858581857</v>
       </c>
       <c r="C11" t="n">
-        <v>759.1356124217834</v>
+        <v>754.8068807440363</v>
       </c>
       <c r="D11" t="n">
-        <v>750.5779133776451</v>
+        <v>742.6185490172081</v>
       </c>
       <c r="E11" t="n">
-        <v>758.686767578125</v>
+        <v>746.9672241210938</v>
       </c>
       <c r="F11" t="n">
-        <v>8828200</v>
+        <v>10591100</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>751.4954858581857</v>
+        <v>748.0544043789391</v>
       </c>
       <c r="C12" t="n">
-        <v>754.8068807440363</v>
+        <v>749.9793904076555</v>
       </c>
       <c r="D12" t="n">
-        <v>742.6185490172081</v>
+        <v>735.4371957410184</v>
       </c>
       <c r="E12" t="n">
-        <v>746.9672241210938</v>
+        <v>741.8206176757812</v>
       </c>
       <c r="F12" t="n">
-        <v>10591100</v>
+        <v>9696300</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>748.0544659269957</v>
+        <v>746.7777648139662</v>
       </c>
       <c r="C13" t="n">
-        <v>749.9794521140951</v>
+        <v>748.832479543402</v>
       </c>
       <c r="D13" t="n">
-        <v>735.4372562509625</v>
+        <v>737.2326433015477</v>
       </c>
       <c r="E13" t="n">
-        <v>741.8206787109375</v>
+        <v>741.4716186523438</v>
       </c>
       <c r="F13" t="n">
-        <v>9696300</v>
+        <v>9246800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>746.777703342028</v>
+        <v>740.3244937368279</v>
       </c>
       <c r="C14" t="n">
-        <v>748.8324179023273</v>
+        <v>741.0425967294805</v>
       </c>
       <c r="D14" t="n">
-        <v>737.2325826153279</v>
+        <v>724.4158582201331</v>
       </c>
       <c r="E14" t="n">
-        <v>741.4715576171875</v>
+        <v>732.4749145507812</v>
       </c>
       <c r="F14" t="n">
-        <v>9246800</v>
+        <v>16226800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>740.3245554260684</v>
+        <v>719.618385039583</v>
       </c>
       <c r="C15" t="n">
-        <v>741.0426584785586</v>
+        <v>719.9774365591268</v>
       </c>
       <c r="D15" t="n">
-        <v>724.4159185837501</v>
+        <v>708.3576941566364</v>
       </c>
       <c r="E15" t="n">
-        <v>732.4749755859375</v>
+        <v>715.4791870117188</v>
       </c>
       <c r="F15" t="n">
-        <v>16226800</v>
+        <v>20419600</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>719.6183236513255</v>
+        <v>720.7055653205383</v>
       </c>
       <c r="C16" t="n">
-        <v>719.9773751402398</v>
+        <v>725.8821043267139</v>
       </c>
       <c r="D16" t="n">
-        <v>708.357633728991</v>
+        <v>716.2770807321521</v>
       </c>
       <c r="E16" t="n">
-        <v>715.4791259765625</v>
+        <v>725.1639404296875</v>
       </c>
       <c r="F16" t="n">
-        <v>20419600</v>
+        <v>11415300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>720.7055653205383</v>
+        <v>727.7372737109582</v>
       </c>
       <c r="C17" t="n">
-        <v>725.8821043267139</v>
+        <v>729.1037149276121</v>
       </c>
       <c r="D17" t="n">
-        <v>716.2770807321521</v>
+        <v>708.3377167266436</v>
       </c>
       <c r="E17" t="n">
-        <v>725.1639404296875</v>
+        <v>708.7167358398438</v>
       </c>
       <c r="F17" t="n">
-        <v>11415300</v>
+        <v>16154300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>727.7372737109582</v>
+        <v>703.3607165744016</v>
       </c>
       <c r="C18" t="n">
-        <v>729.1037149276121</v>
+        <v>715.0203947681905</v>
       </c>
       <c r="D18" t="n">
-        <v>708.3377167266436</v>
+        <v>688.718804278428</v>
       </c>
       <c r="E18" t="n">
-        <v>708.7167358398438</v>
+        <v>713.8035278320312</v>
       </c>
       <c r="F18" t="n">
-        <v>16154300</v>
+        <v>21654700</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>703.3607165744016</v>
+        <v>715.8581417735932</v>
       </c>
       <c r="C19" t="n">
-        <v>715.0203947681905</v>
+        <v>716.6361476056489</v>
       </c>
       <c r="D19" t="n">
-        <v>688.718804278428</v>
+        <v>703.9192222306009</v>
       </c>
       <c r="E19" t="n">
-        <v>713.8035278320312</v>
+        <v>711.230224609375</v>
       </c>
       <c r="F19" t="n">
-        <v>21654700</v>
+        <v>12062900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>715.8581417735932</v>
+        <v>711.599278595462</v>
       </c>
       <c r="C20" t="n">
-        <v>716.6361476056489</v>
+        <v>717.7832075860277</v>
       </c>
       <c r="D20" t="n">
-        <v>703.9192222306009</v>
+        <v>705.9738944950672</v>
       </c>
       <c r="E20" t="n">
-        <v>711.230224609375</v>
+        <v>715.9779052734375</v>
       </c>
       <c r="F20" t="n">
-        <v>12062900</v>
+        <v>10790600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>711.599278595462</v>
+        <v>716.4167658258609</v>
       </c>
       <c r="C21" t="n">
-        <v>717.7832075860277</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="D21" t="n">
-        <v>705.9738944950672</v>
+        <v>710.5918883665408</v>
       </c>
       <c r="E21" t="n">
-        <v>715.9779052734375</v>
+        <v>731.6072387695312</v>
       </c>
       <c r="F21" t="n">
-        <v>10790600</v>
+        <v>12717200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>716.4167658258609</v>
+        <v>729.0239332852144</v>
       </c>
       <c r="C22" t="n">
-        <v>731.6072387695312</v>
+        <v>733.3626856542741</v>
       </c>
       <c r="D22" t="n">
-        <v>710.5918883665408</v>
+        <v>702.6824691715568</v>
       </c>
       <c r="E22" t="n">
-        <v>731.6072387695312</v>
+        <v>703.4703979492188</v>
       </c>
       <c r="F22" t="n">
-        <v>12717200</v>
+        <v>16980100</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>729.0239332852144</v>
+        <v>711.1603595995662</v>
       </c>
       <c r="C23" t="n">
-        <v>733.3626856542741</v>
+        <v>718.072374881022</v>
       </c>
       <c r="D23" t="n">
-        <v>702.6824691715568</v>
+        <v>705.8042950194317</v>
       </c>
       <c r="E23" t="n">
-        <v>703.4703979492188</v>
+        <v>713.8433837890625</v>
       </c>
       <c r="F23" t="n">
-        <v>16980100</v>
+        <v>9251800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>711.1603595995662</v>
+        <v>705.9440292511955</v>
       </c>
       <c r="C24" t="n">
-        <v>718.072374881022</v>
+        <v>713.6938322702155</v>
       </c>
       <c r="D24" t="n">
-        <v>705.8042950194317</v>
+        <v>697.5159365984832</v>
       </c>
       <c r="E24" t="n">
-        <v>713.8433837890625</v>
+        <v>706.811767578125</v>
       </c>
       <c r="F24" t="n">
-        <v>9251800</v>
+        <v>8829800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>705.9439682909708</v>
+        <v>715.1998794771447</v>
       </c>
       <c r="C25" t="n">
-        <v>713.6937706407739</v>
+        <v>722.0221626881838</v>
       </c>
       <c r="D25" t="n">
-        <v>697.5158763660478</v>
+        <v>707.6694770310874</v>
       </c>
       <c r="E25" t="n">
-        <v>706.8117065429688</v>
+        <v>715.6885986328125</v>
       </c>
       <c r="F25" t="n">
-        <v>8829800</v>
+        <v>10246800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>715.1998794771447</v>
+        <v>715.6886043056783</v>
       </c>
       <c r="C26" t="n">
-        <v>722.0221626881838</v>
+        <v>723.6080097298942</v>
       </c>
       <c r="D26" t="n">
-        <v>707.6694770310874</v>
+        <v>702.0540824517458</v>
       </c>
       <c r="E26" t="n">
-        <v>715.6885986328125</v>
+        <v>710.2228393554688</v>
       </c>
       <c r="F26" t="n">
-        <v>10246800</v>
+        <v>9017000</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>715.6886043056783</v>
+        <v>705.2458014471516</v>
       </c>
       <c r="C27" t="n">
-        <v>723.6080097298942</v>
+        <v>716.6760344343375</v>
       </c>
       <c r="D27" t="n">
-        <v>702.0540824517458</v>
+        <v>704.2882698394852</v>
       </c>
       <c r="E27" t="n">
-        <v>710.2228393554688</v>
+        <v>715.0602416992188</v>
       </c>
       <c r="F27" t="n">
-        <v>9017000</v>
+        <v>12232400</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>705.2458014471516</v>
+        <v>719.3191931642514</v>
       </c>
       <c r="C28" t="n">
-        <v>716.6760344343375</v>
+        <v>731.8665769499745</v>
       </c>
       <c r="D28" t="n">
-        <v>704.2882698394852</v>
+        <v>718.3118034233538</v>
       </c>
       <c r="E28" t="n">
-        <v>715.0602416992188</v>
+        <v>730.2706909179688</v>
       </c>
       <c r="F28" t="n">
-        <v>12232400</v>
+        <v>8900200</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>719.3191931642514</v>
+        <v>734.1107251683979</v>
       </c>
       <c r="C29" t="n">
-        <v>731.8665769499745</v>
+        <v>736.5842723709278</v>
       </c>
       <c r="D29" t="n">
-        <v>718.3118034233538</v>
+        <v>726.8595646449745</v>
       </c>
       <c r="E29" t="n">
-        <v>730.2706909179688</v>
+        <v>731.3678588867188</v>
       </c>
       <c r="F29" t="n">
-        <v>8900200</v>
+        <v>7647300</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>734.1107251683979</v>
+        <v>731.9264006052239</v>
       </c>
       <c r="C30" t="n">
-        <v>736.5842723709278</v>
+        <v>738.6787972623451</v>
       </c>
       <c r="D30" t="n">
-        <v>726.8595646449745</v>
+        <v>722.1518348008319</v>
       </c>
       <c r="E30" t="n">
-        <v>731.3678588867188</v>
+        <v>731.5074462890625</v>
       </c>
       <c r="F30" t="n">
-        <v>7647300</v>
+        <v>8734500</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>731.9264006052239</v>
+        <v>732.7941435868839</v>
       </c>
       <c r="C31" t="n">
-        <v>738.6787972623451</v>
+        <v>740.4841042897723</v>
       </c>
       <c r="D31" t="n">
-        <v>722.1518348008319</v>
+        <v>731.1982575844598</v>
       </c>
       <c r="E31" t="n">
-        <v>731.5074462890625</v>
+        <v>732.095947265625</v>
       </c>
       <c r="F31" t="n">
-        <v>8734500</v>
+        <v>9856000</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>732.7941435868839</v>
+        <v>734.8786455644157</v>
       </c>
       <c r="C32" t="n">
-        <v>740.4841042897723</v>
+        <v>739.2872233202683</v>
       </c>
       <c r="D32" t="n">
-        <v>731.1982575844598</v>
+        <v>729.2533227506186</v>
       </c>
       <c r="E32" t="n">
-        <v>732.095947265625</v>
+        <v>736.444580078125</v>
       </c>
       <c r="F32" t="n">
-        <v>9856000</v>
+        <v>9151300</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>734.8786455644157</v>
+        <v>747.7851152228061</v>
       </c>
       <c r="C33" t="n">
-        <v>739.2872233202683</v>
+        <v>753.7895182960361</v>
       </c>
       <c r="D33" t="n">
-        <v>729.2533227506186</v>
+        <v>746.069606274355</v>
       </c>
       <c r="E33" t="n">
-        <v>736.444580078125</v>
+        <v>748.872314453125</v>
       </c>
       <c r="F33" t="n">
-        <v>9151300</v>
+        <v>11321100</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>747.7851152228061</v>
+        <v>750.6776381609803</v>
       </c>
       <c r="C34" t="n">
-        <v>753.7895182960361</v>
+        <v>756.4326899204912</v>
       </c>
       <c r="D34" t="n">
-        <v>746.069606274355</v>
+        <v>743.5860965317024</v>
       </c>
       <c r="E34" t="n">
-        <v>748.872314453125</v>
+        <v>749.49072265625</v>
       </c>
       <c r="F34" t="n">
-        <v>11321100</v>
+        <v>12193800</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>750.6776381609803</v>
+        <v>752.7921813457194</v>
       </c>
       <c r="C35" t="n">
-        <v>756.4326899204912</v>
+        <v>757.1907150365412</v>
       </c>
       <c r="D35" t="n">
-        <v>743.5860965317024</v>
+        <v>740.5839415998626</v>
       </c>
       <c r="E35" t="n">
-        <v>749.49072265625</v>
+        <v>749.7201538085938</v>
       </c>
       <c r="F35" t="n">
-        <v>12193800</v>
+        <v>26818600</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>752.7921200604676</v>
+        <v>667.414190282622</v>
       </c>
       <c r="C36" t="n">
-        <v>757.1906533932021</v>
+        <v>679.1935516668058</v>
       </c>
       <c r="D36" t="n">
-        <v>740.5838813084906</v>
+        <v>648.4833846789722</v>
       </c>
       <c r="E36" t="n">
-        <v>749.7200927734375</v>
+        <v>664.7410888671875</v>
       </c>
       <c r="F36" t="n">
-        <v>26818600</v>
+        <v>88440100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>667.414190282622</v>
+        <v>672.7602632515434</v>
       </c>
       <c r="C37" t="n">
-        <v>679.1935516668058</v>
+        <v>673.1392823636344</v>
       </c>
       <c r="D37" t="n">
-        <v>648.4833846789722</v>
+        <v>643.8953340746643</v>
       </c>
       <c r="E37" t="n">
-        <v>664.7410888671875</v>
+        <v>646.6680908203125</v>
       </c>
       <c r="F37" t="n">
-        <v>88440100</v>
+        <v>56953200</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>672.7602632515434</v>
+        <v>654.298319497033</v>
       </c>
       <c r="C38" t="n">
-        <v>673.1392823636344</v>
+        <v>657.6196984387726</v>
       </c>
       <c r="D38" t="n">
-        <v>643.8953340746643</v>
+        <v>634.5297257704245</v>
       </c>
       <c r="E38" t="n">
-        <v>646.6680908203125</v>
+        <v>636.0557861328125</v>
       </c>
       <c r="F38" t="n">
-        <v>56953200</v>
+        <v>33003600</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>654.2982567113449</v>
+        <v>626.4107910285981</v>
       </c>
       <c r="C39" t="n">
-        <v>657.619635334369</v>
+        <v>640.0752642850032</v>
       </c>
       <c r="D39" t="n">
-        <v>634.5296648817072</v>
+        <v>624.3860886703497</v>
       </c>
       <c r="E39" t="n">
-        <v>636.0557250976562</v>
+        <v>625.6926879882812</v>
       </c>
       <c r="F39" t="n">
-        <v>33003600</v>
+        <v>27356600</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>626.4107910285981</v>
+        <v>630.6697208898194</v>
       </c>
       <c r="C40" t="n">
-        <v>640.0752642850032</v>
+        <v>640.5639703518489</v>
       </c>
       <c r="D40" t="n">
-        <v>624.3860886703497</v>
+        <v>624.9146693781357</v>
       </c>
       <c r="E40" t="n">
-        <v>625.6926879882812</v>
+        <v>634.30029296875</v>
       </c>
       <c r="F40" t="n">
-        <v>27356600</v>
+        <v>20219900</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>630.6697208898194</v>
+        <v>634.2005186436334</v>
       </c>
       <c r="C41" t="n">
-        <v>640.5639703518489</v>
+        <v>634.3501538797125</v>
       </c>
       <c r="D41" t="n">
-        <v>624.9146693781357</v>
+        <v>616.3968476378337</v>
       </c>
       <c r="E41" t="n">
-        <v>634.30029296875</v>
+        <v>617.3344116210938</v>
       </c>
       <c r="F41" t="n">
-        <v>20219900</v>
+        <v>23628800</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>634.2005186436334</v>
+        <v>614.8907386759073</v>
       </c>
       <c r="C42" t="n">
-        <v>634.3501538797125</v>
+        <v>620.5161224262619</v>
       </c>
       <c r="D42" t="n">
-        <v>616.3968476378337</v>
+        <v>599.6404247494841</v>
       </c>
       <c r="E42" t="n">
-        <v>617.3344116210938</v>
+        <v>620.0972290039062</v>
       </c>
       <c r="F42" t="n">
-        <v>23628800</v>
+        <v>29946800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>614.8907386759073</v>
+        <v>629.4529098843899</v>
       </c>
       <c r="C43" t="n">
-        <v>620.5161224262619</v>
+        <v>633.3527401283538</v>
       </c>
       <c r="D43" t="n">
-        <v>599.6404247494841</v>
+        <v>616.5065400363918</v>
       </c>
       <c r="E43" t="n">
-        <v>620.0972290039062</v>
+        <v>630.1211547851562</v>
       </c>
       <c r="F43" t="n">
-        <v>29946800</v>
+        <v>19245000</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>629.4529708548182</v>
+        <v>626.3709656116134</v>
       </c>
       <c r="C44" t="n">
-        <v>633.3528014765299</v>
+        <v>627.9269165306073</v>
       </c>
       <c r="D44" t="n">
-        <v>616.5065997528014</v>
+        <v>617.7833145947981</v>
       </c>
       <c r="E44" t="n">
-        <v>630.1212158203125</v>
+        <v>625.453369140625</v>
       </c>
       <c r="F44" t="n">
-        <v>19245000</v>
+        <v>13302200</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>626.3709044869131</v>
+        <v>626.5005716840028</v>
       </c>
       <c r="C45" t="n">
-        <v>627.9268552540688</v>
+        <v>627.3583261459861</v>
       </c>
       <c r="D45" t="n">
-        <v>617.7832543081277</v>
+        <v>606.1934022078184</v>
       </c>
       <c r="E45" t="n">
-        <v>625.4533081054688</v>
+        <v>607.43017578125</v>
       </c>
       <c r="F45" t="n">
-        <v>13302200</v>
+        <v>24493300</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>626.5005716840028</v>
+        <v>611.4796659420805</v>
       </c>
       <c r="C46" t="n">
-        <v>627.3583261459861</v>
+        <v>616.0478021853295</v>
       </c>
       <c r="D46" t="n">
-        <v>606.1934022078184</v>
+        <v>601.4357808374693</v>
       </c>
       <c r="E46" t="n">
-        <v>607.43017578125</v>
+        <v>608.3079223632812</v>
       </c>
       <c r="F46" t="n">
-        <v>24493300</v>
+        <v>20973800</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>611.4796659420805</v>
+        <v>600.2288811530552</v>
       </c>
       <c r="C47" t="n">
-        <v>616.0478021853295</v>
+        <v>612.088052043071</v>
       </c>
       <c r="D47" t="n">
-        <v>601.4357808374693</v>
+        <v>593.6560102918138</v>
       </c>
       <c r="E47" t="n">
-        <v>608.3079223632812</v>
+        <v>607.8790283203125</v>
       </c>
       <c r="F47" t="n">
-        <v>20973800</v>
+        <v>20724100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>600.2288811530552</v>
+        <v>607.4600346656293</v>
       </c>
       <c r="C48" t="n">
-        <v>612.088052043071</v>
+        <v>610.1031845088386</v>
       </c>
       <c r="D48" t="n">
-        <v>593.6560102918138</v>
+        <v>593.8554651895852</v>
       </c>
       <c r="E48" t="n">
-        <v>607.8790283203125</v>
+        <v>600.4483032226562</v>
       </c>
       <c r="F48" t="n">
-        <v>20724100</v>
+        <v>16501300</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>607.4600964135232</v>
+        <v>590.065358149623</v>
       </c>
       <c r="C49" t="n">
-        <v>610.1032465254069</v>
+        <v>602.0940719298206</v>
       </c>
       <c r="D49" t="n">
-        <v>593.855525554584</v>
+        <v>582.2656968950795</v>
       </c>
       <c r="E49" t="n">
-        <v>600.4483642578125</v>
+        <v>596.1395874023438</v>
       </c>
       <c r="F49" t="n">
-        <v>16501300</v>
+        <v>25500600</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>590.065358149623</v>
+        <v>592.1797786556917</v>
       </c>
       <c r="C50" t="n">
-        <v>602.0940719298206</v>
+        <v>593.7856483585136</v>
       </c>
       <c r="D50" t="n">
-        <v>582.2656968950795</v>
+        <v>579.7421567881397</v>
       </c>
       <c r="E50" t="n">
-        <v>596.1395874023438</v>
+        <v>588.7886352539062</v>
       </c>
       <c r="F50" t="n">
-        <v>25500600</v>
+        <v>24744700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>592.1797786556917</v>
+        <v>601.9345167857809</v>
       </c>
       <c r="C51" t="n">
-        <v>593.7856483585136</v>
+        <v>605.1461348624172</v>
       </c>
       <c r="D51" t="n">
-        <v>579.7421567881397</v>
+        <v>581.8367616757555</v>
       </c>
       <c r="E51" t="n">
-        <v>588.7886352539062</v>
+        <v>587.6217651367188</v>
       </c>
       <c r="F51" t="n">
-        <v>24744700</v>
+        <v>20603000</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>601.9344542639864</v>
+        <v>586.9734117815261</v>
       </c>
       <c r="C52" t="n">
-        <v>605.1460720070379</v>
+        <v>596.5684523172222</v>
       </c>
       <c r="D52" t="n">
-        <v>581.8367012414765</v>
+        <v>580.3506215479276</v>
       </c>
       <c r="E52" t="n">
-        <v>587.6217041015625</v>
+        <v>592.70849609375</v>
       </c>
       <c r="F52" t="n">
-        <v>20603000</v>
+        <v>21052600</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>586.9734117815261</v>
+        <v>597.1668722231478</v>
       </c>
       <c r="C53" t="n">
-        <v>596.5684523172222</v>
+        <v>615.1002729325323</v>
       </c>
       <c r="D53" t="n">
-        <v>580.3506215479276</v>
+        <v>596.0797338085368</v>
       </c>
       <c r="E53" t="n">
-        <v>592.70849609375</v>
+        <v>611.459716796875</v>
       </c>
       <c r="F53" t="n">
-        <v>21052600</v>
+        <v>23554900</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>597.1668126146857</v>
+        <v>622.3813086708644</v>
       </c>
       <c r="C54" t="n">
-        <v>615.1002115339802</v>
+        <v>635.3974440566444</v>
       </c>
       <c r="D54" t="n">
-        <v>596.0796743085915</v>
+        <v>616.696082618217</v>
       </c>
       <c r="E54" t="n">
-        <v>611.4596557617188</v>
+        <v>634.569580078125</v>
       </c>
       <c r="F54" t="n">
-        <v>23554900</v>
+        <v>25213000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>622.3813086708644</v>
+        <v>636.0358643802724</v>
       </c>
       <c r="C55" t="n">
-        <v>635.3974440566444</v>
+        <v>636.7041093860743</v>
       </c>
       <c r="D55" t="n">
-        <v>616.696082618217</v>
+        <v>629.9915861721055</v>
       </c>
       <c r="E55" t="n">
-        <v>634.569580078125</v>
+        <v>631.9664306640625</v>
       </c>
       <c r="F55" t="n">
-        <v>25213000</v>
+        <v>15209500</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>636.0358029520913</v>
+        <v>634.4299618769652</v>
       </c>
       <c r="C56" t="n">
-        <v>636.7040478933542</v>
+        <v>646.3688812783262</v>
       </c>
       <c r="D56" t="n">
-        <v>629.9915253276793</v>
+        <v>633.8514494094911</v>
       </c>
       <c r="E56" t="n">
-        <v>631.9663696289062</v>
+        <v>646.2691650390625</v>
       </c>
       <c r="F56" t="n">
-        <v>15209500</v>
+        <v>11033200</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>634.4299618769652</v>
+        <v>637.890997336621</v>
       </c>
       <c r="C57" t="n">
-        <v>646.3688812783262</v>
+        <v>643.6460494571635</v>
       </c>
       <c r="D57" t="n">
-        <v>633.8514494094911</v>
+        <v>636.1056625060893</v>
       </c>
       <c r="E57" t="n">
-        <v>646.2691650390625</v>
+        <v>639.2075805664062</v>
       </c>
       <c r="F57" t="n">
-        <v>11033200</v>
+        <v>13029900</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>637.8909364271796</v>
+        <v>640.6737247939117</v>
       </c>
       <c r="C58" t="n">
-        <v>643.6459879981971</v>
+        <v>646.1893476978298</v>
       </c>
       <c r="D58" t="n">
-        <v>636.1056017671217</v>
+        <v>636.4147821721649</v>
       </c>
       <c r="E58" t="n">
-        <v>639.20751953125</v>
+        <v>645.4213256835938</v>
       </c>
       <c r="F58" t="n">
-        <v>13029900</v>
+        <v>11640900</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>640.6737853801045</v>
+        <v>642.7383773862279</v>
       </c>
       <c r="C59" t="n">
-        <v>646.1894088056151</v>
+        <v>647.1668624868771</v>
       </c>
       <c r="D59" t="n">
-        <v>636.4148423556049</v>
+        <v>635.8961867971512</v>
       </c>
       <c r="E59" t="n">
-        <v>645.42138671875</v>
+        <v>637.9408569335938</v>
       </c>
       <c r="F59" t="n">
-        <v>11640900</v>
+        <v>11134300</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>642.7383773862279</v>
+        <v>674.2463992276428</v>
       </c>
       <c r="C60" t="n">
-        <v>647.1668624868771</v>
+        <v>674.3461154685141</v>
       </c>
       <c r="D60" t="n">
-        <v>635.8961867971512</v>
+        <v>658.3377626918029</v>
       </c>
       <c r="E60" t="n">
-        <v>637.9408569335938</v>
+        <v>659.81396484375</v>
       </c>
       <c r="F60" t="n">
-        <v>11134300</v>
+        <v>29874600</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>674.2463992276428</v>
+        <v>662.2775487290173</v>
       </c>
       <c r="C61" t="n">
-        <v>674.3461154685141</v>
+        <v>672.9398207362489</v>
       </c>
       <c r="D61" t="n">
-        <v>658.3377626918029</v>
+        <v>660.6717397649775</v>
       </c>
       <c r="E61" t="n">
-        <v>659.81396484375</v>
+        <v>671.673095703125</v>
       </c>
       <c r="F61" t="n">
-        <v>29874600</v>
+        <v>21207900</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>662.2775487290173</v>
+        <v>667.603701448277</v>
       </c>
       <c r="C62" t="n">
-        <v>672.9398207362489</v>
+        <v>674.9545781663558</v>
       </c>
       <c r="D62" t="n">
-        <v>660.6717397649775</v>
+        <v>663.344758713728</v>
       </c>
       <c r="E62" t="n">
-        <v>671.673095703125</v>
+        <v>665.0702514648438</v>
       </c>
       <c r="F62" t="n">
-        <v>21207900</v>
+        <v>13161000</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>667.603701448277</v>
+        <v>662.0481300460407</v>
       </c>
       <c r="C63" t="n">
-        <v>674.9545781663558</v>
+        <v>662.7562492699393</v>
       </c>
       <c r="D63" t="n">
-        <v>663.344758713728</v>
+        <v>651.6451938720459</v>
       </c>
       <c r="E63" t="n">
-        <v>665.0702514648438</v>
+        <v>655.2557983398438</v>
       </c>
       <c r="F63" t="n">
-        <v>13161000</v>
+        <v>12997100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>662.0481300460407</v>
+        <v>648.2639556943986</v>
       </c>
       <c r="C64" t="n">
-        <v>662.7562492699393</v>
+        <v>652.8121240146866</v>
       </c>
       <c r="D64" t="n">
-        <v>651.6451938720459</v>
+        <v>641.730959438269</v>
       </c>
       <c r="E64" t="n">
-        <v>655.2557983398438</v>
+        <v>648.4434814453125</v>
       </c>
       <c r="F64" t="n">
-        <v>12997100</v>
+        <v>16910900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>648.2639556943986</v>
+        <v>641.6212380225077</v>
       </c>
       <c r="C65" t="n">
-        <v>652.8121240146866</v>
+        <v>653.5801862453618</v>
       </c>
       <c r="D65" t="n">
-        <v>641.730959438269</v>
+        <v>639.1377070000864</v>
       </c>
       <c r="E65" t="n">
-        <v>648.4434814453125</v>
+        <v>651.016845703125</v>
       </c>
       <c r="F65" t="n">
-        <v>16910900</v>
+        <v>13056700</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>641.6212380225077</v>
+        <v>648.1143965293088</v>
       </c>
       <c r="C66" t="n">
-        <v>653.5801862453618</v>
+        <v>709.1556549538686</v>
       </c>
       <c r="D66" t="n">
-        <v>639.1377070000864</v>
+        <v>636.9534211280841</v>
       </c>
       <c r="E66" t="n">
-        <v>651.016845703125</v>
+        <v>642.558837890625</v>
       </c>
       <c r="F66" t="n">
-        <v>13056700</v>
+        <v>14016900</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,25 +2159,25 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>648.1143349664432</v>
+        <v>644.5502809809109</v>
       </c>
       <c r="C67" t="n">
-        <v>709.1555875928369</v>
+        <v>651.8372704406642</v>
       </c>
       <c r="D67" t="n">
-        <v>636.9533606253732</v>
+        <v>637.5627451568915</v>
       </c>
       <c r="E67" t="n">
-        <v>642.5587768554688</v>
+        <v>646.3570556640625</v>
       </c>
       <c r="F67" t="n">
-        <v>14016900</v>
+        <v>15549100</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2185,25 +2185,25 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>644.5502809809109</v>
+        <v>642.3541999133257</v>
       </c>
       <c r="C68" t="n">
-        <v>651.8372704406642</v>
+        <v>661.3602758295988</v>
       </c>
       <c r="D68" t="n">
-        <v>637.5627451568915</v>
+        <v>642.054746271156</v>
       </c>
       <c r="E68" t="n">
-        <v>646.3570556640625</v>
+        <v>655.9799194335938</v>
       </c>
       <c r="F68" t="n">
-        <v>15549100</v>
+        <v>14309100</v>
       </c>
       <c r="G68" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>642.3541401459643</v>
+        <v>654.4426118233187</v>
       </c>
       <c r="C69" t="n">
-        <v>661.3602142938313</v>
+        <v>660.0526000253047</v>
       </c>
       <c r="D69" t="n">
-        <v>642.054686531657</v>
+        <v>648.0440522221027</v>
       </c>
       <c r="E69" t="n">
-        <v>655.9798583984375</v>
+        <v>648.343505859375</v>
       </c>
       <c r="F69" t="n">
-        <v>14309100</v>
+        <v>15598500</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>654.4426118233187</v>
+        <v>655.8600753372949</v>
       </c>
       <c r="C70" t="n">
-        <v>660.0526000253047</v>
+        <v>669.3659511843067</v>
       </c>
       <c r="D70" t="n">
-        <v>648.0440522221027</v>
+        <v>655.2910830082761</v>
       </c>
       <c r="E70" t="n">
-        <v>648.343505859375</v>
+        <v>663.266845703125</v>
       </c>
       <c r="F70" t="n">
-        <v>15598500</v>
+        <v>20260300</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>655.8601356908653</v>
+        <v>665.2333263832898</v>
       </c>
       <c r="C71" t="n">
-        <v>669.366012780715</v>
+        <v>669.8051880946751</v>
       </c>
       <c r="D71" t="n">
-        <v>655.2911433094866</v>
+        <v>657.0080086354003</v>
       </c>
       <c r="E71" t="n">
-        <v>663.2669067382812</v>
+        <v>657.5969848632812</v>
       </c>
       <c r="F71" t="n">
-        <v>20260300</v>
+        <v>49977100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>665.2333263832898</v>
+        <v>660.4719008376494</v>
       </c>
       <c r="C72" t="n">
-        <v>669.8051880946751</v>
+        <v>672.3806511570199</v>
       </c>
       <c r="D72" t="n">
-        <v>657.0080086354003</v>
+        <v>655.4808037586267</v>
       </c>
       <c r="E72" t="n">
-        <v>657.5969848632812</v>
+        <v>660.3221435546875</v>
       </c>
       <c r="F72" t="n">
-        <v>49977100</v>
+        <v>15659400</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>660.4718397886508</v>
+        <v>658.8746741689592</v>
       </c>
       <c r="C73" t="n">
-        <v>672.380589007267</v>
+        <v>664.8140915262984</v>
       </c>
       <c r="D73" t="n">
-        <v>655.4807431709672</v>
+        <v>657.0778915122911</v>
       </c>
       <c r="E73" t="n">
-        <v>660.3220825195312</v>
+        <v>663.7559814453125</v>
       </c>
       <c r="F73" t="n">
-        <v>15659400</v>
+        <v>8486800</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>658.8746741689592</v>
+        <v>661.3503083186049</v>
       </c>
       <c r="C74" t="n">
-        <v>664.8140915262984</v>
+        <v>666.9902112020924</v>
       </c>
       <c r="D74" t="n">
-        <v>657.0778915122911</v>
+        <v>661.0208788671576</v>
       </c>
       <c r="E74" t="n">
-        <v>663.7559814453125</v>
+        <v>666.361328125</v>
       </c>
       <c r="F74" t="n">
-        <v>8486800</v>
+        <v>5627500</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>661.3503688947783</v>
+        <v>666.8704739599774</v>
       </c>
       <c r="C75" t="n">
-        <v>666.9902722948509</v>
+        <v>667.7589038803495</v>
       </c>
       <c r="D75" t="n">
-        <v>661.0209394131572</v>
+        <v>660.1424847097468</v>
       </c>
       <c r="E75" t="n">
-        <v>666.3613891601562</v>
+        <v>662.1089477539062</v>
       </c>
       <c r="F75" t="n">
-        <v>5627500</v>
+        <v>7133800</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>666.8704124858896</v>
+        <v>656.8383689858442</v>
       </c>
       <c r="C76" t="n">
-        <v>667.7588423243637</v>
+        <v>659.0743707339258</v>
       </c>
       <c r="D76" t="n">
-        <v>660.1424238558649</v>
+        <v>653.2248195668056</v>
       </c>
       <c r="E76" t="n">
-        <v>662.10888671875</v>
+        <v>657.5171508789062</v>
       </c>
       <c r="F76" t="n">
-        <v>7133800</v>
+        <v>8506500</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>656.8383689858442</v>
+        <v>657.5171386037911</v>
       </c>
       <c r="C77" t="n">
-        <v>659.0743707339258</v>
+        <v>671.0230153954109</v>
       </c>
       <c r="D77" t="n">
-        <v>653.2248195668056</v>
+        <v>656.6686764849229</v>
       </c>
       <c r="E77" t="n">
-        <v>657.5171508789062</v>
+        <v>664.7642211914062</v>
       </c>
       <c r="F77" t="n">
-        <v>8506500</v>
+        <v>9187500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>657.5171386037911</v>
+        <v>663.5662869980947</v>
       </c>
       <c r="C78" t="n">
-        <v>671.0230153954109</v>
+        <v>663.8158418258488</v>
       </c>
       <c r="D78" t="n">
-        <v>656.6686764849229</v>
+        <v>658.2657448936569</v>
       </c>
       <c r="E78" t="n">
-        <v>664.7642211914062</v>
+        <v>658.9146118164062</v>
       </c>
       <c r="F78" t="n">
-        <v>9187500</v>
+        <v>7940400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>663.5663484641349</v>
+        <v>661.5499009554064</v>
       </c>
       <c r="C79" t="n">
-        <v>663.8159033150052</v>
+        <v>663.2069792218492</v>
       </c>
       <c r="D79" t="n">
-        <v>658.2658058687088</v>
+        <v>642.3541620430398</v>
       </c>
       <c r="E79" t="n">
-        <v>658.9146728515625</v>
+        <v>649.2518310546875</v>
       </c>
       <c r="F79" t="n">
-        <v>7940400</v>
+        <v>13726500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>661.5499631466852</v>
+        <v>649.8508280292294</v>
       </c>
       <c r="C80" t="n">
-        <v>663.2070415689074</v>
+        <v>663.3567049684374</v>
       </c>
       <c r="D80" t="n">
-        <v>642.3542224297569</v>
+        <v>646.5966230035071</v>
       </c>
       <c r="E80" t="n">
-        <v>649.2518920898438</v>
+        <v>657.616943359375</v>
       </c>
       <c r="F80" t="n">
-        <v>13726500</v>
+        <v>12213700</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>649.8508280292294</v>
+        <v>658.3955464147172</v>
       </c>
       <c r="C81" t="n">
-        <v>663.3567049684374</v>
+        <v>664.3349637543794</v>
       </c>
       <c r="D81" t="n">
-        <v>646.5966230035071</v>
+        <v>650.7392210314413</v>
       </c>
       <c r="E81" t="n">
-        <v>657.616943359375</v>
+        <v>659.4436645507812</v>
       </c>
       <c r="F81" t="n">
-        <v>12213700</v>
+        <v>11074400</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>658.3956073528642</v>
+        <v>654.4725487720359</v>
       </c>
       <c r="C82" t="n">
-        <v>664.3350252422523</v>
+        <v>657.9763084361789</v>
       </c>
       <c r="D82" t="n">
-        <v>650.7392812609531</v>
+        <v>643.6618161601232</v>
       </c>
       <c r="E82" t="n">
-        <v>659.4437255859375</v>
+        <v>647.534912109375</v>
       </c>
       <c r="F82" t="n">
-        <v>11074400</v>
+        <v>12846300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>654.4726104611178</v>
+        <v>644.7299347572825</v>
       </c>
       <c r="C83" t="n">
-        <v>657.9763704555172</v>
+        <v>645.9477331499952</v>
       </c>
       <c r="D83" t="n">
-        <v>643.6618768302103</v>
+        <v>634.5879917891143</v>
       </c>
       <c r="E83" t="n">
-        <v>647.5349731445312</v>
+        <v>644.9096069335938</v>
       </c>
       <c r="F83" t="n">
-        <v>12846300</v>
+        <v>11921700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>644.7299347572825</v>
+        <v>644.2907288447692</v>
       </c>
       <c r="C84" t="n">
-        <v>645.9477331499952</v>
+        <v>653.7838050409127</v>
       </c>
       <c r="D84" t="n">
-        <v>634.5879917891143</v>
+        <v>641.7053138036724</v>
       </c>
       <c r="E84" t="n">
-        <v>644.9096069335938</v>
+        <v>651.8971557617188</v>
       </c>
       <c r="F84" t="n">
-        <v>11921700</v>
+        <v>11634900</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>644.2906685217797</v>
+        <v>651.3680980277007</v>
       </c>
       <c r="C85" t="n">
-        <v>653.7837438291153</v>
+        <v>652.8054753941815</v>
       </c>
       <c r="D85" t="n">
-        <v>641.7052537227476</v>
+        <v>640.0881706951194</v>
       </c>
       <c r="E85" t="n">
-        <v>651.8970947265625</v>
+        <v>640.8268432617188</v>
       </c>
       <c r="F85" t="n">
-        <v>11634900</v>
+        <v>14797200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>651.3681600668523</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="C86" t="n">
-        <v>652.8055375702352</v>
+        <v>641.1263941859123</v>
       </c>
       <c r="D86" t="n">
-        <v>640.0882316599212</v>
+        <v>622.9887038024194</v>
       </c>
       <c r="E86" t="n">
-        <v>640.826904296875</v>
+        <v>629.96630859375</v>
       </c>
       <c r="F86" t="n">
-        <v>14797200</v>
+        <v>18030400</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>641.1263941859123</v>
+        <v>625.3844405077801</v>
       </c>
       <c r="C87" t="n">
-        <v>641.1263941859123</v>
+        <v>627.3309804807691</v>
       </c>
       <c r="D87" t="n">
-        <v>622.9887038024194</v>
+        <v>613.7252454803604</v>
       </c>
       <c r="E87" t="n">
-        <v>629.96630859375</v>
+        <v>614.4240112304688</v>
       </c>
       <c r="F87" t="n">
-        <v>18030400</v>
+        <v>15527900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>625.3844405077801</v>
+        <v>617.378703801015</v>
       </c>
       <c r="C88" t="n">
-        <v>627.3309804807691</v>
+        <v>623.0585745209008</v>
       </c>
       <c r="D88" t="n">
-        <v>613.7252454803604</v>
+        <v>613.1362714280776</v>
       </c>
       <c r="E88" t="n">
-        <v>614.4240112304688</v>
+        <v>619.694580078125</v>
       </c>
       <c r="F88" t="n">
-        <v>15527900</v>
+        <v>13076100</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>617.378703801015</v>
+        <v>623.0685636897582</v>
       </c>
       <c r="C89" t="n">
-        <v>623.0585745209008</v>
+        <v>627.9598630097294</v>
       </c>
       <c r="D89" t="n">
-        <v>613.1362714280776</v>
+        <v>618.9758886129073</v>
       </c>
       <c r="E89" t="n">
-        <v>619.694580078125</v>
+        <v>619.1455688476562</v>
       </c>
       <c r="F89" t="n">
-        <v>13076100</v>
+        <v>17012500</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>623.0685636897582</v>
+        <v>606.7976262932837</v>
       </c>
       <c r="C90" t="n">
-        <v>627.9598630097294</v>
+        <v>610.3113781504126</v>
       </c>
       <c r="D90" t="n">
-        <v>618.9758886129073</v>
+        <v>598.9316523845154</v>
       </c>
       <c r="E90" t="n">
-        <v>619.1455688476562</v>
+        <v>603.0443115234375</v>
       </c>
       <c r="F90" t="n">
-        <v>17012500</v>
+        <v>15169600</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>606.7976262932837</v>
+        <v>605.659634898437</v>
       </c>
       <c r="C91" t="n">
-        <v>610.3113781504126</v>
+        <v>617.169133937088</v>
       </c>
       <c r="D91" t="n">
-        <v>598.9316523845154</v>
+        <v>599.0115204374271</v>
       </c>
       <c r="E91" t="n">
-        <v>603.0443115234375</v>
+        <v>611.8685913085938</v>
       </c>
       <c r="F91" t="n">
-        <v>15169600</v>
+        <v>14494700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>605.659634898437</v>
+        <v>628.2293275614567</v>
       </c>
       <c r="C92" t="n">
-        <v>617.169133937088</v>
+        <v>659.3937675491238</v>
       </c>
       <c r="D92" t="n">
-        <v>599.0115204374271</v>
+        <v>625.4343255489129</v>
       </c>
       <c r="E92" t="n">
-        <v>611.8685913085938</v>
+        <v>646.476806640625</v>
       </c>
       <c r="F92" t="n">
-        <v>14494700</v>
+        <v>21394700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>628.2293275614567</v>
+        <v>643.6219561683764</v>
       </c>
       <c r="C93" t="n">
-        <v>659.3937675491238</v>
+        <v>665.3032527677875</v>
       </c>
       <c r="D93" t="n">
-        <v>625.4343255489129</v>
+        <v>643.3025186421843</v>
       </c>
       <c r="E93" t="n">
-        <v>646.476806640625</v>
+        <v>657.5870361328125</v>
       </c>
       <c r="F93" t="n">
-        <v>21394700</v>
+        <v>22797700</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>643.6219561683764</v>
+        <v>663.9456136216552</v>
       </c>
       <c r="C94" t="n">
-        <v>665.3032527677875</v>
+        <v>674.0775639748149</v>
       </c>
       <c r="D94" t="n">
-        <v>643.3025186421843</v>
+        <v>660.1124246688775</v>
       </c>
       <c r="E94" t="n">
-        <v>657.5870361328125</v>
+        <v>671.1627197265625</v>
       </c>
       <c r="F94" t="n">
-        <v>22797700</v>
+        <v>16327400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>663.9456740004919</v>
+        <v>673.3888389297905</v>
       </c>
       <c r="C95" t="n">
-        <v>674.0776252750454</v>
+        <v>675.6148486525956</v>
       </c>
       <c r="D95" t="n">
-        <v>660.1124846991261</v>
+        <v>663.4764668627315</v>
       </c>
       <c r="E95" t="n">
-        <v>671.1627807617188</v>
+        <v>671.7716674804688</v>
       </c>
       <c r="F95" t="n">
-        <v>16327400</v>
+        <v>13297400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>673.3888389297905</v>
+        <v>673.2989295276801</v>
       </c>
       <c r="C96" t="n">
-        <v>675.6148486525956</v>
+        <v>676.4732596455591</v>
       </c>
       <c r="D96" t="n">
-        <v>663.4764668627315</v>
+        <v>664.9138628916613</v>
       </c>
       <c r="E96" t="n">
-        <v>671.7716674804688</v>
+        <v>667.5391845703125</v>
       </c>
       <c r="F96" t="n">
-        <v>13297400</v>
+        <v>25709600</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>673.2989910894674</v>
+        <v>736.1169233837337</v>
       </c>
       <c r="C97" t="n">
-        <v>676.4733214975852</v>
+        <v>742.6752321400184</v>
       </c>
       <c r="D97" t="n">
-        <v>664.9139236867763</v>
+        <v>711.2812198864386</v>
       </c>
       <c r="E97" t="n">
-        <v>667.5392456054688</v>
+        <v>736.995361328125</v>
       </c>
       <c r="F97" t="n">
-        <v>25709600</v>
+        <v>59852900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>736.1169233837337</v>
+        <v>726.2045952530067</v>
       </c>
       <c r="C98" t="n">
-        <v>742.6752321400184</v>
+        <v>730.8662626744616</v>
       </c>
       <c r="D98" t="n">
-        <v>711.2812198864386</v>
+        <v>712.3193905555435</v>
       </c>
       <c r="E98" t="n">
-        <v>736.995361328125</v>
+        <v>715.2241821289062</v>
       </c>
       <c r="F98" t="n">
-        <v>59852900</v>
+        <v>23744600</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>726.2045952530067</v>
+        <v>713.3275184694113</v>
       </c>
       <c r="C99" t="n">
-        <v>730.8662626744616</v>
+        <v>720.0156002559207</v>
       </c>
       <c r="D99" t="n">
-        <v>712.3193905555435</v>
+        <v>702.2672920108814</v>
       </c>
       <c r="E99" t="n">
-        <v>715.2241821289062</v>
+        <v>705.152099609375</v>
       </c>
       <c r="F99" t="n">
-        <v>23744600</v>
+        <v>14365200</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>713.3275184694113</v>
+        <v>706.1104025957663</v>
       </c>
       <c r="C100" t="n">
-        <v>720.0156002559207</v>
+        <v>715.7232596178901</v>
       </c>
       <c r="D100" t="n">
-        <v>702.2672920108814</v>
+        <v>685.1877035052055</v>
       </c>
       <c r="E100" t="n">
-        <v>705.152099609375</v>
+        <v>690.4683227539062</v>
       </c>
       <c r="F100" t="n">
-        <v>14365200</v>
+        <v>13760700</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>706.1104025957663</v>
+        <v>686.5054510943589</v>
       </c>
       <c r="C101" t="n">
-        <v>715.7232596178901</v>
+        <v>687.6035290584308</v>
       </c>
       <c r="D101" t="n">
-        <v>685.1877035052055</v>
+        <v>666.2715840299333</v>
       </c>
       <c r="E101" t="n">
-        <v>690.4683227539062</v>
+        <v>667.798828125</v>
       </c>
       <c r="F101" t="n">
-        <v>13760700</v>
+        <v>16882800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>686.5053883494637</v>
+        <v>662.3984629374214</v>
       </c>
       <c r="C102" t="n">
-        <v>687.603466213174</v>
+        <v>680.2865379695924</v>
       </c>
       <c r="D102" t="n">
-        <v>666.2715231343633</v>
+        <v>652.3363940764909</v>
       </c>
       <c r="E102" t="n">
-        <v>667.7987670898438</v>
+        <v>669.0166625976562</v>
       </c>
       <c r="F102" t="n">
-        <v>16882800</v>
+        <v>17131800</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>662.3984025060512</v>
+        <v>664.3050190645899</v>
       </c>
       <c r="C103" t="n">
-        <v>680.2864759062725</v>
+        <v>670.7934451675868</v>
       </c>
       <c r="D103" t="n">
-        <v>652.3363345630947</v>
+        <v>645.3488423980709</v>
       </c>
       <c r="E103" t="n">
-        <v>669.0166015625</v>
+        <v>660.2822265625</v>
       </c>
       <c r="F103" t="n">
-        <v>17131800</v>
+        <v>18159300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>664.3050190645899</v>
+        <v>661.9991209626965</v>
       </c>
       <c r="C104" t="n">
-        <v>670.7934451675868</v>
+        <v>682.0932819515241</v>
       </c>
       <c r="D104" t="n">
-        <v>645.3488423980709</v>
+        <v>657.6069922476072</v>
       </c>
       <c r="E104" t="n">
-        <v>660.2822265625</v>
+        <v>676.0140991210938</v>
       </c>
       <c r="F104" t="n">
-        <v>18159300</v>
+        <v>14837500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>661.9991209626965</v>
+        <v>676.39338857878</v>
       </c>
       <c r="C105" t="n">
-        <v>682.0932819515241</v>
+        <v>679.4380062536881</v>
       </c>
       <c r="D105" t="n">
-        <v>657.6069922476072</v>
+        <v>668.5972981068446</v>
       </c>
       <c r="E105" t="n">
-        <v>676.0140991210938</v>
+        <v>669.525634765625</v>
       </c>
       <c r="F105" t="n">
-        <v>14837500</v>
+        <v>10455800</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>676.3934502400131</v>
+        <v>672.7998711552045</v>
       </c>
       <c r="C106" t="n">
-        <v>679.4380681924739</v>
+        <v>678.0605068549233</v>
       </c>
       <c r="D106" t="n">
-        <v>668.597359057372</v>
+        <v>655.9299390360635</v>
       </c>
       <c r="E106" t="n">
-        <v>669.5256958007812</v>
+        <v>667.4993286132812</v>
       </c>
       <c r="F106" t="n">
-        <v>10455800</v>
+        <v>14323800</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>672.7998711552045</v>
+        <v>668.7770306530766</v>
       </c>
       <c r="C107" t="n">
-        <v>678.0605068549233</v>
+        <v>674.7963229561075</v>
       </c>
       <c r="D107" t="n">
-        <v>655.9299390360635</v>
+        <v>644.1310518439949</v>
       </c>
       <c r="E107" t="n">
-        <v>667.4993286132812</v>
+        <v>648.6529541015625</v>
       </c>
       <c r="F107" t="n">
-        <v>14323800</v>
+        <v>14960100</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>668.7770306530766</v>
+        <v>643.9512634857649</v>
       </c>
       <c r="C108" t="n">
-        <v>674.7963229561075</v>
+        <v>650.2700088851722</v>
       </c>
       <c r="D108" t="n">
-        <v>644.1310518439949</v>
+        <v>633.4400456540794</v>
       </c>
       <c r="E108" t="n">
-        <v>648.6529541015625</v>
+        <v>638.6307983398438</v>
       </c>
       <c r="F108" t="n">
-        <v>14960100</v>
+        <v>12336400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>643.9513250294082</v>
+        <v>638.3613203754355</v>
       </c>
       <c r="C109" t="n">
-        <v>650.2700710327099</v>
+        <v>641.4557762130754</v>
       </c>
       <c r="D109" t="n">
-        <v>633.4401061931457</v>
+        <v>627.6803603746322</v>
       </c>
       <c r="E109" t="n">
-        <v>638.630859375</v>
+        <v>638.1516723632812</v>
       </c>
       <c r="F109" t="n">
-        <v>12336400</v>
+        <v>12674700</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>638.3612593202278</v>
+        <v>632.67143641335</v>
       </c>
       <c r="C110" t="n">
-        <v>641.4557148619026</v>
+        <v>643.8515057528024</v>
       </c>
       <c r="D110" t="n">
-        <v>627.6803003409905</v>
+        <v>627.0315334227189</v>
       </c>
       <c r="E110" t="n">
-        <v>638.151611328125</v>
+        <v>642.0746459960938</v>
       </c>
       <c r="F110" t="n">
-        <v>12674700</v>
+        <v>14649200</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>632.67143641335</v>
+        <v>637.432932921519</v>
       </c>
       <c r="C111" t="n">
-        <v>643.8515057528024</v>
+        <v>646.0375787806976</v>
       </c>
       <c r="D111" t="n">
-        <v>627.0315334227189</v>
+        <v>635.5861905818066</v>
       </c>
       <c r="E111" t="n">
-        <v>642.0746459960938</v>
+        <v>643.6318969726562</v>
       </c>
       <c r="F111" t="n">
-        <v>14649200</v>
+        <v>10035700</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>637.432932921519</v>
+        <v>638.5510179511008</v>
       </c>
       <c r="C112" t="n">
-        <v>646.0375787806976</v>
+        <v>662.1688639053526</v>
       </c>
       <c r="D112" t="n">
-        <v>635.5861905818066</v>
+        <v>637.642665037141</v>
       </c>
       <c r="E112" t="n">
-        <v>643.6318969726562</v>
+        <v>654.4925537109375</v>
       </c>
       <c r="F112" t="n">
-        <v>10035700</v>
+        <v>14183500</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>638.5509584025834</v>
+        <v>651.3781101885919</v>
       </c>
       <c r="C113" t="n">
-        <v>662.1688021543367</v>
+        <v>656.5289567660449</v>
       </c>
       <c r="D113" t="n">
-        <v>637.6426055733327</v>
+        <v>634.8675821094057</v>
       </c>
       <c r="E113" t="n">
-        <v>654.4924926757812</v>
+        <v>636.1153564453125</v>
       </c>
       <c r="F113" t="n">
-        <v>14183500</v>
+        <v>8605900</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>651.3780476889771</v>
+        <v>631.9527863953055</v>
       </c>
       <c r="C114" t="n">
-        <v>656.5288937722072</v>
+        <v>639.9684568961466</v>
       </c>
       <c r="D114" t="n">
-        <v>634.8675211939732</v>
+        <v>627.8600500948714</v>
       </c>
       <c r="E114" t="n">
-        <v>636.1152954101562</v>
+        <v>638.1616821289062</v>
       </c>
       <c r="F114" t="n">
-        <v>8605900</v>
+        <v>10135600</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>631.9527259539814</v>
+        <v>641.3858999809694</v>
       </c>
       <c r="C115" t="n">
-        <v>639.9683956881865</v>
+        <v>652.7156650876909</v>
       </c>
       <c r="D115" t="n">
-        <v>627.8599900449855</v>
+        <v>640.9965798171046</v>
       </c>
       <c r="E115" t="n">
-        <v>638.16162109375</v>
+        <v>652.5260009765625</v>
       </c>
       <c r="F115" t="n">
-        <v>10135600</v>
+        <v>11330700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>641.3859599741169</v>
+        <v>649.3916295582877</v>
       </c>
       <c r="C116" t="n">
-        <v>652.7157261405878</v>
+        <v>659.823034651462</v>
       </c>
       <c r="D116" t="n">
-        <v>640.9966397738364</v>
+        <v>646.3470725216666</v>
       </c>
       <c r="E116" t="n">
-        <v>652.5260620117188</v>
+        <v>655.8401489257812</v>
       </c>
       <c r="F116" t="n">
-        <v>11330700</v>
+        <v>10637700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>649.3916295582877</v>
+        <v>642.3042597917192</v>
       </c>
       <c r="C117" t="n">
-        <v>659.823034651462</v>
+        <v>648.2835840137412</v>
       </c>
       <c r="D117" t="n">
-        <v>646.3470725216666</v>
+        <v>636.9837335400734</v>
       </c>
       <c r="E117" t="n">
-        <v>655.8401489257812</v>
+        <v>647.0258178710938</v>
       </c>
       <c r="F117" t="n">
-        <v>10637700</v>
+        <v>15703000</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>642.3043203814821</v>
+        <v>636.0254184162494</v>
       </c>
       <c r="C118" t="n">
-        <v>648.2836451675449</v>
+        <v>658.764884603327</v>
       </c>
       <c r="D118" t="n">
-        <v>636.9837936279411</v>
+        <v>633.3701817354564</v>
       </c>
       <c r="E118" t="n">
-        <v>647.02587890625</v>
+        <v>652.396240234375</v>
       </c>
       <c r="F118" t="n">
-        <v>15703000</v>
+        <v>9816100</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>636.0254184162494</v>
+        <v>647.1356255764312</v>
       </c>
       <c r="C119" t="n">
-        <v>658.764884603327</v>
+        <v>657.866484005116</v>
       </c>
       <c r="D119" t="n">
-        <v>633.3701817354564</v>
+        <v>637.7025010942567</v>
       </c>
       <c r="E119" t="n">
-        <v>652.396240234375</v>
+        <v>653.91357421875</v>
       </c>
       <c r="F119" t="n">
-        <v>9816100</v>
+        <v>12263800</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>647.1356255764312</v>
+        <v>656.7884535878291</v>
       </c>
       <c r="C120" t="n">
-        <v>657.866484005116</v>
+        <v>671.5720803574089</v>
       </c>
       <c r="D120" t="n">
-        <v>637.7025010942567</v>
+        <v>656.4989309709863</v>
       </c>
       <c r="E120" t="n">
-        <v>653.91357421875</v>
+        <v>666.541015625</v>
       </c>
       <c r="F120" t="n">
-        <v>12263800</v>
+        <v>10810100</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>656.7884535878291</v>
+        <v>660.751362594833</v>
       </c>
       <c r="C121" t="n">
-        <v>671.5720803574089</v>
+        <v>669.5057662619517</v>
       </c>
       <c r="D121" t="n">
-        <v>656.4989309709863</v>
+        <v>649.1520579976961</v>
       </c>
       <c r="E121" t="n">
-        <v>666.541015625</v>
+        <v>659.393798828125</v>
       </c>
       <c r="F121" t="n">
-        <v>10810100</v>
+        <v>13341400</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>660.751362594833</v>
+        <v>646.7463568472266</v>
       </c>
       <c r="C122" t="n">
-        <v>669.5057662619517</v>
+        <v>648.3135076492586</v>
       </c>
       <c r="D122" t="n">
-        <v>649.1520579976961</v>
+        <v>634.9773114336934</v>
       </c>
       <c r="E122" t="n">
-        <v>659.393798828125</v>
+        <v>643.7117309570312</v>
       </c>
       <c r="F122" t="n">
-        <v>13341400</v>
+        <v>13159400</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>646.7463568472266</v>
+        <v>633.6497121926325</v>
       </c>
       <c r="C123" t="n">
-        <v>648.3135076492586</v>
+        <v>646.5965879982328</v>
       </c>
       <c r="D123" t="n">
-        <v>634.9773114336934</v>
+        <v>625.6639573427893</v>
       </c>
       <c r="E123" t="n">
-        <v>643.7117309570312</v>
+        <v>646.2372436523438</v>
       </c>
       <c r="F123" t="n">
-        <v>13159400</v>
+        <v>13489700</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>633.6497720389343</v>
+        <v>652.3962938458964</v>
       </c>
       <c r="C124" t="n">
-        <v>646.596649067328</v>
+        <v>659.1242831137364</v>
       </c>
       <c r="D124" t="n">
-        <v>625.6640164348609</v>
+        <v>647.8444156429986</v>
       </c>
       <c r="E124" t="n">
-        <v>646.2373046875</v>
+        <v>652.9053955078125</v>
       </c>
       <c r="F124" t="n">
-        <v>13489700</v>
+        <v>9859300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>652.3962328583322</v>
+        <v>653.5941721528687</v>
       </c>
       <c r="C125" t="n">
-        <v>659.1242214972237</v>
+        <v>657.9463943013674</v>
       </c>
       <c r="D125" t="n">
-        <v>647.8443550809549</v>
+        <v>647.2055433479961</v>
       </c>
       <c r="E125" t="n">
-        <v>652.9053344726562</v>
+        <v>653.6939697265625</v>
       </c>
       <c r="F125" t="n">
-        <v>9859300</v>
+        <v>8977200</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>653.5941111270305</v>
+        <v>647.5948883988538</v>
       </c>
       <c r="C126" t="n">
-        <v>657.9463328691638</v>
+        <v>652.3364309343367</v>
       </c>
       <c r="D126" t="n">
-        <v>647.2054829186618</v>
+        <v>635.7660119177681</v>
       </c>
       <c r="E126" t="n">
-        <v>653.6939086914062</v>
+        <v>637.043701171875</v>
       </c>
       <c r="F126" t="n">
-        <v>8977200</v>
+        <v>11617500</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>647.5948263527883</v>
+        <v>622.7790526456299</v>
       </c>
       <c r="C127" t="n">
-        <v>652.336368433984</v>
+        <v>628.0496188589474</v>
       </c>
       <c r="D127" t="n">
-        <v>635.7659510050273</v>
+        <v>608.4645611002024</v>
       </c>
       <c r="E127" t="n">
-        <v>637.0436401367188</v>
+        <v>612.6171875</v>
       </c>
       <c r="F127" t="n">
-        <v>11617500</v>
+        <v>18957600</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,25 +3745,25 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>622.7790526456299</v>
+        <v>631.4147932406764</v>
       </c>
       <c r="C128" t="n">
-        <v>628.0496188589474</v>
+        <v>634.1622468505053</v>
       </c>
       <c r="D128" t="n">
-        <v>608.4645611002024</v>
+        <v>622.5230098937741</v>
       </c>
       <c r="E128" t="n">
-        <v>612.6171875</v>
+        <v>626.8690185546875</v>
       </c>
       <c r="F128" t="n">
-        <v>18957600</v>
+        <v>15134900</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -3771,25 +3771,25 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>631.4147932406764</v>
+        <v>627.4085169382369</v>
       </c>
       <c r="C129" t="n">
-        <v>634.1622468505053</v>
+        <v>635.9605885584036</v>
       </c>
       <c r="D129" t="n">
-        <v>622.5230098937741</v>
+        <v>621.1243629754691</v>
       </c>
       <c r="E129" t="n">
-        <v>626.8690185546875</v>
+        <v>622.0834350585938</v>
       </c>
       <c r="F129" t="n">
-        <v>15134900</v>
+        <v>10348800</v>
       </c>
       <c r="G129" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>627.4085169382369</v>
+        <v>615.7693473594539</v>
       </c>
       <c r="C130" t="n">
-        <v>635.9605885584036</v>
+        <v>622.0735023862151</v>
       </c>
       <c r="D130" t="n">
-        <v>621.1243629754691</v>
+        <v>614.04090772979</v>
       </c>
       <c r="E130" t="n">
-        <v>622.0834350585938</v>
+        <v>615.1099243164062</v>
       </c>
       <c r="F130" t="n">
-        <v>10348800</v>
+        <v>11726300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>615.7693473594539</v>
+        <v>611.5832104537112</v>
       </c>
       <c r="C131" t="n">
-        <v>622.0735023862151</v>
+        <v>612.4323990135786</v>
       </c>
       <c r="D131" t="n">
-        <v>614.04090772979</v>
+        <v>601.7023533616688</v>
       </c>
       <c r="E131" t="n">
-        <v>615.1099243164062</v>
+        <v>606.1382446289062</v>
       </c>
       <c r="F131" t="n">
-        <v>11726300</v>
+        <v>13247700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>611.5832104537112</v>
+        <v>602.9712077810872</v>
       </c>
       <c r="C132" t="n">
-        <v>612.4323990135786</v>
+        <v>603.400802317344</v>
       </c>
       <c r="D132" t="n">
-        <v>601.7023533616688</v>
+        <v>586.7062525156723</v>
       </c>
       <c r="E132" t="n">
-        <v>606.1382446289062</v>
+        <v>593.1102905273438</v>
       </c>
       <c r="F132" t="n">
-        <v>13247700</v>
+        <v>21214900</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>602.9712077810872</v>
+        <v>605.2290499891692</v>
       </c>
       <c r="C133" t="n">
-        <v>603.400802317344</v>
+        <v>608.0764476338709</v>
       </c>
       <c r="D133" t="n">
-        <v>586.7062525156723</v>
+        <v>598.4553596033379</v>
       </c>
       <c r="E133" t="n">
-        <v>593.1102905273438</v>
+        <v>603.5006713867188</v>
       </c>
       <c r="F133" t="n">
-        <v>21214900</v>
+        <v>13638000</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>605.2290499891692</v>
+        <v>598.5452420228083</v>
       </c>
       <c r="C134" t="n">
-        <v>608.0764476338709</v>
+        <v>600.443507118967</v>
       </c>
       <c r="D134" t="n">
-        <v>598.4553596033379</v>
+        <v>590.4527665679026</v>
       </c>
       <c r="E134" t="n">
-        <v>603.5006713867188</v>
+        <v>592.3709716796875</v>
       </c>
       <c r="F134" t="n">
-        <v>13638000</v>
+        <v>10739700</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>598.5452420228083</v>
+        <v>598.1855830392399</v>
       </c>
       <c r="C135" t="n">
-        <v>600.443507118967</v>
+        <v>603.1110107561809</v>
       </c>
       <c r="D135" t="n">
-        <v>590.4527665679026</v>
+        <v>592.8505617950721</v>
       </c>
       <c r="E135" t="n">
-        <v>592.3709716796875</v>
+        <v>594.3391723632812</v>
       </c>
       <c r="F135" t="n">
-        <v>10739700</v>
+        <v>12585000</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>598.1855830392399</v>
+        <v>581.9506076701073</v>
       </c>
       <c r="C136" t="n">
-        <v>603.1110107561809</v>
+        <v>582.460145169462</v>
       </c>
       <c r="D136" t="n">
-        <v>592.8505617950721</v>
+        <v>542.8468364624507</v>
       </c>
       <c r="E136" t="n">
-        <v>594.3391723632812</v>
+        <v>547.032958984375</v>
       </c>
       <c r="F136" t="n">
-        <v>12585000</v>
+        <v>35780100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>581.9506076701073</v>
+        <v>539.599843303006</v>
       </c>
       <c r="C137" t="n">
-        <v>582.460145169462</v>
+        <v>543.0966023049141</v>
       </c>
       <c r="D137" t="n">
-        <v>542.8468364624507</v>
+        <v>519.7782492802263</v>
       </c>
       <c r="E137" t="n">
-        <v>547.032958984375</v>
+        <v>525.233154296875</v>
       </c>
       <c r="F137" t="n">
-        <v>35780100</v>
+        <v>30133000</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>539.599843303006</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="C138" t="n">
-        <v>543.0966023049141</v>
+        <v>539.0504095872608</v>
       </c>
       <c r="D138" t="n">
-        <v>519.7782492802263</v>
+        <v>528.0505941707193</v>
       </c>
       <c r="E138" t="n">
-        <v>525.233154296875</v>
+        <v>535.8833618164062</v>
       </c>
       <c r="F138" t="n">
-        <v>30133000</v>
+        <v>22795200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>535.8833618164062</v>
+        <v>549.4707059552647</v>
       </c>
       <c r="C139" t="n">
-        <v>539.0504095872608</v>
+        <v>573.1587727471259</v>
       </c>
       <c r="D139" t="n">
-        <v>528.0505941707193</v>
+        <v>546.2637174010383</v>
       </c>
       <c r="E139" t="n">
-        <v>535.8833618164062</v>
+        <v>571.6002197265625</v>
       </c>
       <c r="F139" t="n">
-        <v>22795200</v>
+        <v>32898300</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>549.4707059552647</v>
+        <v>579.5928556215499</v>
       </c>
       <c r="C140" t="n">
-        <v>573.1587727471259</v>
+        <v>592.0013387220274</v>
       </c>
       <c r="D140" t="n">
-        <v>546.2637174010383</v>
+        <v>573.2887005646345</v>
       </c>
       <c r="E140" t="n">
-        <v>571.6002197265625</v>
+        <v>578.6936645507812</v>
       </c>
       <c r="F140" t="n">
-        <v>32898300</v>
+        <v>23608100</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>579.5928556215499</v>
+        <v>565.5158531822124</v>
       </c>
       <c r="C141" t="n">
-        <v>592.0013387220274</v>
+        <v>577.9643377947169</v>
       </c>
       <c r="D141" t="n">
-        <v>573.2887005646345</v>
+        <v>559.1817578546791</v>
       </c>
       <c r="E141" t="n">
-        <v>578.6936645507812</v>
+        <v>573.9281005859375</v>
       </c>
       <c r="F141" t="n">
-        <v>23608100</v>
+        <v>13518500</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>565.5158531822124</v>
+        <v>577.1550997330287</v>
       </c>
       <c r="C142" t="n">
-        <v>577.9643377947169</v>
+        <v>582.2503530791108</v>
       </c>
       <c r="D142" t="n">
-        <v>559.1817578546791</v>
+        <v>571.4703658572956</v>
       </c>
       <c r="E142" t="n">
-        <v>573.9281005859375</v>
+        <v>572.4894409179688</v>
       </c>
       <c r="F142" t="n">
-        <v>13518500</v>
+        <v>9515700</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>577.1550997330287</v>
+        <v>571.9498894780604</v>
       </c>
       <c r="C143" t="n">
-        <v>582.2503530791108</v>
+        <v>574.6973431004155</v>
       </c>
       <c r="D143" t="n">
-        <v>571.4703658572956</v>
+        <v>564.2370671243236</v>
       </c>
       <c r="E143" t="n">
-        <v>572.4894409179688</v>
+        <v>574.5175170898438</v>
       </c>
       <c r="F143" t="n">
-        <v>9515700</v>
+        <v>9580800</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>571.9498894780604</v>
+        <v>605.4388670235439</v>
       </c>
       <c r="C144" t="n">
-        <v>574.6973431004155</v>
+        <v>629.3667024291958</v>
       </c>
       <c r="D144" t="n">
-        <v>564.2370671243236</v>
+        <v>591.2820049792073</v>
       </c>
       <c r="E144" t="n">
-        <v>574.5175170898438</v>
+        <v>611.8529052734375</v>
       </c>
       <c r="F144" t="n">
-        <v>9580800</v>
+        <v>32036600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>605.4388670235439</v>
+        <v>626.3894374266143</v>
       </c>
       <c r="C145" t="n">
-        <v>629.3667024291958</v>
+        <v>636.9097166035551</v>
       </c>
       <c r="D145" t="n">
-        <v>591.2820049792073</v>
+        <v>622.4231426572783</v>
       </c>
       <c r="E145" t="n">
-        <v>611.8529052734375</v>
+        <v>627.8081665039062</v>
       </c>
       <c r="F145" t="n">
-        <v>32036600</v>
+        <v>19012900</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>626.3894374266143</v>
+        <v>633.882449891805</v>
       </c>
       <c r="C146" t="n">
-        <v>636.9097166035551</v>
+        <v>637.9886903650855</v>
       </c>
       <c r="D146" t="n">
-        <v>622.4231426572783</v>
+        <v>623.7518859014353</v>
       </c>
       <c r="E146" t="n">
-        <v>627.8081665039062</v>
+        <v>629.2767333984375</v>
       </c>
       <c r="F146" t="n">
-        <v>19012900</v>
+        <v>13294800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>633.882449891805</v>
+        <v>628.9171329935918</v>
       </c>
       <c r="C147" t="n">
-        <v>637.9886903650855</v>
+        <v>634.4120404303904</v>
       </c>
       <c r="D147" t="n">
-        <v>623.7518859014353</v>
+        <v>623.8218795800174</v>
       </c>
       <c r="E147" t="n">
-        <v>629.2767333984375</v>
+        <v>633.9425048828125</v>
       </c>
       <c r="F147" t="n">
-        <v>13294800</v>
+        <v>9538900</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>628.9171329935918</v>
+        <v>642.624350345733</v>
       </c>
       <c r="C148" t="n">
-        <v>634.4120404303904</v>
+        <v>665.6430543798978</v>
       </c>
       <c r="D148" t="n">
-        <v>623.8218795800174</v>
+        <v>638.7779398291946</v>
       </c>
       <c r="E148" t="n">
-        <v>633.9425048828125</v>
+        <v>661.8765258789062</v>
       </c>
       <c r="F148" t="n">
-        <v>9538900</v>
+        <v>17818000</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>642.624350345733</v>
+        <v>666.3824145357423</v>
       </c>
       <c r="C149" t="n">
-        <v>665.6430543798978</v>
+        <v>677.8717665104965</v>
       </c>
       <c r="D149" t="n">
-        <v>638.7779398291946</v>
+        <v>663.6049593103575</v>
       </c>
       <c r="E149" t="n">
-        <v>661.8765258789062</v>
+        <v>670.9581909179688</v>
       </c>
       <c r="F149" t="n">
-        <v>17818000</v>
+        <v>14952600</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>666.3824145357423</v>
+        <v>675.3640350842893</v>
       </c>
       <c r="C150" t="n">
-        <v>677.8717665104965</v>
+        <v>676.9525896021297</v>
       </c>
       <c r="D150" t="n">
-        <v>663.6049593103575</v>
+        <v>667.131674939706</v>
       </c>
       <c r="E150" t="n">
-        <v>670.9581909179688</v>
+        <v>676.2432250976562</v>
       </c>
       <c r="F150" t="n">
-        <v>14952600</v>
+        <v>9544800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>675.3640350842893</v>
+        <v>677.9716157075654</v>
       </c>
       <c r="C151" t="n">
-        <v>676.9525896021297</v>
+        <v>690.8796961433965</v>
       </c>
       <c r="D151" t="n">
-        <v>667.131674939706</v>
+        <v>674.5048580761284</v>
       </c>
       <c r="E151" t="n">
-        <v>676.2432250976562</v>
+        <v>687.9124145507812</v>
       </c>
       <c r="F151" t="n">
-        <v>9544800</v>
+        <v>16283500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>677.9716157075654</v>
+        <v>680.7290935491282</v>
       </c>
       <c r="C152" t="n">
-        <v>690.8796961433965</v>
+        <v>682.7472426832454</v>
       </c>
       <c r="D152" t="n">
-        <v>674.5048580761284</v>
+        <v>667.381478611767</v>
       </c>
       <c r="E152" t="n">
-        <v>687.9124145507812</v>
+        <v>670.2887573242188</v>
       </c>
       <c r="F152" t="n">
-        <v>16283500</v>
+        <v>12534000</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>680.7290935491282</v>
+        <v>670.3786762058809</v>
       </c>
       <c r="C153" t="n">
-        <v>682.7472426832454</v>
+        <v>675.5738733736962</v>
       </c>
       <c r="D153" t="n">
-        <v>667.381478611767</v>
+        <v>666.7120915784461</v>
       </c>
       <c r="E153" t="n">
-        <v>670.2887573242188</v>
+        <v>668.220703125</v>
       </c>
       <c r="F153" t="n">
-        <v>12534000</v>
+        <v>8660100</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>670.3786762058809</v>
+        <v>673.7355628200382</v>
       </c>
       <c r="C154" t="n">
-        <v>675.5738733736962</v>
+        <v>677.7518600207422</v>
       </c>
       <c r="D154" t="n">
-        <v>666.7120915784461</v>
+        <v>669.1298460769134</v>
       </c>
       <c r="E154" t="n">
-        <v>668.220703125</v>
+        <v>674.09521484375</v>
       </c>
       <c r="F154" t="n">
-        <v>8660100</v>
+        <v>9215600</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>673.7355628200382</v>
+        <v>663.0854475032797</v>
       </c>
       <c r="C155" t="n">
-        <v>677.7518600207422</v>
+        <v>668.9400066983026</v>
       </c>
       <c r="D155" t="n">
-        <v>669.1298460769134</v>
+        <v>652.4452846667049</v>
       </c>
       <c r="E155" t="n">
-        <v>674.09521484375</v>
+        <v>658.5396728515625</v>
       </c>
       <c r="F155" t="n">
-        <v>9215600</v>
+        <v>11667000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>663.0854475032797</v>
+        <v>659.7085674039201</v>
       </c>
       <c r="C156" t="n">
-        <v>668.9400066983026</v>
+        <v>680.0396994180859</v>
       </c>
       <c r="D156" t="n">
-        <v>652.4452846667049</v>
+        <v>653.2345872360809</v>
       </c>
       <c r="E156" t="n">
-        <v>658.5396728515625</v>
+        <v>674.4049682617188</v>
       </c>
       <c r="F156" t="n">
-        <v>11667000</v>
+        <v>13348300</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>659.7085674039201</v>
+        <v>670.3786986745525</v>
       </c>
       <c r="C157" t="n">
-        <v>680.0396994180859</v>
+        <v>681.8680504402118</v>
       </c>
       <c r="D157" t="n">
-        <v>653.2345872360809</v>
+        <v>670.2188736545023</v>
       </c>
       <c r="E157" t="n">
-        <v>674.4049682617188</v>
+        <v>677.9916381835938</v>
       </c>
       <c r="F157" t="n">
-        <v>13348300</v>
+        <v>12805200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>670.3786986745525</v>
+        <v>673.6156618787633</v>
       </c>
       <c r="C158" t="n">
-        <v>681.8680504402118</v>
+        <v>677.5520159823654</v>
       </c>
       <c r="D158" t="n">
-        <v>670.2188736545023</v>
+        <v>665.0136491453696</v>
       </c>
       <c r="E158" t="n">
-        <v>677.9916381835938</v>
+        <v>670.7183837890625</v>
       </c>
       <c r="F158" t="n">
-        <v>12805200</v>
+        <v>10606800</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>673.6156618787633</v>
+        <v>668.2905997420939</v>
       </c>
       <c r="C159" t="n">
-        <v>677.5520159823654</v>
+        <v>673.6256820299297</v>
       </c>
       <c r="D159" t="n">
-        <v>665.0136491453696</v>
+        <v>663.1953464496755</v>
       </c>
       <c r="E159" t="n">
-        <v>670.7183837890625</v>
+        <v>668.5004272460938</v>
       </c>
       <c r="F159" t="n">
-        <v>10606800</v>
+        <v>18947500</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>668.2905997420939</v>
+        <v>618.7465567527638</v>
       </c>
       <c r="C160" t="n">
-        <v>673.6256820299297</v>
+        <v>620.2751083620838</v>
       </c>
       <c r="D160" t="n">
-        <v>663.1953464496755</v>
+        <v>599.4444385151393</v>
       </c>
       <c r="E160" t="n">
-        <v>668.5004272460938</v>
+        <v>611.3433837890625</v>
       </c>
       <c r="F160" t="n">
-        <v>18947500</v>
+        <v>52765000</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>618.7465567527638</v>
+        <v>614.120842749119</v>
       </c>
       <c r="C161" t="n">
-        <v>620.2751083620838</v>
+        <v>618.3069655430758</v>
       </c>
       <c r="D161" t="n">
-        <v>599.4444385151393</v>
+        <v>605.5487701514051</v>
       </c>
       <c r="E161" t="n">
-        <v>611.3433837890625</v>
+        <v>608.1863403320312</v>
       </c>
       <c r="F161" t="n">
-        <v>52765000</v>
+        <v>21404000</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>614.120842749119</v>
+        <v>607.3771038685389</v>
       </c>
       <c r="C162" t="n">
-        <v>618.3069655430758</v>
+        <v>613.4314904063681</v>
       </c>
       <c r="D162" t="n">
-        <v>605.5487701514051</v>
+        <v>602.1919069095087</v>
       </c>
       <c r="E162" t="n">
-        <v>608.1863403320312</v>
+        <v>609.8447875976562</v>
       </c>
       <c r="F162" t="n">
-        <v>21404000</v>
+        <v>16203900</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>607.3771038685389</v>
+        <v>612.7420849871345</v>
       </c>
       <c r="C163" t="n">
-        <v>613.4314904063681</v>
+        <v>613.7811000159977</v>
       </c>
       <c r="D163" t="n">
-        <v>602.1919069095087</v>
+        <v>599.8040642277598</v>
       </c>
       <c r="E163" t="n">
-        <v>609.8447875976562</v>
+        <v>604.3998413085938</v>
       </c>
       <c r="F163" t="n">
-        <v>16203900</v>
+        <v>17171300</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>612.7420849871345</v>
+        <v>600.4934370812971</v>
       </c>
       <c r="C164" t="n">
-        <v>613.7811000159977</v>
+        <v>619.3759607512419</v>
       </c>
       <c r="D164" t="n">
-        <v>599.8040642277598</v>
+        <v>597.5461564796674</v>
       </c>
       <c r="E164" t="n">
-        <v>604.3998413085938</v>
+        <v>612.3125</v>
       </c>
       <c r="F164" t="n">
-        <v>17171300</v>
+        <v>19915500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>600.4934370812971</v>
+        <v>614.150739078972</v>
       </c>
       <c r="C165" t="n">
-        <v>619.3759607512419</v>
+        <v>624.4012480600104</v>
       </c>
       <c r="D165" t="n">
-        <v>597.5461564796674</v>
+        <v>612.9718390781961</v>
       </c>
       <c r="E165" t="n">
-        <v>612.3125</v>
+        <v>616.2388305664062</v>
       </c>
       <c r="F165" t="n">
-        <v>19915500</v>
+        <v>12307400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>614.150739078972</v>
+        <v>614.6303402495529</v>
       </c>
       <c r="C166" t="n">
-        <v>624.4012480600104</v>
+        <v>616.1988937552933</v>
       </c>
       <c r="D166" t="n">
-        <v>612.9718390781961</v>
+        <v>605.4987892063378</v>
       </c>
       <c r="E166" t="n">
-        <v>616.2388305664062</v>
+        <v>609.0654907226562</v>
       </c>
       <c r="F166" t="n">
-        <v>12307400</v>
+        <v>13557000</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>614.6303402495529</v>
+        <v>604.010215830275</v>
       </c>
       <c r="C167" t="n">
-        <v>616.1988937552933</v>
+        <v>604.3498668649182</v>
       </c>
       <c r="D167" t="n">
-        <v>605.4987892063378</v>
+        <v>597.5262348938886</v>
       </c>
       <c r="E167" t="n">
-        <v>609.0654907226562</v>
+        <v>598.3054809570312</v>
       </c>
       <c r="F167" t="n">
-        <v>13557000</v>
+        <v>15940600</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>604.010215830275</v>
+        <v>594.2692320029287</v>
       </c>
       <c r="C168" t="n">
-        <v>604.3498668649182</v>
+        <v>603.1909559259367</v>
       </c>
       <c r="D168" t="n">
-        <v>597.5262348938886</v>
+        <v>592.0512559095129</v>
       </c>
       <c r="E168" t="n">
-        <v>598.3054809570312</v>
+        <v>602.441650390625</v>
       </c>
       <c r="F168" t="n">
-        <v>15940600</v>
+        <v>11351600</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>594.2692320029287</v>
+        <v>598.275515544453</v>
       </c>
       <c r="C169" t="n">
-        <v>603.1909559259367</v>
+        <v>619.3260125714435</v>
       </c>
       <c r="D169" t="n">
-        <v>592.0512559095129</v>
+        <v>596.1074810052941</v>
       </c>
       <c r="E169" t="n">
-        <v>602.441650390625</v>
+        <v>616.0590209960938</v>
       </c>
       <c r="F169" t="n">
-        <v>11351600</v>
+        <v>14634400</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>598.275515544453</v>
+        <v>615.4296182023591</v>
       </c>
       <c r="C170" t="n">
-        <v>619.3260125714435</v>
+        <v>623.152441138389</v>
       </c>
       <c r="D170" t="n">
-        <v>596.1074810052941</v>
+        <v>614.4305441468357</v>
       </c>
       <c r="E170" t="n">
-        <v>616.0590209960938</v>
+        <v>617.8573608398438</v>
       </c>
       <c r="F170" t="n">
-        <v>14634400</v>
+        <v>10651200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>615.4296182023591</v>
+        <v>613.421486859321</v>
       </c>
       <c r="C171" t="n">
-        <v>623.152441138389</v>
+        <v>620.6248329546977</v>
       </c>
       <c r="D171" t="n">
-        <v>614.4305441468357</v>
+        <v>608.7458274653094</v>
       </c>
       <c r="E171" t="n">
-        <v>617.8573608398438</v>
+        <v>613.6612548828125</v>
       </c>
       <c r="F171" t="n">
-        <v>10651200</v>
+        <v>13272600</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>613.421486859321</v>
+        <v>608.5459509764945</v>
       </c>
       <c r="C172" t="n">
-        <v>620.6248329546977</v>
+        <v>615.0199919776213</v>
       </c>
       <c r="D172" t="n">
-        <v>608.7458274653094</v>
+        <v>603.1309869574205</v>
       </c>
       <c r="E172" t="n">
-        <v>613.6612548828125</v>
+        <v>610.64404296875</v>
       </c>
       <c r="F172" t="n">
-        <v>13272600</v>
+        <v>13772400</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>608.5459509764945</v>
+        <v>608.3561568042173</v>
       </c>
       <c r="C173" t="n">
-        <v>615.0199919776213</v>
+        <v>613.361527578881</v>
       </c>
       <c r="D173" t="n">
-        <v>603.1309869574205</v>
+        <v>599.9939118379299</v>
       </c>
       <c r="E173" t="n">
-        <v>610.64404296875</v>
+        <v>602.052001953125</v>
       </c>
       <c r="F173" t="n">
-        <v>13772400</v>
+        <v>11749900</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>608.3561568042173</v>
+        <v>600.2037495434126</v>
       </c>
       <c r="C174" t="n">
-        <v>613.361527578881</v>
+        <v>607.4370360716302</v>
       </c>
       <c r="D174" t="n">
-        <v>599.9939118379299</v>
+        <v>597.2564688338498</v>
       </c>
       <c r="E174" t="n">
-        <v>602.052001953125</v>
+        <v>604.499755859375</v>
       </c>
       <c r="F174" t="n">
-        <v>11749900</v>
+        <v>11329700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>600.2037495434126</v>
+        <v>599.4443949814065</v>
       </c>
       <c r="C175" t="n">
-        <v>607.4370360716302</v>
+        <v>609.0354809096541</v>
       </c>
       <c r="D175" t="n">
-        <v>597.2564688338498</v>
+        <v>594.2591985256718</v>
       </c>
       <c r="E175" t="n">
-        <v>604.499755859375</v>
+        <v>606.8175659179688</v>
       </c>
       <c r="F175" t="n">
-        <v>11329700</v>
+        <v>13476100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>599.4443949814065</v>
+        <v>607.3171451453314</v>
       </c>
       <c r="C176" t="n">
-        <v>609.0354809096541</v>
+        <v>614.2407210713809</v>
       </c>
       <c r="D176" t="n">
-        <v>594.2591985256718</v>
+        <v>606.3880135859368</v>
       </c>
       <c r="E176" t="n">
-        <v>606.8175659179688</v>
+        <v>609.6949462890625</v>
       </c>
       <c r="F176" t="n">
-        <v>13476100</v>
+        <v>11688600</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>607.3171451453314</v>
+        <v>608.3261927003538</v>
       </c>
       <c r="C177" t="n">
-        <v>614.2407210713809</v>
+        <v>613.9009818092591</v>
       </c>
       <c r="D177" t="n">
-        <v>606.3880135859368</v>
+        <v>604.7394901495815</v>
       </c>
       <c r="E177" t="n">
-        <v>609.6949462890625</v>
+        <v>611.7730102539062</v>
       </c>
       <c r="F177" t="n">
-        <v>11688600</v>
+        <v>12234200</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>608.3261927003538</v>
+        <v>608.8357727220844</v>
       </c>
       <c r="C178" t="n">
-        <v>613.9009818092591</v>
+        <v>637.908804248614</v>
       </c>
       <c r="D178" t="n">
-        <v>604.7394901495815</v>
+        <v>608.4361186960156</v>
       </c>
       <c r="E178" t="n">
-        <v>611.7730102539062</v>
+        <v>634.6718139648438</v>
       </c>
       <c r="F178" t="n">
-        <v>12234200</v>
+        <v>23143600</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>608.8357727220844</v>
+        <v>638.9078448274123</v>
       </c>
       <c r="C179" t="n">
-        <v>637.908804248614</v>
+        <v>642.4046039468743</v>
       </c>
       <c r="D179" t="n">
-        <v>608.4361186960156</v>
+        <v>628.7272779804616</v>
       </c>
       <c r="E179" t="n">
-        <v>634.6718139648438</v>
+        <v>634.7017211914062</v>
       </c>
       <c r="F179" t="n">
-        <v>23143600</v>
+        <v>16772400</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>638.9078448274123</v>
+        <v>632.9133899267435</v>
       </c>
       <c r="C180" t="n">
-        <v>642.4046039468743</v>
+        <v>633.9124639439917</v>
       </c>
       <c r="D180" t="n">
-        <v>628.7272779804616</v>
+        <v>622.7727642602187</v>
       </c>
       <c r="E180" t="n">
-        <v>634.7017211914062</v>
+        <v>631.92431640625</v>
       </c>
       <c r="F180" t="n">
-        <v>16772400</v>
+        <v>19806500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>632.9133899267435</v>
+        <v>629.8162791560948</v>
       </c>
       <c r="C181" t="n">
-        <v>633.9124639439917</v>
+        <v>635.1613007084701</v>
       </c>
       <c r="D181" t="n">
-        <v>622.7727642602187</v>
+        <v>598.9748694014791</v>
       </c>
       <c r="E181" t="n">
-        <v>631.92431640625</v>
+        <v>599.9139404296875</v>
       </c>
       <c r="F181" t="n">
-        <v>19806500</v>
+        <v>29138800</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>629.8162791560948</v>
+        <v>602.6813896226799</v>
       </c>
       <c r="C182" t="n">
-        <v>635.1613007084701</v>
+        <v>608.3161816139932</v>
       </c>
       <c r="D182" t="n">
-        <v>598.9748694014791</v>
+        <v>596.1274666259658</v>
       </c>
       <c r="E182" t="n">
-        <v>599.9139404296875</v>
+        <v>597.0765991210938</v>
       </c>
       <c r="F182" t="n">
-        <v>29138800</v>
+        <v>18252000</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>602.6813896226799</v>
+        <v>602.4416570391962</v>
       </c>
       <c r="C183" t="n">
-        <v>608.3161816139932</v>
+        <v>623.5720977596394</v>
       </c>
       <c r="D183" t="n">
-        <v>596.1274666259658</v>
+        <v>599.7142043737263</v>
       </c>
       <c r="E183" t="n">
-        <v>597.0765991210938</v>
+        <v>622.4031372070312</v>
       </c>
       <c r="F183" t="n">
-        <v>18252000</v>
+        <v>23020100</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>602.4416570391962</v>
+        <v>623.0924785224576</v>
       </c>
       <c r="C184" t="n">
-        <v>623.5720977596394</v>
+        <v>641.8051764288737</v>
       </c>
       <c r="D184" t="n">
-        <v>599.7142043737263</v>
+        <v>621.8536364911718</v>
       </c>
       <c r="E184" t="n">
-        <v>622.4031372070312</v>
+        <v>626.9888916015625</v>
       </c>
       <c r="F184" t="n">
-        <v>23020100</v>
+        <v>21469200</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>623.0924785224576</v>
+        <v>622.8827460758752</v>
       </c>
       <c r="C185" t="n">
-        <v>641.8051764288737</v>
+        <v>628.5674800138549</v>
       </c>
       <c r="D185" t="n">
-        <v>621.8536364911718</v>
+        <v>582.3702434655938</v>
       </c>
       <c r="E185" t="n">
-        <v>626.9888916015625</v>
+        <v>592.450927734375</v>
       </c>
       <c r="F185" t="n">
-        <v>21469200</v>
+        <v>30091600</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>622.8827460758752</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="C186" t="n">
-        <v>628.5674800138549</v>
+        <v>591.4518261333767</v>
       </c>
       <c r="D186" t="n">
-        <v>582.3702434655938</v>
+        <v>578.6836307521693</v>
       </c>
       <c r="E186" t="n">
-        <v>592.450927734375</v>
+        <v>584.8479614257812</v>
       </c>
       <c r="F186" t="n">
-        <v>30091600</v>
+        <v>19512400</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>591.4518261333767</v>
+        <v>590.4527436689563</v>
       </c>
       <c r="C187" t="n">
-        <v>591.4518261333767</v>
+        <v>597.0766092757164</v>
       </c>
       <c r="D187" t="n">
-        <v>578.6836307521693</v>
+        <v>580.4720040020986</v>
       </c>
       <c r="E187" t="n">
-        <v>584.8479614257812</v>
+        <v>584.0487060546875</v>
       </c>
       <c r="F187" t="n">
-        <v>19512400</v>
+        <v>16977400</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>590.4527436689563</v>
+        <v>580.192266144374</v>
       </c>
       <c r="C188" t="n">
-        <v>597.0766092757164</v>
+        <v>590.7724873942649</v>
       </c>
       <c r="D188" t="n">
-        <v>580.4720040020986</v>
+        <v>570.0716409197756</v>
       </c>
       <c r="E188" t="n">
-        <v>584.0487060546875</v>
+        <v>570.4512939453125</v>
       </c>
       <c r="F188" t="n">
-        <v>16977400</v>
+        <v>17064000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>580.192266144374</v>
+        <v>565.3060574843756</v>
       </c>
       <c r="C189" t="n">
-        <v>590.7724873942649</v>
+        <v>571.6401524850257</v>
       </c>
       <c r="D189" t="n">
-        <v>570.0716409197756</v>
+        <v>556.4942175026772</v>
       </c>
       <c r="E189" t="n">
-        <v>570.4512939453125</v>
+        <v>567.9036254882812</v>
       </c>
       <c r="F189" t="n">
-        <v>17064000</v>
+        <v>17628000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>565.3060574843756</v>
+        <v>572.4194595335534</v>
       </c>
       <c r="C190" t="n">
-        <v>571.6401524850257</v>
+        <v>575.5365655300229</v>
       </c>
       <c r="D190" t="n">
-        <v>556.4942175026772</v>
+        <v>560.3806300495169</v>
       </c>
       <c r="E190" t="n">
-        <v>567.9036254882812</v>
+        <v>566.4549560546875</v>
       </c>
       <c r="F190" t="n">
-        <v>17628000</v>
+        <v>14326400</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,25 +5383,25 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>572.4194595335534</v>
+        <v>579.9000244140625</v>
       </c>
       <c r="C191" t="n">
-        <v>575.5365655300229</v>
+        <v>601.27001953125</v>
       </c>
       <c r="D191" t="n">
-        <v>560.3806300495169</v>
+        <v>579.2999877929688</v>
       </c>
       <c r="E191" t="n">
-        <v>566.4549560546875</v>
+        <v>593.47998046875</v>
       </c>
       <c r="F191" t="n">
-        <v>14326400</v>
+        <v>17653300</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>0.525</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5409,25 +5409,25 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>579.9000244140625</v>
+        <v>593.6500244140625</v>
       </c>
       <c r="C192" t="n">
-        <v>601.27001953125</v>
+        <v>605.8099975585938</v>
       </c>
       <c r="D192" t="n">
-        <v>579.2999877929688</v>
+        <v>592</v>
       </c>
       <c r="E192" t="n">
-        <v>593.47998046875</v>
+        <v>600.2100219726562</v>
       </c>
       <c r="F192" t="n">
-        <v>17653300</v>
+        <v>11344400</v>
       </c>
       <c r="G192" t="n">
-        <v>0.525</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>593.6500244140625</v>
+        <v>592</v>
       </c>
       <c r="C193" t="n">
-        <v>605.8099975585938</v>
+        <v>593.8099975585938</v>
       </c>
       <c r="D193" t="n">
-        <v>592</v>
+        <v>566.1900024414062</v>
       </c>
       <c r="E193" t="n">
-        <v>600.2100219726562</v>
+        <v>567.5800170898438</v>
       </c>
       <c r="F193" t="n">
-        <v>11344400</v>
+        <v>20478300</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>592</v>
+        <v>572.8200073242188</v>
       </c>
       <c r="C194" t="n">
-        <v>593.8099975585938</v>
+        <v>580.219970703125</v>
       </c>
       <c r="D194" t="n">
-        <v>566.1900024414062</v>
+        <v>563.0999755859375</v>
       </c>
       <c r="E194" t="n">
-        <v>567.5800170898438</v>
+        <v>577.219970703125</v>
       </c>
       <c r="F194" t="n">
-        <v>20478300</v>
+        <v>28824600</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>572.8200073242188</v>
+        <v>572.02001953125</v>
       </c>
       <c r="C195" t="n">
-        <v>580.219970703125</v>
+        <v>575.8099975585938</v>
       </c>
       <c r="D195" t="n">
-        <v>563.0999755859375</v>
+        <v>559.8099975585938</v>
       </c>
       <c r="E195" t="n">
-        <v>577.219970703125</v>
+        <v>563.8499755859375</v>
       </c>
       <c r="F195" t="n">
-        <v>28824600</v>
+        <v>15405500</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>572.02001953125</v>
+        <v>562.25</v>
       </c>
       <c r="C196" t="n">
-        <v>575.8099975585938</v>
+        <v>572.2000122070312</v>
       </c>
       <c r="D196" t="n">
-        <v>559.8099975585938</v>
+        <v>561.02001953125</v>
       </c>
       <c r="E196" t="n">
-        <v>563.8499755859375</v>
+        <v>562.2000122070312</v>
       </c>
       <c r="F196" t="n">
-        <v>15405500</v>
+        <v>13103300</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>562.25</v>
+        <v>561.8900146484375</v>
       </c>
       <c r="C197" t="n">
-        <v>572.2000122070312</v>
+        <v>569.0399780273438</v>
       </c>
       <c r="D197" t="n">
-        <v>561.02001953125</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="E197" t="n">
-        <v>562.2000122070312</v>
+        <v>557.6699829101562</v>
       </c>
       <c r="F197" t="n">
-        <v>13103300</v>
+        <v>13963600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>561.8900146484375</v>
+        <v>555.5499877929688</v>
       </c>
       <c r="C198" t="n">
-        <v>569.0399780273438</v>
+        <v>556.3400268554688</v>
       </c>
       <c r="D198" t="n">
-        <v>555.5499877929688</v>
+        <v>540.1799926757812</v>
       </c>
       <c r="E198" t="n">
-        <v>557.6699829101562</v>
+        <v>542.8699951171875</v>
       </c>
       <c r="F198" t="n">
-        <v>13963600</v>
+        <v>16968600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>555.5499877929688</v>
+        <v>543.3400268554688</v>
       </c>
       <c r="C199" t="n">
-        <v>556.3400268554688</v>
+        <v>556.8499755859375</v>
       </c>
       <c r="D199" t="n">
-        <v>540.1799926757812</v>
+        <v>540.4000244140625</v>
       </c>
       <c r="E199" t="n">
-        <v>542.8699951171875</v>
+        <v>550.25</v>
       </c>
       <c r="F199" t="n">
-        <v>16968600</v>
+        <v>18867700</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>543.3400268554688</v>
+        <v>560</v>
       </c>
       <c r="C200" t="n">
-        <v>556.8499755859375</v>
+        <v>570.9000244140625</v>
       </c>
       <c r="D200" t="n">
-        <v>540.4000244140625</v>
+        <v>558</v>
       </c>
       <c r="E200" t="n">
-        <v>550.25</v>
+        <v>562.5999755859375</v>
       </c>
       <c r="F200" t="n">
-        <v>18867700</v>
+        <v>15011400</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>560</v>
+        <v>560.9400024414062</v>
       </c>
       <c r="C201" t="n">
-        <v>570.9000244140625</v>
+        <v>565.5399780273438</v>
       </c>
       <c r="D201" t="n">
-        <v>558</v>
+        <v>551.4299926757812</v>
       </c>
       <c r="E201" t="n">
-        <v>562.5999755859375</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F201" t="n">
-        <v>15011400</v>
+        <v>18111100</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>560.9400024414062</v>
+        <v>607.9099731445312</v>
       </c>
       <c r="C202" t="n">
-        <v>565.5399780273438</v>
+        <v>628.280029296875</v>
       </c>
       <c r="D202" t="n">
-        <v>551.4299926757812</v>
+        <v>595.0999755859375</v>
       </c>
       <c r="E202" t="n">
-        <v>563.2899780273438</v>
+        <v>612.9099731445312</v>
       </c>
       <c r="F202" t="n">
-        <v>18111100</v>
+        <v>45536300</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>607.9099731445312</v>
+        <v>607.9000244140625</v>
       </c>
       <c r="C203" t="n">
-        <v>628.280029296875</v>
+        <v>610</v>
       </c>
       <c r="D203" t="n">
-        <v>595.0999755859375</v>
+        <v>580.4199829101562</v>
       </c>
       <c r="E203" t="n">
-        <v>612.9099731445312</v>
+        <v>582.9000244140625</v>
       </c>
       <c r="F203" t="n">
-        <v>45536300</v>
+        <v>21705900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>607.9000244140625</v>
+        <v>594.8400268554688</v>
       </c>
       <c r="C204" t="n">
-        <v>610</v>
+        <v>603.5800170898438</v>
       </c>
       <c r="D204" t="n">
-        <v>580.4199829101562</v>
+        <v>581.760009765625</v>
       </c>
       <c r="E204" t="n">
-        <v>582.9000244140625</v>
+        <v>600.2899780273438</v>
       </c>
       <c r="F204" t="n">
-        <v>21705900</v>
+        <v>17674100</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>594.8400268554688</v>
+        <v>607.5900268554688</v>
       </c>
       <c r="C205" t="n">
-        <v>603.5800170898438</v>
+        <v>625.3699951171875</v>
       </c>
       <c r="D205" t="n">
-        <v>581.760009765625</v>
+        <v>603.6599731445312</v>
       </c>
       <c r="E205" t="n">
-        <v>600.2899780273438</v>
+        <v>615.5800170898438</v>
       </c>
       <c r="F205" t="n">
-        <v>17674100</v>
+        <v>18560800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>607.5900268554688</v>
+        <v>614.3900146484375</v>
       </c>
       <c r="C206" t="n">
-        <v>625.3699951171875</v>
+        <v>616</v>
       </c>
       <c r="D206" t="n">
-        <v>603.6599731445312</v>
+        <v>598.010009765625</v>
       </c>
       <c r="E206" t="n">
-        <v>615.5800170898438</v>
+        <v>603.1199951171875</v>
       </c>
       <c r="F206" t="n">
-        <v>18560800</v>
+        <v>13606500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>614.3900146484375</v>
+        <v>583.989990234375</v>
       </c>
       <c r="C207" t="n">
-        <v>616</v>
+        <v>633.27001953125</v>
       </c>
       <c r="D207" t="n">
-        <v>598.010009765625</v>
+        <v>577.0700073242188</v>
       </c>
       <c r="E207" t="n">
-        <v>603.1199951171875</v>
+        <v>631.47998046875</v>
       </c>
       <c r="F207" t="n">
-        <v>13606500</v>
+        <v>26579700</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>583.989990234375</v>
+        <v>660.3400268554688</v>
       </c>
       <c r="C208" t="n">
-        <v>633.27001953125</v>
+        <v>677.8599853515625</v>
       </c>
       <c r="D208" t="n">
-        <v>577.0700073242188</v>
+        <v>658.010009765625</v>
       </c>
       <c r="E208" t="n">
-        <v>631.47998046875</v>
+        <v>669.2100219726562</v>
       </c>
       <c r="F208" t="n">
-        <v>26579700</v>
+        <v>40608900</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>660.3400268554688</v>
+        <v>661.3800048828125</v>
       </c>
       <c r="C209" t="n">
-        <v>677.8599853515625</v>
+        <v>676.6199951171875</v>
       </c>
       <c r="D209" t="n">
-        <v>658.010009765625</v>
+        <v>654.2000122070312</v>
       </c>
       <c r="E209" t="n">
-        <v>669.2100219726562</v>
+        <v>656.72998046875</v>
       </c>
       <c r="F209" t="n">
-        <v>40608900</v>
+        <v>19840700</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>661.3800048828125</v>
+        <v>652</v>
       </c>
       <c r="C210" t="n">
-        <v>676.6199951171875</v>
+        <v>666.5</v>
       </c>
       <c r="D210" t="n">
-        <v>654.2000122070312</v>
+        <v>649.0499877929688</v>
       </c>
       <c r="E210" t="n">
-        <v>656.72998046875</v>
+        <v>661.0399780273438</v>
       </c>
       <c r="F210" t="n">
-        <v>19840700</v>
+        <v>16748200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>652</v>
+        <v>663.5999755859375</v>
       </c>
       <c r="C211" t="n">
-        <v>666.5</v>
+        <v>686.0800170898438</v>
       </c>
       <c r="D211" t="n">
-        <v>649.0499877929688</v>
+        <v>656.6599731445312</v>
       </c>
       <c r="E211" t="n">
-        <v>661.0399780273438</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="F211" t="n">
-        <v>16748200</v>
+        <v>19003400</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>663.5999755859375</v>
+        <v>677.280029296875</v>
       </c>
       <c r="C212" t="n">
-        <v>686.0800170898438</v>
+        <v>681.9000244140625</v>
       </c>
       <c r="D212" t="n">
-        <v>656.6599731445312</v>
+        <v>660.1599731445312</v>
       </c>
       <c r="E212" t="n">
-        <v>681.3099975585938</v>
+        <v>664.5399780273438</v>
       </c>
       <c r="F212" t="n">
-        <v>19003400</v>
+        <v>15816000</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>677.280029296875</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C213" t="n">
-        <v>681.9000244140625</v>
+        <v>652.2000122070312</v>
       </c>
       <c r="D213" t="n">
-        <v>660.1599731445312</v>
+        <v>626</v>
       </c>
       <c r="E213" t="n">
-        <v>664.5399780273438</v>
+        <v>646.010009765625</v>
       </c>
       <c r="F213" t="n">
-        <v>15816000</v>
+        <v>22267900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>647.7000122070312</v>
+        <v>646.7000122070312</v>
       </c>
       <c r="C214" t="n">
-        <v>652.2000122070312</v>
+        <v>653.2999877929688</v>
       </c>
       <c r="D214" t="n">
-        <v>626</v>
+        <v>636.010009765625</v>
       </c>
       <c r="E214" t="n">
-        <v>646.010009765625</v>
+        <v>645.8499755859375</v>
       </c>
       <c r="F214" t="n">
-        <v>22267900</v>
+        <v>10225200</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>646.7000122070312</v>
+        <v>654.1799926757812</v>
       </c>
       <c r="C215" t="n">
-        <v>653.2999877929688</v>
+        <v>655.8800048828125</v>
       </c>
       <c r="D215" t="n">
-        <v>636.010009765625</v>
+        <v>643.2000122070312</v>
       </c>
       <c r="E215" t="n">
-        <v>645.8499755859375</v>
+        <v>643.8099975585938</v>
       </c>
       <c r="F215" t="n">
-        <v>10225200</v>
+        <v>9140500</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>654.1799926757812</v>
+        <v>647.7000122070312</v>
       </c>
       <c r="C216" t="n">
-        <v>655.8800048828125</v>
+        <v>649</v>
       </c>
       <c r="D216" t="n">
-        <v>643.2000122070312</v>
+        <v>624</v>
       </c>
       <c r="E216" t="n">
-        <v>643.8099975585938</v>
+        <v>627.1699829101562</v>
       </c>
       <c r="F216" t="n">
-        <v>9140500</v>
+        <v>11019600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>647.7000122070312</v>
+        <v>608.4099731445312</v>
       </c>
       <c r="C217" t="n">
-        <v>649</v>
+        <v>614.6500244140625</v>
       </c>
       <c r="D217" t="n">
-        <v>624</v>
+        <v>597.219970703125</v>
       </c>
       <c r="E217" t="n">
-        <v>627.1699829101562</v>
+        <v>606.0999755859375</v>
       </c>
       <c r="F217" t="n">
-        <v>11019600</v>
+        <v>15494800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>608.4099731445312</v>
+        <v>605.2999877929688</v>
       </c>
       <c r="C218" t="n">
-        <v>614.6500244140625</v>
+        <v>609.97998046875</v>
       </c>
       <c r="D218" t="n">
-        <v>597.219970703125</v>
+        <v>594.4500122070312</v>
       </c>
       <c r="E218" t="n">
-        <v>606.0999755859375</v>
+        <v>595.1900024414062</v>
       </c>
       <c r="F218" t="n">
-        <v>15494800</v>
+        <v>11503500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>605.2999877929688</v>
+        <v>607.219970703125</v>
       </c>
       <c r="C219" t="n">
-        <v>609.97998046875</v>
+        <v>611.260009765625</v>
       </c>
       <c r="D219" t="n">
-        <v>594.4500122070312</v>
+        <v>593.1300048828125</v>
       </c>
       <c r="E219" t="n">
-        <v>595.1900024414062</v>
+        <v>593.8699951171875</v>
       </c>
       <c r="F219" t="n">
-        <v>11503500</v>
+        <v>11195300</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>607.219970703125</v>
+        <v>596.8200073242188</v>
       </c>
       <c r="C220" t="n">
-        <v>611.260009765625</v>
+        <v>601</v>
       </c>
       <c r="D220" t="n">
-        <v>593.1300048828125</v>
+        <v>587</v>
       </c>
       <c r="E220" t="n">
-        <v>593.8699951171875</v>
+        <v>593.4099731445312</v>
       </c>
       <c r="F220" t="n">
-        <v>11195300</v>
+        <v>12009300</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>596.8200073242188</v>
+        <v>593.25</v>
       </c>
       <c r="C221" t="n">
-        <v>601</v>
+        <v>599.969970703125</v>
       </c>
       <c r="D221" t="n">
-        <v>587</v>
+        <v>582.219970703125</v>
       </c>
       <c r="E221" t="n">
-        <v>593.4099731445312</v>
+        <v>585.6099853515625</v>
       </c>
       <c r="F221" t="n">
-        <v>12009300</v>
+        <v>22371100</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>593.25</v>
+        <v>526</v>
       </c>
       <c r="C222" t="n">
-        <v>599.969970703125</v>
+        <v>539.8800048828125</v>
       </c>
       <c r="D222" t="n">
-        <v>582.219970703125</v>
+        <v>524.489990234375</v>
       </c>
       <c r="E222" t="n">
-        <v>585.6099853515625</v>
+        <v>539.030029296875</v>
       </c>
       <c r="F222" t="n">
-        <v>22371100</v>
+        <v>42271500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>526</v>
+        <v>543.5999755859375</v>
       </c>
       <c r="C223" t="n">
-        <v>539.8800048828125</v>
+        <v>558.3300170898438</v>
       </c>
       <c r="D223" t="n">
-        <v>524.489990234375</v>
+        <v>540.219970703125</v>
       </c>
       <c r="E223" t="n">
-        <v>539.030029296875</v>
+        <v>556.7100219726562</v>
       </c>
       <c r="F223" t="n">
-        <v>42271500</v>
+        <v>24261500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>543.5999755859375</v>
+        <v>562.239990234375</v>
       </c>
       <c r="C224" t="n">
-        <v>558.3300170898438</v>
+        <v>597.52001953125</v>
       </c>
       <c r="D224" t="n">
-        <v>540.219970703125</v>
+        <v>559.3599853515625</v>
       </c>
       <c r="E224" t="n">
-        <v>556.7100219726562</v>
+        <v>590.239990234375</v>
       </c>
       <c r="F224" t="n">
-        <v>24261500</v>
+        <v>25938100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>562.239990234375</v>
+        <v>581.5</v>
       </c>
       <c r="C225" t="n">
-        <v>597.52001953125</v>
+        <v>592.7899780273438</v>
       </c>
       <c r="D225" t="n">
-        <v>559.3599853515625</v>
+        <v>578.25</v>
       </c>
       <c r="E225" t="n">
-        <v>590.239990234375</v>
+        <v>587.9400024414062</v>
       </c>
       <c r="F225" t="n">
-        <v>25938100</v>
+        <v>17959200</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>581.5</v>
+        <v>600.4600219726562</v>
       </c>
       <c r="C226" t="n">
-        <v>592.7899780273438</v>
+        <v>601</v>
       </c>
       <c r="D226" t="n">
-        <v>578.25</v>
+        <v>580.1199951171875</v>
       </c>
       <c r="E226" t="n">
-        <v>587.9400024414062</v>
+        <v>588.77001953125</v>
       </c>
       <c r="F226" t="n">
-        <v>17959200</v>
+        <v>14897200</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>600.4600219726562</v>
+        <v>586.9500122070312</v>
       </c>
       <c r="C227" t="n">
-        <v>601</v>
+        <v>595.3099975585938</v>
       </c>
       <c r="D227" t="n">
-        <v>580.1199951171875</v>
+        <v>586</v>
       </c>
       <c r="E227" t="n">
-        <v>588.77001953125</v>
+        <v>589.9000244140625</v>
       </c>
       <c r="F227" t="n">
-        <v>14897200</v>
+        <v>11811500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>586.9500122070312</v>
+        <v>585.6400146484375</v>
       </c>
       <c r="C228" t="n">
-        <v>595.3099975585938</v>
+        <v>598.739990234375</v>
       </c>
       <c r="D228" t="n">
-        <v>586</v>
+        <v>585.6199951171875</v>
       </c>
       <c r="E228" t="n">
-        <v>589.9000244140625</v>
+        <v>592.0999755859375</v>
       </c>
       <c r="F228" t="n">
-        <v>11811500</v>
+        <v>11250300</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>585.6400146484375</v>
+        <v>599.1300048828125</v>
       </c>
       <c r="C229" t="n">
-        <v>598.739990234375</v>
+        <v>608.2100219726562</v>
       </c>
       <c r="D229" t="n">
-        <v>585.6199951171875</v>
+        <v>592.030029296875</v>
       </c>
       <c r="E229" t="n">
-        <v>592.0999755859375</v>
+        <v>594.9199829101562</v>
       </c>
       <c r="F229" t="n">
-        <v>11250300</v>
+        <v>14967300</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>599.1300048828125</v>
+        <v>598</v>
       </c>
       <c r="C230" t="n">
-        <v>608.2100219726562</v>
+        <v>612.4299926757812</v>
       </c>
       <c r="D230" t="n">
-        <v>592.030029296875</v>
+        <v>593.4000244140625</v>
       </c>
       <c r="E230" t="n">
-        <v>594.9199829101562</v>
+        <v>599.1199951171875</v>
       </c>
       <c r="F230" t="n">
-        <v>14967300</v>
+        <v>13146900</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>598</v>
+        <v>601.0700073242188</v>
       </c>
       <c r="C231" t="n">
-        <v>612.4299926757812</v>
+        <v>604.5</v>
       </c>
       <c r="D231" t="n">
-        <v>593.4000244140625</v>
+        <v>578.2100219726562</v>
       </c>
       <c r="E231" t="n">
-        <v>599.1199951171875</v>
+        <v>578.8499755859375</v>
       </c>
       <c r="F231" t="n">
-        <v>13146900</v>
+        <v>16186900</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>601.0700073242188</v>
+        <v>580.7100219726562</v>
       </c>
       <c r="C232" t="n">
-        <v>604.5</v>
+        <v>595.8499755859375</v>
       </c>
       <c r="D232" t="n">
-        <v>578.2100219726562</v>
+        <v>579.3900146484375</v>
       </c>
       <c r="E232" t="n">
-        <v>578.8499755859375</v>
+        <v>594.969970703125</v>
       </c>
       <c r="F232" t="n">
-        <v>16186900</v>
+        <v>11164200</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>580.7100219726562</v>
+        <v>596.97998046875</v>
       </c>
       <c r="C233" t="n">
-        <v>595.8499755859375</v>
+        <v>601.8599853515625</v>
       </c>
       <c r="D233" t="n">
-        <v>579.3900146484375</v>
+        <v>589.2899780273438</v>
       </c>
       <c r="E233" t="n">
-        <v>594.969970703125</v>
+        <v>589.8499755859375</v>
       </c>
       <c r="F233" t="n">
-        <v>11164200</v>
+        <v>8758000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>596.97998046875</v>
+        <v>589.75</v>
       </c>
       <c r="C234" t="n">
-        <v>601.8599853515625</v>
+        <v>590.239990234375</v>
       </c>
       <c r="D234" t="n">
-        <v>589.2899780273438</v>
+        <v>564.75</v>
       </c>
       <c r="E234" t="n">
-        <v>589.8499755859375</v>
+        <v>568.969970703125</v>
       </c>
       <c r="F234" t="n">
-        <v>8758000</v>
+        <v>17225600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>589.75</v>
+        <v>557.47998046875</v>
       </c>
       <c r="C235" t="n">
-        <v>590.239990234375</v>
+        <v>560.6599731445312</v>
       </c>
       <c r="D235" t="n">
-        <v>564.75</v>
+        <v>543.2100219726562</v>
       </c>
       <c r="E235" t="n">
-        <v>568.969970703125</v>
+        <v>543.6699829101562</v>
       </c>
       <c r="F235" t="n">
-        <v>17225600</v>
+        <v>27094900</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>557.47998046875</v>
+        <v>541.3400268554688</v>
       </c>
       <c r="C236" t="n">
-        <v>560.6599731445312</v>
+        <v>554.0700073242188</v>
       </c>
       <c r="D236" t="n">
-        <v>543.2100219726562</v>
+        <v>537.27001953125</v>
       </c>
       <c r="E236" t="n">
-        <v>543.6699829101562</v>
+        <v>546.030029296875</v>
       </c>
       <c r="F236" t="n">
-        <v>27094900</v>
+        <v>16971700</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>541.3400268554688</v>
+        <v>546.9500122070312</v>
       </c>
       <c r="C237" t="n">
-        <v>554.0700073242188</v>
+        <v>549.989990234375</v>
       </c>
       <c r="D237" t="n">
-        <v>537.27001953125</v>
+        <v>539.3099975585938</v>
       </c>
       <c r="E237" t="n">
-        <v>546.030029296875</v>
+        <v>545.8300170898438</v>
       </c>
       <c r="F237" t="n">
-        <v>16971700</v>
+        <v>13872200</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>546.9500122070312</v>
+        <v>546.8900146484375</v>
       </c>
       <c r="C238" t="n">
-        <v>549.989990234375</v>
+        <v>553.8699951171875</v>
       </c>
       <c r="D238" t="n">
-        <v>539.3099975585938</v>
+        <v>543.22998046875</v>
       </c>
       <c r="E238" t="n">
-        <v>545.8300170898438</v>
+        <v>549.9000244140625</v>
       </c>
       <c r="F238" t="n">
-        <v>13872200</v>
+        <v>13848000</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>546.8900146484375</v>
+        <v>550.2000122070312</v>
       </c>
       <c r="C239" t="n">
-        <v>553.8699951171875</v>
+        <v>561.4199829101562</v>
       </c>
       <c r="D239" t="n">
-        <v>543.22998046875</v>
+        <v>546.2999877929688</v>
       </c>
       <c r="E239" t="n">
-        <v>549.9000244140625</v>
+        <v>559.02001953125</v>
       </c>
       <c r="F239" t="n">
-        <v>13848000</v>
+        <v>12990600</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>550.2000122070312</v>
+        <v>563.8800048828125</v>
       </c>
       <c r="C240" t="n">
-        <v>561.4199829101562</v>
+        <v>570.7999877929688</v>
       </c>
       <c r="D240" t="n">
-        <v>546.2999877929688</v>
+        <v>561.4000244140625</v>
       </c>
       <c r="E240" t="n">
-        <v>559.02001953125</v>
+        <v>570.0499877929688</v>
       </c>
       <c r="F240" t="n">
-        <v>12990600</v>
+        <v>9769100</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>563.8800048828125</v>
+        <v>590.3099975585938</v>
       </c>
       <c r="C241" t="n">
-        <v>570.7999877929688</v>
+        <v>593.3400268554688</v>
       </c>
       <c r="D241" t="n">
-        <v>561.4000244140625</v>
+        <v>561.8800048828125</v>
       </c>
       <c r="E241" t="n">
-        <v>570.0499877929688</v>
+        <v>576.1400146484375</v>
       </c>
       <c r="F241" t="n">
-        <v>9769100</v>
+        <v>31416300</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>590.3099975585938</v>
+        <v>576.47998046875</v>
       </c>
       <c r="C242" t="n">
-        <v>593.3400268554688</v>
+        <v>588.3900146484375</v>
       </c>
       <c r="D242" t="n">
-        <v>561.8800048828125</v>
+        <v>567.6199951171875</v>
       </c>
       <c r="E242" t="n">
-        <v>576.1400146484375</v>
+        <v>571.0999755859375</v>
       </c>
       <c r="F242" t="n">
-        <v>31416300</v>
+        <v>15221400</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>576.47998046875</v>
+        <v>571.5499877929688</v>
       </c>
       <c r="C243" t="n">
-        <v>588.3900146484375</v>
+        <v>589.1900024414062</v>
       </c>
       <c r="D243" t="n">
-        <v>567.6199951171875</v>
+        <v>571</v>
       </c>
       <c r="E243" t="n">
-        <v>571.0999755859375</v>
+        <v>578.02001953125</v>
       </c>
       <c r="F243" t="n">
-        <v>15221400</v>
+        <v>16042400</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>571.5499877929688</v>
+        <v>577.6300048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>589.1900024414062</v>
+        <v>578.6799926757812</v>
       </c>
       <c r="D244" t="n">
-        <v>571</v>
+        <v>569.1400146484375</v>
       </c>
       <c r="E244" t="n">
-        <v>578.02001953125</v>
+        <v>572.3400268554688</v>
       </c>
       <c r="F244" t="n">
-        <v>16042400</v>
+        <v>13383800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>577.6300048828125</v>
+        <v>558.3499755859375</v>
       </c>
       <c r="C245" t="n">
-        <v>578.6799926757812</v>
+        <v>584.9500122070312</v>
       </c>
       <c r="D245" t="n">
-        <v>569.1400146484375</v>
+        <v>556.0999755859375</v>
       </c>
       <c r="E245" t="n">
-        <v>572.3400268554688</v>
+        <v>578.5399780273438</v>
       </c>
       <c r="F245" t="n">
-        <v>13383800</v>
+        <v>15796900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>558.3499755859375</v>
+        <v>578.7899780273438</v>
       </c>
       <c r="C246" t="n">
-        <v>584.9500122070312</v>
+        <v>600.3800048828125</v>
       </c>
       <c r="D246" t="n">
-        <v>556.0999755859375</v>
+        <v>577</v>
       </c>
       <c r="E246" t="n">
-        <v>578.5399780273438</v>
+        <v>592.8499755859375</v>
       </c>
       <c r="F246" t="n">
-        <v>15796900</v>
+        <v>16552700</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>578.7899780273438</v>
+        <v>604.489990234375</v>
       </c>
       <c r="C247" t="n">
-        <v>600.3800048828125</v>
+        <v>619.4600219726562</v>
       </c>
       <c r="D247" t="n">
-        <v>577</v>
+        <v>604.3499755859375</v>
       </c>
       <c r="E247" t="n">
-        <v>592.8499755859375</v>
+        <v>610.6799926757812</v>
       </c>
       <c r="F247" t="n">
-        <v>16552700</v>
+        <v>19737100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>604.489990234375</v>
+        <v>612.3499755859375</v>
       </c>
       <c r="C248" t="n">
-        <v>619.4600219726562</v>
+        <v>617.4600219726562</v>
       </c>
       <c r="D248" t="n">
-        <v>604.3499755859375</v>
+        <v>605.27001953125</v>
       </c>
       <c r="E248" t="n">
-        <v>610.6799926757812</v>
+        <v>616.77001953125</v>
       </c>
       <c r="F248" t="n">
-        <v>19737100</v>
+        <v>15966200</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>612.3499755859375</v>
+        <v>616.2100219726562</v>
       </c>
       <c r="C249" t="n">
-        <v>617.4600219726562</v>
+        <v>624.7999877929688</v>
       </c>
       <c r="D249" t="n">
-        <v>605.27001953125</v>
+        <v>609.739990234375</v>
       </c>
       <c r="E249" t="n">
-        <v>616.77001953125</v>
+        <v>613.47998046875</v>
       </c>
       <c r="F249" t="n">
-        <v>15966200</v>
+        <v>18909700</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>616.2100219726562</v>
+        <v>648.6400146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>624.7999877929688</v>
+        <v>657.8599853515625</v>
       </c>
       <c r="D250" t="n">
-        <v>609.739990234375</v>
+        <v>638.5599975585938</v>
       </c>
       <c r="E250" t="n">
-        <v>613.47998046875</v>
+        <v>653.6900024414062</v>
       </c>
       <c r="F250" t="n">
-        <v>18909700</v>
+        <v>35900700</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>648.6400146484375</v>
+        <v>653.7100219726562</v>
       </c>
       <c r="C251" t="n">
-        <v>657.8599853515625</v>
+        <v>663.5</v>
       </c>
       <c r="D251" t="n">
-        <v>638.5599975585938</v>
+        <v>642.1400146484375</v>
       </c>
       <c r="E251" t="n">
-        <v>653.6900024414062</v>
+        <v>644.3800048828125</v>
       </c>
       <c r="F251" t="n">
-        <v>35900700</v>
+        <v>21531900</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>653.7100219726562</v>
+        <v>653.510009765625</v>
       </c>
       <c r="C252" t="n">
-        <v>663.5</v>
+        <v>664.239990234375</v>
       </c>
       <c r="D252" t="n">
-        <v>642.1400146484375</v>
+        <v>646.2000122070312</v>
       </c>
       <c r="E252" t="n">
-        <v>644.3800048828125</v>
+        <v>648.030029296875</v>
       </c>
       <c r="F252" t="n">
-        <v>21487500</v>
+        <v>16908400</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10776,37 +10776,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>648.03</v>
+      </c>
+      <c r="D2" t="n">
         <v>644.38</v>
       </c>
-      <c r="D2" t="n">
-        <v>653.6900000000001</v>
-      </c>
       <c r="E2" t="n">
-        <v>653.6</v>
+        <v>653.02</v>
       </c>
       <c r="F2" t="n">
-        <v>663.5</v>
+        <v>664.24</v>
       </c>
       <c r="G2" t="n">
-        <v>642.14</v>
+        <v>646.2</v>
       </c>
       <c r="H2" t="n">
-        <v>20418899</v>
+        <v>16862780</v>
       </c>
       <c r="I2" t="n">
-        <v>18168488</v>
+        <v>18264382</v>
       </c>
       <c r="J2" t="n">
-        <v>1641561980928</v>
+        <v>1650860490752</v>
       </c>
       <c r="K2" t="n">
-        <v>24.270433</v>
+        <v>24.389538</v>
       </c>
       <c r="L2" t="n">
-        <v>18.432102</v>
+        <v>18.536509</v>
       </c>
       <c r="M2" t="n">
-        <v>26.55</v>
+        <v>26.57</v>
       </c>
       <c r="N2" t="n">
         <v>790.8</v>
@@ -10818,7 +10818,7 @@
         <v>1.243</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="R2" t="n">
         <v>0.29834998</v>
@@ -10842,7 +10842,7 @@
         <v>102.52</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.285408</v>
+        <v>6.321011</v>
       </c>
       <c r="Z2" t="n">
         <v>-0.134</v>
@@ -10854,7 +10854,7 @@
         <v>228246994944</v>
       </c>
       <c r="AC2" t="n">
-        <v>1663620087808</v>
+        <v>1672918466560</v>
       </c>
       <c r="AD2" t="n">
         <v>109654999040</v>
@@ -10881,7 +10881,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:02:54</t>
+          <t>2026-09-12 21:47:00</t>
         </is>
       </c>
     </row>
